--- a/Data/ENWR_Creation.xlsx
+++ b/Data/ENWR_Creation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B9CA6BC-AB9A-4864-A8DE-C32A8C0E11AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C13B47C1-9A12-40EF-9DD2-C6B4DDE2D383}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="522" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="121">
   <si>
     <t>commoditySegment</t>
   </si>
@@ -395,10 +395,16 @@
     <t>Phy</t>
   </si>
   <si>
-    <t>sample_ID</t>
+    <t>Used</t>
   </si>
   <si>
-    <t>Used</t>
+    <t>phy</t>
+  </si>
+  <si>
+    <t>place_of_origin</t>
+  </si>
+  <si>
+    <t>ass</t>
   </si>
 </sst>
 </file>
@@ -557,7 +563,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -598,6 +604,7 @@
     <xf numFmtId="1" fontId="1" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1193,7 +1200,7 @@
         <v>15</v>
       </c>
       <c r="N7" s="33" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
@@ -1237,7 +1244,7 @@
         <v>15</v>
       </c>
       <c r="N8" s="33" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
@@ -1281,7 +1288,7 @@
         <v>15</v>
       </c>
       <c r="N9" s="33" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
@@ -18481,7 +18488,7 @@
       <c r="O4" s="7"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="10" t="s">
+      <c r="A5" s="34" t="s">
         <v>70</v>
       </c>
       <c r="B5" s="22">
@@ -18570,7 +18577,9 @@
       <c r="N6" s="7" t="s">
         <v>79</v>
       </c>
-      <c r="O6" s="7"/>
+      <c r="O6" s="7" t="s">
+        <v>118</v>
+      </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A7" s="10" t="s">
@@ -18601,7 +18610,7 @@
         <v>73</v>
       </c>
       <c r="J7" s="7">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="K7" s="7">
         <v>10</v>
@@ -18610,7 +18619,7 @@
         <v>77</v>
       </c>
       <c r="M7" s="7">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="N7" s="7" t="s">
         <v>79</v>
@@ -19261,7 +19270,7 @@
         <v>89</v>
       </c>
       <c r="M1" s="13" t="s">
-        <v>37</v>
+        <v>119</v>
       </c>
       <c r="N1" s="13" t="s">
         <v>38</v>
@@ -19347,13 +19356,13 @@
         <v>10</v>
       </c>
       <c r="M2" s="7" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="N2" s="7">
         <v>46202558</v>
       </c>
       <c r="O2" s="7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P2" s="7">
         <v>1</v>

--- a/Data/ENWR_Creation.xlsx
+++ b/Data/ENWR_Creation.xlsx
@@ -8,17 +8,17 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C13B47C1-9A12-40EF-9DD2-C6B4DDE2D383}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4B9CE95-EC4A-4BD3-92DE-2D2DBABF718D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RP_Deposite_Request_Agriculture" sheetId="1" r:id="rId1"/>
     <sheet name="RP_Exchange_Deposite_Agricultur" sheetId="3" r:id="rId2"/>
     <sheet name="Government_Agency_Deposite" sheetId="6" r:id="rId3"/>
     <sheet name="Exchange_Deposite_Non_Agricult" sheetId="4" r:id="rId4"/>
-    <sheet name="Exchange_Non_Agriculture_Physic" sheetId="5" r:id="rId5"/>
-    <sheet name="Physical_Deposit_Maker" sheetId="2" r:id="rId6"/>
+    <sheet name="Physical_Deposit_Maker" sheetId="2" r:id="rId5"/>
+    <sheet name="Exchange_Non_Agriculture_Physic" sheetId="5" r:id="rId6"/>
     <sheet name="Deposite_Assayer_Maker" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -19217,6 +19217,211 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F8B609F-0B76-470F-B64C-87241C540723}">
+  <dimension ref="A1:AC2"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="23.42578125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="22" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="24.42578125" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="10" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="10" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="10" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A1" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="B1" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="C1" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D1" s="5" t="s">
+        <v>34</v>
+      </c>
+      <c r="E1" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="F1" s="5" t="s">
+        <v>36</v>
+      </c>
+      <c r="G1" s="6" t="s">
+        <v>37</v>
+      </c>
+      <c r="H1" s="6" t="s">
+        <v>38</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="K1" s="6" t="s">
+        <v>41</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>42</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="N1" s="5" t="s">
+        <v>44</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>45</v>
+      </c>
+      <c r="P1" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="Q1" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="R1" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="S1" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="T1" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="U1" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="V1" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="W1" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="X1" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="Y1" s="5" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z1" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA1" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="AB1" s="6" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC1" s="5" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="2" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="A2" s="1">
+        <v>22442</v>
+      </c>
+      <c r="B2" s="1">
+        <v>232324</v>
+      </c>
+      <c r="C2" s="1">
+        <v>500</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>59</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>60</v>
+      </c>
+      <c r="F2" s="1">
+        <v>973015</v>
+      </c>
+      <c r="G2" s="1">
+        <v>46202560</v>
+      </c>
+      <c r="H2" s="1">
+        <v>46202555</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>105</v>
+      </c>
+      <c r="J2" s="1">
+        <v>130000</v>
+      </c>
+      <c r="K2" s="1">
+        <v>850</v>
+      </c>
+      <c r="L2" s="1">
+        <v>5000</v>
+      </c>
+      <c r="M2" s="1">
+        <v>6</v>
+      </c>
+      <c r="N2" s="1">
+        <v>6</v>
+      </c>
+      <c r="O2" s="1">
+        <v>5</v>
+      </c>
+      <c r="P2" s="7" t="s">
+        <v>61</v>
+      </c>
+      <c r="Q2" s="7" t="s">
+        <v>62</v>
+      </c>
+      <c r="R2" s="7" t="s">
+        <v>63</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>64</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>65</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="V2" s="1" t="s">
+        <v>67</v>
+      </c>
+      <c r="W2" s="1" t="s">
+        <v>68</v>
+      </c>
+      <c r="X2" s="1" t="s">
+        <v>69</v>
+      </c>
+      <c r="Y2" s="1">
+        <v>401202</v>
+      </c>
+      <c r="Z2" s="1">
+        <v>179</v>
+      </c>
+      <c r="AA2" s="1">
+        <v>900</v>
+      </c>
+      <c r="AB2" s="7">
+        <v>100</v>
+      </c>
+      <c r="AC2" s="7">
+        <v>5</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECF7E842-C9CD-4111-B0BA-C4A8FEE6BCD1}">
   <dimension ref="A1:AB31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
@@ -19493,211 +19698,6 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F8B609F-0B76-470F-B64C-87241C540723}">
-  <dimension ref="A1:AC2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="16.140625" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="23.42578125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="22" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="24.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="18.28515625" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="24.42578125" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="10" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="11" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="10" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="10" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A1" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="B1" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="C1" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="D1" s="5" t="s">
-        <v>34</v>
-      </c>
-      <c r="E1" s="5" t="s">
-        <v>35</v>
-      </c>
-      <c r="F1" s="5" t="s">
-        <v>36</v>
-      </c>
-      <c r="G1" s="6" t="s">
-        <v>37</v>
-      </c>
-      <c r="H1" s="6" t="s">
-        <v>38</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>39</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>40</v>
-      </c>
-      <c r="K1" s="6" t="s">
-        <v>41</v>
-      </c>
-      <c r="L1" s="5" t="s">
-        <v>42</v>
-      </c>
-      <c r="M1" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="N1" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="O1" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="P1" s="5" t="s">
-        <v>46</v>
-      </c>
-      <c r="Q1" s="5" t="s">
-        <v>47</v>
-      </c>
-      <c r="R1" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="S1" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="T1" s="5" t="s">
-        <v>50</v>
-      </c>
-      <c r="U1" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="V1" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="W1" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="X1" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="Y1" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="Z1" s="5" t="s">
-        <v>56</v>
-      </c>
-      <c r="AA1" s="5" t="s">
-        <v>57</v>
-      </c>
-      <c r="AB1" s="6" t="s">
-        <v>58</v>
-      </c>
-      <c r="AC1" s="5" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="A2" s="1">
-        <v>22442</v>
-      </c>
-      <c r="B2" s="1">
-        <v>232324</v>
-      </c>
-      <c r="C2" s="1">
-        <v>500</v>
-      </c>
-      <c r="D2" s="1" t="s">
-        <v>59</v>
-      </c>
-      <c r="E2" s="1" t="s">
-        <v>60</v>
-      </c>
-      <c r="F2" s="1">
-        <v>973015</v>
-      </c>
-      <c r="G2" s="1">
-        <v>46202560</v>
-      </c>
-      <c r="H2" s="1">
-        <v>46202555</v>
-      </c>
-      <c r="I2" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="J2" s="1">
-        <v>130000</v>
-      </c>
-      <c r="K2" s="1">
-        <v>1190</v>
-      </c>
-      <c r="L2" s="1">
-        <v>5000</v>
-      </c>
-      <c r="M2" s="1">
-        <v>6</v>
-      </c>
-      <c r="N2" s="1">
-        <v>6</v>
-      </c>
-      <c r="O2" s="1">
-        <v>5</v>
-      </c>
-      <c r="P2" s="7" t="s">
-        <v>61</v>
-      </c>
-      <c r="Q2" s="7" t="s">
-        <v>62</v>
-      </c>
-      <c r="R2" s="7" t="s">
-        <v>63</v>
-      </c>
-      <c r="S2" s="1" t="s">
-        <v>64</v>
-      </c>
-      <c r="T2" s="1" t="s">
-        <v>65</v>
-      </c>
-      <c r="U2" s="1" t="s">
-        <v>66</v>
-      </c>
-      <c r="V2" s="1" t="s">
-        <v>67</v>
-      </c>
-      <c r="W2" s="1" t="s">
-        <v>68</v>
-      </c>
-      <c r="X2" s="1" t="s">
-        <v>69</v>
-      </c>
-      <c r="Y2" s="1">
-        <v>401202</v>
-      </c>
-      <c r="Z2" s="1">
-        <v>179</v>
-      </c>
-      <c r="AA2" s="1">
-        <v>900</v>
-      </c>
-      <c r="AB2" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC2" s="7">
-        <v>7</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAC201B6-DCEE-4C93-A919-B2D4018F90C6}">
   <dimension ref="A1:F5"/>
@@ -19732,7 +19732,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="21">
-        <v>100064</v>
+        <v>100071</v>
       </c>
       <c r="B2" s="21">
         <v>90</v>

--- a/Data/ENWR_Creation.xlsx
+++ b/Data/ENWR_Creation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4B9CE95-EC4A-4BD3-92DE-2D2DBABF718D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEB6EB7F-3485-4D3E-94CC-7908815E4105}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RP_Deposite_Request_Agriculture" sheetId="1" r:id="rId1"/>
@@ -18301,6 +18301,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
     <col min="11" max="11" width="14.5703125" customWidth="1"/>
@@ -19359,7 +19360,7 @@
         <v>130000</v>
       </c>
       <c r="K2" s="1">
-        <v>850</v>
+        <v>1190</v>
       </c>
       <c r="L2" s="1">
         <v>5000</v>
@@ -19413,7 +19414,7 @@
         <v>100</v>
       </c>
       <c r="AC2" s="7">
-        <v>5</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -19732,7 +19733,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="21">
-        <v>100071</v>
+        <v>100081</v>
       </c>
       <c r="B2" s="21">
         <v>90</v>

--- a/Data/ENWR_Creation.xlsx
+++ b/Data/ENWR_Creation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEB6EB7F-3485-4D3E-94CC-7908815E4105}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58D3BAC0-03DD-4E86-88C1-6D5006A5C368}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RP_Deposite_Request_Agriculture" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="523" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="121">
   <si>
     <t>commoditySegment</t>
   </si>
@@ -411,6 +411,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -563,7 +566,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -598,13 +601,14 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="1" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1160,134 +1164,134 @@
       </c>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="30" t="s">
+      <c r="A7" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="30">
+      <c r="B7" s="29">
         <v>5555526</v>
       </c>
-      <c r="C7" s="30" t="s">
+      <c r="C7" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="31">
+      <c r="D7" s="30">
         <v>100673000000011</v>
       </c>
-      <c r="E7" s="30">
+      <c r="E7" s="29">
         <v>9999996</v>
       </c>
-      <c r="F7" s="30">
+      <c r="F7" s="29">
         <v>1000421</v>
       </c>
-      <c r="G7" s="30" t="s">
+      <c r="G7" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="H7" s="30">
+      <c r="H7" s="29">
         <v>1</v>
       </c>
-      <c r="I7" s="30">
+      <c r="I7" s="29">
         <v>500</v>
       </c>
-      <c r="J7" s="30">
+      <c r="J7" s="29">
         <v>1.7</v>
       </c>
-      <c r="K7" s="32" t="s">
+      <c r="K7" s="31" t="s">
         <v>102</v>
       </c>
-      <c r="L7" s="30" t="s">
+      <c r="L7" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="M7" s="30" t="s">
+      <c r="M7" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="N7" s="33" t="s">
+      <c r="N7" s="32" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="30" t="s">
+      <c r="A8" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="30">
+      <c r="B8" s="29">
         <v>5555527</v>
       </c>
-      <c r="C8" s="30" t="s">
+      <c r="C8" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="31">
+      <c r="D8" s="30">
         <v>100673000000011</v>
       </c>
-      <c r="E8" s="30">
+      <c r="E8" s="29">
         <v>9999996</v>
       </c>
-      <c r="F8" s="30">
+      <c r="F8" s="29">
         <v>1000421</v>
       </c>
-      <c r="G8" s="30" t="s">
+      <c r="G8" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="H8" s="30">
+      <c r="H8" s="29">
         <v>1</v>
       </c>
-      <c r="I8" s="30">
+      <c r="I8" s="29">
         <v>700</v>
       </c>
-      <c r="J8" s="30">
+      <c r="J8" s="29">
         <v>1.7</v>
       </c>
-      <c r="K8" s="32" t="s">
+      <c r="K8" s="31" t="s">
         <v>102</v>
       </c>
-      <c r="L8" s="30" t="s">
+      <c r="L8" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="M8" s="30" t="s">
+      <c r="M8" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="N8" s="33" t="s">
+      <c r="N8" s="32" t="s">
         <v>117</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="30" t="s">
+      <c r="A9" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="30">
+      <c r="B9" s="29">
         <v>5555528</v>
       </c>
-      <c r="C9" s="30" t="s">
+      <c r="C9" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="31">
+      <c r="D9" s="30">
         <v>100673000000011</v>
       </c>
-      <c r="E9" s="30">
+      <c r="E9" s="29">
         <v>9999996</v>
       </c>
-      <c r="F9" s="30">
+      <c r="F9" s="29">
         <v>1000421</v>
       </c>
-      <c r="G9" s="30" t="s">
+      <c r="G9" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="H9" s="30">
+      <c r="H9" s="29">
         <v>1</v>
       </c>
-      <c r="I9" s="30">
+      <c r="I9" s="29">
         <v>500</v>
       </c>
-      <c r="J9" s="30">
+      <c r="J9" s="29">
         <v>1.7</v>
       </c>
-      <c r="K9" s="32" t="s">
+      <c r="K9" s="31" t="s">
         <v>102</v>
       </c>
-      <c r="L9" s="30" t="s">
+      <c r="L9" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="M9" s="30" t="s">
+      <c r="M9" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="N9" s="33" t="s">
+      <c r="N9" s="32" t="s">
         <v>117</v>
       </c>
     </row>
@@ -1508,7 +1512,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A373F2DD-5EC0-4ACB-A836-AAE06D9D61D0}">
-  <dimension ref="A1:T10"/>
+  <dimension ref="A1:T11"/>
   <sheetFormatPr defaultColWidth="17.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -1597,8 +1601,8 @@
       <c r="H2" s="15">
         <v>700</v>
       </c>
-      <c r="I2" s="15">
-        <v>1</v>
+      <c r="I2" s="34">
+        <v>1.7</v>
       </c>
       <c r="J2" s="15" t="s">
         <v>30</v>
@@ -1641,8 +1645,8 @@
       <c r="H3" s="1">
         <v>750</v>
       </c>
-      <c r="I3" s="28">
-        <v>1</v>
+      <c r="I3" s="34">
+        <v>1.7</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>30</v>
@@ -1683,8 +1687,8 @@
       <c r="H4" s="1">
         <v>700</v>
       </c>
-      <c r="I4" s="28">
-        <v>1</v>
+      <c r="I4" s="34">
+        <v>1.7</v>
       </c>
       <c r="J4" s="1" t="s">
         <v>30</v>
@@ -1725,8 +1729,8 @@
       <c r="H5" s="1">
         <v>850</v>
       </c>
-      <c r="I5" s="28">
-        <v>1</v>
+      <c r="I5" s="34">
+        <v>1.7</v>
       </c>
       <c r="J5" s="1" t="s">
         <v>30</v>
@@ -1767,8 +1771,8 @@
       <c r="H6" s="1">
         <v>700</v>
       </c>
-      <c r="I6" s="28">
-        <v>1</v>
+      <c r="I6" s="34">
+        <v>1.7</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>30</v>
@@ -1809,7 +1813,7 @@
       <c r="H7" s="1">
         <v>500</v>
       </c>
-      <c r="I7" s="28">
+      <c r="I7" s="34">
         <v>1.7</v>
       </c>
       <c r="J7" s="1" t="s">
@@ -1851,8 +1855,8 @@
       <c r="H8" s="1">
         <v>700</v>
       </c>
-      <c r="I8" s="28">
-        <v>1</v>
+      <c r="I8" s="34">
+        <v>1.7</v>
       </c>
       <c r="J8" s="1" t="s">
         <v>30</v>
@@ -1893,8 +1897,8 @@
       <c r="H9" s="1">
         <v>700</v>
       </c>
-      <c r="I9" s="28">
-        <v>1</v>
+      <c r="I9" s="34">
+        <v>1.7</v>
       </c>
       <c r="J9" s="1" t="s">
         <v>30</v>
@@ -1921,10 +1925,10 @@
         <v>100673000000011</v>
       </c>
       <c r="D10" s="1">
-        <v>9999996</v>
+        <v>9997115</v>
       </c>
       <c r="E10" s="1">
-        <v>1000421</v>
+        <v>8211642</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>29</v>
@@ -1935,8 +1939,8 @@
       <c r="H10" s="1">
         <v>700</v>
       </c>
-      <c r="I10" s="28">
-        <v>1</v>
+      <c r="I10" s="35">
+        <v>1.7</v>
       </c>
       <c r="J10" s="1" t="s">
         <v>30</v>
@@ -1951,9 +1955,51 @@
         <v>11</v>
       </c>
       <c r="N10" s="21"/>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="1">
+        <v>1555521</v>
+      </c>
+      <c r="C11" s="2">
+        <v>100673000000011</v>
+      </c>
+      <c r="D11" s="1">
+        <v>9997115</v>
+      </c>
+      <c r="E11" s="1">
+        <v>8211642</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G11" s="1">
+        <v>15</v>
+      </c>
+      <c r="H11" s="1">
+        <v>100</v>
+      </c>
+      <c r="I11" s="35">
+        <v>1.7</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M11" s="1">
+        <v>11</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -18489,7 +18535,7 @@
       <c r="O4" s="7"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="34" t="s">
+      <c r="A5" s="33" t="s">
         <v>70</v>
       </c>
       <c r="B5" s="22">
@@ -18501,7 +18547,7 @@
       <c r="D5" s="22">
         <v>11</v>
       </c>
-      <c r="E5" s="29">
+      <c r="E5" s="28">
         <v>9996059</v>
       </c>
       <c r="F5" s="24">
@@ -19360,7 +19406,7 @@
         <v>130000</v>
       </c>
       <c r="K2" s="1">
-        <v>1190</v>
+        <v>170</v>
       </c>
       <c r="L2" s="1">
         <v>5000</v>
@@ -19410,7 +19456,7 @@
       <c r="AA2" s="1">
         <v>900</v>
       </c>
-      <c r="AB2" s="7">
+      <c r="AB2" s="11">
         <v>100</v>
       </c>
       <c r="AC2" s="7">
@@ -19733,7 +19779,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="21">
-        <v>100081</v>
+        <v>1000621</v>
       </c>
       <c r="B2" s="21">
         <v>90</v>

--- a/Data/ENWR_Creation.xlsx
+++ b/Data/ENWR_Creation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{58D3BAC0-03DD-4E86-88C1-6D5006A5C368}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51A3FB4F-3163-4DA0-9DA5-095B578528FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RP_Deposite_Request_Agriculture" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="528" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="121">
   <si>
     <t>commoditySegment</t>
   </si>
@@ -411,9 +411,6 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="0.0"/>
-  </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -608,7 +605,7 @@
     <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1512,7 +1509,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A373F2DD-5EC0-4ACB-A836-AAE06D9D61D0}">
-  <dimension ref="A1:T11"/>
+  <dimension ref="A1:T13"/>
   <sheetFormatPr defaultColWidth="17.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -1939,7 +1936,7 @@
       <c r="H10" s="1">
         <v>700</v>
       </c>
-      <c r="I10" s="35">
+      <c r="I10" s="34">
         <v>1.7</v>
       </c>
       <c r="J10" s="1" t="s">
@@ -1981,7 +1978,7 @@
       <c r="H11" s="1">
         <v>100</v>
       </c>
-      <c r="I11" s="35">
+      <c r="I11" s="34">
         <v>1.7</v>
       </c>
       <c r="J11" s="1" t="s">
@@ -1994,6 +1991,88 @@
         <v>15</v>
       </c>
       <c r="M11" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="1">
+        <v>1555522</v>
+      </c>
+      <c r="C12" s="2">
+        <v>100673000000011</v>
+      </c>
+      <c r="D12" s="1">
+        <v>9997115</v>
+      </c>
+      <c r="E12" s="1">
+        <v>8211642</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G12" s="1">
+        <v>15</v>
+      </c>
+      <c r="H12" s="1">
+        <v>100</v>
+      </c>
+      <c r="I12" s="34">
+        <v>1.7</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M12" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="1">
+        <v>1555523</v>
+      </c>
+      <c r="C13" s="2">
+        <v>100673000000011</v>
+      </c>
+      <c r="D13" s="35">
+        <v>9999996</v>
+      </c>
+      <c r="E13" s="35">
+        <v>1000421</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G13" s="1">
+        <v>15</v>
+      </c>
+      <c r="H13" s="1">
+        <v>100</v>
+      </c>
+      <c r="I13" s="34">
+        <v>1.7</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M13" s="1">
         <v>11</v>
       </c>
     </row>

--- a/Data/ENWR_Creation.xlsx
+++ b/Data/ENWR_Creation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{51A3FB4F-3163-4DA0-9DA5-095B578528FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A584EB3-64D4-46A4-B641-C0539EF09F11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RP_Deposite_Request_Agriculture" sheetId="1" r:id="rId1"/>
@@ -1444,7 +1444,7 @@
         <v>1</v>
       </c>
       <c r="I13" s="1">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="J13" s="1">
         <v>1.7</v>
@@ -19485,7 +19485,7 @@
         <v>130000</v>
       </c>
       <c r="K2" s="1">
-        <v>170</v>
+        <v>100</v>
       </c>
       <c r="L2" s="1">
         <v>5000</v>

--- a/Data/ENWR_Creation.xlsx
+++ b/Data/ENWR_Creation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4A584EB3-64D4-46A4-B641-C0539EF09F11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{815F55D1-C3E1-47C1-9BA4-28935AF6FDF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RP_Deposite_Request_Agriculture" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="538" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="122">
   <si>
     <t>commoditySegment</t>
   </si>
@@ -405,6 +405,9 @@
   </si>
   <si>
     <t>ass</t>
+  </si>
+  <si>
+    <t>ALUMINUM</t>
   </si>
 </sst>
 </file>
@@ -18422,7 +18425,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4F18DE3F-30A6-4897-A930-C2CD56DF895A}">
-  <dimension ref="A1:O20"/>
+  <dimension ref="A1:O21"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -19336,6 +19339,50 @@
         <v>79</v>
       </c>
       <c r="O20" s="7"/>
+    </row>
+    <row r="21" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A21" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="B21" s="7">
+        <v>5555570</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D21" s="7">
+        <v>11</v>
+      </c>
+      <c r="E21" s="7">
+        <v>9996059</v>
+      </c>
+      <c r="F21" s="7">
+        <v>5750013</v>
+      </c>
+      <c r="G21" s="11">
+        <v>178888880001601</v>
+      </c>
+      <c r="H21" s="7">
+        <v>1001</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>121</v>
+      </c>
+      <c r="J21" s="7">
+        <v>20</v>
+      </c>
+      <c r="K21" s="7">
+        <v>20</v>
+      </c>
+      <c r="L21" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="M21" s="7">
+        <v>100</v>
+      </c>
+      <c r="N21" s="7" t="s">
+        <v>79</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Data/ENWR_Creation.xlsx
+++ b/Data/ENWR_Creation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{815F55D1-C3E1-47C1-9BA4-28935AF6FDF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA10B30E-3BA0-4BAA-892D-AF42CE533B43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RP_Deposite_Request_Agriculture" sheetId="1" r:id="rId1"/>
@@ -2043,10 +2043,10 @@
         <v>13</v>
       </c>
       <c r="B13" s="1">
-        <v>1555523</v>
+        <v>1555524</v>
       </c>
       <c r="C13" s="2">
-        <v>100673000000011</v>
+        <v>120733340001420</v>
       </c>
       <c r="D13" s="35">
         <v>9999996</v>
@@ -2061,7 +2061,7 @@
         <v>15</v>
       </c>
       <c r="H13" s="1">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="I13" s="34">
         <v>1.7</v>
@@ -19532,7 +19532,7 @@
         <v>130000</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>1190</v>
       </c>
       <c r="L2" s="1">
         <v>5000</v>

--- a/Data/ENWR_Creation.xlsx
+++ b/Data/ENWR_Creation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EA10B30E-3BA0-4BAA-892D-AF42CE533B43}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{391BA98E-3DE6-4F9C-A0A8-74EA916B7BEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RP_Deposite_Request_Agriculture" sheetId="1" r:id="rId1"/>
@@ -1318,7 +1318,7 @@
         <v>14</v>
       </c>
       <c r="H10" s="1">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I10" s="1">
         <v>700</v>
@@ -1327,7 +1327,7 @@
         <v>1.7</v>
       </c>
       <c r="K10" s="7" t="s">
-        <v>102</v>
+        <v>58</v>
       </c>
       <c r="L10" s="1" t="s">
         <v>15</v>
@@ -19586,7 +19586,7 @@
         <v>100</v>
       </c>
       <c r="AC2" s="7">
-        <v>7</v>
+        <v>5</v>
       </c>
     </row>
   </sheetData>
@@ -19905,7 +19905,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="21">
-        <v>1000621</v>
+        <v>1000691</v>
       </c>
       <c r="B2" s="21">
         <v>90</v>

--- a/Data/ENWR_Creation.xlsx
+++ b/Data/ENWR_Creation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{391BA98E-3DE6-4F9C-A0A8-74EA916B7BEA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8F5DA80-14B5-43C1-AE55-BD15992BD0FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RP_Deposite_Request_Agriculture" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="543" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="122">
   <si>
     <t>commoditySegment</t>
   </si>
@@ -566,7 +566,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -609,6 +609,7 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -889,11 +890,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N14"/>
+  <dimension ref="A1:N16"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="22.28515625" customWidth="1"/>
     <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.140625" bestFit="1" customWidth="1"/>
@@ -1505,6 +1506,88 @@
       </c>
       <c r="N14" s="21"/>
     </row>
+    <row r="15" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="1">
+        <v>1555530</v>
+      </c>
+      <c r="C15" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D15" s="2">
+        <v>100673000000011</v>
+      </c>
+      <c r="E15" s="35">
+        <v>9999996</v>
+      </c>
+      <c r="F15" s="35">
+        <v>1000421</v>
+      </c>
+      <c r="G15" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H15" s="1">
+        <v>1</v>
+      </c>
+      <c r="I15" s="1">
+        <v>2000</v>
+      </c>
+      <c r="J15" s="34">
+        <v>1</v>
+      </c>
+      <c r="K15" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M15" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="16" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A16" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="1">
+        <v>1555531</v>
+      </c>
+      <c r="C16" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16" s="2">
+        <v>100673001212128</v>
+      </c>
+      <c r="E16" s="35">
+        <v>9999996</v>
+      </c>
+      <c r="F16" s="35">
+        <v>1000421</v>
+      </c>
+      <c r="G16" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H16" s="1">
+        <v>6</v>
+      </c>
+      <c r="I16" s="1">
+        <v>2000</v>
+      </c>
+      <c r="J16" s="34">
+        <v>1</v>
+      </c>
+      <c r="K16" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="L16" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M16" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1512,7 +1595,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A373F2DD-5EC0-4ACB-A836-AAE06D9D61D0}">
-  <dimension ref="A1:T13"/>
+  <dimension ref="A1:T18"/>
   <sheetFormatPr defaultColWidth="17.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
@@ -2078,6 +2161,92 @@
       <c r="M13" s="1">
         <v>11</v>
       </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="1">
+        <v>1555525</v>
+      </c>
+      <c r="C14" s="2">
+        <v>120733340001420</v>
+      </c>
+      <c r="D14" s="35">
+        <v>9999996</v>
+      </c>
+      <c r="E14" s="35">
+        <v>1000421</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G14" s="1">
+        <v>15</v>
+      </c>
+      <c r="H14" s="1">
+        <v>700</v>
+      </c>
+      <c r="I14" s="34">
+        <v>1.7</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M14" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="1">
+        <v>1555529</v>
+      </c>
+      <c r="C15" s="2">
+        <v>100673000000011</v>
+      </c>
+      <c r="D15" s="35">
+        <v>9999996</v>
+      </c>
+      <c r="E15" s="35">
+        <v>1000421</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G15" s="1">
+        <v>1</v>
+      </c>
+      <c r="H15" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I15" s="34">
+        <v>1</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M15" s="1">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="18" spans="8:9" x14ac:dyDescent="0.25">
+      <c r="H18" s="19"/>
+      <c r="I18" s="36"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -19532,7 +19701,7 @@
         <v>130000</v>
       </c>
       <c r="K2" s="1">
-        <v>1190</v>
+        <v>2000</v>
       </c>
       <c r="L2" s="1">
         <v>5000</v>
@@ -19580,13 +19749,13 @@
         <v>179</v>
       </c>
       <c r="AA2" s="1">
-        <v>900</v>
+        <v>6000</v>
       </c>
       <c r="AB2" s="11">
-        <v>100</v>
+        <v>700</v>
       </c>
       <c r="AC2" s="7">
-        <v>5</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -19905,7 +20074,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="21">
-        <v>1000691</v>
+        <v>31111</v>
       </c>
       <c r="B2" s="21">
         <v>90</v>

--- a/Data/ENWR_Creation.xlsx
+++ b/Data/ENWR_Creation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D8F5DA80-14B5-43C1-AE55-BD15992BD0FA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D58CAF4-4013-4EB9-81C9-8747C30F53A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RP_Deposite_Request_Agriculture" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="122">
   <si>
     <t>commoditySegment</t>
   </si>
@@ -890,7 +890,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:N16"/>
+  <dimension ref="A1:N17"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
@@ -1585,6 +1585,47 @@
         <v>15</v>
       </c>
       <c r="M16" s="1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A17" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" s="1">
+        <v>1555532</v>
+      </c>
+      <c r="C17" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" s="2">
+        <v>100673001212128</v>
+      </c>
+      <c r="E17" s="35">
+        <v>9999996</v>
+      </c>
+      <c r="F17" s="35">
+        <v>1000421</v>
+      </c>
+      <c r="G17" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="H17" s="1">
+        <v>1</v>
+      </c>
+      <c r="I17" s="1">
+        <v>100</v>
+      </c>
+      <c r="J17" s="1">
+        <v>1.7</v>
+      </c>
+      <c r="K17" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="L17" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M17" s="1" t="s">
         <v>15</v>
       </c>
     </row>
@@ -2208,7 +2249,7 @@
         <v>13</v>
       </c>
       <c r="B15" s="1">
-        <v>1555529</v>
+        <v>1555631</v>
       </c>
       <c r="C15" s="2">
         <v>100673000000011</v>
@@ -2223,13 +2264,13 @@
         <v>29</v>
       </c>
       <c r="G15" s="1">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H15" s="1">
-        <v>2000</v>
+        <v>700</v>
       </c>
       <c r="I15" s="34">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="J15" s="1" t="s">
         <v>30</v>
@@ -19701,7 +19742,7 @@
         <v>130000</v>
       </c>
       <c r="K2" s="1">
-        <v>2000</v>
+        <v>1190</v>
       </c>
       <c r="L2" s="1">
         <v>5000</v>
@@ -19749,13 +19790,13 @@
         <v>179</v>
       </c>
       <c r="AA2" s="1">
-        <v>6000</v>
+        <v>900</v>
       </c>
       <c r="AB2" s="11">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="AC2" s="7">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -20074,7 +20115,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="21">
-        <v>31111</v>
+        <v>32211</v>
       </c>
       <c r="B2" s="21">
         <v>90</v>

--- a/Data/ENWR_Creation.xlsx
+++ b/Data/ENWR_Creation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D58CAF4-4013-4EB9-81C9-8747C30F53A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E8240E8F-4850-43E0-9E44-A9693F1FFB28}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RP_Deposite_Request_Agriculture" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="571" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="120">
   <si>
     <t>commoditySegment</t>
   </si>
@@ -386,16 +386,10 @@
     <t>Status</t>
   </si>
   <si>
-    <t>Complete</t>
-  </si>
-  <si>
     <t>Auto Rejected By CCRL</t>
   </si>
   <si>
     <t>Phy</t>
-  </si>
-  <si>
-    <t>Used</t>
   </si>
   <si>
     <t>phy</t>
@@ -478,7 +472,7 @@
       <family val="3"/>
     </font>
   </fonts>
-  <fills count="9">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -521,12 +515,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="3">
     <border>
@@ -566,7 +554,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -598,18 +586,16 @@
     <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="1" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="1" fillId="8" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="8" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -945,689 +931,676 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="15" t="s">
+      <c r="A2" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="15">
-        <v>5555513</v>
-      </c>
-      <c r="C2" s="15" t="s">
+      <c r="B2" s="30">
+        <v>5555613</v>
+      </c>
+      <c r="C2" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="16">
+      <c r="D2" s="25">
         <v>100673000000011</v>
       </c>
-      <c r="E2" s="15">
+      <c r="E2" s="30">
         <v>9999996</v>
       </c>
-      <c r="F2" s="15">
+      <c r="F2" s="30">
         <v>1000421</v>
       </c>
-      <c r="G2" s="15" t="s">
+      <c r="G2" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="15">
+      <c r="H2" s="30">
         <v>1</v>
       </c>
-      <c r="I2" s="15">
-        <v>500</v>
-      </c>
-      <c r="J2" s="15">
+      <c r="I2" s="30">
+        <v>4000</v>
+      </c>
+      <c r="J2" s="30">
         <v>1.7</v>
       </c>
-      <c r="K2" s="25" t="s">
+      <c r="K2" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="L2" s="15" t="s">
+      <c r="L2" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="M2" s="15" t="s">
+      <c r="M2" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="N2" s="15" t="s">
-        <v>114</v>
-      </c>
+      <c r="N2" s="30"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
+      <c r="A3" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="15">
-        <v>5555522</v>
-      </c>
-      <c r="C3" s="15" t="s">
+      <c r="B3" s="30">
+        <v>5555614</v>
+      </c>
+      <c r="C3" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="16">
-        <v>120733340001420</v>
-      </c>
-      <c r="E3" s="15">
-        <v>9999996</v>
-      </c>
-      <c r="F3" s="15">
-        <v>1000421</v>
-      </c>
-      <c r="G3" s="15" t="s">
+      <c r="D3" s="25">
+        <v>15500001000761</v>
+      </c>
+      <c r="E3" s="30">
+        <v>9996059</v>
+      </c>
+      <c r="F3" s="30">
+        <v>5750013</v>
+      </c>
+      <c r="G3" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="15">
-        <v>1</v>
-      </c>
-      <c r="I3" s="15">
-        <v>500</v>
-      </c>
-      <c r="J3" s="15">
-        <v>1.7</v>
-      </c>
-      <c r="K3" s="25" t="s">
+      <c r="H3" s="30">
+        <v>6</v>
+      </c>
+      <c r="I3" s="30">
+        <v>5000</v>
+      </c>
+      <c r="J3" s="30">
+        <v>0.5</v>
+      </c>
+      <c r="K3" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="L3" s="15" t="s">
+      <c r="L3" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="M3" s="15" t="s">
+      <c r="M3" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="N3" s="15" t="s">
-        <v>114</v>
-      </c>
+      <c r="N3" s="30"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="15" t="s">
+      <c r="A4" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="15">
-        <v>5555523</v>
-      </c>
-      <c r="C4" s="15" t="s">
+      <c r="B4" s="30">
+        <v>5555615</v>
+      </c>
+      <c r="C4" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="16">
-        <v>100673000000011</v>
-      </c>
-      <c r="E4" s="15">
-        <v>9999996</v>
-      </c>
-      <c r="F4" s="15">
-        <v>1000421</v>
-      </c>
-      <c r="G4" s="15" t="s">
+      <c r="D4" s="25">
+        <v>178888880001601</v>
+      </c>
+      <c r="E4" s="30">
+        <v>9996059</v>
+      </c>
+      <c r="F4" s="30">
+        <v>5750013</v>
+      </c>
+      <c r="G4" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="15">
+      <c r="H4" s="30">
         <v>1</v>
       </c>
-      <c r="I4" s="15">
-        <v>700</v>
-      </c>
-      <c r="J4" s="15">
+      <c r="I4" s="30">
+        <v>500</v>
+      </c>
+      <c r="J4" s="30">
         <v>1.7</v>
       </c>
-      <c r="K4" s="25" t="s">
+      <c r="K4" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="L4" s="15" t="s">
+      <c r="L4" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="M4" s="15" t="s">
+      <c r="M4" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="N4" s="15" t="s">
-        <v>114</v>
-      </c>
+      <c r="N4" s="30"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="15" t="s">
+      <c r="A5" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="15">
-        <v>5555524</v>
-      </c>
-      <c r="C5" s="15" t="s">
+      <c r="B5" s="30">
+        <v>5555616</v>
+      </c>
+      <c r="C5" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="16">
-        <v>120733340001420</v>
-      </c>
-      <c r="E5" s="15">
+      <c r="D5" s="25">
+        <v>15500001000761</v>
+      </c>
+      <c r="E5" s="30">
         <v>9999996</v>
       </c>
-      <c r="F5" s="15">
+      <c r="F5" s="30">
         <v>1000421</v>
       </c>
-      <c r="G5" s="15" t="s">
+      <c r="G5" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="15">
+      <c r="H5" s="30">
         <v>1</v>
       </c>
-      <c r="I5" s="15">
+      <c r="I5" s="30">
         <v>500</v>
       </c>
-      <c r="J5" s="15">
+      <c r="J5" s="30">
         <v>1.7</v>
       </c>
-      <c r="K5" s="25" t="s">
+      <c r="K5" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="L5" s="15" t="s">
+      <c r="L5" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="M5" s="15" t="s">
+      <c r="M5" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="N5" s="15" t="s">
-        <v>114</v>
-      </c>
+      <c r="N5" s="30"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="15" t="s">
+      <c r="A6" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="15">
-        <v>5555525</v>
-      </c>
-      <c r="C6" s="15" t="s">
+      <c r="B6" s="30">
+        <v>5555617</v>
+      </c>
+      <c r="C6" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="16">
+      <c r="D6" s="25">
         <v>100673000000011</v>
       </c>
-      <c r="E6" s="15">
+      <c r="E6" s="30">
         <v>9999996</v>
       </c>
-      <c r="F6" s="15">
+      <c r="F6" s="30">
         <v>1000421</v>
       </c>
-      <c r="G6" s="15" t="s">
+      <c r="G6" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="15">
+      <c r="H6" s="30">
         <v>1</v>
       </c>
-      <c r="I6" s="15">
+      <c r="I6" s="30">
         <v>700</v>
       </c>
-      <c r="J6" s="15">
+      <c r="J6" s="30">
         <v>1.7</v>
       </c>
-      <c r="K6" s="25" t="s">
+      <c r="K6" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="L6" s="15" t="s">
+      <c r="L6" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="M6" s="15" t="s">
+      <c r="M6" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="N6" s="15" t="s">
-        <v>114</v>
-      </c>
+      <c r="N6" s="30"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="29" t="s">
+      <c r="A7" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="29">
-        <v>5555526</v>
-      </c>
-      <c r="C7" s="29" t="s">
+      <c r="B7" s="30">
+        <v>5555618</v>
+      </c>
+      <c r="C7" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="30">
+      <c r="D7" s="25">
         <v>100673000000011</v>
       </c>
-      <c r="E7" s="29">
+      <c r="E7" s="30">
         <v>9999996</v>
       </c>
-      <c r="F7" s="29">
+      <c r="F7" s="30">
         <v>1000421</v>
       </c>
-      <c r="G7" s="29" t="s">
+      <c r="G7" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="H7" s="29">
+      <c r="H7" s="30">
         <v>1</v>
       </c>
-      <c r="I7" s="29">
+      <c r="I7" s="30">
         <v>500</v>
       </c>
-      <c r="J7" s="29">
+      <c r="J7" s="30">
         <v>1.7</v>
       </c>
-      <c r="K7" s="31" t="s">
+      <c r="K7" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="L7" s="29" t="s">
+      <c r="L7" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="M7" s="29" t="s">
+      <c r="M7" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="N7" s="32" t="s">
-        <v>117</v>
-      </c>
+      <c r="N7" s="33"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="29" t="s">
+      <c r="A8" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="29">
-        <v>5555527</v>
-      </c>
-      <c r="C8" s="29" t="s">
+      <c r="B8" s="30">
+        <v>5555619</v>
+      </c>
+      <c r="C8" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="30">
+      <c r="D8" s="25">
         <v>100673000000011</v>
       </c>
-      <c r="E8" s="29">
+      <c r="E8" s="30">
         <v>9999996</v>
       </c>
-      <c r="F8" s="29">
+      <c r="F8" s="30">
         <v>1000421</v>
       </c>
-      <c r="G8" s="29" t="s">
+      <c r="G8" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="H8" s="29">
+      <c r="H8" s="30">
         <v>1</v>
       </c>
-      <c r="I8" s="29">
+      <c r="I8" s="30">
         <v>700</v>
       </c>
-      <c r="J8" s="29">
+      <c r="J8" s="30">
         <v>1.7</v>
       </c>
-      <c r="K8" s="31" t="s">
+      <c r="K8" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="L8" s="29" t="s">
+      <c r="L8" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="M8" s="29" t="s">
+      <c r="M8" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="N8" s="32" t="s">
-        <v>117</v>
-      </c>
+      <c r="N8" s="33"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="29" t="s">
+      <c r="A9" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="29">
-        <v>5555528</v>
-      </c>
-      <c r="C9" s="29" t="s">
+      <c r="B9" s="30">
+        <v>5555620</v>
+      </c>
+      <c r="C9" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="30">
+      <c r="D9" s="25">
         <v>100673000000011</v>
       </c>
-      <c r="E9" s="29">
+      <c r="E9" s="30">
         <v>9999996</v>
       </c>
-      <c r="F9" s="29">
+      <c r="F9" s="30">
         <v>1000421</v>
       </c>
-      <c r="G9" s="29" t="s">
+      <c r="G9" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="H9" s="29">
+      <c r="H9" s="30">
         <v>1</v>
       </c>
-      <c r="I9" s="29">
+      <c r="I9" s="30">
         <v>500</v>
       </c>
-      <c r="J9" s="29">
+      <c r="J9" s="30">
         <v>1.7</v>
       </c>
-      <c r="K9" s="31" t="s">
+      <c r="K9" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="L9" s="29" t="s">
+      <c r="L9" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="M9" s="29" t="s">
+      <c r="M9" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="N9" s="32" t="s">
-        <v>117</v>
-      </c>
+      <c r="N9" s="33"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
+      <c r="A10" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="1">
-        <v>5555529</v>
-      </c>
-      <c r="C10" s="1" t="s">
+      <c r="B10" s="30">
+        <v>5555621</v>
+      </c>
+      <c r="C10" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="26">
+      <c r="D10" s="25">
         <v>100673000000011</v>
       </c>
-      <c r="E10" s="1">
+      <c r="E10" s="30">
         <v>9999996</v>
       </c>
-      <c r="F10" s="1">
+      <c r="F10" s="30">
         <v>1000421</v>
       </c>
-      <c r="G10" s="1" t="s">
+      <c r="G10" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="H10" s="1">
+      <c r="H10" s="30">
         <v>15</v>
       </c>
-      <c r="I10" s="1">
+      <c r="I10" s="30">
         <v>700</v>
       </c>
-      <c r="J10" s="1">
+      <c r="J10" s="30">
         <v>1.7</v>
       </c>
-      <c r="K10" s="7" t="s">
+      <c r="K10" s="32" t="s">
         <v>58</v>
       </c>
-      <c r="L10" s="1" t="s">
+      <c r="L10" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="M10" s="1" t="s">
+      <c r="M10" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="N10" s="21"/>
+      <c r="N10" s="33"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
+      <c r="A11" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="1">
-        <v>5555530</v>
-      </c>
-      <c r="C11" s="1" t="s">
+      <c r="B11" s="30">
+        <v>5555622</v>
+      </c>
+      <c r="C11" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="D11" s="26">
+      <c r="D11" s="25">
         <v>100673000000011</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E11" s="30">
         <v>9999996</v>
       </c>
-      <c r="F11" s="1">
+      <c r="F11" s="30">
         <v>1000421</v>
       </c>
-      <c r="G11" s="1" t="s">
+      <c r="G11" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="H11" s="1">
+      <c r="H11" s="30">
         <v>1</v>
       </c>
-      <c r="I11" s="1">
+      <c r="I11" s="30">
         <v>500</v>
       </c>
-      <c r="J11" s="1">
+      <c r="J11" s="30">
         <v>1.7</v>
       </c>
-      <c r="K11" s="7" t="s">
+      <c r="K11" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="L11" s="1" t="s">
+      <c r="L11" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="M11" s="1" t="s">
+      <c r="M11" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="N11" s="21"/>
+      <c r="N11" s="33"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
+      <c r="A12" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="1">
-        <v>5555531</v>
-      </c>
-      <c r="C12" s="1" t="s">
+      <c r="B12" s="30">
+        <v>5555623</v>
+      </c>
+      <c r="C12" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="26">
+      <c r="D12" s="25">
         <v>100673000000011</v>
       </c>
-      <c r="E12" s="1">
+      <c r="E12" s="30">
         <v>9999996</v>
       </c>
-      <c r="F12" s="1">
+      <c r="F12" s="30">
         <v>1000421</v>
       </c>
-      <c r="G12" s="1" t="s">
+      <c r="G12" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="H12" s="1">
+      <c r="H12" s="30">
         <v>1</v>
       </c>
-      <c r="I12" s="1">
+      <c r="I12" s="30">
         <v>700</v>
       </c>
-      <c r="J12" s="1">
+      <c r="J12" s="30">
         <v>1.7</v>
       </c>
-      <c r="K12" s="7" t="s">
+      <c r="K12" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="L12" s="1" t="s">
+      <c r="L12" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="M12" s="1" t="s">
+      <c r="M12" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="N12" s="21"/>
+      <c r="N12" s="33"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
+      <c r="A13" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="1">
-        <v>5555532</v>
-      </c>
-      <c r="C13" s="1" t="s">
+      <c r="B13" s="30">
+        <v>5555624</v>
+      </c>
+      <c r="C13" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="D13" s="26">
+      <c r="D13" s="25">
         <v>100673000000011</v>
       </c>
-      <c r="E13" s="1">
+      <c r="E13" s="30">
         <v>9999996</v>
       </c>
-      <c r="F13" s="1">
+      <c r="F13" s="30">
         <v>1000421</v>
       </c>
-      <c r="G13" s="1" t="s">
+      <c r="G13" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="H13" s="1">
+      <c r="H13" s="30">
         <v>1</v>
       </c>
-      <c r="I13" s="1">
+      <c r="I13" s="30">
         <v>100</v>
       </c>
-      <c r="J13" s="1">
+      <c r="J13" s="30">
         <v>1.7</v>
       </c>
-      <c r="K13" s="7" t="s">
+      <c r="K13" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="L13" s="1" t="s">
+      <c r="L13" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="M13" s="1" t="s">
+      <c r="M13" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="N13" s="21"/>
+      <c r="N13" s="33"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
+      <c r="A14" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="1">
-        <v>5555533</v>
-      </c>
-      <c r="C14" s="1" t="s">
+      <c r="B14" s="30">
+        <v>5555625</v>
+      </c>
+      <c r="C14" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="D14" s="26">
+      <c r="D14" s="25">
         <v>100673000000011</v>
       </c>
-      <c r="E14" s="1">
+      <c r="E14" s="30">
         <v>9999996</v>
       </c>
-      <c r="F14" s="1">
+      <c r="F14" s="30">
         <v>1000421</v>
       </c>
-      <c r="G14" s="1" t="s">
+      <c r="G14" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="H14" s="1">
+      <c r="H14" s="30">
         <v>1</v>
       </c>
-      <c r="I14" s="1">
+      <c r="I14" s="30">
         <v>700</v>
       </c>
-      <c r="J14" s="1">
+      <c r="J14" s="30">
         <v>1.7</v>
       </c>
-      <c r="K14" s="7" t="s">
+      <c r="K14" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="L14" s="1" t="s">
+      <c r="L14" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="M14" s="1" t="s">
+      <c r="M14" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="N14" s="21"/>
+      <c r="N14" s="33"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
+      <c r="A15" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="1">
-        <v>1555530</v>
-      </c>
-      <c r="C15" s="1" t="s">
+      <c r="B15" s="30">
+        <v>5555626</v>
+      </c>
+      <c r="C15" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="D15" s="2">
+      <c r="D15" s="25">
         <v>100673000000011</v>
       </c>
-      <c r="E15" s="35">
+      <c r="E15" s="30">
         <v>9999996</v>
       </c>
-      <c r="F15" s="35">
+      <c r="F15" s="30">
         <v>1000421</v>
       </c>
-      <c r="G15" s="1" t="s">
+      <c r="G15" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="H15" s="1">
+      <c r="H15" s="30">
         <v>1</v>
       </c>
-      <c r="I15" s="1">
+      <c r="I15" s="30">
         <v>2000</v>
       </c>
-      <c r="J15" s="34">
+      <c r="J15" s="29">
         <v>1</v>
       </c>
-      <c r="K15" s="7" t="s">
+      <c r="K15" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="L15" s="1" t="s">
+      <c r="L15" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="M15" s="1" t="s">
+      <c r="M15" s="30" t="s">
         <v>15</v>
       </c>
+      <c r="N15" s="34"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="1" t="s">
+      <c r="A16" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="1">
-        <v>1555531</v>
-      </c>
-      <c r="C16" s="1" t="s">
+      <c r="B16" s="30">
+        <v>5555627</v>
+      </c>
+      <c r="C16" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="D16" s="2">
+      <c r="D16" s="25">
         <v>100673001212128</v>
       </c>
-      <c r="E16" s="35">
+      <c r="E16" s="30">
         <v>9999996</v>
       </c>
-      <c r="F16" s="35">
+      <c r="F16" s="30">
         <v>1000421</v>
       </c>
-      <c r="G16" s="1" t="s">
+      <c r="G16" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="H16" s="1">
+      <c r="H16" s="30">
         <v>6</v>
       </c>
-      <c r="I16" s="1">
+      <c r="I16" s="30">
         <v>2000</v>
       </c>
-      <c r="J16" s="34">
+      <c r="J16" s="29">
         <v>1</v>
       </c>
-      <c r="K16" s="7" t="s">
+      <c r="K16" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="L16" s="1" t="s">
+      <c r="L16" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="M16" s="1" t="s">
+      <c r="M16" s="30" t="s">
         <v>15</v>
       </c>
+      <c r="N16" s="34"/>
     </row>
-    <row r="17" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="A17" s="1" t="s">
+    <row r="17" spans="1:14" x14ac:dyDescent="0.25">
+      <c r="A17" s="30" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="1">
-        <v>1555532</v>
-      </c>
-      <c r="C17" s="1" t="s">
+      <c r="B17" s="30">
+        <v>5555628</v>
+      </c>
+      <c r="C17" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="D17" s="2">
+      <c r="D17" s="25">
         <v>100673001212128</v>
       </c>
-      <c r="E17" s="35">
+      <c r="E17" s="30">
         <v>9999996</v>
       </c>
-      <c r="F17" s="35">
+      <c r="F17" s="30">
         <v>1000421</v>
       </c>
-      <c r="G17" s="1" t="s">
+      <c r="G17" s="30" t="s">
         <v>14</v>
       </c>
-      <c r="H17" s="1">
+      <c r="H17" s="30">
         <v>1</v>
       </c>
-      <c r="I17" s="1">
+      <c r="I17" s="30">
         <v>100</v>
       </c>
-      <c r="J17" s="1">
+      <c r="J17" s="30">
         <v>1.7</v>
       </c>
-      <c r="K17" s="7" t="s">
+      <c r="K17" s="32" t="s">
         <v>102</v>
       </c>
-      <c r="L17" s="1" t="s">
+      <c r="L17" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="M17" s="1" t="s">
+      <c r="M17" s="30" t="s">
         <v>15</v>
       </c>
+      <c r="N17" s="34"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1725,7 +1698,7 @@
       <c r="H2" s="15">
         <v>700</v>
       </c>
-      <c r="I2" s="34">
+      <c r="I2" s="29">
         <v>1.7</v>
       </c>
       <c r="J2" s="15" t="s">
@@ -1740,8 +1713,8 @@
       <c r="M2" s="15">
         <v>11</v>
       </c>
-      <c r="N2" s="27" t="s">
-        <v>115</v>
+      <c r="N2" s="26" t="s">
+        <v>114</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
@@ -1769,7 +1742,7 @@
       <c r="H3" s="1">
         <v>750</v>
       </c>
-      <c r="I3" s="34">
+      <c r="I3" s="29">
         <v>1.7</v>
       </c>
       <c r="J3" s="1" t="s">
@@ -1811,7 +1784,7 @@
       <c r="H4" s="1">
         <v>700</v>
       </c>
-      <c r="I4" s="34">
+      <c r="I4" s="29">
         <v>1.7</v>
       </c>
       <c r="J4" s="1" t="s">
@@ -1853,7 +1826,7 @@
       <c r="H5" s="1">
         <v>850</v>
       </c>
-      <c r="I5" s="34">
+      <c r="I5" s="29">
         <v>1.7</v>
       </c>
       <c r="J5" s="1" t="s">
@@ -1895,7 +1868,7 @@
       <c r="H6" s="1">
         <v>700</v>
       </c>
-      <c r="I6" s="34">
+      <c r="I6" s="29">
         <v>1.7</v>
       </c>
       <c r="J6" s="1" t="s">
@@ -1937,7 +1910,7 @@
       <c r="H7" s="1">
         <v>500</v>
       </c>
-      <c r="I7" s="34">
+      <c r="I7" s="29">
         <v>1.7</v>
       </c>
       <c r="J7" s="1" t="s">
@@ -1979,7 +1952,7 @@
       <c r="H8" s="1">
         <v>700</v>
       </c>
-      <c r="I8" s="34">
+      <c r="I8" s="29">
         <v>1.7</v>
       </c>
       <c r="J8" s="1" t="s">
@@ -2021,7 +1994,7 @@
       <c r="H9" s="1">
         <v>700</v>
       </c>
-      <c r="I9" s="34">
+      <c r="I9" s="29">
         <v>1.7</v>
       </c>
       <c r="J9" s="1" t="s">
@@ -2063,7 +2036,7 @@
       <c r="H10" s="1">
         <v>700</v>
       </c>
-      <c r="I10" s="34">
+      <c r="I10" s="29">
         <v>1.7</v>
       </c>
       <c r="J10" s="1" t="s">
@@ -2105,7 +2078,7 @@
       <c r="H11" s="1">
         <v>100</v>
       </c>
-      <c r="I11" s="34">
+      <c r="I11" s="29">
         <v>1.7</v>
       </c>
       <c r="J11" s="1" t="s">
@@ -2146,7 +2119,7 @@
       <c r="H12" s="1">
         <v>100</v>
       </c>
-      <c r="I12" s="34">
+      <c r="I12" s="29">
         <v>1.7</v>
       </c>
       <c r="J12" s="1" t="s">
@@ -2172,10 +2145,10 @@
       <c r="C13" s="2">
         <v>120733340001420</v>
       </c>
-      <c r="D13" s="35">
+      <c r="D13" s="30">
         <v>9999996</v>
       </c>
-      <c r="E13" s="35">
+      <c r="E13" s="30">
         <v>1000421</v>
       </c>
       <c r="F13" s="1" t="s">
@@ -2187,7 +2160,7 @@
       <c r="H13" s="1">
         <v>700</v>
       </c>
-      <c r="I13" s="34">
+      <c r="I13" s="29">
         <v>1.7</v>
       </c>
       <c r="J13" s="1" t="s">
@@ -2213,10 +2186,10 @@
       <c r="C14" s="2">
         <v>120733340001420</v>
       </c>
-      <c r="D14" s="35">
+      <c r="D14" s="30">
         <v>9999996</v>
       </c>
-      <c r="E14" s="35">
+      <c r="E14" s="30">
         <v>1000421</v>
       </c>
       <c r="F14" s="1" t="s">
@@ -2228,7 +2201,7 @@
       <c r="H14" s="1">
         <v>700</v>
       </c>
-      <c r="I14" s="34">
+      <c r="I14" s="29">
         <v>1.7</v>
       </c>
       <c r="J14" s="1" t="s">
@@ -2254,10 +2227,10 @@
       <c r="C15" s="2">
         <v>100673000000011</v>
       </c>
-      <c r="D15" s="35">
+      <c r="D15" s="30">
         <v>9999996</v>
       </c>
-      <c r="E15" s="35">
+      <c r="E15" s="30">
         <v>1000421</v>
       </c>
       <c r="F15" s="1" t="s">
@@ -2269,7 +2242,7 @@
       <c r="H15" s="1">
         <v>700</v>
       </c>
-      <c r="I15" s="34">
+      <c r="I15" s="29">
         <v>1.7</v>
       </c>
       <c r="J15" s="1" t="s">
@@ -2287,7 +2260,7 @@
     </row>
     <row r="18" spans="8:9" x14ac:dyDescent="0.25">
       <c r="H18" s="19"/>
-      <c r="I18" s="36"/>
+      <c r="I18" s="31"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -18827,7 +18800,7 @@
       <c r="O4" s="7"/>
     </row>
     <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="33" t="s">
+      <c r="A5" s="28" t="s">
         <v>70</v>
       </c>
       <c r="B5" s="22">
@@ -18839,7 +18812,7 @@
       <c r="D5" s="22">
         <v>11</v>
       </c>
-      <c r="E5" s="28">
+      <c r="E5" s="27">
         <v>9996059</v>
       </c>
       <c r="F5" s="24">
@@ -18870,7 +18843,7 @@
         <v>79</v>
       </c>
       <c r="O5" s="22" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
@@ -18917,7 +18890,7 @@
         <v>79</v>
       </c>
       <c r="O6" s="7" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
@@ -19576,7 +19549,7 @@
         <v>1001</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="J21" s="7">
         <v>20</v>
@@ -19742,7 +19715,7 @@
         <v>130000</v>
       </c>
       <c r="K2" s="1">
-        <v>1190</v>
+        <v>2000</v>
       </c>
       <c r="L2" s="1">
         <v>5000</v>
@@ -19793,10 +19766,10 @@
         <v>900</v>
       </c>
       <c r="AB2" s="11">
-        <v>100</v>
+        <v>200</v>
       </c>
       <c r="AC2" s="7">
-        <v>7</v>
+        <v>8</v>
       </c>
     </row>
   </sheetData>
@@ -19858,7 +19831,7 @@
         <v>89</v>
       </c>
       <c r="M1" s="13" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="N1" s="13" t="s">
         <v>38</v>
@@ -19944,7 +19917,7 @@
         <v>10</v>
       </c>
       <c r="M2" s="7" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="N2" s="7">
         <v>46202558</v>
@@ -20115,7 +20088,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="21">
-        <v>32211</v>
+        <v>32011</v>
       </c>
       <c r="B2" s="21">
         <v>90</v>

--- a/Data/ENWR_Creation.xlsx
+++ b/Data/ENWR_Creation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57BB37B2-E85B-4CF5-A19F-AE57BCE9BFC2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08133F48-1E9C-4DD8-8B6E-49B5AE1B4FF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1716,13 +1716,13 @@
         <v>4555514</v>
       </c>
       <c r="C3" s="2">
-        <v>100673000000011</v>
-      </c>
-      <c r="D3" s="1">
-        <v>9997115</v>
-      </c>
-      <c r="E3" s="1">
-        <v>8211642</v>
+        <v>120733340001420</v>
+      </c>
+      <c r="D3" s="27">
+        <v>9999996</v>
+      </c>
+      <c r="E3" s="27">
+        <v>1000421</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>29</v>
@@ -1731,7 +1731,7 @@
         <v>15</v>
       </c>
       <c r="H3" s="1">
-        <v>750</v>
+        <v>700</v>
       </c>
       <c r="I3" s="26">
         <v>1.7</v>
@@ -20079,7 +20079,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="19">
-        <v>32031</v>
+        <v>32041</v>
       </c>
       <c r="B2" s="19">
         <v>90</v>

--- a/Data/ENWR_Creation.xlsx
+++ b/Data/ENWR_Creation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08133F48-1E9C-4DD8-8B6E-49B5AE1B4FF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40E044A2-8334-46BD-B2DF-26699EDCDB72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RP_Deposite_Request_Agriculture" sheetId="1" r:id="rId1"/>
@@ -408,6 +408,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
   <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -548,7 +551,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="33">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -587,6 +590,7 @@
     <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -974,7 +978,7 @@
         <v>16</v>
       </c>
       <c r="D3" s="23">
-        <v>15500001000761</v>
+        <v>155000010000761</v>
       </c>
       <c r="E3" s="27">
         <v>9996059</v>
@@ -1016,7 +1020,7 @@
         <v>16</v>
       </c>
       <c r="D4" s="23">
-        <v>178888880001601</v>
+        <v>155000010000761</v>
       </c>
       <c r="E4" s="27">
         <v>9996059</v>
@@ -1028,10 +1032,10 @@
         <v>14</v>
       </c>
       <c r="H4" s="27">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I4" s="27">
-        <v>500</v>
+        <v>5000</v>
       </c>
       <c r="J4" s="27">
         <v>1.7</v>
@@ -1058,7 +1062,7 @@
         <v>16</v>
       </c>
       <c r="D5" s="23">
-        <v>15500001000761</v>
+        <v>155000010000761</v>
       </c>
       <c r="E5" s="27">
         <v>9999996</v>
@@ -1478,7 +1482,7 @@
         <v>16</v>
       </c>
       <c r="D15" s="23">
-        <v>100673000000011</v>
+        <v>178888880001601</v>
       </c>
       <c r="E15" s="27">
         <v>9999996</v>
@@ -1689,7 +1693,7 @@
       <c r="H2" s="27">
         <v>700</v>
       </c>
-      <c r="I2" s="26">
+      <c r="I2" s="32">
         <v>1.7</v>
       </c>
       <c r="J2" s="27" t="s">
@@ -1733,7 +1737,7 @@
       <c r="H3" s="1">
         <v>700</v>
       </c>
-      <c r="I3" s="26">
+      <c r="I3" s="32">
         <v>1.7</v>
       </c>
       <c r="J3" s="1" t="s">
@@ -1757,14 +1761,14 @@
       <c r="B4" s="27">
         <v>4555516</v>
       </c>
-      <c r="C4" s="2">
+      <c r="C4" s="23">
         <v>100673000000011</v>
       </c>
-      <c r="D4" s="1">
-        <v>9997115</v>
-      </c>
-      <c r="E4" s="1">
-        <v>8211642</v>
+      <c r="D4" s="27">
+        <v>9999996</v>
+      </c>
+      <c r="E4" s="27">
+        <v>1000421</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>29</v>
@@ -1775,7 +1779,7 @@
       <c r="H4" s="1">
         <v>700</v>
       </c>
-      <c r="I4" s="26">
+      <c r="I4" s="32">
         <v>1.7</v>
       </c>
       <c r="J4" s="1" t="s">
@@ -1817,7 +1821,7 @@
       <c r="H5" s="1">
         <v>850</v>
       </c>
-      <c r="I5" s="26">
+      <c r="I5" s="32">
         <v>1.7</v>
       </c>
       <c r="J5" s="1" t="s">
@@ -1859,7 +1863,7 @@
       <c r="H6" s="1">
         <v>700</v>
       </c>
-      <c r="I6" s="26">
+      <c r="I6" s="32">
         <v>1.7</v>
       </c>
       <c r="J6" s="1" t="s">
@@ -1901,7 +1905,7 @@
       <c r="H7" s="1">
         <v>500</v>
       </c>
-      <c r="I7" s="26">
+      <c r="I7" s="32">
         <v>1.7</v>
       </c>
       <c r="J7" s="1" t="s">
@@ -1943,7 +1947,7 @@
       <c r="H8" s="1">
         <v>700</v>
       </c>
-      <c r="I8" s="26">
+      <c r="I8" s="32">
         <v>1.7</v>
       </c>
       <c r="J8" s="1" t="s">
@@ -1985,7 +1989,7 @@
       <c r="H9" s="1">
         <v>700</v>
       </c>
-      <c r="I9" s="26">
+      <c r="I9" s="32">
         <v>1.7</v>
       </c>
       <c r="J9" s="1" t="s">
@@ -2027,7 +2031,7 @@
       <c r="H10" s="1">
         <v>700</v>
       </c>
-      <c r="I10" s="26">
+      <c r="I10" s="32">
         <v>1.7</v>
       </c>
       <c r="J10" s="1" t="s">
@@ -2069,7 +2073,7 @@
       <c r="H11" s="1">
         <v>100</v>
       </c>
-      <c r="I11" s="26">
+      <c r="I11" s="32">
         <v>1.7</v>
       </c>
       <c r="J11" s="1" t="s">
@@ -2110,7 +2114,7 @@
       <c r="H12" s="1">
         <v>100</v>
       </c>
-      <c r="I12" s="26">
+      <c r="I12" s="32">
         <v>1.7</v>
       </c>
       <c r="J12" s="1" t="s">
@@ -2151,7 +2155,7 @@
       <c r="H13" s="1">
         <v>700</v>
       </c>
-      <c r="I13" s="26">
+      <c r="I13" s="32">
         <v>1.7</v>
       </c>
       <c r="J13" s="1" t="s">
@@ -2192,7 +2196,7 @@
       <c r="H14" s="1">
         <v>700</v>
       </c>
-      <c r="I14" s="26">
+      <c r="I14" s="32">
         <v>1.7</v>
       </c>
       <c r="J14" s="1" t="s">
@@ -2233,7 +2237,7 @@
       <c r="H15" s="1">
         <v>700</v>
       </c>
-      <c r="I15" s="26">
+      <c r="I15" s="32">
         <v>1.7</v>
       </c>
       <c r="J15" s="1" t="s">
@@ -19565,7 +19569,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F8B609F-0B76-470F-B64C-87241C540723}">
-  <dimension ref="A1:AC2"/>
+  <dimension ref="A1:AC12"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
@@ -19706,10 +19710,10 @@
         <v>130000</v>
       </c>
       <c r="K2" s="1">
-        <v>1190</v>
+        <v>2500</v>
       </c>
       <c r="L2" s="1">
-        <v>5000</v>
+        <v>4200</v>
       </c>
       <c r="M2" s="1">
         <v>6</v>
@@ -19754,13 +19758,29 @@
         <v>179</v>
       </c>
       <c r="AA2" s="1">
-        <v>900</v>
+        <v>10000</v>
       </c>
       <c r="AB2" s="11">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="AC2" s="7">
-        <v>7</v>
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="K9">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="K10">
+        <v>2500</v>
+      </c>
+    </row>
+    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="K12">
+        <f>K10/K9</f>
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -20079,7 +20099,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="19">
-        <v>32041</v>
+        <v>32051</v>
       </c>
       <c r="B2" s="19">
         <v>90</v>

--- a/Data/ENWR_Creation.xlsx
+++ b/Data/ENWR_Creation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40E044A2-8334-46BD-B2DF-26699EDCDB72}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C93D9EE4-305B-4AF7-912D-16B9DA7C7E99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RP_Deposite_Request_Agriculture" sheetId="1" r:id="rId1"/>
@@ -19569,7 +19569,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F8B609F-0B76-470F-B64C-87241C540723}">
-  <dimension ref="A1:AC12"/>
+  <dimension ref="A1:AC2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
@@ -19765,22 +19765,6 @@
       </c>
       <c r="AC2" s="7">
         <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="K9">
-        <v>5000</v>
-      </c>
-    </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="K10">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="K12">
-        <f>K10/K9</f>
-        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -20099,7 +20083,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="19">
-        <v>32051</v>
+        <v>32061</v>
       </c>
       <c r="B2" s="19">
         <v>90</v>

--- a/Data/ENWR_Creation.xlsx
+++ b/Data/ENWR_Creation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C93D9EE4-305B-4AF7-912D-16B9DA7C7E99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7516698-D8AC-49F8-BC21-7FF5EE8F6BAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RP_Deposite_Request_Agriculture" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="563" uniqueCount="120">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="121">
   <si>
     <t>commoditySegment</t>
   </si>
@@ -359,9 +359,6 @@
     <t xml:space="preserve">Complete </t>
   </si>
   <si>
-    <t>Abhi625032513</t>
-  </si>
-  <si>
     <t>Assayring_Referance</t>
   </si>
   <si>
@@ -402,6 +399,12 @@
   </si>
   <si>
     <t>ALUMINUM</t>
+  </si>
+  <si>
+    <t>Abhi625032514</t>
+  </si>
+  <si>
+    <t>l</t>
   </si>
 </sst>
 </file>
@@ -922,7 +925,7 @@
         <v>12</v>
       </c>
       <c r="N1" s="5" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
@@ -1659,7 +1662,7 @@
         <v>28</v>
       </c>
       <c r="N1" s="6" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="O1" s="4"/>
       <c r="P1" s="3"/>
@@ -1709,7 +1712,7 @@
         <v>11</v>
       </c>
       <c r="N2" s="30" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
@@ -2508,8 +2511,8 @@
       <c r="G5" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="H5" s="11">
-        <v>120733340001479</v>
+      <c r="H5" s="21">
+        <v>100673001212128</v>
       </c>
       <c r="I5" s="1">
         <v>9999996</v>
@@ -18610,6 +18613,7 @@
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="13.28515625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="18" customWidth="1"/>
+    <col min="10" max="10" width="15.85546875" customWidth="1"/>
     <col min="11" max="11" width="14.5703125" customWidth="1"/>
     <col min="12" max="12" width="17.7109375" customWidth="1"/>
   </cols>
@@ -18664,7 +18668,7 @@
         <v>70</v>
       </c>
       <c r="B2" s="7">
-        <v>5555551</v>
+        <v>1555551</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>29</v>
@@ -18672,11 +18676,11 @@
       <c r="D2" s="7">
         <v>11</v>
       </c>
-      <c r="E2" s="1">
-        <v>9997115</v>
-      </c>
-      <c r="F2" s="1">
-        <v>8211642</v>
+      <c r="E2" s="7">
+        <v>9999996</v>
+      </c>
+      <c r="F2" s="7">
+        <v>1000421</v>
       </c>
       <c r="G2" s="11">
         <v>100673000000011</v>
@@ -18838,7 +18842,7 @@
         <v>79</v>
       </c>
       <c r="O5" s="20" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
@@ -18885,7 +18889,7 @@
         <v>79</v>
       </c>
       <c r="O6" s="7" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
@@ -19544,7 +19548,7 @@
         <v>1001</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="J21" s="7">
         <v>20</v>
@@ -19569,7 +19573,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F8B609F-0B76-470F-B64C-87241C540723}">
-  <dimension ref="A1:AC2"/>
+  <dimension ref="A1:AC8"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
@@ -19675,7 +19679,7 @@
         <v>58</v>
       </c>
       <c r="AC1" s="5" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="2" spans="1:29" x14ac:dyDescent="0.25">
@@ -19704,16 +19708,16 @@
         <v>46202555</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>105</v>
+        <v>119</v>
       </c>
       <c r="J2" s="1">
         <v>130000</v>
       </c>
       <c r="K2" s="1">
-        <v>2500</v>
+        <v>50</v>
       </c>
       <c r="L2" s="1">
-        <v>4200</v>
+        <v>5000</v>
       </c>
       <c r="M2" s="1">
         <v>6</v>
@@ -19761,10 +19765,15 @@
         <v>10000</v>
       </c>
       <c r="AB2" s="11">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="AC2" s="7">
         <v>10</v>
+      </c>
+    </row>
+    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
+      <c r="J8" t="s">
+        <v>120</v>
       </c>
     </row>
   </sheetData>
@@ -19826,7 +19835,7 @@
         <v>89</v>
       </c>
       <c r="M1" s="13" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="N1" s="13" t="s">
         <v>38</v>
@@ -19906,19 +19915,19 @@
         <v>2</v>
       </c>
       <c r="K2" s="7">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="L2" s="7">
         <v>10</v>
       </c>
       <c r="M2" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="N2" s="7">
         <v>46202558</v>
       </c>
       <c r="O2" s="7">
-        <v>1</v>
+        <v>50</v>
       </c>
       <c r="P2" s="7">
         <v>1</v>
@@ -20063,22 +20072,22 @@
   <sheetData>
     <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" s="19" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="B1" s="19" t="s">
         <v>56</v>
       </c>
       <c r="C1" s="19" t="s">
+        <v>106</v>
+      </c>
+      <c r="D1" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="E1" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="F1" s="19" t="s">
         <v>109</v>
-      </c>
-      <c r="F1" s="19" t="s">
-        <v>110</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
@@ -20089,7 +20098,7 @@
         <v>90</v>
       </c>
       <c r="C2" s="19" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D2" s="19">
         <v>1345645</v>

--- a/Data/ENWR_Creation.xlsx
+++ b/Data/ENWR_Creation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A7516698-D8AC-49F8-BC21-7FF5EE8F6BAD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9806700A-EBCC-4071-9828-8441D33A7234}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="4" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RP_Deposite_Request_Agriculture" sheetId="1" r:id="rId1"/>
@@ -401,10 +401,10 @@
     <t>ALUMINUM</t>
   </si>
   <si>
-    <t>Abhi625032514</t>
+    <t>l</t>
   </si>
   <si>
-    <t>l</t>
+    <t>Abhishek1</t>
   </si>
 </sst>
 </file>
@@ -414,7 +414,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -474,6 +474,28 @@
     <font>
       <b/>
       <sz val="10"/>
+      <name val="Consolas"/>
+      <family val="3"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
       <name val="Consolas"/>
       <family val="3"/>
     </font>
@@ -554,7 +576,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -594,6 +616,12 @@
     <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="164" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2333,108 +2361,108 @@
       </c>
     </row>
     <row r="2" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" x14ac:dyDescent="0.25">
-      <c r="A2" s="20">
+      <c r="A2" s="29">
         <v>5555509</v>
       </c>
-      <c r="B2" s="20" t="s">
+      <c r="B2" s="29" t="s">
         <v>93</v>
       </c>
-      <c r="C2" s="20" t="s">
+      <c r="C2" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="20" t="s">
+      <c r="D2" s="29" t="s">
         <v>95</v>
       </c>
-      <c r="E2" s="20">
+      <c r="E2" s="29">
         <v>2025</v>
       </c>
-      <c r="F2" s="20" t="s">
+      <c r="F2" s="29" t="s">
         <v>98</v>
       </c>
-      <c r="G2" s="20" t="s">
+      <c r="G2" s="29" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="21">
+      <c r="H2" s="33">
         <v>100673001212128</v>
       </c>
-      <c r="I2" s="22">
+      <c r="I2" s="27">
         <v>9997115</v>
       </c>
-      <c r="J2" s="22">
+      <c r="J2" s="27">
         <v>8211642</v>
       </c>
-      <c r="K2" s="20">
+      <c r="K2" s="29">
         <v>100</v>
       </c>
-      <c r="L2" s="20">
+      <c r="L2" s="29">
         <v>6</v>
       </c>
-      <c r="M2" s="20">
+      <c r="M2" s="29">
         <v>0.5</v>
       </c>
-      <c r="N2" s="20" t="s">
+      <c r="N2" s="29" t="s">
         <v>102</v>
       </c>
-      <c r="O2" s="20" t="s">
+      <c r="O2" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="P2" s="20" t="s">
+      <c r="P2" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="Q2" s="20" t="s">
+      <c r="Q2" s="29" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" x14ac:dyDescent="0.25">
-      <c r="A3" s="20">
+      <c r="A3" s="29">
         <v>5555534</v>
       </c>
-      <c r="B3" s="20" t="s">
+      <c r="B3" s="29" t="s">
         <v>93</v>
       </c>
-      <c r="C3" s="20" t="s">
+      <c r="C3" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="20" t="s">
+      <c r="D3" s="29" t="s">
         <v>95</v>
       </c>
-      <c r="E3" s="20">
+      <c r="E3" s="29">
         <v>2025</v>
       </c>
-      <c r="F3" s="20" t="s">
+      <c r="F3" s="29" t="s">
         <v>98</v>
       </c>
-      <c r="G3" s="20" t="s">
+      <c r="G3" s="29" t="s">
         <v>100</v>
       </c>
-      <c r="H3" s="21">
+      <c r="H3" s="33">
         <v>100673001212128</v>
       </c>
-      <c r="I3" s="22">
+      <c r="I3" s="27">
         <v>9997115</v>
       </c>
-      <c r="J3" s="22">
+      <c r="J3" s="27">
         <v>8211642</v>
       </c>
-      <c r="K3" s="20">
+      <c r="K3" s="29">
         <v>100</v>
       </c>
-      <c r="L3" s="20">
+      <c r="L3" s="29">
         <v>6</v>
       </c>
-      <c r="M3" s="20">
+      <c r="M3" s="29">
         <v>0.5</v>
       </c>
-      <c r="N3" s="20" t="s">
+      <c r="N3" s="29" t="s">
         <v>102</v>
       </c>
-      <c r="O3" s="20" t="s">
+      <c r="O3" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="P3" s="20" t="s">
+      <c r="P3" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="Q3" s="20" t="s">
+      <c r="Q3" s="29" t="s">
         <v>104</v>
       </c>
     </row>
@@ -2511,7 +2539,7 @@
       <c r="G5" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="H5" s="21">
+      <c r="H5" s="33">
         <v>100673001212128</v>
       </c>
       <c r="I5" s="1">
@@ -2540,56 +2568,56 @@
       </c>
       <c r="Q5" s="19"/>
     </row>
-    <row r="6" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" x14ac:dyDescent="0.25">
-      <c r="A6" s="7">
+    <row r="6" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" s="38" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="34">
         <v>5555537</v>
       </c>
-      <c r="B6" s="7" t="s">
+      <c r="B6" s="34" t="s">
         <v>93</v>
       </c>
-      <c r="C6" s="7" t="s">
+      <c r="C6" s="34" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="7" t="s">
+      <c r="D6" s="34" t="s">
         <v>95</v>
       </c>
-      <c r="E6" s="7">
+      <c r="E6" s="34">
         <v>2025</v>
       </c>
-      <c r="F6" s="7" t="s">
+      <c r="F6" s="34" t="s">
         <v>98</v>
       </c>
-      <c r="G6" s="7" t="s">
+      <c r="G6" s="34" t="s">
         <v>100</v>
       </c>
-      <c r="H6" s="11">
-        <v>120733340001479</v>
-      </c>
-      <c r="I6" s="1">
+      <c r="H6" s="35">
+        <v>100673001212128</v>
+      </c>
+      <c r="I6" s="36">
         <v>9999996</v>
       </c>
-      <c r="J6" s="1">
+      <c r="J6" s="36">
         <v>1000421</v>
       </c>
-      <c r="K6" s="7">
-        <v>100</v>
-      </c>
-      <c r="L6" s="7">
+      <c r="K6" s="34">
+        <v>1150</v>
+      </c>
+      <c r="L6" s="34">
         <v>6</v>
       </c>
-      <c r="M6" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="N6" s="7" t="s">
+      <c r="M6" s="34">
+        <v>0.25</v>
+      </c>
+      <c r="N6" s="34" t="s">
         <v>102</v>
       </c>
-      <c r="O6" s="7" t="s">
+      <c r="O6" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="P6" s="7" t="s">
+      <c r="P6" s="34" t="s">
         <v>15</v>
       </c>
-      <c r="Q6" s="19"/>
+      <c r="Q6" s="37"/>
     </row>
     <row r="7" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" x14ac:dyDescent="0.25">
       <c r="A7" s="7">
@@ -2613,7 +2641,7 @@
       <c r="G7" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="H7" s="11">
+      <c r="H7" s="33">
         <v>120733340001479</v>
       </c>
       <c r="I7" s="1">
@@ -19702,19 +19730,19 @@
         <v>973015</v>
       </c>
       <c r="G2" s="1">
-        <v>46202560</v>
+        <v>46202561</v>
       </c>
       <c r="H2" s="1">
-        <v>46202555</v>
+        <v>46202551</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="J2" s="1">
-        <v>130000</v>
+        <v>130001</v>
       </c>
       <c r="K2" s="1">
-        <v>50</v>
+        <v>287.5</v>
       </c>
       <c r="L2" s="1">
         <v>5000</v>
@@ -19765,7 +19793,7 @@
         <v>10000</v>
       </c>
       <c r="AB2" s="11">
-        <v>100</v>
+        <v>1150</v>
       </c>
       <c r="AC2" s="7">
         <v>10</v>
@@ -19773,7 +19801,7 @@
     </row>
     <row r="8" spans="1:29" x14ac:dyDescent="0.25">
       <c r="J8" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>
@@ -19915,7 +19943,7 @@
         <v>2</v>
       </c>
       <c r="K2" s="7">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="L2" s="7">
         <v>10</v>
@@ -19927,7 +19955,7 @@
         <v>46202558</v>
       </c>
       <c r="O2" s="7">
-        <v>50</v>
+        <v>1</v>
       </c>
       <c r="P2" s="7">
         <v>1</v>

--- a/Data/ENWR_Creation.xlsx
+++ b/Data/ENWR_Creation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9806700A-EBCC-4071-9828-8441D33A7234}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3FD546E-3C1F-4800-B6B5-0E1D34AD528A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RP_Deposite_Request_Agriculture" sheetId="1" r:id="rId1"/>
@@ -18696,7 +18696,7 @@
         <v>70</v>
       </c>
       <c r="B2" s="7">
-        <v>1555551</v>
+        <v>1655551</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>29</v>
@@ -18729,7 +18729,7 @@
         <v>77</v>
       </c>
       <c r="M2" s="7">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="N2" s="7" t="s">
         <v>79</v>

--- a/Data/ENWR_Creation.xlsx
+++ b/Data/ENWR_Creation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3FD546E-3C1F-4800-B6B5-0E1D34AD528A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28885DB6-C291-48B6-A6BC-72433FBE116B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RP_Deposite_Request_Agriculture" sheetId="1" r:id="rId1"/>

--- a/Data/ENWR_Creation.xlsx
+++ b/Data/ENWR_Creation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28885DB6-C291-48B6-A6BC-72433FBE116B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7B321B4-3CAA-4D67-9C25-FD9FF4E5CC77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RP_Deposite_Request_Agriculture" sheetId="1" r:id="rId1"/>
@@ -961,7 +961,7 @@
         <v>13</v>
       </c>
       <c r="B2" s="27">
-        <v>5555613</v>
+        <v>5555624</v>
       </c>
       <c r="C2" s="27" t="s">
         <v>16</v>
@@ -979,13 +979,13 @@
         <v>14</v>
       </c>
       <c r="H2" s="27">
+        <v>15</v>
+      </c>
+      <c r="I2" s="27">
+        <v>100</v>
+      </c>
+      <c r="J2" s="27">
         <v>1</v>
-      </c>
-      <c r="I2" s="27">
-        <v>4000</v>
-      </c>
-      <c r="J2" s="27">
-        <v>1.7</v>
       </c>
       <c r="K2" s="29" t="s">
         <v>102</v>
@@ -19730,10 +19730,10 @@
         <v>973015</v>
       </c>
       <c r="G2" s="1">
-        <v>46202561</v>
+        <v>100001</v>
       </c>
       <c r="H2" s="1">
-        <v>46202551</v>
+        <v>1000011</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>120</v>
@@ -19742,7 +19742,7 @@
         <v>130001</v>
       </c>
       <c r="K2" s="1">
-        <v>287.5</v>
+        <v>100</v>
       </c>
       <c r="L2" s="1">
         <v>5000</v>
@@ -19793,7 +19793,7 @@
         <v>10000</v>
       </c>
       <c r="AB2" s="11">
-        <v>1150</v>
+        <v>100</v>
       </c>
       <c r="AC2" s="7">
         <v>10</v>

--- a/Data/ENWR_Creation.xlsx
+++ b/Data/ENWR_Creation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7B321B4-3CAA-4D67-9C25-FD9FF4E5CC77}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EA9BCAA-9C1B-4F42-9AD0-46A40DF4569E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RP_Deposite_Request_Agriculture" sheetId="1" r:id="rId1"/>
@@ -1790,7 +1790,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="27">
-        <v>4555516</v>
+        <v>4555517</v>
       </c>
       <c r="C4" s="23">
         <v>100673000000011</v>
@@ -19742,7 +19742,7 @@
         <v>130001</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>1190</v>
       </c>
       <c r="L2" s="1">
         <v>5000</v>
@@ -19796,7 +19796,7 @@
         <v>100</v>
       </c>
       <c r="AC2" s="7">
-        <v>10</v>
+        <v>7</v>
       </c>
     </row>
     <row r="8" spans="1:29" x14ac:dyDescent="0.25">

--- a/Data/ENWR_Creation.xlsx
+++ b/Data/ENWR_Creation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0EA9BCAA-9C1B-4F42-9AD0-46A40DF4569E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D27A8F4B-D1AF-42D0-B3D3-201261F4ACC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RP_Deposite_Request_Agriculture" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="123">
   <si>
     <t>commoditySegment</t>
   </si>
@@ -405,6 +405,12 @@
   </si>
   <si>
     <t>Abhishek1</t>
+  </si>
+  <si>
+    <t>Zinc 99</t>
+  </si>
+  <si>
+    <t>Ali 93</t>
   </si>
 </sst>
 </file>
@@ -18696,7 +18702,7 @@
         <v>70</v>
       </c>
       <c r="B2" s="7">
-        <v>1655551</v>
+        <v>1655552</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>29</v>
@@ -18705,13 +18711,13 @@
         <v>11</v>
       </c>
       <c r="E2" s="7">
-        <v>9999996</v>
+        <v>9997115</v>
       </c>
       <c r="F2" s="7">
-        <v>1000421</v>
+        <v>8211642</v>
       </c>
       <c r="G2" s="11">
-        <v>100673000000011</v>
+        <v>102905240000015</v>
       </c>
       <c r="H2" s="7">
         <v>1003</v>
@@ -19928,7 +19934,7 @@
         <v>60</v>
       </c>
       <c r="F2" s="7">
-        <v>12345</v>
+        <v>10</v>
       </c>
       <c r="G2" s="7">
         <v>4000</v>
@@ -20088,7 +20094,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAC201B6-DCEE-4C93-A919-B2D4018F90C6}">
-  <dimension ref="A1:F5"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
@@ -20120,7 +20126,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="19">
-        <v>32061</v>
+        <v>32162</v>
       </c>
       <c r="B2" s="19">
         <v>90</v>
@@ -20135,7 +20141,7 @@
         <v>345679</v>
       </c>
       <c r="F2" s="19">
-        <v>93</v>
+        <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.25">
@@ -20162,6 +20168,16 @@
       <c r="E5" s="19"/>
       <c r="F5" s="19"/>
     </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F10" t="s">
+        <v>121</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="F11" t="s">
+        <v>122</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Data/ENWR_Creation.xlsx
+++ b/Data/ENWR_Creation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D27A8F4B-D1AF-42D0-B3D3-201261F4ACC4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41B11800-1537-48CE-9F8B-1525D9685A85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RP_Deposite_Request_Agriculture" sheetId="1" r:id="rId1"/>
@@ -404,13 +404,13 @@
     <t>l</t>
   </si>
   <si>
-    <t>Abhishek1</t>
-  </si>
-  <si>
     <t>Zinc 99</t>
   </si>
   <si>
     <t>Ali 93</t>
+  </si>
+  <si>
+    <t>hdjh123</t>
   </si>
 </sst>
 </file>
@@ -967,28 +967,28 @@
         <v>13</v>
       </c>
       <c r="B2" s="27">
-        <v>5555624</v>
+        <v>5555626</v>
       </c>
       <c r="C2" s="27" t="s">
         <v>16</v>
       </c>
       <c r="D2" s="23">
-        <v>100673000000011</v>
+        <v>155000010000688</v>
       </c>
       <c r="E2" s="27">
-        <v>9999996</v>
+        <v>8843376</v>
       </c>
       <c r="F2" s="27">
-        <v>1000421</v>
+        <v>1002121</v>
       </c>
       <c r="G2" s="27" t="s">
         <v>14</v>
       </c>
       <c r="H2" s="27">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="I2" s="27">
-        <v>100</v>
+        <v>1000</v>
       </c>
       <c r="J2" s="27">
         <v>1</v>
@@ -2395,7 +2395,7 @@
         <v>9997115</v>
       </c>
       <c r="J2" s="27">
-        <v>8211642</v>
+        <v>9997115</v>
       </c>
       <c r="K2" s="29">
         <v>100</v>
@@ -2448,7 +2448,7 @@
         <v>9997115</v>
       </c>
       <c r="J3" s="27">
-        <v>8211642</v>
+        <v>9997115</v>
       </c>
       <c r="K3" s="29">
         <v>100</v>
@@ -2648,13 +2648,13 @@
         <v>100</v>
       </c>
       <c r="H7" s="33">
-        <v>120733340001479</v>
+        <v>102905240000015</v>
       </c>
       <c r="I7" s="1">
-        <v>9999996</v>
+        <v>9997115</v>
       </c>
       <c r="J7" s="1">
-        <v>1000421</v>
+        <v>8211642</v>
       </c>
       <c r="K7" s="7">
         <v>100</v>
@@ -2663,7 +2663,7 @@
         <v>6</v>
       </c>
       <c r="M7" s="7">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N7" s="7" t="s">
         <v>102</v>
@@ -2699,13 +2699,13 @@
         <v>100</v>
       </c>
       <c r="H8" s="11">
-        <v>120733340001479</v>
+        <v>102905240000015</v>
       </c>
       <c r="I8" s="1">
-        <v>9999996</v>
+        <v>9997115</v>
       </c>
       <c r="J8" s="1">
-        <v>1000421</v>
+        <v>8211642</v>
       </c>
       <c r="K8" s="7">
         <v>100</v>
@@ -2714,7 +2714,7 @@
         <v>6</v>
       </c>
       <c r="M8" s="7">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N8" s="7" t="s">
         <v>102</v>
@@ -2749,14 +2749,14 @@
       <c r="G9" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="H9" s="11">
-        <v>120733340001479</v>
+      <c r="H9" s="33">
+        <v>102905240000015</v>
       </c>
       <c r="I9" s="1">
-        <v>9999996</v>
+        <v>9997115</v>
       </c>
       <c r="J9" s="1">
-        <v>1000421</v>
+        <v>8211642</v>
       </c>
       <c r="K9" s="7">
         <v>100</v>
@@ -2765,7 +2765,7 @@
         <v>6</v>
       </c>
       <c r="M9" s="7">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N9" s="7" t="s">
         <v>102</v>
@@ -2801,13 +2801,13 @@
         <v>100</v>
       </c>
       <c r="H10" s="11">
-        <v>120733340001479</v>
+        <v>102905240000015</v>
       </c>
       <c r="I10" s="1">
-        <v>9999996</v>
+        <v>9997115</v>
       </c>
       <c r="J10" s="1">
-        <v>1000421</v>
+        <v>8211642</v>
       </c>
       <c r="K10" s="7">
         <v>100</v>
@@ -2816,7 +2816,7 @@
         <v>6</v>
       </c>
       <c r="M10" s="7">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N10" s="7" t="s">
         <v>102</v>
@@ -2851,8 +2851,8 @@
       <c r="G11" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="H11" s="11">
-        <v>100673001212128</v>
+      <c r="H11" s="33">
+        <v>102905240000015</v>
       </c>
       <c r="I11" s="1">
         <v>9997115</v>
@@ -2867,7 +2867,7 @@
         <v>6</v>
       </c>
       <c r="M11" s="7">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N11" s="7" t="s">
         <v>102</v>
@@ -2903,7 +2903,7 @@
         <v>100</v>
       </c>
       <c r="H12" s="11">
-        <v>100673001212128</v>
+        <v>102905240000015</v>
       </c>
       <c r="I12" s="1">
         <v>9997115</v>
@@ -2918,7 +2918,7 @@
         <v>6</v>
       </c>
       <c r="M12" s="7">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N12" s="7" t="s">
         <v>102</v>
@@ -2953,8 +2953,8 @@
       <c r="G13" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="H13" s="11">
-        <v>100673001212128</v>
+      <c r="H13" s="33">
+        <v>102905240000015</v>
       </c>
       <c r="I13" s="1">
         <v>9997115</v>
@@ -2969,7 +2969,7 @@
         <v>6</v>
       </c>
       <c r="M13" s="7">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N13" s="7" t="s">
         <v>102</v>
@@ -3005,7 +3005,7 @@
         <v>100</v>
       </c>
       <c r="H14" s="11">
-        <v>100673001212128</v>
+        <v>102905240000015</v>
       </c>
       <c r="I14" s="1">
         <v>9997115</v>
@@ -3020,7 +3020,7 @@
         <v>6</v>
       </c>
       <c r="M14" s="7">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N14" s="7" t="s">
         <v>102</v>
@@ -3055,8 +3055,8 @@
       <c r="G15" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="H15" s="11">
-        <v>100673001212128</v>
+      <c r="H15" s="33">
+        <v>102905240000015</v>
       </c>
       <c r="I15" s="1">
         <v>9997115</v>
@@ -3071,7 +3071,7 @@
         <v>6</v>
       </c>
       <c r="M15" s="7">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N15" s="7" t="s">
         <v>102</v>
@@ -6176,7 +6176,7 @@
         <v>100</v>
       </c>
       <c r="H16" s="11">
-        <v>100673001212128</v>
+        <v>102905240000015</v>
       </c>
       <c r="I16" s="1">
         <v>9997115</v>
@@ -6191,7 +6191,7 @@
         <v>6</v>
       </c>
       <c r="M16" s="7">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N16" s="7" t="s">
         <v>102</v>
@@ -9295,8 +9295,8 @@
       <c r="G17" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="H17" s="11">
-        <v>100673001212128</v>
+      <c r="H17" s="33">
+        <v>102905240000015</v>
       </c>
       <c r="I17" s="1">
         <v>9997115</v>
@@ -9311,7 +9311,7 @@
         <v>6</v>
       </c>
       <c r="M17" s="7">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N17" s="7" t="s">
         <v>102</v>
@@ -12416,7 +12416,7 @@
         <v>100</v>
       </c>
       <c r="H18" s="11">
-        <v>100673001212128</v>
+        <v>102905240000015</v>
       </c>
       <c r="I18" s="1">
         <v>9997115</v>
@@ -12431,7 +12431,7 @@
         <v>6</v>
       </c>
       <c r="M18" s="7">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N18" s="7" t="s">
         <v>102</v>
@@ -15539,7 +15539,7 @@
         <v>100673001212128</v>
       </c>
       <c r="I19" s="1">
-        <v>9999996</v>
+        <v>9997115</v>
       </c>
       <c r="J19" s="1">
         <v>8211642</v>
@@ -15548,10 +15548,10 @@
         <v>100</v>
       </c>
       <c r="L19" s="7">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="M19" s="7">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="N19" s="7" t="s">
         <v>102</v>
@@ -19742,13 +19742,13 @@
         <v>1000011</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="J2" s="1">
-        <v>130001</v>
+        <v>130009</v>
       </c>
       <c r="K2" s="1">
-        <v>1190</v>
+        <v>100</v>
       </c>
       <c r="L2" s="1">
         <v>5000</v>
@@ -19802,7 +19802,7 @@
         <v>100</v>
       </c>
       <c r="AC2" s="7">
-        <v>7</v>
+        <v>10</v>
       </c>
     </row>
     <row r="8" spans="1:29" x14ac:dyDescent="0.25">
@@ -20126,7 +20126,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="19">
-        <v>32162</v>
+        <v>32163</v>
       </c>
       <c r="B2" s="19">
         <v>90</v>
@@ -20170,12 +20170,12 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F10" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F11" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
   </sheetData>

--- a/Data/ENWR_Creation.xlsx
+++ b/Data/ENWR_Creation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{41B11800-1537-48CE-9F8B-1525D9685A85}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAF49A46-264E-4D75-98FD-0CED2F113DE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RP_Deposite_Request_Agriculture" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="566" uniqueCount="123">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="122">
   <si>
     <t>commoditySegment</t>
   </si>
@@ -399,9 +399,6 @@
   </si>
   <si>
     <t>ALUMINUM</t>
-  </si>
-  <si>
-    <t>l</t>
   </si>
   <si>
     <t>Zinc 99</t>
@@ -19607,7 +19604,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F8B609F-0B76-470F-B64C-87241C540723}">
-  <dimension ref="A1:AC8"/>
+  <dimension ref="A1:AC2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
@@ -19742,13 +19739,13 @@
         <v>1000011</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="J2" s="1">
         <v>130009</v>
       </c>
       <c r="K2" s="1">
-        <v>100</v>
+        <v>1190</v>
       </c>
       <c r="L2" s="1">
         <v>5000</v>
@@ -19802,12 +19799,7 @@
         <v>100</v>
       </c>
       <c r="AC2" s="7">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
-      <c r="J8" t="s">
-        <v>119</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -20126,7 +20118,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="19">
-        <v>32163</v>
+        <v>32164</v>
       </c>
       <c r="B2" s="19">
         <v>90</v>
@@ -20170,12 +20162,12 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F10" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F11" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
     </row>
   </sheetData>

--- a/Data/ENWR_Creation.xlsx
+++ b/Data/ENWR_Creation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DAF49A46-264E-4D75-98FD-0CED2F113DE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30E000FD-751B-4EB5-A2CD-1C464BD93585}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -22,6 +22,7 @@
     <sheet name="Deposite_Assayer_Maker" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -964,19 +965,19 @@
         <v>13</v>
       </c>
       <c r="B2" s="27">
-        <v>5555626</v>
+        <v>5555628</v>
       </c>
       <c r="C2" s="27" t="s">
         <v>16</v>
       </c>
       <c r="D2" s="23">
-        <v>155000010000688</v>
+        <v>100673000000011</v>
       </c>
       <c r="E2" s="27">
-        <v>8843376</v>
+        <v>9999996</v>
       </c>
       <c r="F2" s="27">
-        <v>1002121</v>
+        <v>1000421</v>
       </c>
       <c r="G2" s="27" t="s">
         <v>14</v>
@@ -985,10 +986,10 @@
         <v>1</v>
       </c>
       <c r="I2" s="27">
-        <v>1000</v>
+        <v>700</v>
       </c>
       <c r="J2" s="27">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="K2" s="29" t="s">
         <v>102</v>
@@ -1835,31 +1836,31 @@
         <v>13</v>
       </c>
       <c r="B5" s="27">
-        <v>4555518</v>
+        <v>4555519</v>
       </c>
       <c r="C5" s="2">
         <v>100673000000011</v>
       </c>
-      <c r="D5" s="1">
-        <v>9997115</v>
-      </c>
-      <c r="E5" s="1">
-        <v>8211642</v>
+      <c r="D5" s="27">
+        <v>9999996</v>
+      </c>
+      <c r="E5" s="27">
+        <v>1000421</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>29</v>
       </c>
       <c r="G5" s="1">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="H5" s="1">
-        <v>850</v>
+        <v>100</v>
       </c>
       <c r="I5" s="32">
         <v>1.7</v>
       </c>
-      <c r="J5" s="1" t="s">
-        <v>30</v>
+      <c r="J5" s="29" t="s">
+        <v>102</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>15</v>
@@ -19733,10 +19734,10 @@
         <v>973015</v>
       </c>
       <c r="G2" s="1">
-        <v>100001</v>
+        <v>100002</v>
       </c>
       <c r="H2" s="1">
-        <v>1000011</v>
+        <v>1000012</v>
       </c>
       <c r="I2" s="1" t="s">
         <v>121</v>
@@ -19745,7 +19746,7 @@
         <v>130009</v>
       </c>
       <c r="K2" s="1">
-        <v>1190</v>
+        <v>170</v>
       </c>
       <c r="L2" s="1">
         <v>5000</v>
@@ -20118,7 +20119,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="19">
-        <v>32164</v>
+        <v>32167</v>
       </c>
       <c r="B2" s="19">
         <v>90</v>

--- a/Data/ENWR_Creation.xlsx
+++ b/Data/ENWR_Creation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{30E000FD-751B-4EB5-A2CD-1C464BD93585}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F27ADA8-121B-49C6-9E85-167675EE14C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RP_Deposite_Request_Agriculture" sheetId="1" r:id="rId1"/>
@@ -22,7 +22,6 @@
     <sheet name="Deposite_Assayer_Maker" sheetId="7" r:id="rId7"/>
   </sheets>
   <calcPr calcId="191029"/>
-  <fileRecoveryPr repairLoad="1"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -43,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="121">
   <si>
     <t>commoditySegment</t>
   </si>
@@ -382,9 +381,6 @@
   </si>
   <si>
     <t>Status</t>
-  </si>
-  <si>
-    <t>Auto Rejected By CCRL</t>
   </si>
   <si>
     <t>Phy</t>
@@ -1708,15 +1704,15 @@
         <v>13</v>
       </c>
       <c r="B2" s="27">
-        <v>4555512</v>
-      </c>
-      <c r="C2" s="23">
-        <v>100673000000011</v>
-      </c>
-      <c r="D2" s="27">
+        <v>4555523</v>
+      </c>
+      <c r="C2" s="11">
+        <v>120733340001420</v>
+      </c>
+      <c r="D2" s="7">
         <v>9999996</v>
       </c>
-      <c r="E2" s="27">
+      <c r="E2" s="7">
         <v>1000421</v>
       </c>
       <c r="F2" s="27" t="s">
@@ -1726,7 +1722,7 @@
         <v>15</v>
       </c>
       <c r="H2" s="27">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="I2" s="32">
         <v>1.7</v>
@@ -1743,9 +1739,7 @@
       <c r="M2" s="27">
         <v>11</v>
       </c>
-      <c r="N2" s="30" t="s">
-        <v>113</v>
-      </c>
+      <c r="N2" s="30"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -2288,7 +2282,10 @@
         <v>11</v>
       </c>
     </row>
-    <row r="18" spans="8:9" x14ac:dyDescent="0.25">
+    <row r="18" spans="3:9" x14ac:dyDescent="0.25">
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="11"/>
       <c r="H18" s="17"/>
       <c r="I18" s="28"/>
     </row>
@@ -18700,7 +18697,7 @@
         <v>70</v>
       </c>
       <c r="B2" s="7">
-        <v>1655552</v>
+        <v>1655555</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>29</v>
@@ -18709,13 +18706,13 @@
         <v>11</v>
       </c>
       <c r="E2" s="7">
-        <v>9997115</v>
+        <v>9999996</v>
       </c>
       <c r="F2" s="7">
-        <v>8211642</v>
+        <v>1000421</v>
       </c>
       <c r="G2" s="11">
-        <v>102905240000015</v>
+        <v>120733340001420</v>
       </c>
       <c r="H2" s="7">
         <v>1003</v>
@@ -18724,7 +18721,7 @@
         <v>73</v>
       </c>
       <c r="J2" s="7">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="K2" s="7">
         <v>10</v>
@@ -18733,7 +18730,7 @@
         <v>77</v>
       </c>
       <c r="M2" s="7">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="N2" s="7" t="s">
         <v>79</v>
@@ -18874,7 +18871,7 @@
         <v>79</v>
       </c>
       <c r="O5" s="20" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
@@ -18921,7 +18918,7 @@
         <v>79</v>
       </c>
       <c r="O6" s="7" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
@@ -19580,7 +19577,7 @@
         <v>1001</v>
       </c>
       <c r="I21" s="7" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J21" s="7">
         <v>20</v>
@@ -19740,13 +19737,13 @@
         <v>1000012</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="J2" s="1">
         <v>130009</v>
       </c>
       <c r="K2" s="1">
-        <v>170</v>
+        <v>1530</v>
       </c>
       <c r="L2" s="1">
         <v>5000</v>
@@ -19800,7 +19797,7 @@
         <v>100</v>
       </c>
       <c r="AC2" s="7">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -19862,7 +19859,7 @@
         <v>89</v>
       </c>
       <c r="M1" s="13" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="N1" s="13" t="s">
         <v>38</v>
@@ -19927,7 +19924,7 @@
         <v>60</v>
       </c>
       <c r="F2" s="7">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="G2" s="7">
         <v>4000</v>
@@ -19948,7 +19945,7 @@
         <v>10</v>
       </c>
       <c r="M2" s="7" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="N2" s="7">
         <v>46202558</v>
@@ -20119,7 +20116,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="19">
-        <v>32167</v>
+        <v>32171</v>
       </c>
       <c r="B2" s="19">
         <v>90</v>
@@ -20163,12 +20160,12 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F10" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F11" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>

--- a/Data/ENWR_Creation.xlsx
+++ b/Data/ENWR_Creation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0F27ADA8-121B-49C6-9E85-167675EE14C8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D7D144B-C653-4AD3-8C42-C7F30F941252}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RP_Deposite_Request_Agriculture" sheetId="1" r:id="rId1"/>
@@ -1704,7 +1704,7 @@
         <v>13</v>
       </c>
       <c r="B2" s="27">
-        <v>4555523</v>
+        <v>4555524</v>
       </c>
       <c r="C2" s="11">
         <v>120733340001420</v>
@@ -20116,7 +20116,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="19">
-        <v>32171</v>
+        <v>32173</v>
       </c>
       <c r="B2" s="19">
         <v>90</v>

--- a/Data/ENWR_Creation.xlsx
+++ b/Data/ENWR_Creation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6D7D144B-C653-4AD3-8C42-C7F30F941252}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C985B8B0-46FC-41B2-AA26-F363C00349CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="121">
   <si>
     <t>commoditySegment</t>
   </si>
@@ -576,7 +576,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -622,6 +622,7 @@
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -961,13 +962,13 @@
         <v>13</v>
       </c>
       <c r="B2" s="27">
-        <v>5555628</v>
+        <v>5555629</v>
       </c>
       <c r="C2" s="27" t="s">
         <v>16</v>
       </c>
       <c r="D2" s="23">
-        <v>100673000000011</v>
+        <v>120733340001420</v>
       </c>
       <c r="E2" s="27">
         <v>9999996</v>
@@ -979,7 +980,7 @@
         <v>14</v>
       </c>
       <c r="H2" s="27">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I2" s="27">
         <v>700</v>
@@ -18697,7 +18698,7 @@
         <v>70</v>
       </c>
       <c r="B2" s="7">
-        <v>1655555</v>
+        <v>1655556</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>29</v>
@@ -19731,7 +19732,7 @@
         <v>973015</v>
       </c>
       <c r="G2" s="1">
-        <v>100002</v>
+        <v>100004</v>
       </c>
       <c r="H2" s="1">
         <v>1000012</v>
@@ -19743,7 +19744,7 @@
         <v>130009</v>
       </c>
       <c r="K2" s="1">
-        <v>1530</v>
+        <v>1190</v>
       </c>
       <c r="L2" s="1">
         <v>5000</v>
@@ -19797,7 +19798,7 @@
         <v>100</v>
       </c>
       <c r="AC2" s="7">
-        <v>9</v>
+        <v>7</v>
       </c>
     </row>
   </sheetData>
@@ -19807,7 +19808,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECF7E842-C9CD-4111-B0BA-C4A8FEE6BCD1}">
-  <dimension ref="A1:AB31"/>
+  <dimension ref="A1:AC31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -19821,7 +19822,7 @@
     <col min="21" max="21" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
         <v>31</v>
       </c>
@@ -19906,8 +19907,11 @@
       <c r="AB1" s="13" t="s">
         <v>57</v>
       </c>
+      <c r="AC1" s="5" t="s">
+        <v>111</v>
+      </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A2" s="7">
         <v>53409</v>
       </c>
@@ -19992,44 +19996,47 @@
       <c r="AB2" s="7">
         <v>200</v>
       </c>
+      <c r="AC2" s="39">
+        <v>5</v>
+      </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
       <c r="I4" s="14"/>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
       <c r="I5" s="9"/>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
       <c r="I6" s="9"/>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
       <c r="I7" s="9"/>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
       <c r="I8" s="9"/>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
       <c r="I9" s="9"/>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
       <c r="I10" s="9"/>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
       <c r="I11" s="9"/>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
       <c r="I12" s="9"/>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:29" x14ac:dyDescent="0.25">
       <c r="I13" s="9"/>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
       <c r="I14" s="8"/>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
       <c r="I15" s="8"/>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:29" x14ac:dyDescent="0.25">
       <c r="I16" s="8"/>
     </row>
     <row r="17" spans="9:9" x14ac:dyDescent="0.25">
@@ -20116,7 +20123,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="19">
-        <v>32173</v>
+        <v>32175</v>
       </c>
       <c r="B2" s="19">
         <v>90</v>

--- a/Data/ENWR_Creation.xlsx
+++ b/Data/ENWR_Creation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C985B8B0-46FC-41B2-AA26-F363C00349CC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35C141B8-FED8-4187-8EF0-AEC1BCA94CE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -962,7 +962,7 @@
         <v>13</v>
       </c>
       <c r="B2" s="27">
-        <v>5555629</v>
+        <v>5555630</v>
       </c>
       <c r="C2" s="27" t="s">
         <v>16</v>
@@ -980,7 +980,7 @@
         <v>14</v>
       </c>
       <c r="H2" s="27">
-        <v>15</v>
+        <v>111</v>
       </c>
       <c r="I2" s="27">
         <v>700</v>

--- a/Data/ENWR_Creation.xlsx
+++ b/Data/ENWR_Creation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{35C141B8-FED8-4187-8EF0-AEC1BCA94CE2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC1BB9AB-9900-48DC-A437-6BFF0EC8AB5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RP_Deposite_Request_Agriculture" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="565" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="133">
   <si>
     <t>commoditySegment</t>
   </si>
@@ -406,6 +406,42 @@
   <si>
     <t>hdjh123</t>
   </si>
+  <si>
+    <t>Grade</t>
+  </si>
+  <si>
+    <t>Qualification</t>
+  </si>
+  <si>
+    <t>Address1</t>
+  </si>
+  <si>
+    <t>Address2</t>
+  </si>
+  <si>
+    <t>Address3</t>
+  </si>
+  <si>
+    <t>Address4</t>
+  </si>
+  <si>
+    <t>Address5</t>
+  </si>
+  <si>
+    <t>Address6</t>
+  </si>
+  <si>
+    <t>Address7</t>
+  </si>
+  <si>
+    <t>Address8</t>
+  </si>
+  <si>
+    <t>Address9</t>
+  </si>
+  <si>
+    <t>Commodity</t>
+  </si>
 </sst>
 </file>
 
@@ -576,7 +612,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -623,6 +659,8 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -962,13 +1000,13 @@
         <v>13</v>
       </c>
       <c r="B2" s="27">
-        <v>5555630</v>
+        <v>5555631</v>
       </c>
       <c r="C2" s="27" t="s">
         <v>16</v>
       </c>
       <c r="D2" s="23">
-        <v>120733340001420</v>
+        <v>100673000000011</v>
       </c>
       <c r="E2" s="27">
         <v>9999996</v>
@@ -980,10 +1018,10 @@
         <v>14</v>
       </c>
       <c r="H2" s="27">
-        <v>111</v>
+        <v>6</v>
       </c>
       <c r="I2" s="27">
-        <v>700</v>
+        <v>100</v>
       </c>
       <c r="J2" s="27">
         <v>1.7</v>
@@ -1556,7 +1594,7 @@
         <v>16</v>
       </c>
       <c r="D16" s="23">
-        <v>100673001212128</v>
+        <v>120733340001420</v>
       </c>
       <c r="E16" s="27">
         <v>9999996</v>
@@ -2306,7 +2344,7 @@
     <col min="3" max="3" width="20.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="22.140625" customWidth="1"/>
     <col min="7" max="7" width="15.28515625" customWidth="1"/>
-    <col min="8" max="8" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="31.42578125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" x14ac:dyDescent="0.25">
@@ -6172,7 +6210,7 @@
         <v>100</v>
       </c>
       <c r="H16" s="11">
-        <v>102905240000015</v>
+        <v>100673001212128</v>
       </c>
       <c r="I16" s="1">
         <v>9997115</v>
@@ -9291,8 +9329,8 @@
       <c r="G17" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="H17" s="33">
-        <v>102905240000015</v>
+      <c r="H17" s="11">
+        <v>100673001212128</v>
       </c>
       <c r="I17" s="1">
         <v>9997115</v>
@@ -12412,7 +12450,7 @@
         <v>100</v>
       </c>
       <c r="H18" s="11">
-        <v>102905240000015</v>
+        <v>100673001212128</v>
       </c>
       <c r="I18" s="1">
         <v>9997115</v>
@@ -19732,7 +19770,7 @@
         <v>973015</v>
       </c>
       <c r="G2" s="1">
-        <v>100004</v>
+        <v>100005</v>
       </c>
       <c r="H2" s="1">
         <v>1000012</v>
@@ -19744,10 +19782,10 @@
         <v>130009</v>
       </c>
       <c r="K2" s="1">
-        <v>1190</v>
+        <v>170</v>
       </c>
       <c r="L2" s="1">
-        <v>5000</v>
+        <v>4200</v>
       </c>
       <c r="M2" s="1">
         <v>6</v>
@@ -20091,7 +20129,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAC201B6-DCEE-4C93-A919-B2D4018F90C6}">
-  <dimension ref="A1:F11"/>
+  <dimension ref="A1:XFD11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
@@ -20099,29 +20137,70 @@
     <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.42578125" customWidth="1"/>
+    <col min="8" max="8" width="12.42578125" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="13.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A1" s="19" t="s">
+    <row r="1" spans="1:19 16384:16384" x14ac:dyDescent="0.25">
+      <c r="A1" s="40" t="s">
         <v>105</v>
       </c>
-      <c r="B1" s="19" t="s">
+      <c r="B1" s="40" t="s">
         <v>56</v>
       </c>
-      <c r="C1" s="19" t="s">
+      <c r="C1" s="40" t="s">
         <v>106</v>
       </c>
-      <c r="D1" s="19" t="s">
+      <c r="D1" s="40" t="s">
         <v>107</v>
       </c>
-      <c r="E1" s="19" t="s">
+      <c r="E1" s="40" t="s">
         <v>108</v>
       </c>
-      <c r="F1" s="19" t="s">
+      <c r="F1" s="40" t="s">
         <v>109</v>
       </c>
+      <c r="G1" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="H1" s="41" t="s">
+        <v>122</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="J1" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="K1" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="L1" s="5" t="s">
+        <v>126</v>
+      </c>
+      <c r="M1" s="5" t="s">
+        <v>127</v>
+      </c>
+      <c r="N1" s="5" t="s">
+        <v>128</v>
+      </c>
+      <c r="O1" s="5" t="s">
+        <v>129</v>
+      </c>
+      <c r="P1" s="5" t="s">
+        <v>130</v>
+      </c>
+      <c r="Q1" s="5" t="s">
+        <v>131</v>
+      </c>
+      <c r="R1" s="40"/>
+      <c r="S1" s="40" t="s">
+        <v>132</v>
+      </c>
+      <c r="XFD1" s="3"/>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:19 16384:16384" x14ac:dyDescent="0.25">
       <c r="A2" s="19">
         <v>32175</v>
       </c>
@@ -20140,37 +20219,89 @@
       <c r="F2" s="19">
         <v>99</v>
       </c>
+      <c r="G2" s="19"/>
+      <c r="H2" s="19"/>
+      <c r="I2" s="19"/>
+      <c r="J2" s="19"/>
+      <c r="K2" s="19"/>
+      <c r="L2" s="19"/>
+      <c r="M2" s="19"/>
+      <c r="N2" s="19"/>
+      <c r="O2" s="19"/>
+      <c r="P2" s="19"/>
+      <c r="Q2" s="19"/>
+      <c r="R2" s="19"/>
+      <c r="S2" s="19"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:19 16384:16384" x14ac:dyDescent="0.25">
       <c r="A3" s="19"/>
       <c r="B3" s="19"/>
       <c r="C3" s="19"/>
       <c r="D3" s="19"/>
       <c r="E3" s="19"/>
       <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="19"/>
+      <c r="K3" s="19"/>
+      <c r="L3" s="19"/>
+      <c r="M3" s="19"/>
+      <c r="N3" s="19"/>
+      <c r="O3" s="19"/>
+      <c r="P3" s="19"/>
+      <c r="Q3" s="19"/>
+      <c r="R3" s="19"/>
+      <c r="S3" s="19"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:19 16384:16384" x14ac:dyDescent="0.25">
       <c r="A4" s="19"/>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
       <c r="D4" s="19"/>
       <c r="E4" s="19"/>
       <c r="F4" s="19"/>
+      <c r="G4" s="19"/>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+      <c r="J4" s="19"/>
+      <c r="K4" s="19"/>
+      <c r="L4" s="19"/>
+      <c r="M4" s="19"/>
+      <c r="N4" s="19"/>
+      <c r="O4" s="19"/>
+      <c r="P4" s="19"/>
+      <c r="Q4" s="19"/>
+      <c r="R4" s="19"/>
+      <c r="S4" s="19"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:19 16384:16384" x14ac:dyDescent="0.25">
       <c r="A5" s="19"/>
       <c r="B5" s="19"/>
       <c r="C5" s="19"/>
       <c r="D5" s="19"/>
       <c r="E5" s="19"/>
       <c r="F5" s="19"/>
+      <c r="G5" s="19"/>
+      <c r="H5" s="19"/>
+      <c r="I5" s="19"/>
+      <c r="J5" s="19"/>
+      <c r="K5" s="19"/>
+      <c r="L5" s="19"/>
+      <c r="M5" s="19"/>
+      <c r="N5" s="19"/>
+      <c r="O5" s="19"/>
+      <c r="P5" s="19"/>
+      <c r="Q5" s="19"/>
+      <c r="R5" s="19"/>
+      <c r="S5" s="19"/>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:19 16384:16384" x14ac:dyDescent="0.25">
       <c r="F10" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:19 16384:16384" x14ac:dyDescent="0.25">
       <c r="F11" t="s">
         <v>119</v>
       </c>

--- a/Data/ENWR_Creation.xlsx
+++ b/Data/ENWR_Creation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC1BB9AB-9900-48DC-A437-6BFF0EC8AB5D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AC29B0B-68CA-4BAA-B8F4-1B8F87EB9254}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -612,7 +612,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="41">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -660,7 +660,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -18736,7 +18735,7 @@
         <v>70</v>
       </c>
       <c r="B2" s="7">
-        <v>1655556</v>
+        <v>1655557</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>29</v>
@@ -20164,7 +20163,7 @@
       <c r="G1" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="H1" s="41" t="s">
+      <c r="H1" s="40" t="s">
         <v>122</v>
       </c>
       <c r="I1" s="5" t="s">
@@ -20202,7 +20201,7 @@
     </row>
     <row r="2" spans="1:19 16384:16384" x14ac:dyDescent="0.25">
       <c r="A2" s="19">
-        <v>32175</v>
+        <v>32176</v>
       </c>
       <c r="B2" s="19">
         <v>90</v>

--- a/Data/ENWR_Creation.xlsx
+++ b/Data/ENWR_Creation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1AC29B0B-68CA-4BAA-B8F4-1B8F87EB9254}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C40AAB93-DA18-4FD7-B8BB-B671C7AE9EEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -999,7 +999,7 @@
         <v>13</v>
       </c>
       <c r="B2" s="27">
-        <v>5555631</v>
+        <v>5555632</v>
       </c>
       <c r="C2" s="27" t="s">
         <v>16</v>
@@ -20201,7 +20201,7 @@
     </row>
     <row r="2" spans="1:19 16384:16384" x14ac:dyDescent="0.25">
       <c r="A2" s="19">
-        <v>32176</v>
+        <v>32177</v>
       </c>
       <c r="B2" s="19">
         <v>90</v>

--- a/Data/ENWR_Creation.xlsx
+++ b/Data/ENWR_Creation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C40AAB93-DA18-4FD7-B8BB-B671C7AE9EEB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26AD0787-9B0C-42AE-BE16-AC891F4147C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18735,7 +18735,7 @@
         <v>70</v>
       </c>
       <c r="B2" s="7">
-        <v>1655557</v>
+        <v>1655559</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>29</v>
@@ -18759,7 +18759,7 @@
         <v>73</v>
       </c>
       <c r="J2" s="7">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="K2" s="7">
         <v>10</v>
@@ -18768,7 +18768,7 @@
         <v>77</v>
       </c>
       <c r="M2" s="7">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="N2" s="7" t="s">
         <v>79</v>
@@ -19965,7 +19965,7 @@
         <v>60</v>
       </c>
       <c r="F2" s="7">
-        <v>5</v>
+        <v>45</v>
       </c>
       <c r="G2" s="7">
         <v>4000</v>
@@ -19980,7 +19980,7 @@
         <v>2</v>
       </c>
       <c r="K2" s="7">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L2" s="7">
         <v>10</v>
@@ -19992,7 +19992,7 @@
         <v>46202558</v>
       </c>
       <c r="O2" s="7">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P2" s="7">
         <v>1</v>
@@ -20034,7 +20034,7 @@
         <v>200</v>
       </c>
       <c r="AC2" s="39">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.25">
@@ -20201,7 +20201,7 @@
     </row>
     <row r="2" spans="1:19 16384:16384" x14ac:dyDescent="0.25">
       <c r="A2" s="19">
-        <v>32177</v>
+        <v>32180</v>
       </c>
       <c r="B2" s="19">
         <v>90</v>

--- a/Data/ENWR_Creation.xlsx
+++ b/Data/ENWR_Creation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{26AD0787-9B0C-42AE-BE16-AC891F4147C2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B013AE8-87B3-4002-A157-8DEA1B675A3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RP_Deposite_Request_Agriculture" sheetId="1" r:id="rId1"/>
@@ -404,9 +404,6 @@
     <t>Ali 93</t>
   </si>
   <si>
-    <t>hdjh123</t>
-  </si>
-  <si>
     <t>Grade</t>
   </si>
   <si>
@@ -441,6 +438,9 @@
   </si>
   <si>
     <t>Commodity</t>
+  </si>
+  <si>
+    <t>Rudhra121</t>
   </si>
 </sst>
 </file>
@@ -999,13 +999,13 @@
         <v>13</v>
       </c>
       <c r="B2" s="27">
-        <v>5555632</v>
+        <v>5555636</v>
       </c>
       <c r="C2" s="27" t="s">
         <v>16</v>
       </c>
       <c r="D2" s="23">
-        <v>100673000000011</v>
+        <v>120733340001420</v>
       </c>
       <c r="E2" s="27">
         <v>9999996</v>
@@ -1017,7 +1017,7 @@
         <v>14</v>
       </c>
       <c r="H2" s="27">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="I2" s="27">
         <v>100</v>
@@ -2401,7 +2401,7 @@
     </row>
     <row r="2" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" x14ac:dyDescent="0.25">
       <c r="A2" s="29">
-        <v>5555509</v>
+        <v>5555510</v>
       </c>
       <c r="B2" s="29" t="s">
         <v>93</v>
@@ -6188,7 +6188,7 @@
     </row>
     <row r="16" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A16" s="7">
-        <v>5555547</v>
+        <v>5555548</v>
       </c>
       <c r="B16" s="7" t="s">
         <v>93</v>
@@ -9308,7 +9308,7 @@
     </row>
     <row r="17" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" s="15" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A17" s="7">
-        <v>5555548</v>
+        <v>5555550</v>
       </c>
       <c r="B17" s="7" t="s">
         <v>93</v>
@@ -9344,7 +9344,7 @@
         <v>6</v>
       </c>
       <c r="M17" s="7">
-        <v>1</v>
+        <v>1.7</v>
       </c>
       <c r="N17" s="7" t="s">
         <v>102</v>
@@ -19769,13 +19769,13 @@
         <v>973015</v>
       </c>
       <c r="G2" s="1">
-        <v>100005</v>
+        <v>100007</v>
       </c>
       <c r="H2" s="1">
         <v>1000012</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>120</v>
+        <v>132</v>
       </c>
       <c r="J2" s="1">
         <v>130009</v>
@@ -20161,41 +20161,41 @@
         <v>109</v>
       </c>
       <c r="G1" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="H1" s="40" t="s">
         <v>121</v>
       </c>
-      <c r="H1" s="40" t="s">
+      <c r="I1" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="J1" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="K1" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="M1" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="N1" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="O1" s="5" t="s">
         <v>128</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="P1" s="5" t="s">
         <v>129</v>
       </c>
-      <c r="P1" s="5" t="s">
+      <c r="Q1" s="5" t="s">
         <v>130</v>
-      </c>
-      <c r="Q1" s="5" t="s">
-        <v>131</v>
       </c>
       <c r="R1" s="40"/>
       <c r="S1" s="40" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="XFD1" s="3"/>
     </row>

--- a/Data/ENWR_Creation.xlsx
+++ b/Data/ENWR_Creation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B013AE8-87B3-4002-A157-8DEA1B675A3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6040219A-5EC9-4834-9A86-446537ABCB8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RP_Deposite_Request_Agriculture" sheetId="1" r:id="rId1"/>

--- a/Data/ENWR_Creation.xlsx
+++ b/Data/ENWR_Creation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6040219A-5EC9-4834-9A86-446537ABCB8B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5118AB4-2509-4360-B672-2619C5D177F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="1" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RP_Deposite_Request_Agriculture" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="577" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="130">
   <si>
     <t>commoditySegment</t>
   </si>
@@ -383,19 +383,10 @@
     <t>Status</t>
   </si>
   <si>
-    <t>Phy</t>
-  </si>
-  <si>
-    <t>phy</t>
-  </si>
-  <si>
     <t>place_of_origin</t>
   </si>
   <si>
     <t>ass</t>
-  </si>
-  <si>
-    <t>ALUMINUM</t>
   </si>
   <si>
     <t>Zinc 99</t>
@@ -536,7 +527,7 @@
       <family val="3"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -552,18 +543,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -612,7 +591,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="41">
+  <cellXfs count="38">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -639,27 +618,24 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -995,676 +971,364 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="27">
-        <v>5555636</v>
-      </c>
-      <c r="C2" s="27" t="s">
+      <c r="B2" s="22">
+        <v>5555638</v>
+      </c>
+      <c r="C2" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="23">
-        <v>120733340001420</v>
-      </c>
-      <c r="E2" s="27">
+      <c r="D2" s="20">
+        <v>100673000000011</v>
+      </c>
+      <c r="E2" s="22">
         <v>9999996</v>
       </c>
-      <c r="F2" s="27">
+      <c r="F2" s="22">
         <v>1000421</v>
       </c>
-      <c r="G2" s="27" t="s">
+      <c r="G2" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="27">
-        <v>13</v>
-      </c>
-      <c r="I2" s="27">
-        <v>100</v>
-      </c>
-      <c r="J2" s="27">
+      <c r="H2" s="22">
+        <v>1</v>
+      </c>
+      <c r="I2" s="22">
+        <v>900</v>
+      </c>
+      <c r="J2" s="22">
         <v>1.7</v>
       </c>
-      <c r="K2" s="29" t="s">
+      <c r="K2" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="L2" s="27" t="s">
+      <c r="L2" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="M2" s="27" t="s">
+      <c r="M2" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="N2" s="27"/>
+      <c r="N2" s="22"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="27">
+      <c r="B3" s="22">
         <v>5555614</v>
       </c>
-      <c r="C3" s="27" t="s">
+      <c r="C3" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="23">
+      <c r="D3" s="20">
         <v>155000010000761</v>
       </c>
-      <c r="E3" s="27">
+      <c r="E3" s="22">
         <v>9996059</v>
       </c>
-      <c r="F3" s="27">
+      <c r="F3" s="22">
         <v>5750013</v>
       </c>
-      <c r="G3" s="27" t="s">
+      <c r="G3" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="27">
+      <c r="H3" s="22">
         <v>6</v>
       </c>
-      <c r="I3" s="27">
+      <c r="I3" s="22">
         <v>5000</v>
       </c>
-      <c r="J3" s="27">
+      <c r="J3" s="22">
         <v>0.5</v>
       </c>
-      <c r="K3" s="29" t="s">
+      <c r="K3" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="L3" s="27" t="s">
+      <c r="L3" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="M3" s="27" t="s">
+      <c r="M3" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="N3" s="27"/>
+      <c r="N3" s="22"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="27" t="s">
+      <c r="A4" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="27">
+      <c r="B4" s="22">
         <v>5555615</v>
       </c>
-      <c r="C4" s="27" t="s">
+      <c r="C4" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="23">
-        <v>155000010000761</v>
-      </c>
-      <c r="E4" s="27">
-        <v>9996059</v>
-      </c>
-      <c r="F4" s="27">
-        <v>5750013</v>
-      </c>
-      <c r="G4" s="27" t="s">
+      <c r="D4" s="20">
+        <v>100673000000011</v>
+      </c>
+      <c r="E4" s="22">
+        <v>9999996</v>
+      </c>
+      <c r="F4" s="22">
+        <v>1000421</v>
+      </c>
+      <c r="G4" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="27">
+      <c r="H4" s="22">
         <v>6</v>
       </c>
-      <c r="I4" s="27">
+      <c r="I4" s="22">
         <v>5000</v>
       </c>
-      <c r="J4" s="27">
+      <c r="J4" s="22">
         <v>1.7</v>
       </c>
-      <c r="K4" s="29" t="s">
+      <c r="K4" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="L4" s="27" t="s">
+      <c r="L4" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="M4" s="27" t="s">
+      <c r="M4" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="N4" s="27"/>
+      <c r="N4" s="22"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="27" t="s">
+      <c r="A5" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="27">
+      <c r="B5" s="22">
         <v>5555616</v>
       </c>
-      <c r="C5" s="27" t="s">
+      <c r="C5" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="23">
-        <v>155000010000761</v>
-      </c>
-      <c r="E5" s="27">
+      <c r="D5" s="20">
+        <v>100673001212128</v>
+      </c>
+      <c r="E5" s="22">
         <v>9999996</v>
       </c>
-      <c r="F5" s="27">
+      <c r="F5" s="22">
         <v>1000421</v>
       </c>
-      <c r="G5" s="27" t="s">
+      <c r="G5" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="27">
+      <c r="H5" s="22">
         <v>1</v>
       </c>
-      <c r="I5" s="27">
+      <c r="I5" s="22">
         <v>500</v>
       </c>
-      <c r="J5" s="27">
+      <c r="J5" s="22">
         <v>1.7</v>
       </c>
-      <c r="K5" s="29" t="s">
+      <c r="K5" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="L5" s="27" t="s">
+      <c r="L5" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="M5" s="27" t="s">
+      <c r="M5" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="N5" s="27"/>
+      <c r="N5" s="22"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="27">
-        <v>5555617</v>
-      </c>
-      <c r="C6" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="23">
-        <v>100673000000011</v>
-      </c>
-      <c r="E6" s="27">
-        <v>9999996</v>
-      </c>
-      <c r="F6" s="27">
-        <v>1000421</v>
-      </c>
-      <c r="G6" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" s="27">
-        <v>1</v>
-      </c>
-      <c r="I6" s="27">
-        <v>700</v>
-      </c>
-      <c r="J6" s="27">
-        <v>1.7</v>
-      </c>
-      <c r="K6" s="29" t="s">
-        <v>102</v>
-      </c>
-      <c r="L6" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="M6" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="N6" s="27"/>
+      <c r="A6" s="22"/>
+      <c r="B6" s="22"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="22"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="22"/>
+      <c r="J6" s="22"/>
+      <c r="K6" s="24"/>
+      <c r="L6" s="22"/>
+      <c r="M6" s="22"/>
+      <c r="N6" s="22"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="27">
-        <v>5555618</v>
-      </c>
-      <c r="C7" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="23">
-        <v>100673000000011</v>
-      </c>
-      <c r="E7" s="27">
-        <v>9999996</v>
-      </c>
-      <c r="F7" s="27">
-        <v>1000421</v>
-      </c>
-      <c r="G7" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="H7" s="27">
-        <v>1</v>
-      </c>
-      <c r="I7" s="27">
-        <v>500</v>
-      </c>
-      <c r="J7" s="27">
-        <v>1.7</v>
-      </c>
-      <c r="K7" s="29" t="s">
-        <v>102</v>
-      </c>
-      <c r="L7" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="M7" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="N7" s="30"/>
+      <c r="A7" s="22"/>
+      <c r="B7" s="22"/>
+      <c r="C7" s="22"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="22"/>
+      <c r="H7" s="22"/>
+      <c r="I7" s="22"/>
+      <c r="J7" s="22"/>
+      <c r="K7" s="24"/>
+      <c r="L7" s="22"/>
+      <c r="M7" s="22"/>
+      <c r="N7" s="25"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="27">
-        <v>5555619</v>
-      </c>
-      <c r="C8" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="23">
-        <v>100673000000011</v>
-      </c>
-      <c r="E8" s="27">
-        <v>9999996</v>
-      </c>
-      <c r="F8" s="27">
-        <v>1000421</v>
-      </c>
-      <c r="G8" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="H8" s="27">
-        <v>1</v>
-      </c>
-      <c r="I8" s="27">
-        <v>700</v>
-      </c>
-      <c r="J8" s="27">
-        <v>1.7</v>
-      </c>
-      <c r="K8" s="29" t="s">
-        <v>102</v>
-      </c>
-      <c r="L8" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="M8" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="N8" s="30"/>
+      <c r="A8" s="22"/>
+      <c r="B8" s="22"/>
+      <c r="C8" s="22"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="22"/>
+      <c r="G8" s="22"/>
+      <c r="H8" s="22"/>
+      <c r="I8" s="22"/>
+      <c r="J8" s="22"/>
+      <c r="K8" s="24"/>
+      <c r="L8" s="22"/>
+      <c r="M8" s="22"/>
+      <c r="N8" s="25"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="27">
-        <v>5555620</v>
-      </c>
-      <c r="C9" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" s="23">
-        <v>100673000000011</v>
-      </c>
-      <c r="E9" s="27">
-        <v>9999996</v>
-      </c>
-      <c r="F9" s="27">
-        <v>1000421</v>
-      </c>
-      <c r="G9" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="H9" s="27">
-        <v>1</v>
-      </c>
-      <c r="I9" s="27">
-        <v>500</v>
-      </c>
-      <c r="J9" s="27">
-        <v>1.7</v>
-      </c>
-      <c r="K9" s="29" t="s">
-        <v>102</v>
-      </c>
-      <c r="L9" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="M9" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="N9" s="30"/>
+      <c r="A9" s="22"/>
+      <c r="B9" s="22"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="22"/>
+      <c r="G9" s="22"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="22"/>
+      <c r="J9" s="22"/>
+      <c r="K9" s="24"/>
+      <c r="L9" s="22"/>
+      <c r="M9" s="22"/>
+      <c r="N9" s="25"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="27">
-        <v>5555621</v>
-      </c>
-      <c r="C10" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" s="23">
-        <v>100673000000011</v>
-      </c>
-      <c r="E10" s="27">
-        <v>9999996</v>
-      </c>
-      <c r="F10" s="27">
-        <v>1000421</v>
-      </c>
-      <c r="G10" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="H10" s="27">
-        <v>15</v>
-      </c>
-      <c r="I10" s="27">
-        <v>700</v>
-      </c>
-      <c r="J10" s="27">
-        <v>1.7</v>
-      </c>
-      <c r="K10" s="29" t="s">
-        <v>58</v>
-      </c>
-      <c r="L10" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="M10" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="N10" s="30"/>
+      <c r="A10" s="22"/>
+      <c r="B10" s="22"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="22"/>
+      <c r="G10" s="22"/>
+      <c r="H10" s="22"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="22"/>
+      <c r="K10" s="24"/>
+      <c r="L10" s="22"/>
+      <c r="M10" s="22"/>
+      <c r="N10" s="25"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="27">
-        <v>5555622</v>
-      </c>
-      <c r="C11" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" s="23">
-        <v>100673000000011</v>
-      </c>
-      <c r="E11" s="27">
-        <v>9999996</v>
-      </c>
-      <c r="F11" s="27">
-        <v>1000421</v>
-      </c>
-      <c r="G11" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="H11" s="27">
-        <v>1</v>
-      </c>
-      <c r="I11" s="27">
-        <v>500</v>
-      </c>
-      <c r="J11" s="27">
-        <v>1.7</v>
-      </c>
-      <c r="K11" s="29" t="s">
-        <v>102</v>
-      </c>
-      <c r="L11" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="M11" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="N11" s="30"/>
+      <c r="A11" s="22"/>
+      <c r="B11" s="22"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="22"/>
+      <c r="F11" s="22"/>
+      <c r="G11" s="22"/>
+      <c r="H11" s="22"/>
+      <c r="I11" s="22"/>
+      <c r="J11" s="22"/>
+      <c r="K11" s="24"/>
+      <c r="L11" s="22"/>
+      <c r="M11" s="22"/>
+      <c r="N11" s="25"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="27">
-        <v>5555623</v>
-      </c>
-      <c r="C12" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="D12" s="23">
-        <v>100673000000011</v>
-      </c>
-      <c r="E12" s="27">
-        <v>9999996</v>
-      </c>
-      <c r="F12" s="27">
-        <v>1000421</v>
-      </c>
-      <c r="G12" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="H12" s="27">
-        <v>1</v>
-      </c>
-      <c r="I12" s="27">
-        <v>700</v>
-      </c>
-      <c r="J12" s="27">
-        <v>1.7</v>
-      </c>
-      <c r="K12" s="29" t="s">
-        <v>102</v>
-      </c>
-      <c r="L12" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="M12" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="N12" s="30"/>
+      <c r="A12" s="22"/>
+      <c r="B12" s="22"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="22"/>
+      <c r="G12" s="22"/>
+      <c r="H12" s="22"/>
+      <c r="I12" s="22"/>
+      <c r="J12" s="22"/>
+      <c r="K12" s="24"/>
+      <c r="L12" s="22"/>
+      <c r="M12" s="22"/>
+      <c r="N12" s="25"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" s="27">
-        <v>5555624</v>
-      </c>
-      <c r="C13" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="D13" s="23">
-        <v>100673000000011</v>
-      </c>
-      <c r="E13" s="27">
-        <v>9999996</v>
-      </c>
-      <c r="F13" s="27">
-        <v>1000421</v>
-      </c>
-      <c r="G13" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="H13" s="27">
-        <v>1</v>
-      </c>
-      <c r="I13" s="27">
-        <v>100</v>
-      </c>
-      <c r="J13" s="27">
-        <v>1.7</v>
-      </c>
-      <c r="K13" s="29" t="s">
-        <v>102</v>
-      </c>
-      <c r="L13" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="M13" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="N13" s="30"/>
+      <c r="A13" s="22"/>
+      <c r="B13" s="22"/>
+      <c r="C13" s="22"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="22"/>
+      <c r="F13" s="22"/>
+      <c r="G13" s="22"/>
+      <c r="H13" s="22"/>
+      <c r="I13" s="22"/>
+      <c r="J13" s="22"/>
+      <c r="K13" s="24"/>
+      <c r="L13" s="22"/>
+      <c r="M13" s="22"/>
+      <c r="N13" s="25"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" s="27">
-        <v>5555625</v>
-      </c>
-      <c r="C14" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="D14" s="23">
-        <v>100673000000011</v>
-      </c>
-      <c r="E14" s="27">
-        <v>9999996</v>
-      </c>
-      <c r="F14" s="27">
-        <v>1000421</v>
-      </c>
-      <c r="G14" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="H14" s="27">
-        <v>1</v>
-      </c>
-      <c r="I14" s="27">
-        <v>700</v>
-      </c>
-      <c r="J14" s="27">
-        <v>1.7</v>
-      </c>
-      <c r="K14" s="29" t="s">
-        <v>102</v>
-      </c>
-      <c r="L14" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="M14" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="N14" s="30"/>
+      <c r="A14" s="22"/>
+      <c r="B14" s="22"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="22"/>
+      <c r="G14" s="22"/>
+      <c r="H14" s="22"/>
+      <c r="I14" s="22"/>
+      <c r="J14" s="22"/>
+      <c r="K14" s="24"/>
+      <c r="L14" s="22"/>
+      <c r="M14" s="22"/>
+      <c r="N14" s="25"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" s="27">
-        <v>5555626</v>
-      </c>
-      <c r="C15" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="D15" s="23">
-        <v>178888880001601</v>
-      </c>
-      <c r="E15" s="27">
-        <v>9999996</v>
-      </c>
-      <c r="F15" s="27">
-        <v>1000421</v>
-      </c>
-      <c r="G15" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="H15" s="27">
-        <v>1</v>
-      </c>
-      <c r="I15" s="27">
-        <v>2000</v>
-      </c>
-      <c r="J15" s="26">
-        <v>1</v>
-      </c>
-      <c r="K15" s="29" t="s">
-        <v>102</v>
-      </c>
-      <c r="L15" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="M15" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="N15" s="31"/>
+      <c r="A15" s="22"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="22"/>
+      <c r="I15" s="22"/>
+      <c r="J15" s="21"/>
+      <c r="K15" s="24"/>
+      <c r="L15" s="22"/>
+      <c r="M15" s="22"/>
+      <c r="N15" s="26"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="B16" s="27">
-        <v>5555627</v>
-      </c>
-      <c r="C16" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="D16" s="23">
-        <v>120733340001420</v>
-      </c>
-      <c r="E16" s="27">
-        <v>9999996</v>
-      </c>
-      <c r="F16" s="27">
-        <v>1000421</v>
-      </c>
-      <c r="G16" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="H16" s="27">
-        <v>6</v>
-      </c>
-      <c r="I16" s="27">
-        <v>2000</v>
-      </c>
-      <c r="J16" s="26">
-        <v>1</v>
-      </c>
-      <c r="K16" s="29" t="s">
-        <v>102</v>
-      </c>
-      <c r="L16" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="M16" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="N16" s="31"/>
+      <c r="A16" s="22"/>
+      <c r="B16" s="22"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="22"/>
+      <c r="G16" s="22"/>
+      <c r="H16" s="22"/>
+      <c r="I16" s="22"/>
+      <c r="J16" s="21"/>
+      <c r="K16" s="24"/>
+      <c r="L16" s="22"/>
+      <c r="M16" s="22"/>
+      <c r="N16" s="26"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="27" t="s">
-        <v>13</v>
-      </c>
-      <c r="B17" s="27">
-        <v>5555628</v>
-      </c>
-      <c r="C17" s="27" t="s">
-        <v>16</v>
-      </c>
-      <c r="D17" s="23">
-        <v>100673001212128</v>
-      </c>
-      <c r="E17" s="27">
-        <v>9999996</v>
-      </c>
-      <c r="F17" s="27">
-        <v>1000421</v>
-      </c>
-      <c r="G17" s="27" t="s">
-        <v>14</v>
-      </c>
-      <c r="H17" s="27">
-        <v>1</v>
-      </c>
-      <c r="I17" s="27">
-        <v>100</v>
-      </c>
-      <c r="J17" s="27">
-        <v>1.7</v>
-      </c>
-      <c r="K17" s="29" t="s">
-        <v>102</v>
-      </c>
-      <c r="L17" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="M17" s="27" t="s">
-        <v>15</v>
-      </c>
-      <c r="N17" s="31"/>
+      <c r="A17" s="22"/>
+      <c r="B17" s="22"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="22"/>
+      <c r="H17" s="22"/>
+      <c r="I17" s="22"/>
+      <c r="J17" s="22"/>
+      <c r="K17" s="24"/>
+      <c r="L17" s="22"/>
+      <c r="M17" s="22"/>
+      <c r="N17" s="26"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1737,12 +1401,12 @@
       <c r="S1" s="3"/>
       <c r="T1" s="3"/>
     </row>
-    <row r="2" spans="1:20" s="31" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="27" t="s">
+    <row r="2" spans="1:20" s="26" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="27">
-        <v>4555524</v>
+      <c r="B2" s="22">
+        <v>4555539</v>
       </c>
       <c r="C2" s="11">
         <v>120733340001420</v>
@@ -1753,31 +1417,31 @@
       <c r="E2" s="7">
         <v>1000421</v>
       </c>
-      <c r="F2" s="27" t="s">
+      <c r="F2" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="G2" s="27">
+      <c r="G2" s="22">
         <v>15</v>
       </c>
-      <c r="H2" s="27">
+      <c r="H2" s="22">
         <v>900</v>
       </c>
-      <c r="I2" s="32">
+      <c r="I2" s="27">
         <v>1.7</v>
       </c>
-      <c r="J2" s="27" t="s">
+      <c r="J2" s="22" t="s">
         <v>30</v>
       </c>
-      <c r="K2" s="27" t="s">
+      <c r="K2" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="L2" s="27" t="s">
+      <c r="L2" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="M2" s="27">
+      <c r="M2" s="22">
         <v>11</v>
       </c>
-      <c r="N2" s="30"/>
+      <c r="N2" s="25"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -1787,13 +1451,13 @@
         <v>4555514</v>
       </c>
       <c r="C3" s="2">
-        <v>120733340001420</v>
-      </c>
-      <c r="D3" s="27">
-        <v>9999996</v>
-      </c>
-      <c r="E3" s="27">
-        <v>1000421</v>
+        <v>100673000000011</v>
+      </c>
+      <c r="D3" s="1">
+        <v>9997115</v>
+      </c>
+      <c r="E3" s="1">
+        <v>8211642</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>29</v>
@@ -1804,7 +1468,7 @@
       <c r="H3" s="1">
         <v>700</v>
       </c>
-      <c r="I3" s="32">
+      <c r="I3" s="27">
         <v>1.7</v>
       </c>
       <c r="J3" s="1" t="s">
@@ -1825,16 +1489,16 @@
       <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="27">
+      <c r="B4" s="22">
         <v>4555517</v>
       </c>
-      <c r="C4" s="23">
+      <c r="C4" s="20">
         <v>100673000000011</v>
       </c>
-      <c r="D4" s="27">
+      <c r="D4" s="22">
         <v>9999996</v>
       </c>
-      <c r="E4" s="27">
+      <c r="E4" s="22">
         <v>1000421</v>
       </c>
       <c r="F4" s="1" t="s">
@@ -1846,7 +1510,7 @@
       <c r="H4" s="1">
         <v>700</v>
       </c>
-      <c r="I4" s="32">
+      <c r="I4" s="27">
         <v>1.7</v>
       </c>
       <c r="J4" s="1" t="s">
@@ -1864,468 +1528,182 @@
       <c r="N4" s="19"/>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="27">
-        <v>4555519</v>
-      </c>
-      <c r="C5" s="2">
-        <v>100673000000011</v>
-      </c>
-      <c r="D5" s="27">
-        <v>9999996</v>
-      </c>
-      <c r="E5" s="27">
-        <v>1000421</v>
-      </c>
-      <c r="F5" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G5" s="1">
-        <v>1</v>
-      </c>
-      <c r="H5" s="1">
-        <v>100</v>
-      </c>
-      <c r="I5" s="32">
-        <v>1.7</v>
-      </c>
-      <c r="J5" s="29" t="s">
-        <v>102</v>
-      </c>
-      <c r="K5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="L5" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M5" s="1">
-        <v>11</v>
-      </c>
+      <c r="A5" s="1"/>
+      <c r="B5" s="22"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="22"/>
+      <c r="E5" s="22"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="27"/>
+      <c r="J5" s="24"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+      <c r="M5" s="1"/>
       <c r="N5" s="19"/>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="27">
-        <v>4555520</v>
-      </c>
-      <c r="C6" s="2">
-        <v>100673000000011</v>
-      </c>
-      <c r="D6" s="1">
-        <v>9997115</v>
-      </c>
-      <c r="E6" s="1">
-        <v>8211642</v>
-      </c>
-      <c r="F6" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G6" s="1">
-        <v>15</v>
-      </c>
-      <c r="H6" s="1">
-        <v>700</v>
-      </c>
-      <c r="I6" s="32">
-        <v>1.7</v>
-      </c>
-      <c r="J6" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="L6" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M6" s="1">
-        <v>11</v>
-      </c>
+      <c r="A6" s="1"/>
+      <c r="B6" s="22"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="1"/>
+      <c r="F6" s="1"/>
+      <c r="G6" s="1"/>
+      <c r="H6" s="1"/>
+      <c r="I6" s="27"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="1"/>
+      <c r="M6" s="1"/>
       <c r="N6" s="19"/>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="27">
-        <v>4555522</v>
-      </c>
-      <c r="C7" s="2">
-        <v>100673000000011</v>
-      </c>
-      <c r="D7" s="1">
-        <v>9997115</v>
-      </c>
-      <c r="E7" s="1">
-        <v>8211642</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G7" s="1">
-        <v>15</v>
-      </c>
-      <c r="H7" s="1">
-        <v>500</v>
-      </c>
-      <c r="I7" s="32">
-        <v>1.7</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M7" s="1">
-        <v>11</v>
-      </c>
+      <c r="A7" s="1"/>
+      <c r="B7" s="22"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="27"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
       <c r="N7" s="19"/>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="27">
-        <v>4555524</v>
-      </c>
-      <c r="C8" s="2">
-        <v>100673000000011</v>
-      </c>
-      <c r="D8" s="1">
-        <v>9997115</v>
-      </c>
-      <c r="E8" s="1">
-        <v>8211642</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G8" s="1">
-        <v>15</v>
-      </c>
-      <c r="H8" s="1">
-        <v>700</v>
-      </c>
-      <c r="I8" s="32">
-        <v>1.7</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M8" s="1">
-        <v>11</v>
-      </c>
+      <c r="A8" s="1"/>
+      <c r="B8" s="22"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="27"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
       <c r="N8" s="19"/>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="27">
-        <v>4555526</v>
-      </c>
-      <c r="C9" s="2">
-        <v>100673000000011</v>
-      </c>
-      <c r="D9" s="1">
-        <v>9997115</v>
-      </c>
-      <c r="E9" s="1">
-        <v>8211642</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G9" s="1">
-        <v>15</v>
-      </c>
-      <c r="H9" s="1">
-        <v>700</v>
-      </c>
-      <c r="I9" s="32">
-        <v>1.7</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M9" s="1">
-        <v>11</v>
-      </c>
+      <c r="A9" s="1"/>
+      <c r="B9" s="22"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="27"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
       <c r="N9" s="19"/>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="27">
-        <v>4555528</v>
-      </c>
-      <c r="C10" s="2">
-        <v>100673000000011</v>
-      </c>
-      <c r="D10" s="1">
-        <v>9997115</v>
-      </c>
-      <c r="E10" s="1">
-        <v>8211642</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G10" s="1">
-        <v>15</v>
-      </c>
-      <c r="H10" s="1">
-        <v>700</v>
-      </c>
-      <c r="I10" s="32">
-        <v>1.7</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M10" s="1">
-        <v>11</v>
-      </c>
+      <c r="A10" s="1"/>
+      <c r="B10" s="22"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="27"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
       <c r="N10" s="19"/>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="27">
-        <v>4555530</v>
-      </c>
-      <c r="C11" s="2">
-        <v>100673000000011</v>
-      </c>
-      <c r="D11" s="1">
-        <v>9997115</v>
-      </c>
-      <c r="E11" s="1">
-        <v>8211642</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G11" s="1">
-        <v>15</v>
-      </c>
-      <c r="H11" s="1">
-        <v>100</v>
-      </c>
-      <c r="I11" s="32">
-        <v>1.7</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M11" s="1">
-        <v>11</v>
-      </c>
+      <c r="A11" s="1"/>
+      <c r="B11" s="22"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="27"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="27">
-        <v>4555532</v>
-      </c>
-      <c r="C12" s="2">
-        <v>100673000000011</v>
-      </c>
-      <c r="D12" s="1">
-        <v>9997115</v>
-      </c>
-      <c r="E12" s="1">
-        <v>8211642</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G12" s="1">
-        <v>15</v>
-      </c>
-      <c r="H12" s="1">
-        <v>100</v>
-      </c>
-      <c r="I12" s="32">
-        <v>1.7</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="L12" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M12" s="1">
-        <v>11</v>
-      </c>
+      <c r="A12" s="1"/>
+      <c r="B12" s="22"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="27"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" s="27">
-        <v>4555534</v>
-      </c>
-      <c r="C13" s="2">
-        <v>120733340001420</v>
-      </c>
-      <c r="D13" s="27">
-        <v>9999996</v>
-      </c>
-      <c r="E13" s="27">
-        <v>1000421</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G13" s="1">
-        <v>15</v>
-      </c>
-      <c r="H13" s="1">
-        <v>700</v>
-      </c>
-      <c r="I13" s="32">
-        <v>1.7</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M13" s="1">
-        <v>11</v>
-      </c>
+      <c r="A13" s="1"/>
+      <c r="B13" s="22"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="22"/>
+      <c r="E13" s="22"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="27"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" s="27">
-        <v>4555536</v>
-      </c>
-      <c r="C14" s="2">
-        <v>120733340001420</v>
-      </c>
-      <c r="D14" s="27">
-        <v>9999996</v>
-      </c>
-      <c r="E14" s="27">
-        <v>1000421</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G14" s="1">
-        <v>15</v>
-      </c>
-      <c r="H14" s="1">
-        <v>700</v>
-      </c>
-      <c r="I14" s="32">
-        <v>1.7</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="L14" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M14" s="1">
-        <v>11</v>
-      </c>
+      <c r="A14" s="1"/>
+      <c r="B14" s="22"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="22"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="27"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" s="27">
-        <v>4555538</v>
-      </c>
-      <c r="C15" s="2">
-        <v>100673000000011</v>
-      </c>
-      <c r="D15" s="27">
-        <v>9999996</v>
-      </c>
-      <c r="E15" s="27">
-        <v>1000421</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G15" s="1">
-        <v>15</v>
-      </c>
-      <c r="H15" s="1">
-        <v>700</v>
-      </c>
-      <c r="I15" s="32">
-        <v>1.7</v>
-      </c>
-      <c r="J15" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="L15" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M15" s="1">
-        <v>11</v>
-      </c>
+      <c r="A15" s="1"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="22"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="27"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
     </row>
     <row r="18" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C18" s="7"/>
       <c r="D18" s="7"/>
       <c r="E18" s="11"/>
       <c r="H18" s="17"/>
-      <c r="I18" s="28"/>
+      <c r="I18" s="23"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2400,108 +1778,108 @@
       </c>
     </row>
     <row r="2" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" x14ac:dyDescent="0.25">
-      <c r="A2" s="29">
-        <v>5555510</v>
-      </c>
-      <c r="B2" s="29" t="s">
+      <c r="A2" s="24">
+        <v>5555550</v>
+      </c>
+      <c r="B2" s="24" t="s">
         <v>93</v>
       </c>
-      <c r="C2" s="29" t="s">
+      <c r="C2" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="29" t="s">
+      <c r="D2" s="24" t="s">
         <v>95</v>
       </c>
-      <c r="E2" s="29">
+      <c r="E2" s="24">
         <v>2025</v>
       </c>
-      <c r="F2" s="29" t="s">
+      <c r="F2" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="G2" s="29" t="s">
+      <c r="G2" s="24" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="33">
+      <c r="H2" s="28">
         <v>100673001212128</v>
       </c>
-      <c r="I2" s="27">
-        <v>9997115</v>
-      </c>
-      <c r="J2" s="27">
-        <v>9997115</v>
-      </c>
-      <c r="K2" s="29">
+      <c r="I2" s="1">
+        <v>9999996</v>
+      </c>
+      <c r="J2" s="1">
+        <v>1000421</v>
+      </c>
+      <c r="K2" s="24">
         <v>100</v>
       </c>
-      <c r="L2" s="29">
+      <c r="L2" s="24">
         <v>6</v>
       </c>
-      <c r="M2" s="29">
+      <c r="M2" s="24">
         <v>0.5</v>
       </c>
-      <c r="N2" s="29" t="s">
+      <c r="N2" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="O2" s="29" t="s">
+      <c r="O2" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="P2" s="29" t="s">
+      <c r="P2" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="Q2" s="29" t="s">
+      <c r="Q2" s="24" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" x14ac:dyDescent="0.25">
-      <c r="A3" s="29">
+      <c r="A3" s="24">
         <v>5555534</v>
       </c>
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="24" t="s">
         <v>93</v>
       </c>
-      <c r="C3" s="29" t="s">
+      <c r="C3" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="29" t="s">
+      <c r="D3" s="24" t="s">
         <v>95</v>
       </c>
-      <c r="E3" s="29">
+      <c r="E3" s="24">
         <v>2025</v>
       </c>
-      <c r="F3" s="29" t="s">
+      <c r="F3" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="G3" s="29" t="s">
+      <c r="G3" s="24" t="s">
         <v>100</v>
       </c>
-      <c r="H3" s="33">
+      <c r="H3" s="28">
         <v>100673001212128</v>
       </c>
-      <c r="I3" s="27">
+      <c r="I3" s="22">
         <v>9997115</v>
       </c>
-      <c r="J3" s="27">
+      <c r="J3" s="22">
         <v>9997115</v>
       </c>
-      <c r="K3" s="29">
+      <c r="K3" s="24">
         <v>100</v>
       </c>
-      <c r="L3" s="29">
+      <c r="L3" s="24">
         <v>6</v>
       </c>
-      <c r="M3" s="29">
+      <c r="M3" s="24">
         <v>0.5</v>
       </c>
-      <c r="N3" s="29" t="s">
+      <c r="N3" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="O3" s="29" t="s">
+      <c r="O3" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="P3" s="29" t="s">
+      <c r="P3" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="Q3" s="29" t="s">
+      <c r="Q3" s="24" t="s">
         <v>104</v>
       </c>
     </row>
@@ -2578,14 +1956,14 @@
       <c r="G5" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="H5" s="33">
-        <v>100673001212128</v>
+      <c r="H5" s="28">
+        <v>102905240000015</v>
       </c>
       <c r="I5" s="1">
-        <v>9999996</v>
+        <v>9997115</v>
       </c>
       <c r="J5" s="1">
-        <v>1000421</v>
+        <v>8211642</v>
       </c>
       <c r="K5" s="7">
         <v>100</v>
@@ -2607,514 +1985,194 @@
       </c>
       <c r="Q5" s="19"/>
     </row>
-    <row r="6" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" s="38" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="34">
-        <v>5555537</v>
-      </c>
-      <c r="B6" s="34" t="s">
-        <v>93</v>
-      </c>
-      <c r="C6" s="34" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="E6" s="34">
-        <v>2025</v>
-      </c>
-      <c r="F6" s="34" t="s">
-        <v>98</v>
-      </c>
-      <c r="G6" s="34" t="s">
-        <v>100</v>
-      </c>
-      <c r="H6" s="35">
-        <v>100673001212128</v>
-      </c>
-      <c r="I6" s="36">
-        <v>9999996</v>
-      </c>
-      <c r="J6" s="36">
-        <v>1000421</v>
-      </c>
-      <c r="K6" s="34">
-        <v>1150</v>
-      </c>
-      <c r="L6" s="34">
-        <v>6</v>
-      </c>
-      <c r="M6" s="34">
-        <v>0.25</v>
-      </c>
-      <c r="N6" s="34" t="s">
-        <v>102</v>
-      </c>
-      <c r="O6" s="34" t="s">
-        <v>15</v>
-      </c>
-      <c r="P6" s="34" t="s">
-        <v>15</v>
-      </c>
-      <c r="Q6" s="37"/>
+    <row r="6" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" s="33" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="29"/>
+      <c r="B6" s="29"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="29"/>
+      <c r="E6" s="29"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="29"/>
+      <c r="H6" s="30"/>
+      <c r="I6" s="31"/>
+      <c r="J6" s="31"/>
+      <c r="K6" s="29"/>
+      <c r="L6" s="29"/>
+      <c r="M6" s="29"/>
+      <c r="N6" s="29"/>
+      <c r="O6" s="29"/>
+      <c r="P6" s="29"/>
+      <c r="Q6" s="32"/>
     </row>
     <row r="7" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" x14ac:dyDescent="0.25">
-      <c r="A7" s="7">
-        <v>5555538</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="E7" s="7">
-        <v>2025</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="H7" s="33">
-        <v>102905240000015</v>
-      </c>
-      <c r="I7" s="1">
-        <v>9997115</v>
-      </c>
-      <c r="J7" s="1">
-        <v>8211642</v>
-      </c>
-      <c r="K7" s="7">
-        <v>100</v>
-      </c>
-      <c r="L7" s="7">
-        <v>6</v>
-      </c>
-      <c r="M7" s="7">
-        <v>1</v>
-      </c>
-      <c r="N7" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="O7" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="P7" s="7" t="s">
-        <v>15</v>
-      </c>
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="28"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
+      <c r="O7" s="7"/>
+      <c r="P7" s="7"/>
       <c r="Q7" s="19"/>
     </row>
     <row r="8" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" x14ac:dyDescent="0.25">
-      <c r="A8" s="7">
-        <v>5555539</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="E8" s="7">
-        <v>2025</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="H8" s="11">
-        <v>102905240000015</v>
-      </c>
-      <c r="I8" s="1">
-        <v>9997115</v>
-      </c>
-      <c r="J8" s="1">
-        <v>8211642</v>
-      </c>
-      <c r="K8" s="7">
-        <v>100</v>
-      </c>
-      <c r="L8" s="7">
-        <v>6</v>
-      </c>
-      <c r="M8" s="7">
-        <v>1</v>
-      </c>
-      <c r="N8" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="O8" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="P8" s="7" t="s">
-        <v>15</v>
-      </c>
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="7"/>
+      <c r="O8" s="7"/>
+      <c r="P8" s="7"/>
       <c r="Q8" s="19"/>
     </row>
     <row r="9" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" x14ac:dyDescent="0.25">
-      <c r="A9" s="7">
-        <v>5555540</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="E9" s="7">
-        <v>2025</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="H9" s="33">
-        <v>102905240000015</v>
-      </c>
-      <c r="I9" s="1">
-        <v>9997115</v>
-      </c>
-      <c r="J9" s="1">
-        <v>8211642</v>
-      </c>
-      <c r="K9" s="7">
-        <v>100</v>
-      </c>
-      <c r="L9" s="7">
-        <v>6</v>
-      </c>
-      <c r="M9" s="7">
-        <v>1</v>
-      </c>
-      <c r="N9" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="O9" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="P9" s="7" t="s">
-        <v>15</v>
-      </c>
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="28"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
+      <c r="N9" s="7"/>
+      <c r="O9" s="7"/>
+      <c r="P9" s="7"/>
       <c r="Q9" s="19"/>
     </row>
     <row r="10" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" x14ac:dyDescent="0.25">
-      <c r="A10" s="7">
-        <v>5555541</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="E10" s="7">
-        <v>2025</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="H10" s="11">
-        <v>102905240000015</v>
-      </c>
-      <c r="I10" s="1">
-        <v>9997115</v>
-      </c>
-      <c r="J10" s="1">
-        <v>8211642</v>
-      </c>
-      <c r="K10" s="7">
-        <v>100</v>
-      </c>
-      <c r="L10" s="7">
-        <v>6</v>
-      </c>
-      <c r="M10" s="7">
-        <v>1</v>
-      </c>
-      <c r="N10" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="O10" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="P10" s="7" t="s">
-        <v>15</v>
-      </c>
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
+      <c r="N10" s="7"/>
+      <c r="O10" s="7"/>
+      <c r="P10" s="7"/>
       <c r="Q10" s="19"/>
     </row>
     <row r="11" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" x14ac:dyDescent="0.25">
-      <c r="A11" s="7">
-        <v>5555542</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="E11" s="7">
-        <v>2025</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="H11" s="33">
-        <v>102905240000015</v>
-      </c>
-      <c r="I11" s="1">
-        <v>9997115</v>
-      </c>
-      <c r="J11" s="1">
-        <v>8211642</v>
-      </c>
-      <c r="K11" s="7">
-        <v>100</v>
-      </c>
-      <c r="L11" s="7">
-        <v>6</v>
-      </c>
-      <c r="M11" s="7">
-        <v>1</v>
-      </c>
-      <c r="N11" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="O11" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="P11" s="7" t="s">
-        <v>15</v>
-      </c>
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="7"/>
+      <c r="O11" s="7"/>
+      <c r="P11" s="7"/>
       <c r="Q11" s="19"/>
     </row>
     <row r="12" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" x14ac:dyDescent="0.25">
-      <c r="A12" s="7">
-        <v>5555543</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="E12" s="7">
-        <v>2025</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="H12" s="11">
-        <v>102905240000015</v>
-      </c>
-      <c r="I12" s="1">
-        <v>9997115</v>
-      </c>
-      <c r="J12" s="1">
-        <v>8211642</v>
-      </c>
-      <c r="K12" s="7">
-        <v>100</v>
-      </c>
-      <c r="L12" s="7">
-        <v>6</v>
-      </c>
-      <c r="M12" s="7">
-        <v>1</v>
-      </c>
-      <c r="N12" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="O12" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="P12" s="7" t="s">
-        <v>15</v>
-      </c>
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="7"/>
+      <c r="N12" s="7"/>
+      <c r="O12" s="7"/>
+      <c r="P12" s="7"/>
       <c r="Q12" s="19"/>
     </row>
     <row r="13" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" x14ac:dyDescent="0.25">
-      <c r="A13" s="7">
-        <v>5555544</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="E13" s="7">
-        <v>2025</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="H13" s="33">
-        <v>102905240000015</v>
-      </c>
-      <c r="I13" s="1">
-        <v>9997115</v>
-      </c>
-      <c r="J13" s="1">
-        <v>8211642</v>
-      </c>
-      <c r="K13" s="7">
-        <v>100</v>
-      </c>
-      <c r="L13" s="7">
-        <v>6</v>
-      </c>
-      <c r="M13" s="7">
-        <v>1</v>
-      </c>
-      <c r="N13" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="O13" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="P13" s="7" t="s">
-        <v>15</v>
-      </c>
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="28"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="7"/>
+      <c r="N13" s="7"/>
+      <c r="O13" s="7"/>
+      <c r="P13" s="7"/>
       <c r="Q13" s="19"/>
     </row>
     <row r="14" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" x14ac:dyDescent="0.25">
-      <c r="A14" s="7">
-        <v>5555545</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="E14" s="7">
-        <v>2025</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="H14" s="11">
-        <v>102905240000015</v>
-      </c>
-      <c r="I14" s="1">
-        <v>9997115</v>
-      </c>
-      <c r="J14" s="1">
-        <v>8211642</v>
-      </c>
-      <c r="K14" s="7">
-        <v>100</v>
-      </c>
-      <c r="L14" s="7">
-        <v>6</v>
-      </c>
-      <c r="M14" s="7">
-        <v>1</v>
-      </c>
-      <c r="N14" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="O14" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="P14" s="7" t="s">
-        <v>15</v>
-      </c>
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="7"/>
+      <c r="M14" s="7"/>
+      <c r="N14" s="7"/>
+      <c r="O14" s="7"/>
+      <c r="P14" s="7"/>
       <c r="Q14" s="19"/>
     </row>
     <row r="15" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="7">
-        <v>5555546</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="E15" s="7">
-        <v>2025</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="H15" s="33">
-        <v>102905240000015</v>
-      </c>
-      <c r="I15" s="1">
-        <v>9997115</v>
-      </c>
-      <c r="J15" s="1">
-        <v>8211642</v>
-      </c>
-      <c r="K15" s="7">
-        <v>100</v>
-      </c>
-      <c r="L15" s="7">
-        <v>6</v>
-      </c>
-      <c r="M15" s="7">
-        <v>1</v>
-      </c>
-      <c r="N15" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="O15" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="P15" s="7" t="s">
-        <v>15</v>
-      </c>
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="28"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="7"/>
+      <c r="M15" s="7"/>
+      <c r="N15" s="7"/>
+      <c r="O15" s="7"/>
+      <c r="P15" s="7"/>
       <c r="Q15" s="19"/>
       <c r="X15" s="16"/>
       <c r="Y15" s="17"/>
@@ -6187,54 +5245,22 @@
       <c r="XEX15" s="17"/>
     </row>
     <row r="16" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="7">
-        <v>5555548</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="E16" s="7">
-        <v>2025</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="H16" s="11">
-        <v>100673001212128</v>
-      </c>
-      <c r="I16" s="1">
-        <v>9997115</v>
-      </c>
-      <c r="J16" s="1">
-        <v>8211642</v>
-      </c>
-      <c r="K16" s="7">
-        <v>100</v>
-      </c>
-      <c r="L16" s="7">
-        <v>6</v>
-      </c>
-      <c r="M16" s="7">
-        <v>1</v>
-      </c>
-      <c r="N16" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="O16" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="P16" s="7" t="s">
-        <v>15</v>
-      </c>
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="7"/>
+      <c r="L16" s="7"/>
+      <c r="M16" s="7"/>
+      <c r="N16" s="7"/>
+      <c r="O16" s="7"/>
+      <c r="P16" s="7"/>
       <c r="Q16" s="7"/>
       <c r="X16" s="16"/>
       <c r="Y16" s="17"/>
@@ -9307,54 +8333,22 @@
       <c r="XEX16" s="17"/>
     </row>
     <row r="17" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="7">
-        <v>5555550</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="E17" s="7">
-        <v>2025</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="H17" s="11">
-        <v>100673001212128</v>
-      </c>
-      <c r="I17" s="1">
-        <v>9997115</v>
-      </c>
-      <c r="J17" s="1">
-        <v>8211642</v>
-      </c>
-      <c r="K17" s="7">
-        <v>100</v>
-      </c>
-      <c r="L17" s="7">
-        <v>6</v>
-      </c>
-      <c r="M17" s="7">
-        <v>1.7</v>
-      </c>
-      <c r="N17" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="O17" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="P17" s="7" t="s">
-        <v>15</v>
-      </c>
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="11"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="7"/>
+      <c r="L17" s="7"/>
+      <c r="M17" s="7"/>
+      <c r="N17" s="7"/>
+      <c r="O17" s="7"/>
+      <c r="P17" s="7"/>
       <c r="Q17" s="7"/>
       <c r="X17" s="16"/>
       <c r="Y17" s="17"/>
@@ -12427,54 +11421,22 @@
       <c r="XEX17" s="17"/>
     </row>
     <row r="18" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="7">
-        <v>5555549</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="E18" s="7">
-        <v>2025</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="H18" s="11">
-        <v>100673001212128</v>
-      </c>
-      <c r="I18" s="1">
-        <v>9997115</v>
-      </c>
-      <c r="J18" s="1">
-        <v>8211642</v>
-      </c>
-      <c r="K18" s="7">
-        <v>100</v>
-      </c>
-      <c r="L18" s="7">
-        <v>6</v>
-      </c>
-      <c r="M18" s="7">
-        <v>1</v>
-      </c>
-      <c r="N18" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="O18" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="P18" s="7" t="s">
-        <v>15</v>
-      </c>
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="7"/>
+      <c r="L18" s="7"/>
+      <c r="M18" s="7"/>
+      <c r="N18" s="7"/>
+      <c r="O18" s="7"/>
+      <c r="P18" s="7"/>
       <c r="Q18" s="7"/>
       <c r="X18" s="16"/>
       <c r="Y18" s="17"/>
@@ -15547,54 +14509,22 @@
       <c r="XEX18" s="17"/>
     </row>
     <row r="19" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="7">
-        <v>5555550</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="E19" s="7">
-        <v>2025</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="H19" s="11">
-        <v>100673001212128</v>
-      </c>
-      <c r="I19" s="1">
-        <v>9997115</v>
-      </c>
-      <c r="J19" s="1">
-        <v>8211642</v>
-      </c>
-      <c r="K19" s="7">
-        <v>100</v>
-      </c>
-      <c r="L19" s="7">
-        <v>1</v>
-      </c>
-      <c r="M19" s="7">
-        <v>1</v>
-      </c>
-      <c r="N19" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="O19" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="P19" s="7" t="s">
-        <v>15</v>
-      </c>
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="7"/>
+      <c r="L19" s="7"/>
+      <c r="M19" s="7"/>
+      <c r="N19" s="7"/>
+      <c r="O19" s="7"/>
+      <c r="P19" s="7"/>
       <c r="Q19" s="7"/>
       <c r="X19" s="16"/>
       <c r="Y19" s="17"/>
@@ -18821,817 +17751,309 @@
       <c r="O3" s="7"/>
     </row>
     <row r="4" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="B4" s="7">
-        <v>5555553</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D4" s="7">
-        <v>11</v>
-      </c>
-      <c r="E4" s="7">
-        <v>9999996</v>
-      </c>
-      <c r="F4" s="7">
-        <v>1000421</v>
-      </c>
-      <c r="G4" s="11">
-        <v>100673000000011</v>
-      </c>
-      <c r="H4" s="7">
-        <v>1003</v>
-      </c>
-      <c r="I4" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="J4" s="7">
-        <v>10</v>
-      </c>
-      <c r="K4" s="7">
-        <v>10</v>
-      </c>
-      <c r="L4" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="M4" s="7">
-        <v>50</v>
-      </c>
-      <c r="N4" s="7" t="s">
-        <v>79</v>
-      </c>
+      <c r="A4" s="10"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="11"/>
+      <c r="H4" s="7"/>
+      <c r="I4" s="7"/>
+      <c r="J4" s="7"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
       <c r="O4" s="7"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="B5" s="20">
-        <v>5555554</v>
-      </c>
-      <c r="C5" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" s="20">
-        <v>11</v>
-      </c>
-      <c r="E5" s="24">
-        <v>9996059</v>
-      </c>
-      <c r="F5" s="22">
-        <v>5750013</v>
-      </c>
-      <c r="G5" s="21">
-        <v>100673000000011</v>
-      </c>
-      <c r="H5" s="20">
-        <v>1003</v>
-      </c>
-      <c r="I5" s="20" t="s">
-        <v>73</v>
-      </c>
-      <c r="J5" s="20">
-        <v>10</v>
-      </c>
-      <c r="K5" s="20">
-        <v>10</v>
-      </c>
-      <c r="L5" s="20" t="s">
-        <v>77</v>
-      </c>
-      <c r="M5" s="20">
-        <v>50</v>
-      </c>
-      <c r="N5" s="20" t="s">
-        <v>79</v>
-      </c>
-      <c r="O5" s="20" t="s">
-        <v>113</v>
-      </c>
+    <row r="5" spans="1:15" s="26" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="36"/>
+      <c r="B5" s="24"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="37"/>
+      <c r="F5" s="22"/>
+      <c r="G5" s="28"/>
+      <c r="H5" s="24"/>
+      <c r="I5" s="24"/>
+      <c r="J5" s="24"/>
+      <c r="K5" s="24"/>
+      <c r="L5" s="24"/>
+      <c r="M5" s="24"/>
+      <c r="N5" s="24"/>
+      <c r="O5" s="24"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="B6" s="7">
-        <v>5555555</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" s="7">
-        <v>11</v>
-      </c>
-      <c r="E6" s="7">
-        <v>9999996</v>
-      </c>
-      <c r="F6" s="7">
-        <v>1000421</v>
-      </c>
-      <c r="G6" s="11">
-        <v>100673000000011</v>
-      </c>
-      <c r="H6" s="7">
-        <v>1003</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="J6" s="7">
-        <v>1</v>
-      </c>
-      <c r="K6" s="7">
-        <v>10</v>
-      </c>
-      <c r="L6" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="M6" s="7">
-        <v>50</v>
-      </c>
-      <c r="N6" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="O6" s="7" t="s">
-        <v>114</v>
-      </c>
+      <c r="A6" s="10"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7"/>
+      <c r="O6" s="7"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="B7" s="7">
-        <v>5555556</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" s="7">
-        <v>11</v>
-      </c>
-      <c r="E7" s="7">
-        <v>9999996</v>
-      </c>
-      <c r="F7" s="7">
-        <v>1000421</v>
-      </c>
-      <c r="G7" s="11">
-        <v>100673000000011</v>
-      </c>
-      <c r="H7" s="7">
-        <v>1003</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="J7" s="7">
-        <v>1</v>
-      </c>
-      <c r="K7" s="7">
-        <v>10</v>
-      </c>
-      <c r="L7" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="M7" s="7">
-        <v>1</v>
-      </c>
-      <c r="N7" s="7" t="s">
-        <v>79</v>
-      </c>
+      <c r="A7" s="10"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
       <c r="O7" s="7"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="B8" s="7">
-        <v>5555557</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" s="7">
-        <v>11</v>
-      </c>
-      <c r="E8" s="7">
-        <v>9999996</v>
-      </c>
-      <c r="F8" s="7">
-        <v>1000421</v>
-      </c>
-      <c r="G8" s="11">
-        <v>100673000000011</v>
-      </c>
-      <c r="H8" s="7">
-        <v>1003</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="J8" s="7">
-        <v>10</v>
-      </c>
-      <c r="K8" s="7">
-        <v>10</v>
-      </c>
-      <c r="L8" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="M8" s="7">
-        <v>50</v>
-      </c>
-      <c r="N8" s="7" t="s">
-        <v>79</v>
-      </c>
+      <c r="A8" s="10"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="7"/>
       <c r="O8" s="7"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="B9" s="7">
-        <v>5555558</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" s="7">
-        <v>11</v>
-      </c>
-      <c r="E9" s="7">
-        <v>9999996</v>
-      </c>
-      <c r="F9" s="7">
-        <v>1000421</v>
-      </c>
-      <c r="G9" s="11">
-        <v>100673000000011</v>
-      </c>
-      <c r="H9" s="7">
-        <v>1003</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="J9" s="7">
-        <v>10</v>
-      </c>
-      <c r="K9" s="7">
-        <v>10</v>
-      </c>
-      <c r="L9" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="M9" s="7">
-        <v>50</v>
-      </c>
-      <c r="N9" s="7" t="s">
-        <v>79</v>
-      </c>
+      <c r="A9" s="10"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
+      <c r="N9" s="7"/>
       <c r="O9" s="7"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="B10" s="7">
-        <v>5555559</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" s="7">
-        <v>11</v>
-      </c>
-      <c r="E10" s="7">
-        <v>9999996</v>
-      </c>
-      <c r="F10" s="7">
-        <v>1000421</v>
-      </c>
-      <c r="G10" s="11">
-        <v>100673000000011</v>
-      </c>
-      <c r="H10" s="7">
-        <v>1003</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="J10" s="7">
-        <v>10</v>
-      </c>
-      <c r="K10" s="7">
-        <v>10</v>
-      </c>
-      <c r="L10" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="M10" s="7">
-        <v>50</v>
-      </c>
-      <c r="N10" s="7" t="s">
-        <v>79</v>
-      </c>
+      <c r="A10" s="10"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
+      <c r="N10" s="7"/>
       <c r="O10" s="7"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="B11" s="7">
-        <v>5555560</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" s="7">
-        <v>11</v>
-      </c>
-      <c r="E11" s="7">
-        <v>9999996</v>
-      </c>
-      <c r="F11" s="7">
-        <v>1000421</v>
-      </c>
-      <c r="G11" s="11">
-        <v>100673000000011</v>
-      </c>
-      <c r="H11" s="7">
-        <v>1003</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="J11" s="7">
-        <v>10</v>
-      </c>
-      <c r="K11" s="7">
-        <v>10</v>
-      </c>
-      <c r="L11" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="M11" s="7">
-        <v>50</v>
-      </c>
-      <c r="N11" s="7" t="s">
-        <v>79</v>
-      </c>
+      <c r="A11" s="10"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="7"/>
       <c r="O11" s="7"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="B12" s="7">
-        <v>5555561</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12" s="7">
-        <v>11</v>
-      </c>
-      <c r="E12" s="7">
-        <v>9999996</v>
-      </c>
-      <c r="F12" s="7">
-        <v>1000421</v>
-      </c>
-      <c r="G12" s="11">
-        <v>100673000000011</v>
-      </c>
-      <c r="H12" s="7">
-        <v>1003</v>
-      </c>
-      <c r="I12" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="J12" s="7">
-        <v>10</v>
-      </c>
-      <c r="K12" s="7">
-        <v>10</v>
-      </c>
-      <c r="L12" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="M12" s="7">
-        <v>50</v>
-      </c>
-      <c r="N12" s="7" t="s">
-        <v>79</v>
-      </c>
+      <c r="A12" s="10"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="7"/>
+      <c r="N12" s="7"/>
       <c r="O12" s="7"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="B13" s="7">
-        <v>5555562</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D13" s="7">
-        <v>11</v>
-      </c>
-      <c r="E13" s="7">
-        <v>9999996</v>
-      </c>
-      <c r="F13" s="7">
-        <v>1000421</v>
-      </c>
-      <c r="G13" s="11">
-        <v>100673000000011</v>
-      </c>
-      <c r="H13" s="7">
-        <v>1003</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="J13" s="7">
-        <v>10</v>
-      </c>
-      <c r="K13" s="7">
-        <v>10</v>
-      </c>
-      <c r="L13" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="M13" s="7">
-        <v>50</v>
-      </c>
-      <c r="N13" s="7" t="s">
-        <v>79</v>
-      </c>
+      <c r="A13" s="10"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="7"/>
+      <c r="N13" s="7"/>
       <c r="O13" s="7"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="B14" s="7">
-        <v>5555563</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D14" s="7">
-        <v>11</v>
-      </c>
-      <c r="E14" s="7">
-        <v>9999996</v>
-      </c>
-      <c r="F14" s="7">
-        <v>1000421</v>
-      </c>
-      <c r="G14" s="11">
-        <v>100673000000011</v>
-      </c>
-      <c r="H14" s="7">
-        <v>1003</v>
-      </c>
-      <c r="I14" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="J14" s="7">
-        <v>10</v>
-      </c>
-      <c r="K14" s="7">
-        <v>10</v>
-      </c>
-      <c r="L14" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="M14" s="7">
-        <v>50</v>
-      </c>
-      <c r="N14" s="7" t="s">
-        <v>79</v>
-      </c>
+      <c r="A14" s="10"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="7"/>
+      <c r="M14" s="7"/>
+      <c r="N14" s="7"/>
       <c r="O14" s="7"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="B15" s="7">
-        <v>5555564</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D15" s="7">
-        <v>11</v>
-      </c>
-      <c r="E15" s="7">
-        <v>9999996</v>
-      </c>
-      <c r="F15" s="7">
-        <v>1000421</v>
-      </c>
-      <c r="G15" s="11">
-        <v>100673000000011</v>
-      </c>
-      <c r="H15" s="7">
-        <v>1003</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="J15" s="7">
-        <v>10</v>
-      </c>
-      <c r="K15" s="7">
-        <v>10</v>
-      </c>
-      <c r="L15" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="M15" s="7">
-        <v>50</v>
-      </c>
-      <c r="N15" s="7" t="s">
-        <v>79</v>
-      </c>
+      <c r="A15" s="10"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="7"/>
+      <c r="M15" s="7"/>
+      <c r="N15" s="7"/>
       <c r="O15" s="7"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="B16" s="7">
-        <v>5555565</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D16" s="7">
-        <v>11</v>
-      </c>
-      <c r="E16" s="7">
-        <v>9999996</v>
-      </c>
-      <c r="F16" s="7">
-        <v>1000421</v>
-      </c>
-      <c r="G16" s="11">
-        <v>100673000000011</v>
-      </c>
-      <c r="H16" s="7">
-        <v>1003</v>
-      </c>
-      <c r="I16" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="J16" s="7">
-        <v>10</v>
-      </c>
-      <c r="K16" s="7">
-        <v>10</v>
-      </c>
-      <c r="L16" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="M16" s="7">
-        <v>50</v>
-      </c>
-      <c r="N16" s="7" t="s">
-        <v>79</v>
-      </c>
+      <c r="A16" s="10"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="7"/>
+      <c r="K16" s="7"/>
+      <c r="L16" s="7"/>
+      <c r="M16" s="7"/>
+      <c r="N16" s="7"/>
       <c r="O16" s="7"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="B17" s="7">
-        <v>5555566</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D17" s="7">
-        <v>11</v>
-      </c>
-      <c r="E17" s="7">
-        <v>9999996</v>
-      </c>
-      <c r="F17" s="7">
-        <v>1000421</v>
-      </c>
-      <c r="G17" s="11">
-        <v>100673000000011</v>
-      </c>
-      <c r="H17" s="7">
-        <v>1003</v>
-      </c>
-      <c r="I17" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="J17" s="7">
-        <v>10</v>
-      </c>
-      <c r="K17" s="7">
-        <v>10</v>
-      </c>
-      <c r="L17" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="M17" s="7">
-        <v>50</v>
-      </c>
-      <c r="N17" s="7" t="s">
-        <v>79</v>
-      </c>
+      <c r="A17" s="10"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="7"/>
+      <c r="L17" s="7"/>
+      <c r="M17" s="7"/>
+      <c r="N17" s="7"/>
       <c r="O17" s="7"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="B18" s="7">
-        <v>5555567</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D18" s="7">
-        <v>11</v>
-      </c>
-      <c r="E18" s="7">
-        <v>9999996</v>
-      </c>
-      <c r="F18" s="7">
-        <v>1000421</v>
-      </c>
-      <c r="G18" s="11">
-        <v>100673000000011</v>
-      </c>
-      <c r="H18" s="7">
-        <v>1003</v>
-      </c>
-      <c r="I18" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="J18" s="7">
-        <v>10</v>
-      </c>
-      <c r="K18" s="7">
-        <v>10</v>
-      </c>
-      <c r="L18" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="M18" s="7">
-        <v>50</v>
-      </c>
-      <c r="N18" s="7" t="s">
-        <v>79</v>
-      </c>
+      <c r="A18" s="10"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="7"/>
+      <c r="L18" s="7"/>
+      <c r="M18" s="7"/>
+      <c r="N18" s="7"/>
       <c r="O18" s="7"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="B19" s="7">
-        <v>5555568</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D19" s="7">
-        <v>11</v>
-      </c>
-      <c r="E19" s="7">
-        <v>9999996</v>
-      </c>
-      <c r="F19" s="7">
-        <v>1000421</v>
-      </c>
-      <c r="G19" s="11">
-        <v>100673000000011</v>
-      </c>
-      <c r="H19" s="7">
-        <v>1003</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="J19" s="7">
-        <v>10</v>
-      </c>
-      <c r="K19" s="7">
-        <v>10</v>
-      </c>
-      <c r="L19" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="M19" s="7">
-        <v>50</v>
-      </c>
-      <c r="N19" s="7" t="s">
-        <v>79</v>
-      </c>
+      <c r="A19" s="10"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="7"/>
+      <c r="J19" s="7"/>
+      <c r="K19" s="7"/>
+      <c r="L19" s="7"/>
+      <c r="M19" s="7"/>
+      <c r="N19" s="7"/>
       <c r="O19" s="7"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="B20" s="7">
-        <v>5555569</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D20" s="7">
-        <v>11</v>
-      </c>
-      <c r="E20" s="7">
-        <v>9999996</v>
-      </c>
-      <c r="F20" s="7">
-        <v>1000421</v>
-      </c>
-      <c r="G20" s="11">
-        <v>100673000000011</v>
-      </c>
-      <c r="H20" s="7">
-        <v>1003</v>
-      </c>
-      <c r="I20" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="J20" s="7">
-        <v>10</v>
-      </c>
-      <c r="K20" s="7">
-        <v>10</v>
-      </c>
-      <c r="L20" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="M20" s="7">
-        <v>50</v>
-      </c>
-      <c r="N20" s="7" t="s">
-        <v>79</v>
-      </c>
+      <c r="A20" s="10"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="7"/>
+      <c r="J20" s="7"/>
+      <c r="K20" s="7"/>
+      <c r="L20" s="7"/>
+      <c r="M20" s="7"/>
+      <c r="N20" s="7"/>
       <c r="O20" s="7"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="B21" s="7">
-        <v>5555570</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D21" s="7">
-        <v>11</v>
-      </c>
-      <c r="E21" s="7">
-        <v>9996059</v>
-      </c>
-      <c r="F21" s="7">
-        <v>5750013</v>
-      </c>
-      <c r="G21" s="11">
-        <v>178888880001601</v>
-      </c>
-      <c r="H21" s="7">
-        <v>1001</v>
-      </c>
-      <c r="I21" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="J21" s="7">
-        <v>20</v>
-      </c>
-      <c r="K21" s="7">
-        <v>20</v>
-      </c>
-      <c r="L21" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="M21" s="7">
-        <v>100</v>
-      </c>
-      <c r="N21" s="7" t="s">
-        <v>79</v>
-      </c>
+      <c r="A21" s="10"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="7"/>
+      <c r="J21" s="7"/>
+      <c r="K21" s="7"/>
+      <c r="L21" s="7"/>
+      <c r="M21" s="7"/>
+      <c r="N21" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -19775,13 +18197,13 @@
         <v>1000012</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>132</v>
+        <v>129</v>
       </c>
       <c r="J2" s="1">
         <v>130009</v>
       </c>
       <c r="K2" s="1">
-        <v>170</v>
+        <v>1530</v>
       </c>
       <c r="L2" s="1">
         <v>4200</v>
@@ -19835,7 +18257,7 @@
         <v>100</v>
       </c>
       <c r="AC2" s="7">
-        <v>7</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -19897,7 +18319,7 @@
         <v>89</v>
       </c>
       <c r="M1" s="13" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="N1" s="13" t="s">
         <v>38</v>
@@ -19986,7 +18408,7 @@
         <v>10</v>
       </c>
       <c r="M2" s="7" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="N2" s="7">
         <v>46202558</v>
@@ -20033,7 +18455,7 @@
       <c r="AB2" s="7">
         <v>200</v>
       </c>
-      <c r="AC2" s="39">
+      <c r="AC2" s="34">
         <v>9</v>
       </c>
     </row>
@@ -20142,66 +18564,66 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19 16384:16384" x14ac:dyDescent="0.25">
-      <c r="A1" s="40" t="s">
+      <c r="A1" s="35" t="s">
         <v>105</v>
       </c>
-      <c r="B1" s="40" t="s">
+      <c r="B1" s="35" t="s">
         <v>56</v>
       </c>
-      <c r="C1" s="40" t="s">
+      <c r="C1" s="35" t="s">
         <v>106</v>
       </c>
-      <c r="D1" s="40" t="s">
+      <c r="D1" s="35" t="s">
         <v>107</v>
       </c>
-      <c r="E1" s="40" t="s">
+      <c r="E1" s="35" t="s">
         <v>108</v>
       </c>
-      <c r="F1" s="40" t="s">
+      <c r="F1" s="35" t="s">
         <v>109</v>
       </c>
       <c r="G1" s="5" t="s">
+        <v>117</v>
+      </c>
+      <c r="H1" s="35" t="s">
+        <v>118</v>
+      </c>
+      <c r="I1" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="J1" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="H1" s="40" t="s">
+      <c r="K1" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="I1" s="5" t="s">
+      <c r="L1" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="J1" s="5" t="s">
+      <c r="M1" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="K1" s="5" t="s">
+      <c r="N1" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="L1" s="5" t="s">
+      <c r="O1" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="M1" s="5" t="s">
+      <c r="P1" s="5" t="s">
         <v>126</v>
       </c>
-      <c r="N1" s="5" t="s">
+      <c r="Q1" s="5" t="s">
         <v>127</v>
       </c>
-      <c r="O1" s="5" t="s">
+      <c r="R1" s="35"/>
+      <c r="S1" s="35" t="s">
         <v>128</v>
-      </c>
-      <c r="P1" s="5" t="s">
-        <v>129</v>
-      </c>
-      <c r="Q1" s="5" t="s">
-        <v>130</v>
-      </c>
-      <c r="R1" s="40"/>
-      <c r="S1" s="40" t="s">
-        <v>131</v>
       </c>
       <c r="XFD1" s="3"/>
     </row>
     <row r="2" spans="1:19 16384:16384" x14ac:dyDescent="0.25">
       <c r="A2" s="19">
-        <v>32180</v>
+        <v>32181</v>
       </c>
       <c r="B2" s="19">
         <v>90</v>
@@ -20297,12 +18719,12 @@
     </row>
     <row r="10" spans="1:19 16384:16384" x14ac:dyDescent="0.25">
       <c r="F10" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11" spans="1:19 16384:16384" x14ac:dyDescent="0.25">
       <c r="F11" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/Data/ENWR_Creation.xlsx
+++ b/Data/ENWR_Creation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E5118AB4-2509-4360-B672-2619C5D177F5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C636A5F5-2847-4418-9DCC-C3ABC1301A38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RP_Deposite_Request_Agriculture" sheetId="1" r:id="rId1"/>
@@ -1406,16 +1406,16 @@
         <v>13</v>
       </c>
       <c r="B2" s="22">
-        <v>4555539</v>
+        <v>4555541</v>
       </c>
       <c r="C2" s="11">
-        <v>120733340001420</v>
+        <v>178888880001601</v>
       </c>
       <c r="D2" s="7">
-        <v>9999996</v>
+        <v>8888999</v>
       </c>
       <c r="E2" s="7">
-        <v>1000421</v>
+        <v>8888888</v>
       </c>
       <c r="F2" s="22" t="s">
         <v>29</v>
@@ -17665,7 +17665,7 @@
         <v>70</v>
       </c>
       <c r="B2" s="7">
-        <v>1655559</v>
+        <v>1655560</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>29</v>
@@ -17674,13 +17674,13 @@
         <v>11</v>
       </c>
       <c r="E2" s="7">
-        <v>9999996</v>
+        <v>8888999</v>
       </c>
       <c r="F2" s="7">
-        <v>1000421</v>
+        <v>8888888</v>
       </c>
       <c r="G2" s="11">
-        <v>120733340001420</v>
+        <v>178888880001601</v>
       </c>
       <c r="H2" s="7">
         <v>1003</v>
@@ -18206,7 +18206,7 @@
         <v>1530</v>
       </c>
       <c r="L2" s="1">
-        <v>4200</v>
+        <v>5000</v>
       </c>
       <c r="M2" s="1">
         <v>6</v>
@@ -18390,7 +18390,7 @@
         <v>45</v>
       </c>
       <c r="G2" s="7">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="H2" s="7">
         <v>30</v>
@@ -18623,7 +18623,7 @@
     </row>
     <row r="2" spans="1:19 16384:16384" x14ac:dyDescent="0.25">
       <c r="A2" s="19">
-        <v>32181</v>
+        <v>32184</v>
       </c>
       <c r="B2" s="19">
         <v>90</v>

--- a/Data/ENWR_Creation.xlsx
+++ b/Data/ENWR_Creation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C636A5F5-2847-4418-9DCC-C3ABC1301A38}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1E0BED3-15C1-40AF-9739-3CFDAA2EC4A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1406,7 +1406,7 @@
         <v>13</v>
       </c>
       <c r="B2" s="22">
-        <v>4555541</v>
+        <v>4555543</v>
       </c>
       <c r="C2" s="11">
         <v>178888880001601</v>
@@ -1421,13 +1421,13 @@
         <v>29</v>
       </c>
       <c r="G2" s="22">
-        <v>15</v>
+        <v>947</v>
       </c>
       <c r="H2" s="22">
-        <v>900</v>
+        <v>40</v>
       </c>
       <c r="I2" s="27">
-        <v>1.7</v>
+        <v>0.6</v>
       </c>
       <c r="J2" s="22" t="s">
         <v>30</v>
@@ -17665,7 +17665,7 @@
         <v>70</v>
       </c>
       <c r="B2" s="7">
-        <v>1655560</v>
+        <v>1655563</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>29</v>
@@ -17689,7 +17689,7 @@
         <v>73</v>
       </c>
       <c r="J2" s="7">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="K2" s="7">
         <v>10</v>
@@ -17698,7 +17698,7 @@
         <v>77</v>
       </c>
       <c r="M2" s="7">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="N2" s="7" t="s">
         <v>79</v>
@@ -18203,7 +18203,7 @@
         <v>130009</v>
       </c>
       <c r="K2" s="1">
-        <v>1530</v>
+        <v>72</v>
       </c>
       <c r="L2" s="1">
         <v>5000</v>
@@ -18254,10 +18254,10 @@
         <v>10000</v>
       </c>
       <c r="AB2" s="11">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="AC2" s="7">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -18387,7 +18387,7 @@
         <v>60</v>
       </c>
       <c r="F2" s="7">
-        <v>45</v>
+        <v>50</v>
       </c>
       <c r="G2" s="7">
         <v>5000</v>
@@ -18402,7 +18402,7 @@
         <v>2</v>
       </c>
       <c r="K2" s="7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L2" s="7">
         <v>10</v>
@@ -18414,7 +18414,7 @@
         <v>46202558</v>
       </c>
       <c r="O2" s="7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P2" s="7">
         <v>1</v>
@@ -18456,7 +18456,7 @@
         <v>200</v>
       </c>
       <c r="AC2" s="34">
-        <v>9</v>
+        <v>50</v>
       </c>
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.25">
@@ -18623,7 +18623,7 @@
     </row>
     <row r="2" spans="1:19 16384:16384" x14ac:dyDescent="0.25">
       <c r="A2" s="19">
-        <v>32184</v>
+        <v>321852</v>
       </c>
       <c r="B2" s="19">
         <v>90</v>

--- a/Data/ENWR_Creation.xlsx
+++ b/Data/ENWR_Creation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D1E0BED3-15C1-40AF-9739-3CFDAA2EC4A7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{767E97E3-CEC6-4C22-B47E-BFF49FD2C526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RP_Deposite_Request_Agriculture" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="130">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="131">
   <si>
     <t>commoditySegment</t>
   </si>
@@ -433,6 +433,9 @@
   <si>
     <t>Rudhra121</t>
   </si>
+  <si>
+    <t>ZINCMINI</t>
+  </si>
 </sst>
 </file>
 
@@ -441,7 +444,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -526,6 +529,12 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -553,7 +562,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="5">
     <border>
       <left/>
       <right/>
@@ -587,11 +596,35 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color indexed="64"/>
+      </left>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -636,6 +669,12 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -17660,12 +17699,12 @@
       </c>
       <c r="O1" s="13"/>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
         <v>70</v>
       </c>
       <c r="B2" s="7">
-        <v>1655563</v>
+        <v>1655564</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>29</v>
@@ -17673,10 +17712,10 @@
       <c r="D2" s="7">
         <v>11</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="38">
         <v>8888999</v>
       </c>
-      <c r="F2" s="7">
+      <c r="F2" s="39">
         <v>8888888</v>
       </c>
       <c r="G2" s="11">
@@ -17686,10 +17725,10 @@
         <v>1003</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>73</v>
+        <v>130</v>
       </c>
       <c r="J2" s="7">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="K2" s="7">
         <v>10</v>
@@ -17698,7 +17737,7 @@
         <v>77</v>
       </c>
       <c r="M2" s="7">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="N2" s="7" t="s">
         <v>79</v>
@@ -18057,6 +18096,7 @@
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -18387,7 +18427,7 @@
         <v>60</v>
       </c>
       <c r="F2" s="7">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="G2" s="7">
         <v>5000</v>
@@ -18456,7 +18496,7 @@
         <v>200</v>
       </c>
       <c r="AC2" s="34">
-        <v>50</v>
+        <v>10</v>
       </c>
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.25">
@@ -18623,7 +18663,7 @@
     </row>
     <row r="2" spans="1:19 16384:16384" x14ac:dyDescent="0.25">
       <c r="A2" s="19">
-        <v>321852</v>
+        <v>321853</v>
       </c>
       <c r="B2" s="19">
         <v>90</v>

--- a/Data/ENWR_Creation.xlsx
+++ b/Data/ENWR_Creation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{767E97E3-CEC6-4C22-B47E-BFF49FD2C526}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5D1CDFD-5A41-4EB1-9E50-FFA09A2E44D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19725" windowHeight="11760" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RP_Deposite_Request_Agriculture" sheetId="1" r:id="rId1"/>
@@ -17699,12 +17699,12 @@
       </c>
       <c r="O1" s="13"/>
     </row>
-    <row r="2" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>70</v>
       </c>
       <c r="B2" s="7">
-        <v>1655564</v>
+        <v>1655566</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>29</v>
@@ -17712,14 +17712,14 @@
       <c r="D2" s="7">
         <v>11</v>
       </c>
-      <c r="E2" s="38">
-        <v>8888999</v>
-      </c>
-      <c r="F2" s="39">
-        <v>8888888</v>
+      <c r="E2" s="7">
+        <v>9999996</v>
+      </c>
+      <c r="F2" s="7">
+        <v>1000421</v>
       </c>
       <c r="G2" s="11">
-        <v>178888880001601</v>
+        <v>120733340001420</v>
       </c>
       <c r="H2" s="7">
         <v>1003</v>
@@ -17789,14 +17789,20 @@
       </c>
       <c r="O3" s="7"/>
     </row>
-    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="10"/>
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
-      <c r="E4" s="7"/>
-      <c r="F4" s="7"/>
-      <c r="G4" s="11"/>
+      <c r="E4" s="38">
+        <v>8888999</v>
+      </c>
+      <c r="F4" s="39">
+        <v>8888888</v>
+      </c>
+      <c r="G4" s="11">
+        <v>178888880001601</v>
+      </c>
       <c r="H4" s="7"/>
       <c r="I4" s="7"/>
       <c r="J4" s="7"/>
@@ -18663,7 +18669,7 @@
     </row>
     <row r="2" spans="1:19 16384:16384" x14ac:dyDescent="0.25">
       <c r="A2" s="19">
-        <v>321853</v>
+        <v>321855</v>
       </c>
       <c r="B2" s="19">
         <v>90</v>

--- a/Data/ENWR_Creation.xlsx
+++ b/Data/ENWR_Creation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B5D1CDFD-5A41-4EB1-9E50-FFA09A2E44D6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6B813DC-2549-4CEA-8A95-A8878B0663BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19725" windowHeight="11760" firstSheet="3" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19725" windowHeight="11760" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RP_Deposite_Request_Agriculture" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="246" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="131">
   <si>
     <t>commoditySegment</t>
   </si>
@@ -1381,7 +1381,7 @@
   <cols>
     <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.28515625" customWidth="1"/>
-    <col min="6" max="6" width="13.7109375" customWidth="1"/>
+    <col min="6" max="6" width="16.140625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="15.28515625" customWidth="1"/>
     <col min="8" max="8" width="8.85546875" customWidth="1"/>
     <col min="9" max="9" width="10.85546875" customWidth="1"/>
@@ -1583,19 +1583,45 @@
       <c r="N5" s="19"/>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A6" s="1"/>
-      <c r="B6" s="22"/>
-      <c r="C6" s="2"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="1"/>
-      <c r="F6" s="1"/>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="27"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
+      <c r="A6" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="22">
+        <v>1602261</v>
+      </c>
+      <c r="C6" s="11">
+        <v>120733340001420</v>
+      </c>
+      <c r="D6" s="7">
+        <v>9999996</v>
+      </c>
+      <c r="E6" s="7">
+        <v>1000421</v>
+      </c>
+      <c r="F6" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G6" s="1">
+        <v>15</v>
+      </c>
+      <c r="H6" s="1">
+        <v>900</v>
+      </c>
+      <c r="I6" s="27">
+        <v>1.7</v>
+      </c>
+      <c r="J6" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L6" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M6" s="1">
+        <v>11</v>
+      </c>
       <c r="N6" s="19"/>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
@@ -18249,7 +18275,7 @@
         <v>130009</v>
       </c>
       <c r="K2" s="1">
-        <v>72</v>
+        <v>1530</v>
       </c>
       <c r="L2" s="1">
         <v>5000</v>
@@ -18300,10 +18326,10 @@
         <v>10000</v>
       </c>
       <c r="AB2" s="11">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="AC2" s="7">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>

--- a/Data/ENWR_Creation.xlsx
+++ b/Data/ENWR_Creation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6B813DC-2549-4CEA-8A95-A8878B0663BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{807C89EC-4F27-412D-BFE2-45A6FB87921C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19725" windowHeight="11760" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19725" windowHeight="11760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RP_Deposite_Request_Agriculture" sheetId="1" r:id="rId1"/>
@@ -1587,10 +1587,10 @@
         <v>13</v>
       </c>
       <c r="B6" s="22">
-        <v>1602261</v>
-      </c>
-      <c r="C6" s="11">
-        <v>120733340001420</v>
+        <v>1702262</v>
+      </c>
+      <c r="C6" s="2">
+        <v>100673000000011</v>
       </c>
       <c r="D6" s="7">
         <v>9999996</v>
@@ -18695,7 +18695,7 @@
     </row>
     <row r="2" spans="1:19 16384:16384" x14ac:dyDescent="0.25">
       <c r="A2" s="19">
-        <v>321855</v>
+        <v>321857</v>
       </c>
       <c r="B2" s="19">
         <v>90</v>

--- a/Data/ENWR_Creation.xlsx
+++ b/Data/ENWR_Creation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{807C89EC-4F27-412D-BFE2-45A6FB87921C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70228A4D-562B-4510-B13F-388CD9CAA408}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19725" windowHeight="11760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19725" windowHeight="11760" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RP_Deposite_Request_Agriculture" sheetId="1" r:id="rId1"/>
@@ -17730,7 +17730,7 @@
         <v>70</v>
       </c>
       <c r="B2" s="7">
-        <v>1655566</v>
+        <v>1655567</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>29</v>
@@ -18695,7 +18695,7 @@
     </row>
     <row r="2" spans="1:19 16384:16384" x14ac:dyDescent="0.25">
       <c r="A2" s="19">
-        <v>321857</v>
+        <v>321858</v>
       </c>
       <c r="B2" s="19">
         <v>90</v>

--- a/Data/ENWR_Creation.xlsx
+++ b/Data/ENWR_Creation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{70228A4D-562B-4510-B13F-388CD9CAA408}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B37A4091-224D-4872-94BA-AC077E43BA92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19725" windowHeight="11760" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="251" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="131">
   <si>
     <t>commoditySegment</t>
   </si>
@@ -624,7 +624,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -668,7 +668,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
@@ -1445,7 +1444,7 @@
         <v>13</v>
       </c>
       <c r="B2" s="22">
-        <v>4555543</v>
+        <v>4555603</v>
       </c>
       <c r="C2" s="11">
         <v>178888880001601</v>
@@ -1459,22 +1458,22 @@
       <c r="F2" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="G2" s="22">
-        <v>947</v>
-      </c>
-      <c r="H2" s="22">
-        <v>40</v>
+      <c r="G2" s="1">
+        <v>15</v>
+      </c>
+      <c r="H2" s="1">
+        <v>900</v>
       </c>
       <c r="I2" s="27">
-        <v>0.6</v>
-      </c>
-      <c r="J2" s="22" t="s">
+        <v>1.7</v>
+      </c>
+      <c r="J2" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="K2" s="22" t="s">
+      <c r="K2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="L2" s="22" t="s">
+      <c r="L2" s="1" t="s">
         <v>15</v>
       </c>
       <c r="M2" s="22">
@@ -1529,7 +1528,7 @@
         <v>13</v>
       </c>
       <c r="B4" s="22">
-        <v>4555517</v>
+        <v>4555604</v>
       </c>
       <c r="C4" s="20">
         <v>100673000000011</v>
@@ -1547,7 +1546,7 @@
         <v>15</v>
       </c>
       <c r="H4" s="1">
-        <v>700</v>
+        <v>900</v>
       </c>
       <c r="I4" s="27">
         <v>1.7</v>
@@ -17725,12 +17724,12 @@
       </c>
       <c r="O1" s="13"/>
     </row>
-    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="10" t="s">
         <v>70</v>
       </c>
       <c r="B2" s="7">
-        <v>1655567</v>
+        <v>1656502</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>29</v>
@@ -17738,23 +17737,23 @@
       <c r="D2" s="7">
         <v>11</v>
       </c>
-      <c r="E2" s="7">
-        <v>9999996</v>
-      </c>
-      <c r="F2" s="7">
-        <v>1000421</v>
+      <c r="E2" s="37">
+        <v>8888999</v>
+      </c>
+      <c r="F2" s="38">
+        <v>8888888</v>
       </c>
       <c r="G2" s="11">
-        <v>120733340001420</v>
+        <v>178888880001601</v>
       </c>
       <c r="H2" s="7">
         <v>1003</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>130</v>
+        <v>73</v>
       </c>
       <c r="J2" s="7">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="K2" s="7">
         <v>10</v>
@@ -17763,7 +17762,7 @@
         <v>77</v>
       </c>
       <c r="M2" s="7">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="N2" s="7" t="s">
         <v>79</v>
@@ -17820,17 +17819,19 @@
       <c r="B4" s="7"/>
       <c r="C4" s="7"/>
       <c r="D4" s="7"/>
-      <c r="E4" s="38">
+      <c r="E4" s="37">
         <v>8888999</v>
       </c>
-      <c r="F4" s="39">
+      <c r="F4" s="38">
         <v>8888888</v>
       </c>
       <c r="G4" s="11">
         <v>178888880001601</v>
       </c>
       <c r="H4" s="7"/>
-      <c r="I4" s="7"/>
+      <c r="I4" s="7" t="s">
+        <v>130</v>
+      </c>
       <c r="J4" s="7"/>
       <c r="K4" s="7"/>
       <c r="L4" s="7"/>
@@ -17843,9 +17844,15 @@
       <c r="B5" s="24"/>
       <c r="C5" s="24"/>
       <c r="D5" s="24"/>
-      <c r="E5" s="37"/>
-      <c r="F5" s="22"/>
-      <c r="G5" s="28"/>
+      <c r="E5" s="7">
+        <v>9999996</v>
+      </c>
+      <c r="F5" s="7">
+        <v>1000421</v>
+      </c>
+      <c r="G5" s="11">
+        <v>120733340001420</v>
+      </c>
       <c r="H5" s="24"/>
       <c r="I5" s="24"/>
       <c r="J5" s="24"/>
@@ -18459,7 +18466,7 @@
         <v>60</v>
       </c>
       <c r="F2" s="7">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G2" s="7">
         <v>5000</v>
@@ -18474,10 +18481,10 @@
         <v>2</v>
       </c>
       <c r="K2" s="7">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L2" s="7">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="M2" s="7" t="s">
         <v>114</v>
@@ -18486,10 +18493,10 @@
         <v>46202558</v>
       </c>
       <c r="O2" s="7">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P2" s="7">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="Q2" s="7" t="s">
         <v>61</v>
@@ -18528,7 +18535,7 @@
         <v>200</v>
       </c>
       <c r="AC2" s="34">
-        <v>10</v>
+        <v>20</v>
       </c>
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.25">
@@ -18695,7 +18702,7 @@
     </row>
     <row r="2" spans="1:19 16384:16384" x14ac:dyDescent="0.25">
       <c r="A2" s="19">
-        <v>321858</v>
+        <v>321865</v>
       </c>
       <c r="B2" s="19">
         <v>90</v>

--- a/Data/ENWR_Creation.xlsx
+++ b/Data/ENWR_Creation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B37A4091-224D-4872-94BA-AC077E43BA92}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D35B331-77A2-4A9A-AD02-330D4EBFE131}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19725" windowHeight="11760" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1013,19 +1013,19 @@
         <v>13</v>
       </c>
       <c r="B2" s="22">
-        <v>5555638</v>
+        <v>5555640</v>
       </c>
       <c r="C2" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="20">
-        <v>100673000000011</v>
-      </c>
-      <c r="E2" s="22">
-        <v>9999996</v>
-      </c>
-      <c r="F2" s="22">
-        <v>1000421</v>
+      <c r="D2" s="11">
+        <v>178888880001601</v>
+      </c>
+      <c r="E2" s="7">
+        <v>8888999</v>
+      </c>
+      <c r="F2" s="7">
+        <v>8888888</v>
       </c>
       <c r="G2" s="22" t="s">
         <v>14</v>
@@ -1034,7 +1034,7 @@
         <v>1</v>
       </c>
       <c r="I2" s="22">
-        <v>900</v>
+        <v>2000</v>
       </c>
       <c r="J2" s="22">
         <v>1.7</v>
@@ -1180,9 +1180,15 @@
       <c r="A6" s="22"/>
       <c r="B6" s="22"/>
       <c r="C6" s="22"/>
-      <c r="D6" s="20"/>
-      <c r="E6" s="22"/>
-      <c r="F6" s="22"/>
+      <c r="D6" s="11">
+        <v>178888880001601</v>
+      </c>
+      <c r="E6" s="7">
+        <v>8888999</v>
+      </c>
+      <c r="F6" s="7">
+        <v>8888888</v>
+      </c>
       <c r="G6" s="22"/>
       <c r="H6" s="22"/>
       <c r="I6" s="22"/>
@@ -1196,9 +1202,15 @@
       <c r="A7" s="22"/>
       <c r="B7" s="22"/>
       <c r="C7" s="22"/>
-      <c r="D7" s="20"/>
-      <c r="E7" s="22"/>
-      <c r="F7" s="22"/>
+      <c r="D7" s="20">
+        <v>100673000000011</v>
+      </c>
+      <c r="E7" s="22">
+        <v>9999996</v>
+      </c>
+      <c r="F7" s="22">
+        <v>1000421</v>
+      </c>
       <c r="G7" s="22"/>
       <c r="H7" s="22"/>
       <c r="I7" s="22"/>
@@ -18282,7 +18294,7 @@
         <v>130009</v>
       </c>
       <c r="K2" s="1">
-        <v>1530</v>
+        <v>3400</v>
       </c>
       <c r="L2" s="1">
         <v>5000</v>
@@ -18336,7 +18348,7 @@
         <v>100</v>
       </c>
       <c r="AC2" s="7">
-        <v>9</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -18702,7 +18714,7 @@
     </row>
     <row r="2" spans="1:19 16384:16384" x14ac:dyDescent="0.25">
       <c r="A2" s="19">
-        <v>321865</v>
+        <v>321867</v>
       </c>
       <c r="B2" s="19">
         <v>90</v>

--- a/Data/ENWR_Creation.xlsx
+++ b/Data/ENWR_Creation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8D35B331-77A2-4A9A-AD02-330D4EBFE131}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFB658CA-18C2-41E1-9CE8-2996AAC823CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19725" windowHeight="11760" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19725" windowHeight="11760" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RP_Deposite_Request_Agriculture" sheetId="1" r:id="rId1"/>
@@ -624,7 +624,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -673,6 +673,9 @@
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -1013,25 +1016,25 @@
         <v>13</v>
       </c>
       <c r="B2" s="22">
-        <v>5555640</v>
+        <v>5555641</v>
       </c>
       <c r="C2" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="11">
-        <v>178888880001601</v>
+      <c r="D2" s="39">
+        <v>102905240000023</v>
       </c>
       <c r="E2" s="7">
-        <v>8888999</v>
+        <v>9997115</v>
       </c>
       <c r="F2" s="7">
-        <v>8888888</v>
+        <v>8211642</v>
       </c>
       <c r="G2" s="22" t="s">
         <v>14</v>
       </c>
       <c r="H2" s="22">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="I2" s="22">
         <v>2000</v>
@@ -17786,7 +17789,7 @@
         <v>70</v>
       </c>
       <c r="B3" s="7">
-        <v>5555552</v>
+        <v>1656503</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>29</v>
@@ -17801,7 +17804,7 @@
         <v>1000421</v>
       </c>
       <c r="G3" s="11">
-        <v>100673000000011</v>
+        <v>120733340001420</v>
       </c>
       <c r="H3" s="7">
         <v>1003</v>
@@ -17810,7 +17813,7 @@
         <v>73</v>
       </c>
       <c r="J3" s="7">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="K3" s="7">
         <v>10</v>
@@ -17819,7 +17822,7 @@
         <v>77</v>
       </c>
       <c r="M3" s="7">
-        <v>50</v>
+        <v>20</v>
       </c>
       <c r="N3" s="7" t="s">
         <v>79</v>
@@ -18297,7 +18300,7 @@
         <v>3400</v>
       </c>
       <c r="L2" s="1">
-        <v>5000</v>
+        <v>4200</v>
       </c>
       <c r="M2" s="1">
         <v>6</v>
@@ -18493,7 +18496,7 @@
         <v>2</v>
       </c>
       <c r="K2" s="7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L2" s="7">
         <v>20</v>
@@ -18505,10 +18508,10 @@
         <v>46202558</v>
       </c>
       <c r="O2" s="7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="P2" s="7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="Q2" s="7" t="s">
         <v>61</v>
@@ -18714,7 +18717,7 @@
     </row>
     <row r="2" spans="1:19 16384:16384" x14ac:dyDescent="0.25">
       <c r="A2" s="19">
-        <v>321867</v>
+        <v>321869</v>
       </c>
       <c r="B2" s="19">
         <v>90</v>

--- a/Data/ENWR_Creation.xlsx
+++ b/Data/ENWR_Creation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AFB658CA-18C2-41E1-9CE8-2996AAC823CF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C265FF7F-BD19-4FC6-9565-2924F5636CD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19725" windowHeight="11760" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19725" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RP_Deposite_Request_Agriculture" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="131">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="132">
   <si>
     <t>commoditySegment</t>
   </si>
@@ -435,6 +435,9 @@
   </si>
   <si>
     <t>ZINCMINI</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Assayer Maker </t>
   </si>
 </sst>
 </file>
@@ -1016,7 +1019,7 @@
         <v>13</v>
       </c>
       <c r="B2" s="22">
-        <v>5555641</v>
+        <v>5555642</v>
       </c>
       <c r="C2" s="22" t="s">
         <v>16</v>
@@ -1034,10 +1037,10 @@
         <v>14</v>
       </c>
       <c r="H2" s="22">
-        <v>6</v>
+        <v>1</v>
       </c>
       <c r="I2" s="22">
-        <v>2000</v>
+        <v>3000</v>
       </c>
       <c r="J2" s="22">
         <v>1.7</v>
@@ -1257,8 +1260,12 @@
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A10" s="22"/>
-      <c r="B10" s="22"/>
-      <c r="C10" s="22"/>
+      <c r="B10" s="22">
+        <v>5555642</v>
+      </c>
+      <c r="C10" s="22" t="s">
+        <v>131</v>
+      </c>
       <c r="D10" s="20"/>
       <c r="E10" s="22"/>
       <c r="F10" s="22"/>
@@ -18297,7 +18304,7 @@
         <v>130009</v>
       </c>
       <c r="K2" s="1">
-        <v>3400</v>
+        <v>5100</v>
       </c>
       <c r="L2" s="1">
         <v>4200</v>
@@ -18351,7 +18358,7 @@
         <v>100</v>
       </c>
       <c r="AC2" s="7">
-        <v>20</v>
+        <v>30</v>
       </c>
     </row>
   </sheetData>
@@ -18717,7 +18724,7 @@
     </row>
     <row r="2" spans="1:19 16384:16384" x14ac:dyDescent="0.25">
       <c r="A2" s="19">
-        <v>321869</v>
+        <v>321870</v>
       </c>
       <c r="B2" s="19">
         <v>90</v>

--- a/Data/ENWR_Creation.xlsx
+++ b/Data/ENWR_Creation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C265FF7F-BD19-4FC6-9565-2924F5636CD0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{769C1F16-30CB-4160-BBDD-5C195596CBA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19725" windowHeight="11760" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19725" windowHeight="11760" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RP_Deposite_Request_Agriculture" sheetId="1" r:id="rId1"/>
@@ -17796,7 +17796,7 @@
         <v>70</v>
       </c>
       <c r="B3" s="7">
-        <v>1656503</v>
+        <v>1656504</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>29</v>
@@ -18724,7 +18724,7 @@
     </row>
     <row r="2" spans="1:19 16384:16384" x14ac:dyDescent="0.25">
       <c r="A2" s="19">
-        <v>321870</v>
+        <v>321871</v>
       </c>
       <c r="B2" s="19">
         <v>90</v>

--- a/Data/ENWR_Creation.xlsx
+++ b/Data/ENWR_Creation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{769C1F16-30CB-4160-BBDD-5C195596CBA1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{359604EF-CEB2-4103-9A1C-269896E2D58D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19725" windowHeight="11760" firstSheet="5" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19725" windowHeight="11760" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RP_Deposite_Request_Agriculture" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="133">
   <si>
     <t>commoditySegment</t>
   </si>
@@ -439,6 +439,9 @@
   <si>
     <t xml:space="preserve">Assayer Maker </t>
   </si>
+  <si>
+    <t>DRUM</t>
+  </si>
 </sst>
 </file>
 
@@ -627,7 +630,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -677,9 +680,9 @@
     <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
+    <xf numFmtId="1" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1015,46 +1018,46 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="22" t="s">
+      <c r="A2" s="1" t="s">
         <v>13</v>
       </c>
       <c r="B2" s="22">
-        <v>5555642</v>
+        <v>4555609</v>
       </c>
       <c r="C2" s="22" t="s">
         <v>16</v>
       </c>
       <c r="D2" s="39">
-        <v>102905240000023</v>
-      </c>
-      <c r="E2" s="7">
-        <v>9997115</v>
-      </c>
-      <c r="F2" s="7">
-        <v>8211642</v>
-      </c>
-      <c r="G2" s="22" t="s">
+        <v>178888880001601</v>
+      </c>
+      <c r="E2" s="40">
+        <v>8888999</v>
+      </c>
+      <c r="F2" s="40">
+        <v>3052022</v>
+      </c>
+      <c r="G2" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="22">
-        <v>1</v>
-      </c>
-      <c r="I2" s="22">
-        <v>3000</v>
-      </c>
-      <c r="J2" s="22">
+      <c r="H2" s="1">
+        <v>947</v>
+      </c>
+      <c r="I2" s="1">
+        <v>5000</v>
+      </c>
+      <c r="J2" s="27">
         <v>1.7</v>
       </c>
-      <c r="K2" s="24" t="s">
-        <v>102</v>
-      </c>
-      <c r="L2" s="22" t="s">
+      <c r="K2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="L2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="M2" s="22" t="s">
+      <c r="M2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="N2" s="22"/>
+      <c r="N2" s="19"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
       <c r="A3" s="22" t="s">
@@ -1588,19 +1591,45 @@
       <c r="N4" s="19"/>
     </row>
     <row r="5" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A5" s="1"/>
-      <c r="B5" s="22"/>
-      <c r="C5" s="2"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
-      <c r="F5" s="1"/>
-      <c r="G5" s="1"/>
-      <c r="H5" s="1"/>
-      <c r="I5" s="27"/>
-      <c r="J5" s="24"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
-      <c r="M5" s="1"/>
+      <c r="A5" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B5" s="22">
+        <v>4555605</v>
+      </c>
+      <c r="C5" s="39">
+        <v>178888880001601</v>
+      </c>
+      <c r="D5" s="40">
+        <v>8888999</v>
+      </c>
+      <c r="E5" s="40">
+        <v>3052022</v>
+      </c>
+      <c r="F5" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G5" s="1">
+        <v>15</v>
+      </c>
+      <c r="H5" s="1">
+        <v>5000</v>
+      </c>
+      <c r="I5" s="27">
+        <v>1.7</v>
+      </c>
+      <c r="J5" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L5" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M5" s="1">
+        <v>11</v>
+      </c>
       <c r="N5" s="19"/>
     </row>
     <row r="6" spans="1:20" x14ac:dyDescent="0.25">
@@ -1608,28 +1637,28 @@
         <v>13</v>
       </c>
       <c r="B6" s="22">
-        <v>1702262</v>
-      </c>
-      <c r="C6" s="2">
-        <v>100673000000011</v>
-      </c>
-      <c r="D6" s="7">
-        <v>9999996</v>
-      </c>
-      <c r="E6" s="7">
-        <v>1000421</v>
+        <v>4555611</v>
+      </c>
+      <c r="C6" s="39">
+        <v>178888880001601</v>
+      </c>
+      <c r="D6" s="40">
+        <v>8888999</v>
+      </c>
+      <c r="E6" s="40">
+        <v>3052022</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>29</v>
       </c>
       <c r="G6" s="1">
-        <v>15</v>
+        <v>947</v>
       </c>
       <c r="H6" s="1">
-        <v>900</v>
-      </c>
-      <c r="I6" s="27">
-        <v>1.7</v>
+        <v>100</v>
+      </c>
+      <c r="I6" s="21">
+        <v>1.8</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>30</v>
@@ -1638,7 +1667,7 @@
         <v>15</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>15</v>
+        <v>132</v>
       </c>
       <c r="M6" s="1">
         <v>11</v>
@@ -1783,6 +1812,25 @@
       <c r="K15" s="1"/>
       <c r="L15" s="1"/>
       <c r="M15" s="1"/>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="G16">
+        <v>100</v>
+      </c>
+      <c r="H16" s="41">
+        <v>1.8</v>
+      </c>
+      <c r="I16">
+        <f>G16*H16</f>
+        <v>180</v>
+      </c>
+      <c r="J16">
+        <v>50</v>
+      </c>
+      <c r="K16">
+        <f>I16/J16</f>
+        <v>3.6</v>
+      </c>
     </row>
     <row r="18" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C18" s="7"/>
@@ -18304,7 +18352,7 @@
         <v>130009</v>
       </c>
       <c r="K2" s="1">
-        <v>5100</v>
+        <v>180</v>
       </c>
       <c r="L2" s="1">
         <v>4200</v>
@@ -18355,10 +18403,10 @@
         <v>10000</v>
       </c>
       <c r="AB2" s="11">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="AC2" s="7">
-        <v>30</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -18724,7 +18772,7 @@
     </row>
     <row r="2" spans="1:19 16384:16384" x14ac:dyDescent="0.25">
       <c r="A2" s="19">
-        <v>321871</v>
+        <v>321875</v>
       </c>
       <c r="B2" s="19">
         <v>90</v>

--- a/Data/ENWR_Creation.xlsx
+++ b/Data/ENWR_Creation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{359604EF-CEB2-4103-9A1C-269896E2D58D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40018AD8-30AA-4357-BEB9-B16E5F5A6E21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19725" windowHeight="11760" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19725" windowHeight="11760" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RP_Deposite_Request_Agriculture" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="258" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="133">
   <si>
     <t>commoditySegment</t>
   </si>
@@ -1022,34 +1022,34 @@
         <v>13</v>
       </c>
       <c r="B2" s="22">
-        <v>4555609</v>
+        <v>4555615</v>
       </c>
       <c r="C2" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="39">
-        <v>178888880001601</v>
-      </c>
-      <c r="E2" s="40">
-        <v>8888999</v>
-      </c>
-      <c r="F2" s="40">
-        <v>3052022</v>
+      <c r="D2" s="20">
+        <v>100673000000011</v>
+      </c>
+      <c r="E2" s="22">
+        <v>9999996</v>
+      </c>
+      <c r="F2" s="22">
+        <v>1000421</v>
       </c>
       <c r="G2" s="1" t="s">
         <v>14</v>
       </c>
       <c r="H2" s="1">
-        <v>947</v>
+        <v>1</v>
       </c>
       <c r="I2" s="1">
-        <v>5000</v>
+        <v>100</v>
       </c>
       <c r="J2" s="27">
         <v>1.7</v>
       </c>
-      <c r="K2" s="1" t="s">
-        <v>30</v>
+      <c r="K2" s="24" t="s">
+        <v>102</v>
       </c>
       <c r="L2" s="1" t="s">
         <v>15</v>
@@ -1240,7 +1240,9 @@
       <c r="H8" s="22"/>
       <c r="I8" s="22"/>
       <c r="J8" s="22"/>
-      <c r="K8" s="24"/>
+      <c r="K8" s="1" t="s">
+        <v>30</v>
+      </c>
       <c r="L8" s="22"/>
       <c r="M8" s="22"/>
       <c r="N8" s="25"/>
@@ -1469,31 +1471,31 @@
         <v>13</v>
       </c>
       <c r="B2" s="22">
-        <v>4555603</v>
-      </c>
-      <c r="C2" s="11">
-        <v>178888880001601</v>
-      </c>
-      <c r="D2" s="7">
-        <v>8888999</v>
-      </c>
-      <c r="E2" s="7">
-        <v>8888888</v>
+        <v>4555701</v>
+      </c>
+      <c r="C2" s="20">
+        <v>100673000000011</v>
+      </c>
+      <c r="D2" s="22">
+        <v>9999996</v>
+      </c>
+      <c r="E2" s="22">
+        <v>1000421</v>
       </c>
       <c r="F2" s="22" t="s">
         <v>29</v>
       </c>
       <c r="G2" s="1">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="H2" s="1">
-        <v>900</v>
+        <v>100</v>
       </c>
       <c r="I2" s="27">
         <v>1.7</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>30</v>
+        <v>102</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>15</v>
@@ -1913,7 +1915,7 @@
     </row>
     <row r="2" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" x14ac:dyDescent="0.25">
       <c r="A2" s="24">
-        <v>5555550</v>
+        <v>5000003</v>
       </c>
       <c r="B2" s="24" t="s">
         <v>93</v>
@@ -17794,12 +17796,12 @@
       </c>
       <c r="O1" s="13"/>
     </row>
-    <row r="2" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
         <v>70</v>
       </c>
       <c r="B2" s="7">
-        <v>1656502</v>
+        <v>1656503</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>29</v>
@@ -17807,14 +17809,14 @@
       <c r="D2" s="7">
         <v>11</v>
       </c>
-      <c r="E2" s="37">
-        <v>8888999</v>
-      </c>
-      <c r="F2" s="38">
-        <v>8888888</v>
-      </c>
-      <c r="G2" s="11">
-        <v>178888880001601</v>
+      <c r="E2" s="22">
+        <v>9999996</v>
+      </c>
+      <c r="F2" s="22">
+        <v>1000421</v>
+      </c>
+      <c r="G2" s="20">
+        <v>100673000000011</v>
       </c>
       <c r="H2" s="7">
         <v>1003</v>
@@ -17973,9 +17975,9 @@
       <c r="D8" s="7"/>
       <c r="E8" s="7"/>
       <c r="F8" s="7"/>
-      <c r="G8" s="11"/>
-      <c r="H8" s="7"/>
-      <c r="I8" s="7"/>
+      <c r="G8" s="20"/>
+      <c r="H8" s="22"/>
+      <c r="I8" s="22"/>
       <c r="J8" s="7"/>
       <c r="K8" s="7"/>
       <c r="L8" s="7"/>
@@ -18328,7 +18330,7 @@
         <v>232324</v>
       </c>
       <c r="C2" s="1">
-        <v>500</v>
+        <v>100</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>59</v>
@@ -18340,7 +18342,7 @@
         <v>973015</v>
       </c>
       <c r="G2" s="1">
-        <v>100007</v>
+        <v>100010</v>
       </c>
       <c r="H2" s="1">
         <v>1000012</v>
@@ -18352,7 +18354,7 @@
         <v>130009</v>
       </c>
       <c r="K2" s="1">
-        <v>180</v>
+        <v>50</v>
       </c>
       <c r="L2" s="1">
         <v>4200</v>
@@ -18772,7 +18774,7 @@
     </row>
     <row r="2" spans="1:19 16384:16384" x14ac:dyDescent="0.25">
       <c r="A2" s="19">
-        <v>321875</v>
+        <v>321879</v>
       </c>
       <c r="B2" s="19">
         <v>90</v>

--- a/Data/ENWR_Creation.xlsx
+++ b/Data/ENWR_Creation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{40018AD8-30AA-4357-BEB9-B16E5F5A6E21}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4E90A33-64D5-44BA-B12A-E0C71FEA75C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19725" windowHeight="11760" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19725" windowHeight="11760" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RP_Deposite_Request_Agriculture" sheetId="1" r:id="rId1"/>
@@ -1471,31 +1471,31 @@
         <v>13</v>
       </c>
       <c r="B2" s="22">
-        <v>4555701</v>
+        <v>4555703</v>
       </c>
       <c r="C2" s="20">
-        <v>100673000000011</v>
+        <v>120484000001272</v>
       </c>
       <c r="D2" s="22">
-        <v>9999996</v>
+        <v>6656413</v>
       </c>
       <c r="E2" s="22">
-        <v>1000421</v>
+        <v>6539191</v>
       </c>
       <c r="F2" s="22" t="s">
         <v>29</v>
       </c>
       <c r="G2" s="1">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="H2" s="1">
-        <v>100</v>
+        <v>2000</v>
       </c>
       <c r="I2" s="27">
         <v>1.7</v>
       </c>
       <c r="J2" s="1" t="s">
-        <v>102</v>
+        <v>30</v>
       </c>
       <c r="K2" s="1" t="s">
         <v>15</v>
@@ -18354,7 +18354,7 @@
         <v>130009</v>
       </c>
       <c r="K2" s="1">
-        <v>50</v>
+        <v>3400</v>
       </c>
       <c r="L2" s="1">
         <v>4200</v>
@@ -18405,10 +18405,10 @@
         <v>10000</v>
       </c>
       <c r="AB2" s="11">
-        <v>2</v>
+        <v>100</v>
       </c>
       <c r="AC2" s="7">
-        <v>50</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -18774,7 +18774,7 @@
     </row>
     <row r="2" spans="1:19 16384:16384" x14ac:dyDescent="0.25">
       <c r="A2" s="19">
-        <v>321879</v>
+        <v>321880</v>
       </c>
       <c r="B2" s="19">
         <v>90</v>

--- a/Data/ENWR_Creation.xlsx
+++ b/Data/ENWR_Creation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D4E90A33-64D5-44BA-B12A-E0C71FEA75C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6A83A3F-0E1A-471A-BD33-3FE3F9261958}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19725" windowHeight="11760" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19770" windowHeight="11760" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RP_Deposite_Request_Agriculture" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="134">
   <si>
     <t>commoditySegment</t>
   </si>
@@ -441,6 +441,9 @@
   </si>
   <si>
     <t>DRUM</t>
+  </si>
+  <si>
+    <t>BPTPT1212N</t>
   </si>
 </sst>
 </file>
@@ -1022,7 +1025,7 @@
         <v>13</v>
       </c>
       <c r="B2" s="22">
-        <v>4555615</v>
+        <v>4555616</v>
       </c>
       <c r="C2" s="22" t="s">
         <v>16</v>
@@ -1043,7 +1046,7 @@
         <v>1</v>
       </c>
       <c r="I2" s="1">
-        <v>100</v>
+        <v>2000</v>
       </c>
       <c r="J2" s="27">
         <v>1.7</v>
@@ -1471,16 +1474,16 @@
         <v>13</v>
       </c>
       <c r="B2" s="22">
-        <v>4555703</v>
+        <v>4555713</v>
       </c>
       <c r="C2" s="20">
-        <v>120484000001272</v>
+        <v>120484000000134</v>
       </c>
       <c r="D2" s="22">
-        <v>6656413</v>
+        <v>9999996</v>
       </c>
       <c r="E2" s="22">
-        <v>6539191</v>
+        <v>1000421</v>
       </c>
       <c r="F2" s="22" t="s">
         <v>29</v>
@@ -1680,8 +1683,12 @@
       <c r="A7" s="1"/>
       <c r="B7" s="22"/>
       <c r="C7" s="2"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="1"/>
+      <c r="D7" s="22">
+        <v>6656413</v>
+      </c>
+      <c r="E7" s="22">
+        <v>6539191</v>
+      </c>
       <c r="F7" s="1"/>
       <c r="G7" s="1"/>
       <c r="H7" s="1"/>
@@ -17801,7 +17808,7 @@
         <v>70</v>
       </c>
       <c r="B2" s="7">
-        <v>1656503</v>
+        <v>1656504</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>29</v>
@@ -17822,10 +17829,10 @@
         <v>1003</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>73</v>
+        <v>130</v>
       </c>
       <c r="J2" s="7">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="K2" s="7">
         <v>10</v>
@@ -17834,7 +17841,7 @@
         <v>77</v>
       </c>
       <c r="M2" s="7">
-        <v>100</v>
+        <v>20</v>
       </c>
       <c r="N2" s="7" t="s">
         <v>79</v>
@@ -18342,7 +18349,7 @@
         <v>973015</v>
       </c>
       <c r="G2" s="1">
-        <v>100010</v>
+        <v>100011</v>
       </c>
       <c r="H2" s="1">
         <v>1000012</v>
@@ -18357,7 +18364,7 @@
         <v>3400</v>
       </c>
       <c r="L2" s="1">
-        <v>4200</v>
+        <v>5000</v>
       </c>
       <c r="M2" s="1">
         <v>6</v>
@@ -18378,7 +18385,7 @@
         <v>63</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>64</v>
+        <v>133</v>
       </c>
       <c r="T2" s="1" t="s">
         <v>65</v>
@@ -18604,7 +18611,7 @@
         <v>179</v>
       </c>
       <c r="AB2" s="7">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="AC2" s="34">
         <v>20</v>
@@ -18774,7 +18781,7 @@
     </row>
     <row r="2" spans="1:19 16384:16384" x14ac:dyDescent="0.25">
       <c r="A2" s="19">
-        <v>321880</v>
+        <v>321884</v>
       </c>
       <c r="B2" s="19">
         <v>90</v>

--- a/Data/ENWR_Creation.xlsx
+++ b/Data/ENWR_Creation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B6A83A3F-0E1A-471A-BD33-3FE3F9261958}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E131951-BCE7-4BB4-9A20-20BEB01CDE51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19770" windowHeight="11760" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19770" windowHeight="11760" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RP_Deposite_Request_Agriculture" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="259" uniqueCount="134">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="121">
   <si>
     <t>commoditySegment</t>
   </si>
@@ -383,10 +383,19 @@
     <t>Status</t>
   </si>
   <si>
+    <t>Phy</t>
+  </si>
+  <si>
+    <t>phy</t>
+  </si>
+  <si>
     <t>place_of_origin</t>
   </si>
   <si>
     <t>ass</t>
+  </si>
+  <si>
+    <t>ALUMINUM</t>
   </si>
   <si>
     <t>Zinc 99</t>
@@ -395,55 +404,7 @@
     <t>Ali 93</t>
   </si>
   <si>
-    <t>Grade</t>
-  </si>
-  <si>
-    <t>Qualification</t>
-  </si>
-  <si>
-    <t>Address1</t>
-  </si>
-  <si>
-    <t>Address2</t>
-  </si>
-  <si>
-    <t>Address3</t>
-  </si>
-  <si>
-    <t>Address4</t>
-  </si>
-  <si>
-    <t>Address5</t>
-  </si>
-  <si>
-    <t>Address6</t>
-  </si>
-  <si>
-    <t>Address7</t>
-  </si>
-  <si>
-    <t>Address8</t>
-  </si>
-  <si>
-    <t>Address9</t>
-  </si>
-  <si>
-    <t>Commodity</t>
-  </si>
-  <si>
-    <t>Rudhra121</t>
-  </si>
-  <si>
-    <t>ZINCMINI</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Assayer Maker </t>
-  </si>
-  <si>
-    <t>DRUM</t>
-  </si>
-  <si>
-    <t>BPTPT1212N</t>
+    <t>hdjh123</t>
   </si>
 </sst>
 </file>
@@ -453,7 +414,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="13" x14ac:knownFonts="1">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -538,14 +499,8 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-      <family val="2"/>
-    </font>
   </fonts>
-  <fills count="5">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -566,12 +521,24 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FF92D050"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="0"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="5">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -605,35 +572,11 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="medium">
-        <color indexed="64"/>
-      </left>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="42">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -660,32 +603,25 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="1" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="12" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1021,382 +957,676 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="1" t="s">
+      <c r="A2" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="22">
-        <v>4555616</v>
-      </c>
-      <c r="C2" s="22" t="s">
+      <c r="B2" s="27">
+        <v>5555628</v>
+      </c>
+      <c r="C2" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="20">
+      <c r="D2" s="23">
         <v>100673000000011</v>
       </c>
-      <c r="E2" s="22">
+      <c r="E2" s="27">
         <v>9999996</v>
       </c>
-      <c r="F2" s="22">
+      <c r="F2" s="27">
         <v>1000421</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="1">
+      <c r="H2" s="27">
         <v>1</v>
       </c>
-      <c r="I2" s="1">
-        <v>2000</v>
+      <c r="I2" s="27">
+        <v>700</v>
       </c>
       <c r="J2" s="27">
         <v>1.7</v>
       </c>
-      <c r="K2" s="24" t="s">
+      <c r="K2" s="29" t="s">
         <v>102</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="M2" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="N2" s="19"/>
+      <c r="N2" s="27"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="22" t="s">
+      <c r="A3" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="22">
+      <c r="B3" s="27">
         <v>5555614</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="20">
+      <c r="D3" s="23">
         <v>155000010000761</v>
       </c>
-      <c r="E3" s="22">
+      <c r="E3" s="27">
         <v>9996059</v>
       </c>
-      <c r="F3" s="22">
+      <c r="F3" s="27">
         <v>5750013</v>
       </c>
-      <c r="G3" s="22" t="s">
+      <c r="G3" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="22">
+      <c r="H3" s="27">
         <v>6</v>
       </c>
-      <c r="I3" s="22">
+      <c r="I3" s="27">
         <v>5000</v>
       </c>
-      <c r="J3" s="22">
+      <c r="J3" s="27">
         <v>0.5</v>
       </c>
-      <c r="K3" s="24" t="s">
+      <c r="K3" s="29" t="s">
         <v>102</v>
       </c>
-      <c r="L3" s="22" t="s">
+      <c r="L3" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="M3" s="22" t="s">
+      <c r="M3" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="N3" s="22"/>
+      <c r="N3" s="27"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="22" t="s">
+      <c r="A4" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="22">
+      <c r="B4" s="27">
         <v>5555615</v>
       </c>
-      <c r="C4" s="22" t="s">
+      <c r="C4" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="20">
-        <v>100673000000011</v>
-      </c>
-      <c r="E4" s="22">
-        <v>9999996</v>
-      </c>
-      <c r="F4" s="22">
-        <v>1000421</v>
-      </c>
-      <c r="G4" s="22" t="s">
+      <c r="D4" s="23">
+        <v>155000010000761</v>
+      </c>
+      <c r="E4" s="27">
+        <v>9996059</v>
+      </c>
+      <c r="F4" s="27">
+        <v>5750013</v>
+      </c>
+      <c r="G4" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="22">
+      <c r="H4" s="27">
         <v>6</v>
       </c>
-      <c r="I4" s="22">
+      <c r="I4" s="27">
         <v>5000</v>
       </c>
-      <c r="J4" s="22">
+      <c r="J4" s="27">
         <v>1.7</v>
       </c>
-      <c r="K4" s="24" t="s">
+      <c r="K4" s="29" t="s">
         <v>102</v>
       </c>
-      <c r="L4" s="22" t="s">
+      <c r="L4" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="M4" s="22" t="s">
+      <c r="M4" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="N4" s="22"/>
+      <c r="N4" s="27"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="22" t="s">
+      <c r="A5" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="22">
+      <c r="B5" s="27">
         <v>5555616</v>
       </c>
-      <c r="C5" s="22" t="s">
+      <c r="C5" s="27" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="20">
-        <v>100673001212128</v>
-      </c>
-      <c r="E5" s="22">
+      <c r="D5" s="23">
+        <v>155000010000761</v>
+      </c>
+      <c r="E5" s="27">
         <v>9999996</v>
       </c>
-      <c r="F5" s="22">
+      <c r="F5" s="27">
         <v>1000421</v>
       </c>
-      <c r="G5" s="22" t="s">
+      <c r="G5" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="22">
+      <c r="H5" s="27">
         <v>1</v>
       </c>
-      <c r="I5" s="22">
+      <c r="I5" s="27">
         <v>500</v>
       </c>
-      <c r="J5" s="22">
+      <c r="J5" s="27">
         <v>1.7</v>
       </c>
-      <c r="K5" s="24" t="s">
+      <c r="K5" s="29" t="s">
         <v>102</v>
       </c>
-      <c r="L5" s="22" t="s">
+      <c r="L5" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="M5" s="22" t="s">
+      <c r="M5" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="N5" s="22"/>
+      <c r="N5" s="27"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="22"/>
-      <c r="B6" s="22"/>
-      <c r="C6" s="22"/>
-      <c r="D6" s="11">
-        <v>178888880001601</v>
-      </c>
-      <c r="E6" s="7">
-        <v>8888999</v>
-      </c>
-      <c r="F6" s="7">
-        <v>8888888</v>
-      </c>
-      <c r="G6" s="22"/>
-      <c r="H6" s="22"/>
-      <c r="I6" s="22"/>
-      <c r="J6" s="22"/>
-      <c r="K6" s="24"/>
-      <c r="L6" s="22"/>
-      <c r="M6" s="22"/>
-      <c r="N6" s="22"/>
+      <c r="A6" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="B6" s="27">
+        <v>5555617</v>
+      </c>
+      <c r="C6" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="D6" s="23">
+        <v>100673000000011</v>
+      </c>
+      <c r="E6" s="27">
+        <v>9999996</v>
+      </c>
+      <c r="F6" s="27">
+        <v>1000421</v>
+      </c>
+      <c r="G6" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="H6" s="27">
+        <v>1</v>
+      </c>
+      <c r="I6" s="27">
+        <v>700</v>
+      </c>
+      <c r="J6" s="27">
+        <v>1.7</v>
+      </c>
+      <c r="K6" s="29" t="s">
+        <v>102</v>
+      </c>
+      <c r="L6" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="M6" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="N6" s="27"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="22"/>
-      <c r="B7" s="22"/>
-      <c r="C7" s="22"/>
-      <c r="D7" s="20">
+      <c r="A7" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="27">
+        <v>5555618</v>
+      </c>
+      <c r="C7" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="D7" s="23">
         <v>100673000000011</v>
       </c>
-      <c r="E7" s="22">
+      <c r="E7" s="27">
         <v>9999996</v>
       </c>
-      <c r="F7" s="22">
+      <c r="F7" s="27">
         <v>1000421</v>
       </c>
-      <c r="G7" s="22"/>
-      <c r="H7" s="22"/>
-      <c r="I7" s="22"/>
-      <c r="J7" s="22"/>
-      <c r="K7" s="24"/>
-      <c r="L7" s="22"/>
-      <c r="M7" s="22"/>
-      <c r="N7" s="25"/>
+      <c r="G7" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="H7" s="27">
+        <v>1</v>
+      </c>
+      <c r="I7" s="27">
+        <v>500</v>
+      </c>
+      <c r="J7" s="27">
+        <v>1.7</v>
+      </c>
+      <c r="K7" s="29" t="s">
+        <v>102</v>
+      </c>
+      <c r="L7" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="M7" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="N7" s="30"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="22"/>
-      <c r="B8" s="22"/>
-      <c r="C8" s="22"/>
-      <c r="D8" s="20"/>
-      <c r="E8" s="22"/>
-      <c r="F8" s="22"/>
-      <c r="G8" s="22"/>
-      <c r="H8" s="22"/>
-      <c r="I8" s="22"/>
-      <c r="J8" s="22"/>
-      <c r="K8" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="L8" s="22"/>
-      <c r="M8" s="22"/>
-      <c r="N8" s="25"/>
+      <c r="A8" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="27">
+        <v>5555619</v>
+      </c>
+      <c r="C8" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="D8" s="23">
+        <v>100673000000011</v>
+      </c>
+      <c r="E8" s="27">
+        <v>9999996</v>
+      </c>
+      <c r="F8" s="27">
+        <v>1000421</v>
+      </c>
+      <c r="G8" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="H8" s="27">
+        <v>1</v>
+      </c>
+      <c r="I8" s="27">
+        <v>700</v>
+      </c>
+      <c r="J8" s="27">
+        <v>1.7</v>
+      </c>
+      <c r="K8" s="29" t="s">
+        <v>102</v>
+      </c>
+      <c r="L8" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="M8" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="N8" s="30"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="22"/>
-      <c r="B9" s="22"/>
-      <c r="C9" s="22"/>
-      <c r="D9" s="20"/>
-      <c r="E9" s="22"/>
-      <c r="F9" s="22"/>
-      <c r="G9" s="22"/>
-      <c r="H9" s="22"/>
-      <c r="I9" s="22"/>
-      <c r="J9" s="22"/>
-      <c r="K9" s="24"/>
-      <c r="L9" s="22"/>
-      <c r="M9" s="22"/>
-      <c r="N9" s="25"/>
+      <c r="A9" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="27">
+        <v>5555620</v>
+      </c>
+      <c r="C9" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="D9" s="23">
+        <v>100673000000011</v>
+      </c>
+      <c r="E9" s="27">
+        <v>9999996</v>
+      </c>
+      <c r="F9" s="27">
+        <v>1000421</v>
+      </c>
+      <c r="G9" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="H9" s="27">
+        <v>1</v>
+      </c>
+      <c r="I9" s="27">
+        <v>500</v>
+      </c>
+      <c r="J9" s="27">
+        <v>1.7</v>
+      </c>
+      <c r="K9" s="29" t="s">
+        <v>102</v>
+      </c>
+      <c r="L9" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="M9" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="N9" s="30"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="22"/>
-      <c r="B10" s="22">
-        <v>5555642</v>
-      </c>
-      <c r="C10" s="22" t="s">
-        <v>131</v>
-      </c>
-      <c r="D10" s="20"/>
-      <c r="E10" s="22"/>
-      <c r="F10" s="22"/>
-      <c r="G10" s="22"/>
-      <c r="H10" s="22"/>
-      <c r="I10" s="22"/>
-      <c r="J10" s="22"/>
-      <c r="K10" s="24"/>
-      <c r="L10" s="22"/>
-      <c r="M10" s="22"/>
-      <c r="N10" s="25"/>
+      <c r="A10" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="27">
+        <v>5555621</v>
+      </c>
+      <c r="C10" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="D10" s="23">
+        <v>100673000000011</v>
+      </c>
+      <c r="E10" s="27">
+        <v>9999996</v>
+      </c>
+      <c r="F10" s="27">
+        <v>1000421</v>
+      </c>
+      <c r="G10" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="H10" s="27">
+        <v>15</v>
+      </c>
+      <c r="I10" s="27">
+        <v>700</v>
+      </c>
+      <c r="J10" s="27">
+        <v>1.7</v>
+      </c>
+      <c r="K10" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="L10" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="M10" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="N10" s="30"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="22"/>
-      <c r="B11" s="22"/>
-      <c r="C11" s="22"/>
-      <c r="D11" s="20"/>
-      <c r="E11" s="22"/>
-      <c r="F11" s="22"/>
-      <c r="G11" s="22"/>
-      <c r="H11" s="22"/>
-      <c r="I11" s="22"/>
-      <c r="J11" s="22"/>
-      <c r="K11" s="24"/>
-      <c r="L11" s="22"/>
-      <c r="M11" s="22"/>
-      <c r="N11" s="25"/>
+      <c r="A11" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="27">
+        <v>5555622</v>
+      </c>
+      <c r="C11" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="D11" s="23">
+        <v>100673000000011</v>
+      </c>
+      <c r="E11" s="27">
+        <v>9999996</v>
+      </c>
+      <c r="F11" s="27">
+        <v>1000421</v>
+      </c>
+      <c r="G11" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="H11" s="27">
+        <v>1</v>
+      </c>
+      <c r="I11" s="27">
+        <v>500</v>
+      </c>
+      <c r="J11" s="27">
+        <v>1.7</v>
+      </c>
+      <c r="K11" s="29" t="s">
+        <v>102</v>
+      </c>
+      <c r="L11" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="M11" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="N11" s="30"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="22"/>
-      <c r="B12" s="22"/>
-      <c r="C12" s="22"/>
-      <c r="D12" s="20"/>
-      <c r="E12" s="22"/>
-      <c r="F12" s="22"/>
-      <c r="G12" s="22"/>
-      <c r="H12" s="22"/>
-      <c r="I12" s="22"/>
-      <c r="J12" s="22"/>
-      <c r="K12" s="24"/>
-      <c r="L12" s="22"/>
-      <c r="M12" s="22"/>
-      <c r="N12" s="25"/>
+      <c r="A12" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="27">
+        <v>5555623</v>
+      </c>
+      <c r="C12" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="D12" s="23">
+        <v>100673000000011</v>
+      </c>
+      <c r="E12" s="27">
+        <v>9999996</v>
+      </c>
+      <c r="F12" s="27">
+        <v>1000421</v>
+      </c>
+      <c r="G12" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="H12" s="27">
+        <v>1</v>
+      </c>
+      <c r="I12" s="27">
+        <v>700</v>
+      </c>
+      <c r="J12" s="27">
+        <v>1.7</v>
+      </c>
+      <c r="K12" s="29" t="s">
+        <v>102</v>
+      </c>
+      <c r="L12" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="M12" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="N12" s="30"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="22"/>
-      <c r="B13" s="22"/>
-      <c r="C13" s="22"/>
-      <c r="D13" s="20"/>
-      <c r="E13" s="22"/>
-      <c r="F13" s="22"/>
-      <c r="G13" s="22"/>
-      <c r="H13" s="22"/>
-      <c r="I13" s="22"/>
-      <c r="J13" s="22"/>
-      <c r="K13" s="24"/>
-      <c r="L13" s="22"/>
-      <c r="M13" s="22"/>
-      <c r="N13" s="25"/>
+      <c r="A13" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="27">
+        <v>5555624</v>
+      </c>
+      <c r="C13" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="D13" s="23">
+        <v>100673000000011</v>
+      </c>
+      <c r="E13" s="27">
+        <v>9999996</v>
+      </c>
+      <c r="F13" s="27">
+        <v>1000421</v>
+      </c>
+      <c r="G13" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="H13" s="27">
+        <v>1</v>
+      </c>
+      <c r="I13" s="27">
+        <v>100</v>
+      </c>
+      <c r="J13" s="27">
+        <v>1.7</v>
+      </c>
+      <c r="K13" s="29" t="s">
+        <v>102</v>
+      </c>
+      <c r="L13" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="M13" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="N13" s="30"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="22"/>
-      <c r="B14" s="22"/>
-      <c r="C14" s="22"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="22"/>
-      <c r="G14" s="22"/>
-      <c r="H14" s="22"/>
-      <c r="I14" s="22"/>
-      <c r="J14" s="22"/>
-      <c r="K14" s="24"/>
-      <c r="L14" s="22"/>
-      <c r="M14" s="22"/>
-      <c r="N14" s="25"/>
+      <c r="A14" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="27">
+        <v>5555625</v>
+      </c>
+      <c r="C14" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="D14" s="23">
+        <v>100673000000011</v>
+      </c>
+      <c r="E14" s="27">
+        <v>9999996</v>
+      </c>
+      <c r="F14" s="27">
+        <v>1000421</v>
+      </c>
+      <c r="G14" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="H14" s="27">
+        <v>1</v>
+      </c>
+      <c r="I14" s="27">
+        <v>700</v>
+      </c>
+      <c r="J14" s="27">
+        <v>1.7</v>
+      </c>
+      <c r="K14" s="29" t="s">
+        <v>102</v>
+      </c>
+      <c r="L14" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="M14" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="N14" s="30"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="22"/>
-      <c r="B15" s="22"/>
-      <c r="C15" s="22"/>
-      <c r="D15" s="20"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="22"/>
-      <c r="G15" s="22"/>
-      <c r="H15" s="22"/>
-      <c r="I15" s="22"/>
-      <c r="J15" s="21"/>
-      <c r="K15" s="24"/>
-      <c r="L15" s="22"/>
-      <c r="M15" s="22"/>
-      <c r="N15" s="26"/>
+      <c r="A15" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="27">
+        <v>5555626</v>
+      </c>
+      <c r="C15" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="D15" s="23">
+        <v>178888880001601</v>
+      </c>
+      <c r="E15" s="27">
+        <v>9999996</v>
+      </c>
+      <c r="F15" s="27">
+        <v>1000421</v>
+      </c>
+      <c r="G15" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="H15" s="27">
+        <v>1</v>
+      </c>
+      <c r="I15" s="27">
+        <v>2000</v>
+      </c>
+      <c r="J15" s="26">
+        <v>1</v>
+      </c>
+      <c r="K15" s="29" t="s">
+        <v>102</v>
+      </c>
+      <c r="L15" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="M15" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="N15" s="31"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="22"/>
-      <c r="B16" s="22"/>
-      <c r="C16" s="22"/>
-      <c r="D16" s="20"/>
-      <c r="E16" s="22"/>
-      <c r="F16" s="22"/>
-      <c r="G16" s="22"/>
-      <c r="H16" s="22"/>
-      <c r="I16" s="22"/>
-      <c r="J16" s="21"/>
-      <c r="K16" s="24"/>
-      <c r="L16" s="22"/>
-      <c r="M16" s="22"/>
-      <c r="N16" s="26"/>
+      <c r="A16" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="B16" s="27">
+        <v>5555627</v>
+      </c>
+      <c r="C16" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="D16" s="23">
+        <v>100673001212128</v>
+      </c>
+      <c r="E16" s="27">
+        <v>9999996</v>
+      </c>
+      <c r="F16" s="27">
+        <v>1000421</v>
+      </c>
+      <c r="G16" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="H16" s="27">
+        <v>6</v>
+      </c>
+      <c r="I16" s="27">
+        <v>2000</v>
+      </c>
+      <c r="J16" s="26">
+        <v>1</v>
+      </c>
+      <c r="K16" s="29" t="s">
+        <v>102</v>
+      </c>
+      <c r="L16" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="M16" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="N16" s="31"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="22"/>
-      <c r="B17" s="22"/>
-      <c r="C17" s="22"/>
-      <c r="D17" s="20"/>
-      <c r="E17" s="22"/>
-      <c r="F17" s="22"/>
-      <c r="G17" s="22"/>
-      <c r="H17" s="22"/>
-      <c r="I17" s="22"/>
-      <c r="J17" s="22"/>
-      <c r="K17" s="24"/>
-      <c r="L17" s="22"/>
-      <c r="M17" s="22"/>
-      <c r="N17" s="26"/>
+      <c r="A17" s="27" t="s">
+        <v>13</v>
+      </c>
+      <c r="B17" s="27">
+        <v>5555628</v>
+      </c>
+      <c r="C17" s="27" t="s">
+        <v>16</v>
+      </c>
+      <c r="D17" s="23">
+        <v>100673001212128</v>
+      </c>
+      <c r="E17" s="27">
+        <v>9999996</v>
+      </c>
+      <c r="F17" s="27">
+        <v>1000421</v>
+      </c>
+      <c r="G17" s="27" t="s">
+        <v>14</v>
+      </c>
+      <c r="H17" s="27">
+        <v>1</v>
+      </c>
+      <c r="I17" s="27">
+        <v>100</v>
+      </c>
+      <c r="J17" s="27">
+        <v>1.7</v>
+      </c>
+      <c r="K17" s="29" t="s">
+        <v>102</v>
+      </c>
+      <c r="L17" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="M17" s="27" t="s">
+        <v>15</v>
+      </c>
+      <c r="N17" s="31"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1410,7 +1640,7 @@
   <cols>
     <col min="1" max="1" width="18.28515625" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13.28515625" customWidth="1"/>
-    <col min="6" max="6" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="13.7109375" customWidth="1"/>
     <col min="7" max="7" width="15.28515625" customWidth="1"/>
     <col min="8" max="8" width="8.85546875" customWidth="1"/>
     <col min="9" max="9" width="10.85546875" customWidth="1"/>
@@ -1469,47 +1699,47 @@
       <c r="S1" s="3"/>
       <c r="T1" s="3"/>
     </row>
-    <row r="2" spans="1:20" s="26" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="22" t="s">
+    <row r="2" spans="1:20" s="31" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="22">
-        <v>4555713</v>
-      </c>
-      <c r="C2" s="20">
-        <v>120484000000134</v>
-      </c>
-      <c r="D2" s="22">
+      <c r="B2" s="27">
+        <v>4555525</v>
+      </c>
+      <c r="C2" s="11">
+        <v>120733340001685</v>
+      </c>
+      <c r="D2" s="7">
         <v>9999996</v>
       </c>
-      <c r="E2" s="22">
+      <c r="E2" s="7">
         <v>1000421</v>
       </c>
-      <c r="F2" s="22" t="s">
+      <c r="F2" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="G2" s="1">
+      <c r="G2" s="27">
         <v>15</v>
       </c>
-      <c r="H2" s="1">
+      <c r="H2" s="27">
         <v>2000</v>
       </c>
-      <c r="I2" s="27">
+      <c r="I2" s="32">
         <v>1.7</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" s="27" t="s">
         <v>15</v>
       </c>
-      <c r="M2" s="22">
+      <c r="M2" s="27">
         <v>11</v>
       </c>
-      <c r="N2" s="25"/>
+      <c r="N2" s="30"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -1519,13 +1749,13 @@
         <v>4555514</v>
       </c>
       <c r="C3" s="2">
-        <v>100673000000011</v>
-      </c>
-      <c r="D3" s="1">
-        <v>9997115</v>
-      </c>
-      <c r="E3" s="1">
-        <v>8211642</v>
+        <v>120733340001420</v>
+      </c>
+      <c r="D3" s="27">
+        <v>9999996</v>
+      </c>
+      <c r="E3" s="27">
+        <v>1000421</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>29</v>
@@ -1536,7 +1766,7 @@
       <c r="H3" s="1">
         <v>700</v>
       </c>
-      <c r="I3" s="27">
+      <c r="I3" s="32">
         <v>1.7</v>
       </c>
       <c r="J3" s="1" t="s">
@@ -1557,16 +1787,16 @@
       <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="22">
-        <v>4555604</v>
-      </c>
-      <c r="C4" s="20">
+      <c r="B4" s="27">
+        <v>4555517</v>
+      </c>
+      <c r="C4" s="23">
         <v>100673000000011</v>
       </c>
-      <c r="D4" s="22">
+      <c r="D4" s="27">
         <v>9999996</v>
       </c>
-      <c r="E4" s="22">
+      <c r="E4" s="27">
         <v>1000421</v>
       </c>
       <c r="F4" s="1" t="s">
@@ -1576,9 +1806,9 @@
         <v>15</v>
       </c>
       <c r="H4" s="1">
-        <v>900</v>
-      </c>
-      <c r="I4" s="27">
+        <v>700</v>
+      </c>
+      <c r="I4" s="32">
         <v>1.7</v>
       </c>
       <c r="J4" s="1" t="s">
@@ -1599,32 +1829,32 @@
       <c r="A5" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="22">
-        <v>4555605</v>
-      </c>
-      <c r="C5" s="39">
-        <v>178888880001601</v>
-      </c>
-      <c r="D5" s="40">
-        <v>8888999</v>
-      </c>
-      <c r="E5" s="40">
-        <v>3052022</v>
+      <c r="B5" s="27">
+        <v>4555519</v>
+      </c>
+      <c r="C5" s="2">
+        <v>100673000000011</v>
+      </c>
+      <c r="D5" s="27">
+        <v>9999996</v>
+      </c>
+      <c r="E5" s="27">
+        <v>1000421</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>29</v>
       </c>
       <c r="G5" s="1">
-        <v>15</v>
+        <v>1</v>
       </c>
       <c r="H5" s="1">
-        <v>5000</v>
-      </c>
-      <c r="I5" s="27">
+        <v>100</v>
+      </c>
+      <c r="I5" s="32">
         <v>1.7</v>
       </c>
-      <c r="J5" s="1" t="s">
-        <v>30</v>
+      <c r="J5" s="29" t="s">
+        <v>102</v>
       </c>
       <c r="K5" s="1" t="s">
         <v>15</v>
@@ -1641,29 +1871,29 @@
       <c r="A6" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="22">
-        <v>4555611</v>
-      </c>
-      <c r="C6" s="39">
-        <v>178888880001601</v>
-      </c>
-      <c r="D6" s="40">
-        <v>8888999</v>
-      </c>
-      <c r="E6" s="40">
-        <v>3052022</v>
+      <c r="B6" s="27">
+        <v>4555520</v>
+      </c>
+      <c r="C6" s="2">
+        <v>100673000000011</v>
+      </c>
+      <c r="D6" s="1">
+        <v>9997115</v>
+      </c>
+      <c r="E6" s="1">
+        <v>8211642</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>29</v>
       </c>
       <c r="G6" s="1">
-        <v>947</v>
+        <v>15</v>
       </c>
       <c r="H6" s="1">
-        <v>100</v>
-      </c>
-      <c r="I6" s="21">
-        <v>1.8</v>
+        <v>700</v>
+      </c>
+      <c r="I6" s="32">
+        <v>1.7</v>
       </c>
       <c r="J6" s="1" t="s">
         <v>30</v>
@@ -1672,7 +1902,7 @@
         <v>15</v>
       </c>
       <c r="L6" s="1" t="s">
-        <v>132</v>
+        <v>15</v>
       </c>
       <c r="M6" s="1">
         <v>11</v>
@@ -1680,165 +1910,376 @@
       <c r="N6" s="19"/>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A7" s="1"/>
-      <c r="B7" s="22"/>
-      <c r="C7" s="2"/>
-      <c r="D7" s="22">
-        <v>6656413</v>
-      </c>
-      <c r="E7" s="22">
-        <v>6539191</v>
-      </c>
-      <c r="F7" s="1"/>
-      <c r="G7" s="1"/>
-      <c r="H7" s="1"/>
-      <c r="I7" s="27"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="1"/>
-      <c r="L7" s="1"/>
-      <c r="M7" s="1"/>
+      <c r="A7" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7" s="27">
+        <v>4555522</v>
+      </c>
+      <c r="C7" s="2">
+        <v>100673000000011</v>
+      </c>
+      <c r="D7" s="1">
+        <v>9997115</v>
+      </c>
+      <c r="E7" s="1">
+        <v>8211642</v>
+      </c>
+      <c r="F7" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G7" s="1">
+        <v>15</v>
+      </c>
+      <c r="H7" s="1">
+        <v>500</v>
+      </c>
+      <c r="I7" s="32">
+        <v>1.7</v>
+      </c>
+      <c r="J7" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L7" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M7" s="1">
+        <v>11</v>
+      </c>
       <c r="N7" s="19"/>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A8" s="1"/>
-      <c r="B8" s="22"/>
-      <c r="C8" s="2"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="1"/>
-      <c r="F8" s="1"/>
-      <c r="G8" s="1"/>
-      <c r="H8" s="1"/>
-      <c r="I8" s="27"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="1"/>
-      <c r="M8" s="1"/>
+      <c r="A8" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B8" s="27">
+        <v>4555524</v>
+      </c>
+      <c r="C8" s="2">
+        <v>100673000000011</v>
+      </c>
+      <c r="D8" s="1">
+        <v>9997115</v>
+      </c>
+      <c r="E8" s="1">
+        <v>8211642</v>
+      </c>
+      <c r="F8" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G8" s="1">
+        <v>15</v>
+      </c>
+      <c r="H8" s="1">
+        <v>700</v>
+      </c>
+      <c r="I8" s="32">
+        <v>1.7</v>
+      </c>
+      <c r="J8" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L8" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M8" s="1">
+        <v>11</v>
+      </c>
       <c r="N8" s="19"/>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A9" s="1"/>
-      <c r="B9" s="22"/>
-      <c r="C9" s="2"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="1"/>
-      <c r="F9" s="1"/>
-      <c r="G9" s="1"/>
-      <c r="H9" s="1"/>
-      <c r="I9" s="27"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="1"/>
-      <c r="M9" s="1"/>
+      <c r="A9" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B9" s="27">
+        <v>4555526</v>
+      </c>
+      <c r="C9" s="2">
+        <v>100673000000011</v>
+      </c>
+      <c r="D9" s="1">
+        <v>9997115</v>
+      </c>
+      <c r="E9" s="1">
+        <v>8211642</v>
+      </c>
+      <c r="F9" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G9" s="1">
+        <v>15</v>
+      </c>
+      <c r="H9" s="1">
+        <v>700</v>
+      </c>
+      <c r="I9" s="32">
+        <v>1.7</v>
+      </c>
+      <c r="J9" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L9" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M9" s="1">
+        <v>11</v>
+      </c>
       <c r="N9" s="19"/>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A10" s="1"/>
-      <c r="B10" s="22"/>
-      <c r="C10" s="2"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="1"/>
-      <c r="F10" s="1"/>
-      <c r="G10" s="1"/>
-      <c r="H10" s="1"/>
-      <c r="I10" s="27"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="1"/>
-      <c r="M10" s="1"/>
+      <c r="A10" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B10" s="27">
+        <v>4555528</v>
+      </c>
+      <c r="C10" s="2">
+        <v>100673000000011</v>
+      </c>
+      <c r="D10" s="1">
+        <v>9997115</v>
+      </c>
+      <c r="E10" s="1">
+        <v>8211642</v>
+      </c>
+      <c r="F10" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G10" s="1">
+        <v>15</v>
+      </c>
+      <c r="H10" s="1">
+        <v>700</v>
+      </c>
+      <c r="I10" s="32">
+        <v>1.7</v>
+      </c>
+      <c r="J10" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L10" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M10" s="1">
+        <v>11</v>
+      </c>
       <c r="N10" s="19"/>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A11" s="1"/>
-      <c r="B11" s="22"/>
-      <c r="C11" s="2"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="1"/>
-      <c r="F11" s="1"/>
-      <c r="G11" s="1"/>
-      <c r="H11" s="1"/>
-      <c r="I11" s="27"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="1"/>
-      <c r="M11" s="1"/>
+      <c r="A11" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B11" s="27">
+        <v>4555530</v>
+      </c>
+      <c r="C11" s="2">
+        <v>100673000000011</v>
+      </c>
+      <c r="D11" s="1">
+        <v>9997115</v>
+      </c>
+      <c r="E11" s="1">
+        <v>8211642</v>
+      </c>
+      <c r="F11" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G11" s="1">
+        <v>15</v>
+      </c>
+      <c r="H11" s="1">
+        <v>100</v>
+      </c>
+      <c r="I11" s="32">
+        <v>1.7</v>
+      </c>
+      <c r="J11" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L11" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M11" s="1">
+        <v>11</v>
+      </c>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A12" s="1"/>
-      <c r="B12" s="22"/>
-      <c r="C12" s="2"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="1"/>
-      <c r="F12" s="1"/>
-      <c r="G12" s="1"/>
-      <c r="H12" s="1"/>
-      <c r="I12" s="27"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="1"/>
-      <c r="L12" s="1"/>
-      <c r="M12" s="1"/>
+      <c r="A12" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B12" s="27">
+        <v>4555532</v>
+      </c>
+      <c r="C12" s="2">
+        <v>100673000000011</v>
+      </c>
+      <c r="D12" s="1">
+        <v>9997115</v>
+      </c>
+      <c r="E12" s="1">
+        <v>8211642</v>
+      </c>
+      <c r="F12" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G12" s="1">
+        <v>15</v>
+      </c>
+      <c r="H12" s="1">
+        <v>100</v>
+      </c>
+      <c r="I12" s="32">
+        <v>1.7</v>
+      </c>
+      <c r="J12" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L12" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M12" s="1">
+        <v>11</v>
+      </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A13" s="1"/>
-      <c r="B13" s="22"/>
-      <c r="C13" s="2"/>
-      <c r="D13" s="22"/>
-      <c r="E13" s="22"/>
-      <c r="F13" s="1"/>
-      <c r="G13" s="1"/>
-      <c r="H13" s="1"/>
-      <c r="I13" s="27"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="1"/>
-      <c r="L13" s="1"/>
-      <c r="M13" s="1"/>
+      <c r="A13" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B13" s="27">
+        <v>4555534</v>
+      </c>
+      <c r="C13" s="2">
+        <v>120733340001420</v>
+      </c>
+      <c r="D13" s="27">
+        <v>9999996</v>
+      </c>
+      <c r="E13" s="27">
+        <v>1000421</v>
+      </c>
+      <c r="F13" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G13" s="1">
+        <v>15</v>
+      </c>
+      <c r="H13" s="1">
+        <v>700</v>
+      </c>
+      <c r="I13" s="32">
+        <v>1.7</v>
+      </c>
+      <c r="J13" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L13" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M13" s="1">
+        <v>11</v>
+      </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A14" s="1"/>
-      <c r="B14" s="22"/>
-      <c r="C14" s="2"/>
-      <c r="D14" s="22"/>
-      <c r="E14" s="22"/>
-      <c r="F14" s="1"/>
-      <c r="G14" s="1"/>
-      <c r="H14" s="1"/>
-      <c r="I14" s="27"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="1"/>
-      <c r="L14" s="1"/>
-      <c r="M14" s="1"/>
+      <c r="A14" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B14" s="27">
+        <v>4555536</v>
+      </c>
+      <c r="C14" s="2">
+        <v>120733340001420</v>
+      </c>
+      <c r="D14" s="27">
+        <v>9999996</v>
+      </c>
+      <c r="E14" s="27">
+        <v>1000421</v>
+      </c>
+      <c r="F14" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G14" s="1">
+        <v>15</v>
+      </c>
+      <c r="H14" s="1">
+        <v>700</v>
+      </c>
+      <c r="I14" s="32">
+        <v>1.7</v>
+      </c>
+      <c r="J14" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L14" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M14" s="1">
+        <v>11</v>
+      </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A15" s="1"/>
-      <c r="B15" s="22"/>
-      <c r="C15" s="2"/>
-      <c r="D15" s="22"/>
-      <c r="E15" s="22"/>
-      <c r="F15" s="1"/>
-      <c r="G15" s="1"/>
-      <c r="H15" s="1"/>
-      <c r="I15" s="27"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="1"/>
-      <c r="L15" s="1"/>
-      <c r="M15" s="1"/>
-    </row>
-    <row r="16" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="G16">
-        <v>100</v>
-      </c>
-      <c r="H16" s="41">
-        <v>1.8</v>
-      </c>
-      <c r="I16">
-        <f>G16*H16</f>
-        <v>180</v>
-      </c>
-      <c r="J16">
-        <v>50</v>
-      </c>
-      <c r="K16">
-        <f>I16/J16</f>
-        <v>3.6</v>
+      <c r="A15" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="B15" s="27">
+        <v>4555538</v>
+      </c>
+      <c r="C15" s="2">
+        <v>100673000000011</v>
+      </c>
+      <c r="D15" s="27">
+        <v>9999996</v>
+      </c>
+      <c r="E15" s="27">
+        <v>1000421</v>
+      </c>
+      <c r="F15" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="G15" s="1">
+        <v>15</v>
+      </c>
+      <c r="H15" s="1">
+        <v>700</v>
+      </c>
+      <c r="I15" s="32">
+        <v>1.7</v>
+      </c>
+      <c r="J15" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="L15" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M15" s="1">
+        <v>11</v>
       </c>
     </row>
     <row r="18" spans="3:9" x14ac:dyDescent="0.25">
@@ -1846,7 +2287,7 @@
       <c r="D18" s="7"/>
       <c r="E18" s="11"/>
       <c r="H18" s="17"/>
-      <c r="I18" s="23"/>
+      <c r="I18" s="28"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1864,7 +2305,7 @@
     <col min="3" max="3" width="20.42578125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="22.140625" customWidth="1"/>
     <col min="7" max="7" width="15.28515625" customWidth="1"/>
-    <col min="8" max="8" width="31.42578125" customWidth="1"/>
+    <col min="8" max="8" width="16.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" x14ac:dyDescent="0.25">
@@ -1921,108 +2362,108 @@
       </c>
     </row>
     <row r="2" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" x14ac:dyDescent="0.25">
-      <c r="A2" s="24">
-        <v>5000003</v>
-      </c>
-      <c r="B2" s="24" t="s">
+      <c r="A2" s="29">
+        <v>5555509</v>
+      </c>
+      <c r="B2" s="29" t="s">
         <v>93</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="24" t="s">
+      <c r="D2" s="29" t="s">
         <v>95</v>
       </c>
-      <c r="E2" s="24">
+      <c r="E2" s="29">
         <v>2025</v>
       </c>
-      <c r="F2" s="24" t="s">
+      <c r="F2" s="29" t="s">
         <v>98</v>
       </c>
-      <c r="G2" s="24" t="s">
+      <c r="G2" s="29" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="28">
+      <c r="H2" s="33">
         <v>100673001212128</v>
       </c>
-      <c r="I2" s="1">
-        <v>9999996</v>
-      </c>
-      <c r="J2" s="1">
-        <v>1000421</v>
-      </c>
-      <c r="K2" s="24">
+      <c r="I2" s="27">
+        <v>9997115</v>
+      </c>
+      <c r="J2" s="27">
+        <v>9997115</v>
+      </c>
+      <c r="K2" s="29">
         <v>100</v>
       </c>
-      <c r="L2" s="24">
+      <c r="L2" s="29">
         <v>6</v>
       </c>
-      <c r="M2" s="24">
+      <c r="M2" s="29">
         <v>0.5</v>
       </c>
-      <c r="N2" s="24" t="s">
+      <c r="N2" s="29" t="s">
         <v>102</v>
       </c>
-      <c r="O2" s="24" t="s">
+      <c r="O2" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="P2" s="24" t="s">
+      <c r="P2" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="Q2" s="24" t="s">
+      <c r="Q2" s="29" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" x14ac:dyDescent="0.25">
-      <c r="A3" s="24">
+      <c r="A3" s="29">
         <v>5555534</v>
       </c>
-      <c r="B3" s="24" t="s">
+      <c r="B3" s="29" t="s">
         <v>93</v>
       </c>
-      <c r="C3" s="24" t="s">
+      <c r="C3" s="29" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="24" t="s">
+      <c r="D3" s="29" t="s">
         <v>95</v>
       </c>
-      <c r="E3" s="24">
+      <c r="E3" s="29">
         <v>2025</v>
       </c>
-      <c r="F3" s="24" t="s">
+      <c r="F3" s="29" t="s">
         <v>98</v>
       </c>
-      <c r="G3" s="24" t="s">
+      <c r="G3" s="29" t="s">
         <v>100</v>
       </c>
-      <c r="H3" s="28">
+      <c r="H3" s="33">
         <v>100673001212128</v>
       </c>
-      <c r="I3" s="22">
+      <c r="I3" s="27">
         <v>9997115</v>
       </c>
-      <c r="J3" s="22">
+      <c r="J3" s="27">
         <v>9997115</v>
       </c>
-      <c r="K3" s="24">
+      <c r="K3" s="29">
         <v>100</v>
       </c>
-      <c r="L3" s="24">
+      <c r="L3" s="29">
         <v>6</v>
       </c>
-      <c r="M3" s="24">
+      <c r="M3" s="29">
         <v>0.5</v>
       </c>
-      <c r="N3" s="24" t="s">
+      <c r="N3" s="29" t="s">
         <v>102</v>
       </c>
-      <c r="O3" s="24" t="s">
+      <c r="O3" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="P3" s="24" t="s">
+      <c r="P3" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="Q3" s="24" t="s">
+      <c r="Q3" s="29" t="s">
         <v>104</v>
       </c>
     </row>
@@ -2099,14 +2540,14 @@
       <c r="G5" s="7" t="s">
         <v>100</v>
       </c>
-      <c r="H5" s="28">
-        <v>102905240000015</v>
+      <c r="H5" s="33">
+        <v>100673001212128</v>
       </c>
       <c r="I5" s="1">
-        <v>9997115</v>
+        <v>9999996</v>
       </c>
       <c r="J5" s="1">
-        <v>8211642</v>
+        <v>1000421</v>
       </c>
       <c r="K5" s="7">
         <v>100</v>
@@ -2128,194 +2569,514 @@
       </c>
       <c r="Q5" s="19"/>
     </row>
-    <row r="6" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" s="33" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="29"/>
-      <c r="B6" s="29"/>
-      <c r="C6" s="29"/>
-      <c r="D6" s="29"/>
-      <c r="E6" s="29"/>
-      <c r="F6" s="29"/>
-      <c r="G6" s="29"/>
-      <c r="H6" s="30"/>
-      <c r="I6" s="31"/>
-      <c r="J6" s="31"/>
-      <c r="K6" s="29"/>
-      <c r="L6" s="29"/>
-      <c r="M6" s="29"/>
-      <c r="N6" s="29"/>
-      <c r="O6" s="29"/>
-      <c r="P6" s="29"/>
-      <c r="Q6" s="32"/>
+    <row r="6" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" s="38" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="34">
+        <v>5555537</v>
+      </c>
+      <c r="B6" s="34" t="s">
+        <v>93</v>
+      </c>
+      <c r="C6" s="34" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6" s="34" t="s">
+        <v>95</v>
+      </c>
+      <c r="E6" s="34">
+        <v>2025</v>
+      </c>
+      <c r="F6" s="34" t="s">
+        <v>98</v>
+      </c>
+      <c r="G6" s="34" t="s">
+        <v>100</v>
+      </c>
+      <c r="H6" s="35">
+        <v>100673001212128</v>
+      </c>
+      <c r="I6" s="36">
+        <v>9999996</v>
+      </c>
+      <c r="J6" s="36">
+        <v>1000421</v>
+      </c>
+      <c r="K6" s="34">
+        <v>1150</v>
+      </c>
+      <c r="L6" s="34">
+        <v>6</v>
+      </c>
+      <c r="M6" s="34">
+        <v>0.25</v>
+      </c>
+      <c r="N6" s="34" t="s">
+        <v>102</v>
+      </c>
+      <c r="O6" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="P6" s="34" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q6" s="37"/>
     </row>
     <row r="7" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" x14ac:dyDescent="0.25">
-      <c r="A7" s="7"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="7"/>
-      <c r="H7" s="28"/>
-      <c r="I7" s="1"/>
-      <c r="J7" s="1"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-      <c r="N7" s="7"/>
-      <c r="O7" s="7"/>
-      <c r="P7" s="7"/>
+      <c r="A7" s="7">
+        <v>5555538</v>
+      </c>
+      <c r="B7" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D7" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="E7" s="7">
+        <v>2025</v>
+      </c>
+      <c r="F7" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="G7" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="H7" s="33">
+        <v>102905240000015</v>
+      </c>
+      <c r="I7" s="1">
+        <v>9997115</v>
+      </c>
+      <c r="J7" s="1">
+        <v>8211642</v>
+      </c>
+      <c r="K7" s="7">
+        <v>100</v>
+      </c>
+      <c r="L7" s="7">
+        <v>6</v>
+      </c>
+      <c r="M7" s="7">
+        <v>1</v>
+      </c>
+      <c r="N7" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="O7" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="P7" s="7" t="s">
+        <v>15</v>
+      </c>
       <c r="Q7" s="19"/>
     </row>
     <row r="8" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" x14ac:dyDescent="0.25">
-      <c r="A8" s="7"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="7"/>
-      <c r="H8" s="11"/>
-      <c r="I8" s="1"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7"/>
-      <c r="N8" s="7"/>
-      <c r="O8" s="7"/>
-      <c r="P8" s="7"/>
+      <c r="A8" s="7">
+        <v>5555539</v>
+      </c>
+      <c r="B8" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="E8" s="7">
+        <v>2025</v>
+      </c>
+      <c r="F8" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="G8" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="H8" s="11">
+        <v>102905240000015</v>
+      </c>
+      <c r="I8" s="1">
+        <v>9997115</v>
+      </c>
+      <c r="J8" s="1">
+        <v>8211642</v>
+      </c>
+      <c r="K8" s="7">
+        <v>100</v>
+      </c>
+      <c r="L8" s="7">
+        <v>6</v>
+      </c>
+      <c r="M8" s="7">
+        <v>1</v>
+      </c>
+      <c r="N8" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="O8" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="P8" s="7" t="s">
+        <v>15</v>
+      </c>
       <c r="Q8" s="19"/>
     </row>
     <row r="9" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" x14ac:dyDescent="0.25">
-      <c r="A9" s="7"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="7"/>
-      <c r="H9" s="28"/>
-      <c r="I9" s="1"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="7"/>
-      <c r="N9" s="7"/>
-      <c r="O9" s="7"/>
-      <c r="P9" s="7"/>
+      <c r="A9" s="7">
+        <v>5555540</v>
+      </c>
+      <c r="B9" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="E9" s="7">
+        <v>2025</v>
+      </c>
+      <c r="F9" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="G9" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="H9" s="33">
+        <v>102905240000015</v>
+      </c>
+      <c r="I9" s="1">
+        <v>9997115</v>
+      </c>
+      <c r="J9" s="1">
+        <v>8211642</v>
+      </c>
+      <c r="K9" s="7">
+        <v>100</v>
+      </c>
+      <c r="L9" s="7">
+        <v>6</v>
+      </c>
+      <c r="M9" s="7">
+        <v>1</v>
+      </c>
+      <c r="N9" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="O9" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="P9" s="7" t="s">
+        <v>15</v>
+      </c>
       <c r="Q9" s="19"/>
     </row>
     <row r="10" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" x14ac:dyDescent="0.25">
-      <c r="A10" s="7"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="7"/>
-      <c r="H10" s="11"/>
-      <c r="I10" s="1"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="7"/>
-      <c r="M10" s="7"/>
-      <c r="N10" s="7"/>
-      <c r="O10" s="7"/>
-      <c r="P10" s="7"/>
+      <c r="A10" s="7">
+        <v>5555541</v>
+      </c>
+      <c r="B10" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="E10" s="7">
+        <v>2025</v>
+      </c>
+      <c r="F10" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="G10" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="H10" s="11">
+        <v>102905240000015</v>
+      </c>
+      <c r="I10" s="1">
+        <v>9997115</v>
+      </c>
+      <c r="J10" s="1">
+        <v>8211642</v>
+      </c>
+      <c r="K10" s="7">
+        <v>100</v>
+      </c>
+      <c r="L10" s="7">
+        <v>6</v>
+      </c>
+      <c r="M10" s="7">
+        <v>1</v>
+      </c>
+      <c r="N10" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="O10" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="P10" s="7" t="s">
+        <v>15</v>
+      </c>
       <c r="Q10" s="19"/>
     </row>
     <row r="11" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" x14ac:dyDescent="0.25">
-      <c r="A11" s="7"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="7"/>
-      <c r="H11" s="28"/>
-      <c r="I11" s="1"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="7"/>
-      <c r="M11" s="7"/>
-      <c r="N11" s="7"/>
-      <c r="O11" s="7"/>
-      <c r="P11" s="7"/>
+      <c r="A11" s="7">
+        <v>5555542</v>
+      </c>
+      <c r="B11" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D11" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="E11" s="7">
+        <v>2025</v>
+      </c>
+      <c r="F11" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="G11" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="H11" s="33">
+        <v>102905240000015</v>
+      </c>
+      <c r="I11" s="1">
+        <v>9997115</v>
+      </c>
+      <c r="J11" s="1">
+        <v>8211642</v>
+      </c>
+      <c r="K11" s="7">
+        <v>100</v>
+      </c>
+      <c r="L11" s="7">
+        <v>6</v>
+      </c>
+      <c r="M11" s="7">
+        <v>1</v>
+      </c>
+      <c r="N11" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="O11" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="P11" s="7" t="s">
+        <v>15</v>
+      </c>
       <c r="Q11" s="19"/>
     </row>
     <row r="12" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" x14ac:dyDescent="0.25">
-      <c r="A12" s="7"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="7"/>
-      <c r="H12" s="11"/>
-      <c r="I12" s="1"/>
-      <c r="J12" s="1"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="7"/>
-      <c r="M12" s="7"/>
-      <c r="N12" s="7"/>
-      <c r="O12" s="7"/>
-      <c r="P12" s="7"/>
+      <c r="A12" s="7">
+        <v>5555543</v>
+      </c>
+      <c r="B12" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="E12" s="7">
+        <v>2025</v>
+      </c>
+      <c r="F12" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="G12" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="H12" s="11">
+        <v>102905240000015</v>
+      </c>
+      <c r="I12" s="1">
+        <v>9997115</v>
+      </c>
+      <c r="J12" s="1">
+        <v>8211642</v>
+      </c>
+      <c r="K12" s="7">
+        <v>100</v>
+      </c>
+      <c r="L12" s="7">
+        <v>6</v>
+      </c>
+      <c r="M12" s="7">
+        <v>1</v>
+      </c>
+      <c r="N12" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="O12" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="P12" s="7" t="s">
+        <v>15</v>
+      </c>
       <c r="Q12" s="19"/>
     </row>
     <row r="13" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" x14ac:dyDescent="0.25">
-      <c r="A13" s="7"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="7"/>
-      <c r="H13" s="28"/>
-      <c r="I13" s="1"/>
-      <c r="J13" s="1"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="7"/>
-      <c r="M13" s="7"/>
-      <c r="N13" s="7"/>
-      <c r="O13" s="7"/>
-      <c r="P13" s="7"/>
+      <c r="A13" s="7">
+        <v>5555544</v>
+      </c>
+      <c r="B13" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="E13" s="7">
+        <v>2025</v>
+      </c>
+      <c r="F13" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="G13" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="H13" s="33">
+        <v>102905240000015</v>
+      </c>
+      <c r="I13" s="1">
+        <v>9997115</v>
+      </c>
+      <c r="J13" s="1">
+        <v>8211642</v>
+      </c>
+      <c r="K13" s="7">
+        <v>100</v>
+      </c>
+      <c r="L13" s="7">
+        <v>6</v>
+      </c>
+      <c r="M13" s="7">
+        <v>1</v>
+      </c>
+      <c r="N13" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="O13" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="P13" s="7" t="s">
+        <v>15</v>
+      </c>
       <c r="Q13" s="19"/>
     </row>
     <row r="14" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" x14ac:dyDescent="0.25">
-      <c r="A14" s="7"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="7"/>
-      <c r="H14" s="11"/>
-      <c r="I14" s="1"/>
-      <c r="J14" s="1"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="7"/>
-      <c r="M14" s="7"/>
-      <c r="N14" s="7"/>
-      <c r="O14" s="7"/>
-      <c r="P14" s="7"/>
+      <c r="A14" s="7">
+        <v>5555545</v>
+      </c>
+      <c r="B14" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D14" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="E14" s="7">
+        <v>2025</v>
+      </c>
+      <c r="F14" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="G14" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="H14" s="11">
+        <v>102905240000015</v>
+      </c>
+      <c r="I14" s="1">
+        <v>9997115</v>
+      </c>
+      <c r="J14" s="1">
+        <v>8211642</v>
+      </c>
+      <c r="K14" s="7">
+        <v>100</v>
+      </c>
+      <c r="L14" s="7">
+        <v>6</v>
+      </c>
+      <c r="M14" s="7">
+        <v>1</v>
+      </c>
+      <c r="N14" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="O14" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="P14" s="7" t="s">
+        <v>15</v>
+      </c>
       <c r="Q14" s="19"/>
     </row>
     <row r="15" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="7"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="7"/>
-      <c r="H15" s="28"/>
-      <c r="I15" s="1"/>
-      <c r="J15" s="1"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="7"/>
-      <c r="M15" s="7"/>
-      <c r="N15" s="7"/>
-      <c r="O15" s="7"/>
-      <c r="P15" s="7"/>
+      <c r="A15" s="7">
+        <v>5555546</v>
+      </c>
+      <c r="B15" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D15" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="E15" s="7">
+        <v>2025</v>
+      </c>
+      <c r="F15" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="G15" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="H15" s="33">
+        <v>102905240000015</v>
+      </c>
+      <c r="I15" s="1">
+        <v>9997115</v>
+      </c>
+      <c r="J15" s="1">
+        <v>8211642</v>
+      </c>
+      <c r="K15" s="7">
+        <v>100</v>
+      </c>
+      <c r="L15" s="7">
+        <v>6</v>
+      </c>
+      <c r="M15" s="7">
+        <v>1</v>
+      </c>
+      <c r="N15" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="O15" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="P15" s="7" t="s">
+        <v>15</v>
+      </c>
       <c r="Q15" s="19"/>
       <c r="X15" s="16"/>
       <c r="Y15" s="17"/>
@@ -5388,22 +6149,54 @@
       <c r="XEX15" s="17"/>
     </row>
     <row r="16" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="7"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="7"/>
-      <c r="H16" s="11"/>
-      <c r="I16" s="1"/>
-      <c r="J16" s="1"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
-      <c r="M16" s="7"/>
-      <c r="N16" s="7"/>
-      <c r="O16" s="7"/>
-      <c r="P16" s="7"/>
+      <c r="A16" s="7">
+        <v>5555547</v>
+      </c>
+      <c r="B16" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D16" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="E16" s="7">
+        <v>2025</v>
+      </c>
+      <c r="F16" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="G16" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="H16" s="11">
+        <v>102905240000015</v>
+      </c>
+      <c r="I16" s="1">
+        <v>9997115</v>
+      </c>
+      <c r="J16" s="1">
+        <v>8211642</v>
+      </c>
+      <c r="K16" s="7">
+        <v>100</v>
+      </c>
+      <c r="L16" s="7">
+        <v>6</v>
+      </c>
+      <c r="M16" s="7">
+        <v>1</v>
+      </c>
+      <c r="N16" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="O16" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="P16" s="7" t="s">
+        <v>15</v>
+      </c>
       <c r="Q16" s="7"/>
       <c r="X16" s="16"/>
       <c r="Y16" s="17"/>
@@ -8476,22 +9269,54 @@
       <c r="XEX16" s="17"/>
     </row>
     <row r="17" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="7"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="7"/>
-      <c r="H17" s="11"/>
-      <c r="I17" s="1"/>
-      <c r="J17" s="1"/>
-      <c r="K17" s="7"/>
-      <c r="L17" s="7"/>
-      <c r="M17" s="7"/>
-      <c r="N17" s="7"/>
-      <c r="O17" s="7"/>
-      <c r="P17" s="7"/>
+      <c r="A17" s="7">
+        <v>5555548</v>
+      </c>
+      <c r="B17" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D17" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="E17" s="7">
+        <v>2025</v>
+      </c>
+      <c r="F17" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="G17" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="H17" s="33">
+        <v>102905240000015</v>
+      </c>
+      <c r="I17" s="1">
+        <v>9997115</v>
+      </c>
+      <c r="J17" s="1">
+        <v>8211642</v>
+      </c>
+      <c r="K17" s="7">
+        <v>100</v>
+      </c>
+      <c r="L17" s="7">
+        <v>6</v>
+      </c>
+      <c r="M17" s="7">
+        <v>1</v>
+      </c>
+      <c r="N17" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="O17" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="P17" s="7" t="s">
+        <v>15</v>
+      </c>
       <c r="Q17" s="7"/>
       <c r="X17" s="16"/>
       <c r="Y17" s="17"/>
@@ -11564,22 +12389,54 @@
       <c r="XEX17" s="17"/>
     </row>
     <row r="18" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="7"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="7"/>
-      <c r="H18" s="11"/>
-      <c r="I18" s="1"/>
-      <c r="J18" s="1"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="7"/>
-      <c r="M18" s="7"/>
-      <c r="N18" s="7"/>
-      <c r="O18" s="7"/>
-      <c r="P18" s="7"/>
+      <c r="A18" s="7">
+        <v>5555549</v>
+      </c>
+      <c r="B18" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D18" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="E18" s="7">
+        <v>2025</v>
+      </c>
+      <c r="F18" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="G18" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="H18" s="11">
+        <v>102905240000015</v>
+      </c>
+      <c r="I18" s="1">
+        <v>9997115</v>
+      </c>
+      <c r="J18" s="1">
+        <v>8211642</v>
+      </c>
+      <c r="K18" s="7">
+        <v>100</v>
+      </c>
+      <c r="L18" s="7">
+        <v>6</v>
+      </c>
+      <c r="M18" s="7">
+        <v>1</v>
+      </c>
+      <c r="N18" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="O18" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="P18" s="7" t="s">
+        <v>15</v>
+      </c>
       <c r="Q18" s="7"/>
       <c r="X18" s="16"/>
       <c r="Y18" s="17"/>
@@ -14652,22 +15509,54 @@
       <c r="XEX18" s="17"/>
     </row>
     <row r="19" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="7"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="7"/>
-      <c r="H19" s="11"/>
-      <c r="I19" s="1"/>
-      <c r="J19" s="1"/>
-      <c r="K19" s="7"/>
-      <c r="L19" s="7"/>
-      <c r="M19" s="7"/>
-      <c r="N19" s="7"/>
-      <c r="O19" s="7"/>
-      <c r="P19" s="7"/>
+      <c r="A19" s="7">
+        <v>5555550</v>
+      </c>
+      <c r="B19" s="7" t="s">
+        <v>93</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>13</v>
+      </c>
+      <c r="D19" s="7" t="s">
+        <v>95</v>
+      </c>
+      <c r="E19" s="7">
+        <v>2025</v>
+      </c>
+      <c r="F19" s="7" t="s">
+        <v>98</v>
+      </c>
+      <c r="G19" s="7" t="s">
+        <v>100</v>
+      </c>
+      <c r="H19" s="11">
+        <v>100673001212128</v>
+      </c>
+      <c r="I19" s="1">
+        <v>9997115</v>
+      </c>
+      <c r="J19" s="1">
+        <v>8211642</v>
+      </c>
+      <c r="K19" s="7">
+        <v>100</v>
+      </c>
+      <c r="L19" s="7">
+        <v>1</v>
+      </c>
+      <c r="M19" s="7">
+        <v>1</v>
+      </c>
+      <c r="N19" s="7" t="s">
+        <v>102</v>
+      </c>
+      <c r="O19" s="7" t="s">
+        <v>15</v>
+      </c>
+      <c r="P19" s="7" t="s">
+        <v>15</v>
+      </c>
       <c r="Q19" s="7"/>
       <c r="X19" s="16"/>
       <c r="Y19" s="17"/>
@@ -17808,7 +18697,7 @@
         <v>70</v>
       </c>
       <c r="B2" s="7">
-        <v>1656504</v>
+        <v>1655555</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>29</v>
@@ -17816,23 +18705,23 @@
       <c r="D2" s="7">
         <v>11</v>
       </c>
-      <c r="E2" s="22">
+      <c r="E2" s="7">
         <v>9999996</v>
       </c>
-      <c r="F2" s="22">
+      <c r="F2" s="7">
         <v>1000421</v>
       </c>
-      <c r="G2" s="20">
-        <v>100673000000011</v>
+      <c r="G2" s="11">
+        <v>120733340001420</v>
       </c>
       <c r="H2" s="7">
         <v>1003</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>130</v>
+        <v>73</v>
       </c>
       <c r="J2" s="7">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="K2" s="7">
         <v>10</v>
@@ -17841,7 +18730,7 @@
         <v>77</v>
       </c>
       <c r="M2" s="7">
-        <v>20</v>
+        <v>5</v>
       </c>
       <c r="N2" s="7" t="s">
         <v>79</v>
@@ -17853,7 +18742,7 @@
         <v>70</v>
       </c>
       <c r="B3" s="7">
-        <v>1656504</v>
+        <v>5555552</v>
       </c>
       <c r="C3" s="7" t="s">
         <v>29</v>
@@ -17868,7 +18757,7 @@
         <v>1000421</v>
       </c>
       <c r="G3" s="11">
-        <v>120733340001420</v>
+        <v>100673000000011</v>
       </c>
       <c r="H3" s="7">
         <v>1003</v>
@@ -17877,7 +18766,7 @@
         <v>73</v>
       </c>
       <c r="J3" s="7">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="K3" s="7">
         <v>10</v>
@@ -17886,335 +18775,828 @@
         <v>77</v>
       </c>
       <c r="M3" s="7">
-        <v>20</v>
+        <v>50</v>
       </c>
       <c r="N3" s="7" t="s">
         <v>79</v>
       </c>
       <c r="O3" s="7"/>
     </row>
-    <row r="4" spans="1:15" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="10"/>
-      <c r="B4" s="7"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="37">
-        <v>8888999</v>
-      </c>
-      <c r="F4" s="38">
-        <v>8888888</v>
+    <row r="4" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="B4" s="7">
+        <v>5555553</v>
+      </c>
+      <c r="C4" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D4" s="7">
+        <v>11</v>
+      </c>
+      <c r="E4" s="7">
+        <v>9999996</v>
+      </c>
+      <c r="F4" s="7">
+        <v>1000421</v>
       </c>
       <c r="G4" s="11">
-        <v>178888880001601</v>
-      </c>
-      <c r="H4" s="7"/>
+        <v>100673000000011</v>
+      </c>
+      <c r="H4" s="7">
+        <v>1003</v>
+      </c>
       <c r="I4" s="7" t="s">
-        <v>130</v>
-      </c>
-      <c r="J4" s="7"/>
-      <c r="K4" s="7"/>
-      <c r="L4" s="7"/>
-      <c r="M4" s="7"/>
-      <c r="N4" s="7"/>
+        <v>73</v>
+      </c>
+      <c r="J4" s="7">
+        <v>10</v>
+      </c>
+      <c r="K4" s="7">
+        <v>10</v>
+      </c>
+      <c r="L4" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="M4" s="7">
+        <v>50</v>
+      </c>
+      <c r="N4" s="7" t="s">
+        <v>79</v>
+      </c>
       <c r="O4" s="7"/>
     </row>
-    <row r="5" spans="1:15" s="26" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="36"/>
-      <c r="B5" s="24"/>
-      <c r="C5" s="24"/>
-      <c r="D5" s="24"/>
-      <c r="E5" s="7">
-        <v>9999996</v>
-      </c>
-      <c r="F5" s="7">
-        <v>1000421</v>
-      </c>
-      <c r="G5" s="11">
-        <v>120733340001420</v>
-      </c>
-      <c r="H5" s="24"/>
-      <c r="I5" s="24"/>
-      <c r="J5" s="24"/>
-      <c r="K5" s="24"/>
-      <c r="L5" s="24"/>
-      <c r="M5" s="24"/>
-      <c r="N5" s="24"/>
-      <c r="O5" s="24"/>
+    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
+      <c r="A5" s="25" t="s">
+        <v>70</v>
+      </c>
+      <c r="B5" s="20">
+        <v>5555554</v>
+      </c>
+      <c r="C5" s="20" t="s">
+        <v>29</v>
+      </c>
+      <c r="D5" s="20">
+        <v>11</v>
+      </c>
+      <c r="E5" s="24">
+        <v>9996059</v>
+      </c>
+      <c r="F5" s="22">
+        <v>5750013</v>
+      </c>
+      <c r="G5" s="21">
+        <v>100673000000011</v>
+      </c>
+      <c r="H5" s="20">
+        <v>1003</v>
+      </c>
+      <c r="I5" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="J5" s="20">
+        <v>10</v>
+      </c>
+      <c r="K5" s="20">
+        <v>10</v>
+      </c>
+      <c r="L5" s="20" t="s">
+        <v>77</v>
+      </c>
+      <c r="M5" s="20">
+        <v>50</v>
+      </c>
+      <c r="N5" s="20" t="s">
+        <v>79</v>
+      </c>
+      <c r="O5" s="20" t="s">
+        <v>113</v>
+      </c>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="10"/>
-      <c r="B6" s="7"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="7"/>
-      <c r="F6" s="7"/>
-      <c r="G6" s="11"/>
-      <c r="H6" s="7"/>
-      <c r="I6" s="7"/>
-      <c r="J6" s="7"/>
-      <c r="K6" s="7"/>
-      <c r="L6" s="7"/>
-      <c r="M6" s="7"/>
-      <c r="N6" s="7"/>
-      <c r="O6" s="7"/>
+      <c r="A6" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="B6" s="7">
+        <v>5555555</v>
+      </c>
+      <c r="C6" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D6" s="7">
+        <v>11</v>
+      </c>
+      <c r="E6" s="7">
+        <v>9999996</v>
+      </c>
+      <c r="F6" s="7">
+        <v>1000421</v>
+      </c>
+      <c r="G6" s="11">
+        <v>100673000000011</v>
+      </c>
+      <c r="H6" s="7">
+        <v>1003</v>
+      </c>
+      <c r="I6" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="J6" s="7">
+        <v>1</v>
+      </c>
+      <c r="K6" s="7">
+        <v>10</v>
+      </c>
+      <c r="L6" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="M6" s="7">
+        <v>50</v>
+      </c>
+      <c r="N6" s="7" t="s">
+        <v>79</v>
+      </c>
+      <c r="O6" s="7" t="s">
+        <v>114</v>
+      </c>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="10"/>
-      <c r="B7" s="7"/>
-      <c r="C7" s="7"/>
-      <c r="D7" s="7"/>
-      <c r="E7" s="7"/>
-      <c r="F7" s="7"/>
-      <c r="G7" s="11"/>
-      <c r="H7" s="7"/>
-      <c r="I7" s="7"/>
-      <c r="J7" s="7"/>
-      <c r="K7" s="7"/>
-      <c r="L7" s="7"/>
-      <c r="M7" s="7"/>
-      <c r="N7" s="7"/>
+      <c r="A7" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="B7" s="7">
+        <v>5555556</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D7" s="7">
+        <v>11</v>
+      </c>
+      <c r="E7" s="7">
+        <v>9999996</v>
+      </c>
+      <c r="F7" s="7">
+        <v>1000421</v>
+      </c>
+      <c r="G7" s="11">
+        <v>100673000000011</v>
+      </c>
+      <c r="H7" s="7">
+        <v>1003</v>
+      </c>
+      <c r="I7" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="J7" s="7">
+        <v>1</v>
+      </c>
+      <c r="K7" s="7">
+        <v>10</v>
+      </c>
+      <c r="L7" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="M7" s="7">
+        <v>1</v>
+      </c>
+      <c r="N7" s="7" t="s">
+        <v>79</v>
+      </c>
       <c r="O7" s="7"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="10"/>
-      <c r="B8" s="7"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="7"/>
-      <c r="F8" s="7"/>
-      <c r="G8" s="20"/>
-      <c r="H8" s="22"/>
-      <c r="I8" s="22"/>
-      <c r="J8" s="7"/>
-      <c r="K8" s="7"/>
-      <c r="L8" s="7"/>
-      <c r="M8" s="7"/>
-      <c r="N8" s="7"/>
+      <c r="A8" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="B8" s="7">
+        <v>5555557</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D8" s="7">
+        <v>11</v>
+      </c>
+      <c r="E8" s="7">
+        <v>9999996</v>
+      </c>
+      <c r="F8" s="7">
+        <v>1000421</v>
+      </c>
+      <c r="G8" s="11">
+        <v>100673000000011</v>
+      </c>
+      <c r="H8" s="7">
+        <v>1003</v>
+      </c>
+      <c r="I8" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="J8" s="7">
+        <v>10</v>
+      </c>
+      <c r="K8" s="7">
+        <v>10</v>
+      </c>
+      <c r="L8" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="M8" s="7">
+        <v>50</v>
+      </c>
+      <c r="N8" s="7" t="s">
+        <v>79</v>
+      </c>
       <c r="O8" s="7"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="10"/>
-      <c r="B9" s="7"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="7"/>
-      <c r="F9" s="7"/>
-      <c r="G9" s="11"/>
-      <c r="H9" s="7"/>
-      <c r="I9" s="7"/>
-      <c r="J9" s="7"/>
-      <c r="K9" s="7"/>
-      <c r="L9" s="7"/>
-      <c r="M9" s="7"/>
-      <c r="N9" s="7"/>
+      <c r="A9" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="B9" s="7">
+        <v>5555558</v>
+      </c>
+      <c r="C9" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D9" s="7">
+        <v>11</v>
+      </c>
+      <c r="E9" s="7">
+        <v>9999996</v>
+      </c>
+      <c r="F9" s="7">
+        <v>1000421</v>
+      </c>
+      <c r="G9" s="11">
+        <v>100673000000011</v>
+      </c>
+      <c r="H9" s="7">
+        <v>1003</v>
+      </c>
+      <c r="I9" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="J9" s="7">
+        <v>10</v>
+      </c>
+      <c r="K9" s="7">
+        <v>10</v>
+      </c>
+      <c r="L9" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="M9" s="7">
+        <v>50</v>
+      </c>
+      <c r="N9" s="7" t="s">
+        <v>79</v>
+      </c>
       <c r="O9" s="7"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="10"/>
-      <c r="B10" s="7"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="7"/>
-      <c r="F10" s="7"/>
-      <c r="G10" s="11"/>
-      <c r="H10" s="7"/>
-      <c r="I10" s="7"/>
-      <c r="J10" s="7"/>
-      <c r="K10" s="7"/>
-      <c r="L10" s="7"/>
-      <c r="M10" s="7"/>
-      <c r="N10" s="7"/>
+      <c r="A10" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="B10" s="7">
+        <v>5555559</v>
+      </c>
+      <c r="C10" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D10" s="7">
+        <v>11</v>
+      </c>
+      <c r="E10" s="7">
+        <v>9999996</v>
+      </c>
+      <c r="F10" s="7">
+        <v>1000421</v>
+      </c>
+      <c r="G10" s="11">
+        <v>100673000000011</v>
+      </c>
+      <c r="H10" s="7">
+        <v>1003</v>
+      </c>
+      <c r="I10" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="J10" s="7">
+        <v>10</v>
+      </c>
+      <c r="K10" s="7">
+        <v>10</v>
+      </c>
+      <c r="L10" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="M10" s="7">
+        <v>50</v>
+      </c>
+      <c r="N10" s="7" t="s">
+        <v>79</v>
+      </c>
       <c r="O10" s="7"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="10"/>
-      <c r="B11" s="7"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="7"/>
-      <c r="F11" s="7"/>
-      <c r="G11" s="11"/>
-      <c r="H11" s="7"/>
-      <c r="I11" s="7"/>
-      <c r="J11" s="7"/>
-      <c r="K11" s="7"/>
-      <c r="L11" s="7"/>
-      <c r="M11" s="7"/>
-      <c r="N11" s="7"/>
+      <c r="A11" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="B11" s="7">
+        <v>5555560</v>
+      </c>
+      <c r="C11" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D11" s="7">
+        <v>11</v>
+      </c>
+      <c r="E11" s="7">
+        <v>9999996</v>
+      </c>
+      <c r="F11" s="7">
+        <v>1000421</v>
+      </c>
+      <c r="G11" s="11">
+        <v>100673000000011</v>
+      </c>
+      <c r="H11" s="7">
+        <v>1003</v>
+      </c>
+      <c r="I11" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="J11" s="7">
+        <v>10</v>
+      </c>
+      <c r="K11" s="7">
+        <v>10</v>
+      </c>
+      <c r="L11" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="M11" s="7">
+        <v>50</v>
+      </c>
+      <c r="N11" s="7" t="s">
+        <v>79</v>
+      </c>
       <c r="O11" s="7"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="10"/>
-      <c r="B12" s="7"/>
-      <c r="C12" s="7"/>
-      <c r="D12" s="7"/>
-      <c r="E12" s="7"/>
-      <c r="F12" s="7"/>
-      <c r="G12" s="11"/>
-      <c r="H12" s="7"/>
-      <c r="I12" s="7"/>
-      <c r="J12" s="7"/>
-      <c r="K12" s="7"/>
-      <c r="L12" s="7"/>
-      <c r="M12" s="7"/>
-      <c r="N12" s="7"/>
+      <c r="A12" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="B12" s="7">
+        <v>5555561</v>
+      </c>
+      <c r="C12" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D12" s="7">
+        <v>11</v>
+      </c>
+      <c r="E12" s="7">
+        <v>9999996</v>
+      </c>
+      <c r="F12" s="7">
+        <v>1000421</v>
+      </c>
+      <c r="G12" s="11">
+        <v>100673000000011</v>
+      </c>
+      <c r="H12" s="7">
+        <v>1003</v>
+      </c>
+      <c r="I12" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="J12" s="7">
+        <v>10</v>
+      </c>
+      <c r="K12" s="7">
+        <v>10</v>
+      </c>
+      <c r="L12" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="M12" s="7">
+        <v>50</v>
+      </c>
+      <c r="N12" s="7" t="s">
+        <v>79</v>
+      </c>
       <c r="O12" s="7"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="10"/>
-      <c r="B13" s="7"/>
-      <c r="C13" s="7"/>
-      <c r="D13" s="7"/>
-      <c r="E13" s="7"/>
-      <c r="F13" s="7"/>
-      <c r="G13" s="11"/>
-      <c r="H13" s="7"/>
-      <c r="I13" s="7"/>
-      <c r="J13" s="7"/>
-      <c r="K13" s="7"/>
-      <c r="L13" s="7"/>
-      <c r="M13" s="7"/>
-      <c r="N13" s="7"/>
+      <c r="A13" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="B13" s="7">
+        <v>5555562</v>
+      </c>
+      <c r="C13" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D13" s="7">
+        <v>11</v>
+      </c>
+      <c r="E13" s="7">
+        <v>9999996</v>
+      </c>
+      <c r="F13" s="7">
+        <v>1000421</v>
+      </c>
+      <c r="G13" s="11">
+        <v>100673000000011</v>
+      </c>
+      <c r="H13" s="7">
+        <v>1003</v>
+      </c>
+      <c r="I13" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="J13" s="7">
+        <v>10</v>
+      </c>
+      <c r="K13" s="7">
+        <v>10</v>
+      </c>
+      <c r="L13" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="M13" s="7">
+        <v>50</v>
+      </c>
+      <c r="N13" s="7" t="s">
+        <v>79</v>
+      </c>
       <c r="O13" s="7"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="10"/>
-      <c r="B14" s="7"/>
-      <c r="C14" s="7"/>
-      <c r="D14" s="7"/>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7"/>
-      <c r="G14" s="11"/>
-      <c r="H14" s="7"/>
-      <c r="I14" s="7"/>
-      <c r="J14" s="7"/>
-      <c r="K14" s="7"/>
-      <c r="L14" s="7"/>
-      <c r="M14" s="7"/>
-      <c r="N14" s="7"/>
+      <c r="A14" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="B14" s="7">
+        <v>5555563</v>
+      </c>
+      <c r="C14" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D14" s="7">
+        <v>11</v>
+      </c>
+      <c r="E14" s="7">
+        <v>9999996</v>
+      </c>
+      <c r="F14" s="7">
+        <v>1000421</v>
+      </c>
+      <c r="G14" s="11">
+        <v>100673000000011</v>
+      </c>
+      <c r="H14" s="7">
+        <v>1003</v>
+      </c>
+      <c r="I14" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="J14" s="7">
+        <v>10</v>
+      </c>
+      <c r="K14" s="7">
+        <v>10</v>
+      </c>
+      <c r="L14" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="M14" s="7">
+        <v>50</v>
+      </c>
+      <c r="N14" s="7" t="s">
+        <v>79</v>
+      </c>
       <c r="O14" s="7"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="10"/>
-      <c r="B15" s="7"/>
-      <c r="C15" s="7"/>
-      <c r="D15" s="7"/>
-      <c r="E15" s="7"/>
-      <c r="F15" s="7"/>
-      <c r="G15" s="11"/>
-      <c r="H15" s="7"/>
-      <c r="I15" s="7"/>
-      <c r="J15" s="7"/>
-      <c r="K15" s="7"/>
-      <c r="L15" s="7"/>
-      <c r="M15" s="7"/>
-      <c r="N15" s="7"/>
+      <c r="A15" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="B15" s="7">
+        <v>5555564</v>
+      </c>
+      <c r="C15" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D15" s="7">
+        <v>11</v>
+      </c>
+      <c r="E15" s="7">
+        <v>9999996</v>
+      </c>
+      <c r="F15" s="7">
+        <v>1000421</v>
+      </c>
+      <c r="G15" s="11">
+        <v>100673000000011</v>
+      </c>
+      <c r="H15" s="7">
+        <v>1003</v>
+      </c>
+      <c r="I15" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="J15" s="7">
+        <v>10</v>
+      </c>
+      <c r="K15" s="7">
+        <v>10</v>
+      </c>
+      <c r="L15" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="M15" s="7">
+        <v>50</v>
+      </c>
+      <c r="N15" s="7" t="s">
+        <v>79</v>
+      </c>
       <c r="O15" s="7"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="10"/>
-      <c r="B16" s="7"/>
-      <c r="C16" s="7"/>
-      <c r="D16" s="7"/>
-      <c r="E16" s="7"/>
-      <c r="F16" s="7"/>
-      <c r="G16" s="11"/>
-      <c r="H16" s="7"/>
-      <c r="I16" s="7"/>
-      <c r="J16" s="7"/>
-      <c r="K16" s="7"/>
-      <c r="L16" s="7"/>
-      <c r="M16" s="7"/>
-      <c r="N16" s="7"/>
+      <c r="A16" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="B16" s="7">
+        <v>5555565</v>
+      </c>
+      <c r="C16" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D16" s="7">
+        <v>11</v>
+      </c>
+      <c r="E16" s="7">
+        <v>9999996</v>
+      </c>
+      <c r="F16" s="7">
+        <v>1000421</v>
+      </c>
+      <c r="G16" s="11">
+        <v>100673000000011</v>
+      </c>
+      <c r="H16" s="7">
+        <v>1003</v>
+      </c>
+      <c r="I16" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="J16" s="7">
+        <v>10</v>
+      </c>
+      <c r="K16" s="7">
+        <v>10</v>
+      </c>
+      <c r="L16" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="M16" s="7">
+        <v>50</v>
+      </c>
+      <c r="N16" s="7" t="s">
+        <v>79</v>
+      </c>
       <c r="O16" s="7"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="10"/>
-      <c r="B17" s="7"/>
-      <c r="C17" s="7"/>
-      <c r="D17" s="7"/>
-      <c r="E17" s="7"/>
-      <c r="F17" s="7"/>
-      <c r="G17" s="11"/>
-      <c r="H17" s="7"/>
-      <c r="I17" s="7"/>
-      <c r="J17" s="7"/>
-      <c r="K17" s="7"/>
-      <c r="L17" s="7"/>
-      <c r="M17" s="7"/>
-      <c r="N17" s="7"/>
+      <c r="A17" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="B17" s="7">
+        <v>5555566</v>
+      </c>
+      <c r="C17" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D17" s="7">
+        <v>11</v>
+      </c>
+      <c r="E17" s="7">
+        <v>9999996</v>
+      </c>
+      <c r="F17" s="7">
+        <v>1000421</v>
+      </c>
+      <c r="G17" s="11">
+        <v>100673000000011</v>
+      </c>
+      <c r="H17" s="7">
+        <v>1003</v>
+      </c>
+      <c r="I17" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="J17" s="7">
+        <v>10</v>
+      </c>
+      <c r="K17" s="7">
+        <v>10</v>
+      </c>
+      <c r="L17" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="M17" s="7">
+        <v>50</v>
+      </c>
+      <c r="N17" s="7" t="s">
+        <v>79</v>
+      </c>
       <c r="O17" s="7"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="10"/>
-      <c r="B18" s="7"/>
-      <c r="C18" s="7"/>
-      <c r="D18" s="7"/>
-      <c r="E18" s="7"/>
-      <c r="F18" s="7"/>
-      <c r="G18" s="11"/>
-      <c r="H18" s="7"/>
-      <c r="I18" s="7"/>
-      <c r="J18" s="7"/>
-      <c r="K18" s="7"/>
-      <c r="L18" s="7"/>
-      <c r="M18" s="7"/>
-      <c r="N18" s="7"/>
+      <c r="A18" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="B18" s="7">
+        <v>5555567</v>
+      </c>
+      <c r="C18" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D18" s="7">
+        <v>11</v>
+      </c>
+      <c r="E18" s="7">
+        <v>9999996</v>
+      </c>
+      <c r="F18" s="7">
+        <v>1000421</v>
+      </c>
+      <c r="G18" s="11">
+        <v>100673000000011</v>
+      </c>
+      <c r="H18" s="7">
+        <v>1003</v>
+      </c>
+      <c r="I18" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="J18" s="7">
+        <v>10</v>
+      </c>
+      <c r="K18" s="7">
+        <v>10</v>
+      </c>
+      <c r="L18" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="M18" s="7">
+        <v>50</v>
+      </c>
+      <c r="N18" s="7" t="s">
+        <v>79</v>
+      </c>
       <c r="O18" s="7"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="10"/>
-      <c r="B19" s="7"/>
-      <c r="C19" s="7"/>
-      <c r="D19" s="7"/>
-      <c r="E19" s="7"/>
-      <c r="F19" s="7"/>
-      <c r="G19" s="11"/>
-      <c r="H19" s="7"/>
-      <c r="I19" s="7"/>
-      <c r="J19" s="7"/>
-      <c r="K19" s="7"/>
-      <c r="L19" s="7"/>
-      <c r="M19" s="7"/>
-      <c r="N19" s="7"/>
+      <c r="A19" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="B19" s="7">
+        <v>5555568</v>
+      </c>
+      <c r="C19" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D19" s="7">
+        <v>11</v>
+      </c>
+      <c r="E19" s="7">
+        <v>9999996</v>
+      </c>
+      <c r="F19" s="7">
+        <v>1000421</v>
+      </c>
+      <c r="G19" s="11">
+        <v>100673000000011</v>
+      </c>
+      <c r="H19" s="7">
+        <v>1003</v>
+      </c>
+      <c r="I19" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="J19" s="7">
+        <v>10</v>
+      </c>
+      <c r="K19" s="7">
+        <v>10</v>
+      </c>
+      <c r="L19" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="M19" s="7">
+        <v>50</v>
+      </c>
+      <c r="N19" s="7" t="s">
+        <v>79</v>
+      </c>
       <c r="O19" s="7"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="10"/>
-      <c r="B20" s="7"/>
-      <c r="C20" s="7"/>
-      <c r="D20" s="7"/>
-      <c r="E20" s="7"/>
-      <c r="F20" s="7"/>
-      <c r="G20" s="11"/>
-      <c r="H20" s="7"/>
-      <c r="I20" s="7"/>
-      <c r="J20" s="7"/>
-      <c r="K20" s="7"/>
-      <c r="L20" s="7"/>
-      <c r="M20" s="7"/>
-      <c r="N20" s="7"/>
+      <c r="A20" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="B20" s="7">
+        <v>5555569</v>
+      </c>
+      <c r="C20" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D20" s="7">
+        <v>11</v>
+      </c>
+      <c r="E20" s="7">
+        <v>9999996</v>
+      </c>
+      <c r="F20" s="7">
+        <v>1000421</v>
+      </c>
+      <c r="G20" s="11">
+        <v>100673000000011</v>
+      </c>
+      <c r="H20" s="7">
+        <v>1003</v>
+      </c>
+      <c r="I20" s="7" t="s">
+        <v>73</v>
+      </c>
+      <c r="J20" s="7">
+        <v>10</v>
+      </c>
+      <c r="K20" s="7">
+        <v>10</v>
+      </c>
+      <c r="L20" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="M20" s="7">
+        <v>50</v>
+      </c>
+      <c r="N20" s="7" t="s">
+        <v>79</v>
+      </c>
       <c r="O20" s="7"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="10"/>
-      <c r="B21" s="7"/>
-      <c r="C21" s="7"/>
-      <c r="D21" s="7"/>
-      <c r="E21" s="7"/>
-      <c r="F21" s="7"/>
-      <c r="G21" s="11"/>
-      <c r="H21" s="7"/>
-      <c r="I21" s="7"/>
-      <c r="J21" s="7"/>
-      <c r="K21" s="7"/>
-      <c r="L21" s="7"/>
-      <c r="M21" s="7"/>
-      <c r="N21" s="7"/>
+      <c r="A21" s="10" t="s">
+        <v>70</v>
+      </c>
+      <c r="B21" s="7">
+        <v>5555570</v>
+      </c>
+      <c r="C21" s="7" t="s">
+        <v>29</v>
+      </c>
+      <c r="D21" s="7">
+        <v>11</v>
+      </c>
+      <c r="E21" s="7">
+        <v>9996059</v>
+      </c>
+      <c r="F21" s="7">
+        <v>5750013</v>
+      </c>
+      <c r="G21" s="11">
+        <v>178888880001601</v>
+      </c>
+      <c r="H21" s="7">
+        <v>1001</v>
+      </c>
+      <c r="I21" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="J21" s="7">
+        <v>20</v>
+      </c>
+      <c r="K21" s="7">
+        <v>20</v>
+      </c>
+      <c r="L21" s="7" t="s">
+        <v>77</v>
+      </c>
+      <c r="M21" s="7">
+        <v>100</v>
+      </c>
+      <c r="N21" s="7" t="s">
+        <v>79</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -18337,7 +19719,7 @@
         <v>232324</v>
       </c>
       <c r="C2" s="1">
-        <v>100</v>
+        <v>500</v>
       </c>
       <c r="D2" s="1" t="s">
         <v>59</v>
@@ -18349,13 +19731,13 @@
         <v>973015</v>
       </c>
       <c r="G2" s="1">
-        <v>100011</v>
+        <v>100002</v>
       </c>
       <c r="H2" s="1">
         <v>1000012</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>129</v>
+        <v>120</v>
       </c>
       <c r="J2" s="1">
         <v>130009</v>
@@ -18385,7 +19767,7 @@
         <v>63</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>133</v>
+        <v>64</v>
       </c>
       <c r="T2" s="1" t="s">
         <v>65</v>
@@ -18425,7 +19807,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECF7E842-C9CD-4111-B0BA-C4A8FEE6BCD1}">
-  <dimension ref="A1:AC31"/>
+  <dimension ref="A1:AB31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -18439,7 +19821,7 @@
     <col min="21" max="21" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
         <v>31</v>
       </c>
@@ -18477,7 +19859,7 @@
         <v>89</v>
       </c>
       <c r="M1" s="13" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="N1" s="13" t="s">
         <v>38</v>
@@ -18524,11 +19906,8 @@
       <c r="AB1" s="13" t="s">
         <v>57</v>
       </c>
-      <c r="AC1" s="5" t="s">
-        <v>111</v>
-      </c>
     </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" s="7">
         <v>53409</v>
       </c>
@@ -18545,10 +19924,10 @@
         <v>60</v>
       </c>
       <c r="F2" s="7">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="G2" s="7">
-        <v>5000</v>
+        <v>4000</v>
       </c>
       <c r="H2" s="7">
         <v>30</v>
@@ -18563,10 +19942,10 @@
         <v>1</v>
       </c>
       <c r="L2" s="7">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="M2" s="7" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="N2" s="7">
         <v>46202558</v>
@@ -18611,49 +19990,46 @@
         <v>179</v>
       </c>
       <c r="AB2" s="7">
-        <v>100</v>
-      </c>
-      <c r="AC2" s="34">
-        <v>20</v>
+        <v>200</v>
       </c>
     </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
       <c r="I4" s="14"/>
     </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
       <c r="I5" s="9"/>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
       <c r="I6" s="9"/>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
       <c r="I7" s="9"/>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="I8" s="9"/>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
       <c r="I9" s="9"/>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
       <c r="I10" s="9"/>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
       <c r="I11" s="9"/>
     </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
       <c r="I12" s="9"/>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
       <c r="I13" s="9"/>
     </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
       <c r="I14" s="8"/>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
       <c r="I15" s="8"/>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
       <c r="I16" s="8"/>
     </row>
     <row r="17" spans="9:9" x14ac:dyDescent="0.25">
@@ -18708,7 +20084,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EAC201B6-DCEE-4C93-A919-B2D4018F90C6}">
-  <dimension ref="A1:XFD11"/>
+  <dimension ref="A1:F11"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="19.7109375" bestFit="1" customWidth="1"/>
@@ -18716,75 +20092,34 @@
     <col min="4" max="4" width="14" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="22.7109375" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.42578125" customWidth="1"/>
-    <col min="8" max="8" width="12.42578125" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="13.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19 16384:16384" x14ac:dyDescent="0.25">
-      <c r="A1" s="35" t="s">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="A1" s="19" t="s">
         <v>105</v>
       </c>
-      <c r="B1" s="35" t="s">
+      <c r="B1" s="19" t="s">
         <v>56</v>
       </c>
-      <c r="C1" s="35" t="s">
+      <c r="C1" s="19" t="s">
         <v>106</v>
       </c>
-      <c r="D1" s="35" t="s">
+      <c r="D1" s="19" t="s">
         <v>107</v>
       </c>
-      <c r="E1" s="35" t="s">
+      <c r="E1" s="19" t="s">
         <v>108</v>
       </c>
-      <c r="F1" s="35" t="s">
+      <c r="F1" s="19" t="s">
         <v>109</v>
       </c>
-      <c r="G1" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="H1" s="35" t="s">
-        <v>118</v>
-      </c>
-      <c r="I1" s="5" t="s">
-        <v>119</v>
-      </c>
-      <c r="J1" s="5" t="s">
-        <v>120</v>
-      </c>
-      <c r="K1" s="5" t="s">
-        <v>121</v>
-      </c>
-      <c r="L1" s="5" t="s">
-        <v>122</v>
-      </c>
-      <c r="M1" s="5" t="s">
-        <v>123</v>
-      </c>
-      <c r="N1" s="5" t="s">
-        <v>124</v>
-      </c>
-      <c r="O1" s="5" t="s">
-        <v>125</v>
-      </c>
-      <c r="P1" s="5" t="s">
-        <v>126</v>
-      </c>
-      <c r="Q1" s="5" t="s">
-        <v>127</v>
-      </c>
-      <c r="R1" s="35"/>
-      <c r="S1" s="35" t="s">
-        <v>128</v>
-      </c>
-      <c r="XFD1" s="3"/>
     </row>
-    <row r="2" spans="1:19 16384:16384" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="19">
-        <v>321884</v>
+        <v>321731</v>
       </c>
       <c r="B2" s="19">
-        <v>90</v>
+        <v>180</v>
       </c>
       <c r="C2" s="19" t="s">
         <v>110</v>
@@ -18798,91 +20133,39 @@
       <c r="F2" s="19">
         <v>99</v>
       </c>
-      <c r="G2" s="19"/>
-      <c r="H2" s="19"/>
-      <c r="I2" s="19"/>
-      <c r="J2" s="19"/>
-      <c r="K2" s="19"/>
-      <c r="L2" s="19"/>
-      <c r="M2" s="19"/>
-      <c r="N2" s="19"/>
-      <c r="O2" s="19"/>
-      <c r="P2" s="19"/>
-      <c r="Q2" s="19"/>
-      <c r="R2" s="19"/>
-      <c r="S2" s="19"/>
     </row>
-    <row r="3" spans="1:19 16384:16384" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="19"/>
       <c r="B3" s="19"/>
       <c r="C3" s="19"/>
       <c r="D3" s="19"/>
       <c r="E3" s="19"/>
       <c r="F3" s="19"/>
-      <c r="G3" s="19"/>
-      <c r="H3" s="19"/>
-      <c r="I3" s="19"/>
-      <c r="J3" s="19"/>
-      <c r="K3" s="19"/>
-      <c r="L3" s="19"/>
-      <c r="M3" s="19"/>
-      <c r="N3" s="19"/>
-      <c r="O3" s="19"/>
-      <c r="P3" s="19"/>
-      <c r="Q3" s="19"/>
-      <c r="R3" s="19"/>
-      <c r="S3" s="19"/>
     </row>
-    <row r="4" spans="1:19 16384:16384" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="19"/>
       <c r="B4" s="19"/>
       <c r="C4" s="19"/>
       <c r="D4" s="19"/>
       <c r="E4" s="19"/>
       <c r="F4" s="19"/>
-      <c r="G4" s="19"/>
-      <c r="H4" s="19"/>
-      <c r="I4" s="19"/>
-      <c r="J4" s="19"/>
-      <c r="K4" s="19"/>
-      <c r="L4" s="19"/>
-      <c r="M4" s="19"/>
-      <c r="N4" s="19"/>
-      <c r="O4" s="19"/>
-      <c r="P4" s="19"/>
-      <c r="Q4" s="19"/>
-      <c r="R4" s="19"/>
-      <c r="S4" s="19"/>
     </row>
-    <row r="5" spans="1:19 16384:16384" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="19"/>
       <c r="B5" s="19"/>
       <c r="C5" s="19"/>
       <c r="D5" s="19"/>
       <c r="E5" s="19"/>
       <c r="F5" s="19"/>
-      <c r="G5" s="19"/>
-      <c r="H5" s="19"/>
-      <c r="I5" s="19"/>
-      <c r="J5" s="19"/>
-      <c r="K5" s="19"/>
-      <c r="L5" s="19"/>
-      <c r="M5" s="19"/>
-      <c r="N5" s="19"/>
-      <c r="O5" s="19"/>
-      <c r="P5" s="19"/>
-      <c r="Q5" s="19"/>
-      <c r="R5" s="19"/>
-      <c r="S5" s="19"/>
     </row>
-    <row r="10" spans="1:19 16384:16384" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F10" t="s">
-        <v>115</v>
+        <v>118</v>
       </c>
     </row>
-    <row r="11" spans="1:19 16384:16384" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F11" t="s">
-        <v>116</v>
+        <v>119</v>
       </c>
     </row>
   </sheetData>

--- a/Data/ENWR_Creation.xlsx
+++ b/Data/ENWR_Creation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2E131951-BCE7-4BB4-9A20-20BEB01CDE51}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA239F51-2521-46EC-AA4A-B3A54AD3B4DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19770" windowHeight="11760" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RP_Deposite_Request_Agriculture" sheetId="1" r:id="rId1"/>
@@ -1707,13 +1707,13 @@
         <v>4555525</v>
       </c>
       <c r="C2" s="11">
-        <v>120733340001685</v>
+        <v>120484000000134</v>
       </c>
       <c r="D2" s="7">
-        <v>9999996</v>
+        <v>6656413</v>
       </c>
       <c r="E2" s="7">
-        <v>1000421</v>
+        <v>6539191</v>
       </c>
       <c r="F2" s="27" t="s">
         <v>29</v>
@@ -1722,7 +1722,7 @@
         <v>15</v>
       </c>
       <c r="H2" s="27">
-        <v>2000</v>
+        <v>900</v>
       </c>
       <c r="I2" s="32">
         <v>1.7</v>
@@ -19743,7 +19743,7 @@
         <v>130009</v>
       </c>
       <c r="K2" s="1">
-        <v>3400</v>
+        <v>1530</v>
       </c>
       <c r="L2" s="1">
         <v>5000</v>
@@ -19797,7 +19797,7 @@
         <v>100</v>
       </c>
       <c r="AC2" s="7">
-        <v>20</v>
+        <v>9</v>
       </c>
     </row>
   </sheetData>
@@ -20116,7 +20116,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="19">
-        <v>321731</v>
+        <v>321732</v>
       </c>
       <c r="B2" s="19">
         <v>180</v>

--- a/Data/ENWR_Creation.xlsx
+++ b/Data/ENWR_Creation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DA239F51-2521-46EC-AA4A-B3A54AD3B4DA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37120F58-3B8B-4CA4-8912-47E1918C7215}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RP_Deposite_Request_Agriculture" sheetId="1" r:id="rId1"/>

--- a/Data/ENWR_Creation.xlsx
+++ b/Data/ENWR_Creation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{37120F58-3B8B-4CA4-8912-47E1918C7215}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44596ADB-BC89-4AA0-8585-9CB0D5C6288C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="2" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RP_Deposite_Request_Agriculture" sheetId="1" r:id="rId1"/>
@@ -1704,7 +1704,7 @@
         <v>13</v>
       </c>
       <c r="B2" s="27">
-        <v>4555525</v>
+        <v>4555526</v>
       </c>
       <c r="C2" s="11">
         <v>120484000000134</v>
@@ -20116,7 +20116,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="19">
-        <v>321732</v>
+        <v>32170090</v>
       </c>
       <c r="B2" s="19">
         <v>180</v>

--- a/Data/ENWR_Creation.xlsx
+++ b/Data/ENWR_Creation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{44596ADB-BC89-4AA0-8585-9CB0D5C6288C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F25C5921-9779-407C-8E2B-6DFB93EBE9D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="564" uniqueCount="121">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="122">
   <si>
     <t>commoditySegment</t>
   </si>
@@ -405,6 +405,9 @@
   </si>
   <si>
     <t>hdjh123</t>
+  </si>
+  <si>
+    <t>DRUM</t>
   </si>
 </sst>
 </file>
@@ -906,6 +909,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="16.140625" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="22.28515625" customWidth="1"/>
     <col min="7" max="7" width="12" bestFit="1" customWidth="1"/>
@@ -961,19 +965,19 @@
         <v>13</v>
       </c>
       <c r="B2" s="27">
-        <v>5555628</v>
+        <v>250520262</v>
       </c>
       <c r="C2" s="27" t="s">
         <v>16</v>
       </c>
       <c r="D2" s="23">
-        <v>100673000000011</v>
+        <v>178888880001601</v>
       </c>
       <c r="E2" s="27">
-        <v>9999996</v>
+        <v>8888999</v>
       </c>
       <c r="F2" s="27">
-        <v>1000421</v>
+        <v>9878999</v>
       </c>
       <c r="G2" s="27" t="s">
         <v>14</v>
@@ -982,7 +986,7 @@
         <v>1</v>
       </c>
       <c r="I2" s="27">
-        <v>700</v>
+        <v>5000</v>
       </c>
       <c r="J2" s="27">
         <v>1.7</v>
@@ -1704,31 +1708,31 @@
         <v>13</v>
       </c>
       <c r="B2" s="27">
-        <v>4555526</v>
+        <v>250520261</v>
       </c>
       <c r="C2" s="11">
-        <v>120484000000134</v>
+        <v>178888880001601</v>
       </c>
       <c r="D2" s="7">
-        <v>6656413</v>
+        <v>8888999</v>
       </c>
       <c r="E2" s="7">
-        <v>6539191</v>
+        <v>3052022</v>
       </c>
       <c r="F2" s="27" t="s">
         <v>29</v>
       </c>
       <c r="G2" s="27">
-        <v>15</v>
+        <v>947</v>
       </c>
       <c r="H2" s="27">
-        <v>900</v>
+        <v>100</v>
       </c>
       <c r="I2" s="32">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J2" s="27" t="s">
-        <v>30</v>
+        <v>121</v>
       </c>
       <c r="K2" s="27" t="s">
         <v>15</v>
@@ -2363,7 +2367,7 @@
     </row>
     <row r="2" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" x14ac:dyDescent="0.25">
       <c r="A2" s="29">
-        <v>5555509</v>
+        <v>220520261</v>
       </c>
       <c r="B2" s="29" t="s">
         <v>93</v>
@@ -2387,10 +2391,10 @@
         <v>100673001212128</v>
       </c>
       <c r="I2" s="27">
-        <v>9997115</v>
+        <v>9999996</v>
       </c>
       <c r="J2" s="27">
-        <v>9997115</v>
+        <v>1000421</v>
       </c>
       <c r="K2" s="29">
         <v>100</v>
@@ -2399,7 +2403,7 @@
         <v>6</v>
       </c>
       <c r="M2" s="29">
-        <v>0.5</v>
+        <v>1.7</v>
       </c>
       <c r="N2" s="29" t="s">
         <v>102</v>
@@ -2468,615 +2472,231 @@
       </c>
     </row>
     <row r="4" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" x14ac:dyDescent="0.25">
-      <c r="A4" s="11">
-        <v>5555535</v>
-      </c>
-      <c r="B4" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D4" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="E4" s="7">
-        <v>2025</v>
-      </c>
-      <c r="F4" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="G4" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="H4" s="11">
-        <v>120733340001479</v>
-      </c>
-      <c r="I4" s="1">
-        <v>9999996</v>
-      </c>
-      <c r="J4" s="1">
-        <v>1000421</v>
-      </c>
-      <c r="K4" s="7">
-        <v>100</v>
-      </c>
-      <c r="L4" s="7">
-        <v>6</v>
-      </c>
-      <c r="M4" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="N4" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="O4" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="P4" s="7" t="s">
-        <v>15</v>
-      </c>
+      <c r="A4" s="11"/>
+      <c r="B4" s="7"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="7"/>
+      <c r="F4" s="7"/>
+      <c r="G4" s="7"/>
+      <c r="H4" s="11"/>
+      <c r="I4" s="1"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="7"/>
+      <c r="L4" s="7"/>
+      <c r="M4" s="7"/>
+      <c r="N4" s="7"/>
+      <c r="O4" s="7"/>
+      <c r="P4" s="7"/>
       <c r="Q4" s="19"/>
     </row>
     <row r="5" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" x14ac:dyDescent="0.25">
-      <c r="A5" s="7">
-        <v>5555536</v>
-      </c>
-      <c r="B5" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D5" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="E5" s="7">
-        <v>2025</v>
-      </c>
-      <c r="F5" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="G5" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="H5" s="33">
-        <v>100673001212128</v>
-      </c>
-      <c r="I5" s="1">
-        <v>9999996</v>
-      </c>
-      <c r="J5" s="1">
-        <v>1000421</v>
-      </c>
-      <c r="K5" s="7">
-        <v>100</v>
-      </c>
-      <c r="L5" s="7">
-        <v>6</v>
-      </c>
-      <c r="M5" s="7">
-        <v>0.5</v>
-      </c>
-      <c r="N5" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="O5" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="P5" s="7" t="s">
-        <v>15</v>
-      </c>
+      <c r="A5" s="7"/>
+      <c r="B5" s="7"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="7"/>
+      <c r="G5" s="7"/>
+      <c r="H5" s="33"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="7"/>
+      <c r="L5" s="7"/>
+      <c r="M5" s="7"/>
+      <c r="N5" s="7"/>
+      <c r="O5" s="7"/>
+      <c r="P5" s="7"/>
       <c r="Q5" s="19"/>
     </row>
     <row r="6" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" s="38" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="34">
-        <v>5555537</v>
-      </c>
-      <c r="B6" s="34" t="s">
-        <v>93</v>
-      </c>
-      <c r="C6" s="34" t="s">
-        <v>13</v>
-      </c>
-      <c r="D6" s="34" t="s">
-        <v>95</v>
-      </c>
-      <c r="E6" s="34">
-        <v>2025</v>
-      </c>
-      <c r="F6" s="34" t="s">
-        <v>98</v>
-      </c>
-      <c r="G6" s="34" t="s">
-        <v>100</v>
-      </c>
-      <c r="H6" s="35">
-        <v>100673001212128</v>
-      </c>
-      <c r="I6" s="36">
-        <v>9999996</v>
-      </c>
-      <c r="J6" s="36">
-        <v>1000421</v>
-      </c>
-      <c r="K6" s="34">
-        <v>1150</v>
-      </c>
-      <c r="L6" s="34">
-        <v>6</v>
-      </c>
-      <c r="M6" s="34">
-        <v>0.25</v>
-      </c>
-      <c r="N6" s="34" t="s">
-        <v>102</v>
-      </c>
-      <c r="O6" s="34" t="s">
-        <v>15</v>
-      </c>
-      <c r="P6" s="34" t="s">
-        <v>15</v>
-      </c>
+      <c r="A6" s="34"/>
+      <c r="B6" s="34"/>
+      <c r="C6" s="34"/>
+      <c r="D6" s="34"/>
+      <c r="E6" s="34"/>
+      <c r="F6" s="34"/>
+      <c r="G6" s="34"/>
+      <c r="H6" s="35"/>
+      <c r="I6" s="36"/>
+      <c r="J6" s="36"/>
+      <c r="K6" s="34"/>
+      <c r="L6" s="34"/>
+      <c r="M6" s="34"/>
+      <c r="N6" s="34"/>
+      <c r="O6" s="34"/>
+      <c r="P6" s="34"/>
       <c r="Q6" s="37"/>
     </row>
     <row r="7" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" x14ac:dyDescent="0.25">
-      <c r="A7" s="7">
-        <v>5555538</v>
-      </c>
-      <c r="B7" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D7" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="E7" s="7">
-        <v>2025</v>
-      </c>
-      <c r="F7" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="G7" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="H7" s="33">
-        <v>102905240000015</v>
-      </c>
-      <c r="I7" s="1">
-        <v>9997115</v>
-      </c>
-      <c r="J7" s="1">
-        <v>8211642</v>
-      </c>
-      <c r="K7" s="7">
-        <v>100</v>
-      </c>
-      <c r="L7" s="7">
-        <v>6</v>
-      </c>
-      <c r="M7" s="7">
-        <v>1</v>
-      </c>
-      <c r="N7" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="O7" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="P7" s="7" t="s">
-        <v>15</v>
-      </c>
+      <c r="A7" s="7"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="7"/>
+      <c r="H7" s="33"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
+      <c r="O7" s="7"/>
+      <c r="P7" s="7"/>
       <c r="Q7" s="19"/>
     </row>
     <row r="8" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" x14ac:dyDescent="0.25">
-      <c r="A8" s="7">
-        <v>5555539</v>
-      </c>
-      <c r="B8" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="E8" s="7">
-        <v>2025</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="G8" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="H8" s="11">
-        <v>102905240000015</v>
-      </c>
-      <c r="I8" s="1">
-        <v>9997115</v>
-      </c>
-      <c r="J8" s="1">
-        <v>8211642</v>
-      </c>
-      <c r="K8" s="7">
-        <v>100</v>
-      </c>
-      <c r="L8" s="7">
-        <v>6</v>
-      </c>
-      <c r="M8" s="7">
-        <v>1</v>
-      </c>
-      <c r="N8" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="O8" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="P8" s="7" t="s">
-        <v>15</v>
-      </c>
+      <c r="A8" s="7"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="7"/>
+      <c r="H8" s="11"/>
+      <c r="I8" s="1"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="7"/>
+      <c r="O8" s="7"/>
+      <c r="P8" s="7"/>
       <c r="Q8" s="19"/>
     </row>
     <row r="9" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" x14ac:dyDescent="0.25">
-      <c r="A9" s="7">
-        <v>5555540</v>
-      </c>
-      <c r="B9" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D9" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="E9" s="7">
-        <v>2025</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="G9" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="H9" s="33">
-        <v>102905240000015</v>
-      </c>
-      <c r="I9" s="1">
-        <v>9997115</v>
-      </c>
-      <c r="J9" s="1">
-        <v>8211642</v>
-      </c>
-      <c r="K9" s="7">
-        <v>100</v>
-      </c>
-      <c r="L9" s="7">
-        <v>6</v>
-      </c>
-      <c r="M9" s="7">
-        <v>1</v>
-      </c>
-      <c r="N9" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="O9" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="P9" s="7" t="s">
-        <v>15</v>
-      </c>
+      <c r="A9" s="7"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="7"/>
+      <c r="H9" s="33"/>
+      <c r="I9" s="1"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
+      <c r="N9" s="7"/>
+      <c r="O9" s="7"/>
+      <c r="P9" s="7"/>
       <c r="Q9" s="19"/>
     </row>
     <row r="10" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" x14ac:dyDescent="0.25">
-      <c r="A10" s="7">
-        <v>5555541</v>
-      </c>
-      <c r="B10" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="E10" s="7">
-        <v>2025</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="G10" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="H10" s="11">
-        <v>102905240000015</v>
-      </c>
-      <c r="I10" s="1">
-        <v>9997115</v>
-      </c>
-      <c r="J10" s="1">
-        <v>8211642</v>
-      </c>
-      <c r="K10" s="7">
-        <v>100</v>
-      </c>
-      <c r="L10" s="7">
-        <v>6</v>
-      </c>
-      <c r="M10" s="7">
-        <v>1</v>
-      </c>
-      <c r="N10" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="O10" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="P10" s="7" t="s">
-        <v>15</v>
-      </c>
+      <c r="A10" s="7"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="7"/>
+      <c r="H10" s="11"/>
+      <c r="I10" s="1"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
+      <c r="N10" s="7"/>
+      <c r="O10" s="7"/>
+      <c r="P10" s="7"/>
       <c r="Q10" s="19"/>
     </row>
     <row r="11" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" x14ac:dyDescent="0.25">
-      <c r="A11" s="7">
-        <v>5555542</v>
-      </c>
-      <c r="B11" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D11" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="E11" s="7">
-        <v>2025</v>
-      </c>
-      <c r="F11" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="G11" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="H11" s="33">
-        <v>102905240000015</v>
-      </c>
-      <c r="I11" s="1">
-        <v>9997115</v>
-      </c>
-      <c r="J11" s="1">
-        <v>8211642</v>
-      </c>
-      <c r="K11" s="7">
-        <v>100</v>
-      </c>
-      <c r="L11" s="7">
-        <v>6</v>
-      </c>
-      <c r="M11" s="7">
-        <v>1</v>
-      </c>
-      <c r="N11" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="O11" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="P11" s="7" t="s">
-        <v>15</v>
-      </c>
+      <c r="A11" s="7"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="7"/>
+      <c r="H11" s="33"/>
+      <c r="I11" s="1"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="7"/>
+      <c r="O11" s="7"/>
+      <c r="P11" s="7"/>
       <c r="Q11" s="19"/>
     </row>
     <row r="12" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" x14ac:dyDescent="0.25">
-      <c r="A12" s="7">
-        <v>5555543</v>
-      </c>
-      <c r="B12" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D12" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="E12" s="7">
-        <v>2025</v>
-      </c>
-      <c r="F12" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="G12" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="H12" s="11">
-        <v>102905240000015</v>
-      </c>
-      <c r="I12" s="1">
-        <v>9997115</v>
-      </c>
-      <c r="J12" s="1">
-        <v>8211642</v>
-      </c>
-      <c r="K12" s="7">
-        <v>100</v>
-      </c>
-      <c r="L12" s="7">
-        <v>6</v>
-      </c>
-      <c r="M12" s="7">
-        <v>1</v>
-      </c>
-      <c r="N12" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="O12" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="P12" s="7" t="s">
-        <v>15</v>
-      </c>
+      <c r="A12" s="7"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="7"/>
+      <c r="H12" s="11"/>
+      <c r="I12" s="1"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="7"/>
+      <c r="N12" s="7"/>
+      <c r="O12" s="7"/>
+      <c r="P12" s="7"/>
       <c r="Q12" s="19"/>
     </row>
     <row r="13" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" x14ac:dyDescent="0.25">
-      <c r="A13" s="7">
-        <v>5555544</v>
-      </c>
-      <c r="B13" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D13" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="E13" s="7">
-        <v>2025</v>
-      </c>
-      <c r="F13" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="G13" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="H13" s="33">
-        <v>102905240000015</v>
-      </c>
-      <c r="I13" s="1">
-        <v>9997115</v>
-      </c>
-      <c r="J13" s="1">
-        <v>8211642</v>
-      </c>
-      <c r="K13" s="7">
-        <v>100</v>
-      </c>
-      <c r="L13" s="7">
-        <v>6</v>
-      </c>
-      <c r="M13" s="7">
-        <v>1</v>
-      </c>
-      <c r="N13" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="O13" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="P13" s="7" t="s">
-        <v>15</v>
-      </c>
+      <c r="A13" s="7"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="7"/>
+      <c r="H13" s="33"/>
+      <c r="I13" s="1"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="7"/>
+      <c r="N13" s="7"/>
+      <c r="O13" s="7"/>
+      <c r="P13" s="7"/>
       <c r="Q13" s="19"/>
     </row>
     <row r="14" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" x14ac:dyDescent="0.25">
-      <c r="A14" s="7">
-        <v>5555545</v>
-      </c>
-      <c r="B14" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D14" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="E14" s="7">
-        <v>2025</v>
-      </c>
-      <c r="F14" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="G14" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="H14" s="11">
-        <v>102905240000015</v>
-      </c>
-      <c r="I14" s="1">
-        <v>9997115</v>
-      </c>
-      <c r="J14" s="1">
-        <v>8211642</v>
-      </c>
-      <c r="K14" s="7">
-        <v>100</v>
-      </c>
-      <c r="L14" s="7">
-        <v>6</v>
-      </c>
-      <c r="M14" s="7">
-        <v>1</v>
-      </c>
-      <c r="N14" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="O14" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="P14" s="7" t="s">
-        <v>15</v>
-      </c>
+      <c r="A14" s="7"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="7"/>
+      <c r="H14" s="11"/>
+      <c r="I14" s="1"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="7"/>
+      <c r="M14" s="7"/>
+      <c r="N14" s="7"/>
+      <c r="O14" s="7"/>
+      <c r="P14" s="7"/>
       <c r="Q14" s="19"/>
     </row>
     <row r="15" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="7">
-        <v>5555546</v>
-      </c>
-      <c r="B15" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D15" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="E15" s="7">
-        <v>2025</v>
-      </c>
-      <c r="F15" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="G15" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="H15" s="33">
-        <v>102905240000015</v>
-      </c>
-      <c r="I15" s="1">
-        <v>9997115</v>
-      </c>
-      <c r="J15" s="1">
-        <v>8211642</v>
-      </c>
-      <c r="K15" s="7">
-        <v>100</v>
-      </c>
-      <c r="L15" s="7">
-        <v>6</v>
-      </c>
-      <c r="M15" s="7">
-        <v>1</v>
-      </c>
-      <c r="N15" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="O15" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="P15" s="7" t="s">
-        <v>15</v>
-      </c>
+      <c r="A15" s="7"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="7"/>
+      <c r="H15" s="33"/>
+      <c r="I15" s="1"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="7"/>
+      <c r="M15" s="7"/>
+      <c r="N15" s="7"/>
+      <c r="O15" s="7"/>
+      <c r="P15" s="7"/>
       <c r="Q15" s="19"/>
       <c r="X15" s="16"/>
       <c r="Y15" s="17"/>
@@ -6149,54 +5769,22 @@
       <c r="XEX15" s="17"/>
     </row>
     <row r="16" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="7">
-        <v>5555547</v>
-      </c>
-      <c r="B16" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D16" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="E16" s="7">
-        <v>2025</v>
-      </c>
-      <c r="F16" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="G16" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="H16" s="11">
-        <v>102905240000015</v>
-      </c>
-      <c r="I16" s="1">
-        <v>9997115</v>
-      </c>
-      <c r="J16" s="1">
-        <v>8211642</v>
-      </c>
-      <c r="K16" s="7">
-        <v>100</v>
-      </c>
-      <c r="L16" s="7">
-        <v>6</v>
-      </c>
-      <c r="M16" s="7">
-        <v>1</v>
-      </c>
-      <c r="N16" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="O16" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="P16" s="7" t="s">
-        <v>15</v>
-      </c>
+      <c r="A16" s="7"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="7"/>
+      <c r="H16" s="11"/>
+      <c r="I16" s="1"/>
+      <c r="J16" s="1"/>
+      <c r="K16" s="7"/>
+      <c r="L16" s="7"/>
+      <c r="M16" s="7"/>
+      <c r="N16" s="7"/>
+      <c r="O16" s="7"/>
+      <c r="P16" s="7"/>
       <c r="Q16" s="7"/>
       <c r="X16" s="16"/>
       <c r="Y16" s="17"/>
@@ -9269,54 +8857,22 @@
       <c r="XEX16" s="17"/>
     </row>
     <row r="17" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="7">
-        <v>5555548</v>
-      </c>
-      <c r="B17" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D17" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="E17" s="7">
-        <v>2025</v>
-      </c>
-      <c r="F17" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="G17" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="H17" s="33">
-        <v>102905240000015</v>
-      </c>
-      <c r="I17" s="1">
-        <v>9997115</v>
-      </c>
-      <c r="J17" s="1">
-        <v>8211642</v>
-      </c>
-      <c r="K17" s="7">
-        <v>100</v>
-      </c>
-      <c r="L17" s="7">
-        <v>6</v>
-      </c>
-      <c r="M17" s="7">
-        <v>1</v>
-      </c>
-      <c r="N17" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="O17" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="P17" s="7" t="s">
-        <v>15</v>
-      </c>
+      <c r="A17" s="7"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="7"/>
+      <c r="H17" s="33"/>
+      <c r="I17" s="1"/>
+      <c r="J17" s="1"/>
+      <c r="K17" s="7"/>
+      <c r="L17" s="7"/>
+      <c r="M17" s="7"/>
+      <c r="N17" s="7"/>
+      <c r="O17" s="7"/>
+      <c r="P17" s="7"/>
       <c r="Q17" s="7"/>
       <c r="X17" s="16"/>
       <c r="Y17" s="17"/>
@@ -12389,54 +11945,22 @@
       <c r="XEX17" s="17"/>
     </row>
     <row r="18" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="7">
-        <v>5555549</v>
-      </c>
-      <c r="B18" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D18" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="E18" s="7">
-        <v>2025</v>
-      </c>
-      <c r="F18" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="G18" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="H18" s="11">
-        <v>102905240000015</v>
-      </c>
-      <c r="I18" s="1">
-        <v>9997115</v>
-      </c>
-      <c r="J18" s="1">
-        <v>8211642</v>
-      </c>
-      <c r="K18" s="7">
-        <v>100</v>
-      </c>
-      <c r="L18" s="7">
-        <v>6</v>
-      </c>
-      <c r="M18" s="7">
-        <v>1</v>
-      </c>
-      <c r="N18" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="O18" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="P18" s="7" t="s">
-        <v>15</v>
-      </c>
+      <c r="A18" s="7"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="7"/>
+      <c r="H18" s="11"/>
+      <c r="I18" s="1"/>
+      <c r="J18" s="1"/>
+      <c r="K18" s="7"/>
+      <c r="L18" s="7"/>
+      <c r="M18" s="7"/>
+      <c r="N18" s="7"/>
+      <c r="O18" s="7"/>
+      <c r="P18" s="7"/>
       <c r="Q18" s="7"/>
       <c r="X18" s="16"/>
       <c r="Y18" s="17"/>
@@ -15509,54 +15033,22 @@
       <c r="XEX18" s="17"/>
     </row>
     <row r="19" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" s="15" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="7">
-        <v>5555550</v>
-      </c>
-      <c r="B19" s="7" t="s">
-        <v>93</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>13</v>
-      </c>
-      <c r="D19" s="7" t="s">
-        <v>95</v>
-      </c>
-      <c r="E19" s="7">
-        <v>2025</v>
-      </c>
-      <c r="F19" s="7" t="s">
-        <v>98</v>
-      </c>
-      <c r="G19" s="7" t="s">
-        <v>100</v>
-      </c>
-      <c r="H19" s="11">
-        <v>100673001212128</v>
-      </c>
-      <c r="I19" s="1">
-        <v>9997115</v>
-      </c>
-      <c r="J19" s="1">
-        <v>8211642</v>
-      </c>
-      <c r="K19" s="7">
-        <v>100</v>
-      </c>
-      <c r="L19" s="7">
-        <v>1</v>
-      </c>
-      <c r="M19" s="7">
-        <v>1</v>
-      </c>
-      <c r="N19" s="7" t="s">
-        <v>102</v>
-      </c>
-      <c r="O19" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="P19" s="7" t="s">
-        <v>15</v>
-      </c>
+      <c r="A19" s="7"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="7"/>
+      <c r="H19" s="11"/>
+      <c r="I19" s="1"/>
+      <c r="J19" s="1"/>
+      <c r="K19" s="7"/>
+      <c r="L19" s="7"/>
+      <c r="M19" s="7"/>
+      <c r="N19" s="7"/>
+      <c r="O19" s="7"/>
+      <c r="P19" s="7"/>
       <c r="Q19" s="7"/>
       <c r="X19" s="16"/>
       <c r="Y19" s="17"/>
@@ -19731,7 +19223,7 @@
         <v>973015</v>
       </c>
       <c r="G2" s="1">
-        <v>100002</v>
+        <v>100003</v>
       </c>
       <c r="H2" s="1">
         <v>1000012</v>
@@ -19743,7 +19235,7 @@
         <v>130009</v>
       </c>
       <c r="K2" s="1">
-        <v>1530</v>
+        <v>8500</v>
       </c>
       <c r="L2" s="1">
         <v>5000</v>
@@ -19797,7 +19289,7 @@
         <v>100</v>
       </c>
       <c r="AC2" s="7">
-        <v>9</v>
+        <v>50</v>
       </c>
     </row>
   </sheetData>
@@ -20116,7 +19608,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="19">
-        <v>32170090</v>
+        <v>32170092</v>
       </c>
       <c r="B2" s="19">
         <v>180</v>

--- a/Data/ENWR_Creation.xlsx
+++ b/Data/ENWR_Creation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F25C5921-9779-407C-8E2B-6DFB93EBE9D7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{463210FD-0A44-46A1-9358-53635E059C5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RP_Deposite_Request_Agriculture" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="436" uniqueCount="122">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="119">
   <si>
     <t>commoditySegment</t>
   </si>
@@ -383,19 +383,10 @@
     <t>Status</t>
   </si>
   <si>
-    <t>Phy</t>
-  </si>
-  <si>
-    <t>phy</t>
-  </si>
-  <si>
     <t>place_of_origin</t>
   </si>
   <si>
     <t>ass</t>
-  </si>
-  <si>
-    <t>ALUMINUM</t>
   </si>
   <si>
     <t>Zinc 99</t>
@@ -503,7 +494,7 @@
       <family val="3"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -519,18 +510,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -579,7 +558,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -606,25 +585,22 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="2" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="1" fillId="6" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="6" borderId="0" xfId="0" applyFill="1"/>
-    <xf numFmtId="164" fontId="1" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="2" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="1" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="164" fontId="1" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="2" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="1" fontId="10" fillId="6" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="1" fontId="10" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -961,676 +937,676 @@
       </c>
     </row>
     <row r="2" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A2" s="27" t="s">
+      <c r="A2" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="27">
+      <c r="B2" s="22">
         <v>250520262</v>
       </c>
-      <c r="C2" s="27" t="s">
+      <c r="C2" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="23">
+      <c r="D2" s="20">
         <v>178888880001601</v>
       </c>
-      <c r="E2" s="27">
+      <c r="E2" s="22">
         <v>8888999</v>
       </c>
-      <c r="F2" s="27">
+      <c r="F2" s="22">
         <v>9878999</v>
       </c>
-      <c r="G2" s="27" t="s">
+      <c r="G2" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="H2" s="27">
+      <c r="H2" s="22">
         <v>1</v>
       </c>
-      <c r="I2" s="27">
+      <c r="I2" s="22">
         <v>5000</v>
       </c>
-      <c r="J2" s="27">
+      <c r="J2" s="22">
         <v>1.7</v>
       </c>
-      <c r="K2" s="29" t="s">
+      <c r="K2" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="L2" s="27" t="s">
+      <c r="L2" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="M2" s="27" t="s">
+      <c r="M2" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="N2" s="27"/>
+      <c r="N2" s="22"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="B3" s="27">
+      <c r="B3" s="22">
         <v>5555614</v>
       </c>
-      <c r="C3" s="27" t="s">
+      <c r="C3" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="D3" s="23">
+      <c r="D3" s="20">
         <v>155000010000761</v>
       </c>
-      <c r="E3" s="27">
+      <c r="E3" s="22">
         <v>9996059</v>
       </c>
-      <c r="F3" s="27">
+      <c r="F3" s="22">
         <v>5750013</v>
       </c>
-      <c r="G3" s="27" t="s">
+      <c r="G3" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="27">
+      <c r="H3" s="22">
         <v>6</v>
       </c>
-      <c r="I3" s="27">
+      <c r="I3" s="22">
         <v>5000</v>
       </c>
-      <c r="J3" s="27">
+      <c r="J3" s="22">
         <v>0.5</v>
       </c>
-      <c r="K3" s="29" t="s">
+      <c r="K3" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="L3" s="27" t="s">
+      <c r="L3" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="M3" s="27" t="s">
+      <c r="M3" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="N3" s="27"/>
+      <c r="N3" s="22"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="27" t="s">
+      <c r="A4" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="27">
+      <c r="B4" s="22">
         <v>5555615</v>
       </c>
-      <c r="C4" s="27" t="s">
+      <c r="C4" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="D4" s="23">
+      <c r="D4" s="20">
         <v>155000010000761</v>
       </c>
-      <c r="E4" s="27">
+      <c r="E4" s="22">
         <v>9996059</v>
       </c>
-      <c r="F4" s="27">
+      <c r="F4" s="22">
         <v>5750013</v>
       </c>
-      <c r="G4" s="27" t="s">
+      <c r="G4" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="27">
+      <c r="H4" s="22">
         <v>6</v>
       </c>
-      <c r="I4" s="27">
+      <c r="I4" s="22">
         <v>5000</v>
       </c>
-      <c r="J4" s="27">
+      <c r="J4" s="22">
         <v>1.7</v>
       </c>
-      <c r="K4" s="29" t="s">
+      <c r="K4" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="L4" s="27" t="s">
+      <c r="L4" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="M4" s="27" t="s">
+      <c r="M4" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="N4" s="27"/>
+      <c r="N4" s="22"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="27" t="s">
+      <c r="A5" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="27">
+      <c r="B5" s="22">
         <v>5555616</v>
       </c>
-      <c r="C5" s="27" t="s">
+      <c r="C5" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="D5" s="23">
+      <c r="D5" s="20">
         <v>155000010000761</v>
       </c>
-      <c r="E5" s="27">
+      <c r="E5" s="22">
         <v>9999996</v>
       </c>
-      <c r="F5" s="27">
+      <c r="F5" s="22">
         <v>1000421</v>
       </c>
-      <c r="G5" s="27" t="s">
+      <c r="G5" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="H5" s="27">
+      <c r="H5" s="22">
         <v>1</v>
       </c>
-      <c r="I5" s="27">
+      <c r="I5" s="22">
         <v>500</v>
       </c>
-      <c r="J5" s="27">
+      <c r="J5" s="22">
         <v>1.7</v>
       </c>
-      <c r="K5" s="29" t="s">
+      <c r="K5" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="L5" s="27" t="s">
+      <c r="L5" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="M5" s="27" t="s">
+      <c r="M5" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="N5" s="27"/>
+      <c r="N5" s="22"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="27" t="s">
+      <c r="A6" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="27">
+      <c r="B6" s="22">
         <v>5555617</v>
       </c>
-      <c r="C6" s="27" t="s">
+      <c r="C6" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="D6" s="23">
+      <c r="D6" s="20">
         <v>100673000000011</v>
       </c>
-      <c r="E6" s="27">
+      <c r="E6" s="22">
         <v>9999996</v>
       </c>
-      <c r="F6" s="27">
+      <c r="F6" s="22">
         <v>1000421</v>
       </c>
-      <c r="G6" s="27" t="s">
+      <c r="G6" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="H6" s="27">
+      <c r="H6" s="22">
         <v>1</v>
       </c>
-      <c r="I6" s="27">
+      <c r="I6" s="22">
         <v>700</v>
       </c>
-      <c r="J6" s="27">
+      <c r="J6" s="22">
         <v>1.7</v>
       </c>
-      <c r="K6" s="29" t="s">
+      <c r="K6" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="L6" s="27" t="s">
+      <c r="L6" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="M6" s="27" t="s">
+      <c r="M6" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="N6" s="27"/>
+      <c r="N6" s="22"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="27" t="s">
+      <c r="A7" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="27">
+      <c r="B7" s="22">
         <v>5555618</v>
       </c>
-      <c r="C7" s="27" t="s">
+      <c r="C7" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="D7" s="23">
+      <c r="D7" s="20">
         <v>100673000000011</v>
       </c>
-      <c r="E7" s="27">
+      <c r="E7" s="22">
         <v>9999996</v>
       </c>
-      <c r="F7" s="27">
+      <c r="F7" s="22">
         <v>1000421</v>
       </c>
-      <c r="G7" s="27" t="s">
+      <c r="G7" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="H7" s="27">
+      <c r="H7" s="22">
         <v>1</v>
       </c>
-      <c r="I7" s="27">
+      <c r="I7" s="22">
         <v>500</v>
       </c>
-      <c r="J7" s="27">
+      <c r="J7" s="22">
         <v>1.7</v>
       </c>
-      <c r="K7" s="29" t="s">
+      <c r="K7" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="L7" s="27" t="s">
+      <c r="L7" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="M7" s="27" t="s">
+      <c r="M7" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="N7" s="30"/>
+      <c r="N7" s="25"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="27">
+      <c r="B8" s="22">
         <v>5555619</v>
       </c>
-      <c r="C8" s="27" t="s">
+      <c r="C8" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="D8" s="23">
+      <c r="D8" s="20">
         <v>100673000000011</v>
       </c>
-      <c r="E8" s="27">
+      <c r="E8" s="22">
         <v>9999996</v>
       </c>
-      <c r="F8" s="27">
+      <c r="F8" s="22">
         <v>1000421</v>
       </c>
-      <c r="G8" s="27" t="s">
+      <c r="G8" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="H8" s="27">
+      <c r="H8" s="22">
         <v>1</v>
       </c>
-      <c r="I8" s="27">
+      <c r="I8" s="22">
         <v>700</v>
       </c>
-      <c r="J8" s="27">
+      <c r="J8" s="22">
         <v>1.7</v>
       </c>
-      <c r="K8" s="29" t="s">
+      <c r="K8" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="L8" s="27" t="s">
+      <c r="L8" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="M8" s="27" t="s">
+      <c r="M8" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="N8" s="30"/>
+      <c r="N8" s="25"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="27" t="s">
+      <c r="A9" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="27">
+      <c r="B9" s="22">
         <v>5555620</v>
       </c>
-      <c r="C9" s="27" t="s">
+      <c r="C9" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="D9" s="23">
+      <c r="D9" s="20">
         <v>100673000000011</v>
       </c>
-      <c r="E9" s="27">
+      <c r="E9" s="22">
         <v>9999996</v>
       </c>
-      <c r="F9" s="27">
+      <c r="F9" s="22">
         <v>1000421</v>
       </c>
-      <c r="G9" s="27" t="s">
+      <c r="G9" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="H9" s="27">
+      <c r="H9" s="22">
         <v>1</v>
       </c>
-      <c r="I9" s="27">
+      <c r="I9" s="22">
         <v>500</v>
       </c>
-      <c r="J9" s="27">
+      <c r="J9" s="22">
         <v>1.7</v>
       </c>
-      <c r="K9" s="29" t="s">
+      <c r="K9" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="L9" s="27" t="s">
+      <c r="L9" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="M9" s="27" t="s">
+      <c r="M9" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="N9" s="30"/>
+      <c r="N9" s="25"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="27" t="s">
+      <c r="A10" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="27">
+      <c r="B10" s="22">
         <v>5555621</v>
       </c>
-      <c r="C10" s="27" t="s">
+      <c r="C10" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="D10" s="23">
+      <c r="D10" s="20">
         <v>100673000000011</v>
       </c>
-      <c r="E10" s="27">
+      <c r="E10" s="22">
         <v>9999996</v>
       </c>
-      <c r="F10" s="27">
+      <c r="F10" s="22">
         <v>1000421</v>
       </c>
-      <c r="G10" s="27" t="s">
+      <c r="G10" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="H10" s="27">
+      <c r="H10" s="22">
         <v>15</v>
       </c>
-      <c r="I10" s="27">
+      <c r="I10" s="22">
         <v>700</v>
       </c>
-      <c r="J10" s="27">
+      <c r="J10" s="22">
         <v>1.7</v>
       </c>
-      <c r="K10" s="29" t="s">
+      <c r="K10" s="24" t="s">
         <v>58</v>
       </c>
-      <c r="L10" s="27" t="s">
+      <c r="L10" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="M10" s="27" t="s">
+      <c r="M10" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="N10" s="30"/>
+      <c r="N10" s="25"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="27" t="s">
+      <c r="A11" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="27">
+      <c r="B11" s="22">
         <v>5555622</v>
       </c>
-      <c r="C11" s="27" t="s">
+      <c r="C11" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="D11" s="23">
+      <c r="D11" s="20">
         <v>100673000000011</v>
       </c>
-      <c r="E11" s="27">
+      <c r="E11" s="22">
         <v>9999996</v>
       </c>
-      <c r="F11" s="27">
+      <c r="F11" s="22">
         <v>1000421</v>
       </c>
-      <c r="G11" s="27" t="s">
+      <c r="G11" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="H11" s="27">
+      <c r="H11" s="22">
         <v>1</v>
       </c>
-      <c r="I11" s="27">
+      <c r="I11" s="22">
         <v>500</v>
       </c>
-      <c r="J11" s="27">
+      <c r="J11" s="22">
         <v>1.7</v>
       </c>
-      <c r="K11" s="29" t="s">
+      <c r="K11" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="L11" s="27" t="s">
+      <c r="L11" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="M11" s="27" t="s">
+      <c r="M11" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="N11" s="30"/>
+      <c r="N11" s="25"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="27" t="s">
+      <c r="A12" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="27">
+      <c r="B12" s="22">
         <v>5555623</v>
       </c>
-      <c r="C12" s="27" t="s">
+      <c r="C12" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="D12" s="23">
+      <c r="D12" s="20">
         <v>100673000000011</v>
       </c>
-      <c r="E12" s="27">
+      <c r="E12" s="22">
         <v>9999996</v>
       </c>
-      <c r="F12" s="27">
+      <c r="F12" s="22">
         <v>1000421</v>
       </c>
-      <c r="G12" s="27" t="s">
+      <c r="G12" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="H12" s="27">
+      <c r="H12" s="22">
         <v>1</v>
       </c>
-      <c r="I12" s="27">
+      <c r="I12" s="22">
         <v>700</v>
       </c>
-      <c r="J12" s="27">
+      <c r="J12" s="22">
         <v>1.7</v>
       </c>
-      <c r="K12" s="29" t="s">
+      <c r="K12" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="L12" s="27" t="s">
+      <c r="L12" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="M12" s="27" t="s">
+      <c r="M12" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="N12" s="30"/>
+      <c r="N12" s="25"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="27" t="s">
+      <c r="A13" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="27">
+      <c r="B13" s="22">
         <v>5555624</v>
       </c>
-      <c r="C13" s="27" t="s">
+      <c r="C13" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="D13" s="23">
+      <c r="D13" s="20">
         <v>100673000000011</v>
       </c>
-      <c r="E13" s="27">
+      <c r="E13" s="22">
         <v>9999996</v>
       </c>
-      <c r="F13" s="27">
+      <c r="F13" s="22">
         <v>1000421</v>
       </c>
-      <c r="G13" s="27" t="s">
+      <c r="G13" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="H13" s="27">
+      <c r="H13" s="22">
         <v>1</v>
       </c>
-      <c r="I13" s="27">
+      <c r="I13" s="22">
         <v>100</v>
       </c>
-      <c r="J13" s="27">
+      <c r="J13" s="22">
         <v>1.7</v>
       </c>
-      <c r="K13" s="29" t="s">
+      <c r="K13" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="L13" s="27" t="s">
+      <c r="L13" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="M13" s="27" t="s">
+      <c r="M13" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="N13" s="30"/>
+      <c r="N13" s="25"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="27" t="s">
+      <c r="A14" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="27">
+      <c r="B14" s="22">
         <v>5555625</v>
       </c>
-      <c r="C14" s="27" t="s">
+      <c r="C14" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="D14" s="23">
+      <c r="D14" s="20">
         <v>100673000000011</v>
       </c>
-      <c r="E14" s="27">
+      <c r="E14" s="22">
         <v>9999996</v>
       </c>
-      <c r="F14" s="27">
+      <c r="F14" s="22">
         <v>1000421</v>
       </c>
-      <c r="G14" s="27" t="s">
+      <c r="G14" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="H14" s="27">
+      <c r="H14" s="22">
         <v>1</v>
       </c>
-      <c r="I14" s="27">
+      <c r="I14" s="22">
         <v>700</v>
       </c>
-      <c r="J14" s="27">
+      <c r="J14" s="22">
         <v>1.7</v>
       </c>
-      <c r="K14" s="29" t="s">
+      <c r="K14" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="L14" s="27" t="s">
+      <c r="L14" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="M14" s="27" t="s">
+      <c r="M14" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="N14" s="30"/>
+      <c r="N14" s="25"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="27" t="s">
+      <c r="A15" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="27">
+      <c r="B15" s="22">
         <v>5555626</v>
       </c>
-      <c r="C15" s="27" t="s">
+      <c r="C15" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="D15" s="23">
+      <c r="D15" s="20">
         <v>178888880001601</v>
       </c>
-      <c r="E15" s="27">
+      <c r="E15" s="22">
         <v>9999996</v>
       </c>
-      <c r="F15" s="27">
+      <c r="F15" s="22">
         <v>1000421</v>
       </c>
-      <c r="G15" s="27" t="s">
+      <c r="G15" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="H15" s="27">
+      <c r="H15" s="22">
         <v>1</v>
       </c>
-      <c r="I15" s="27">
+      <c r="I15" s="22">
         <v>2000</v>
       </c>
-      <c r="J15" s="26">
+      <c r="J15" s="21">
         <v>1</v>
       </c>
-      <c r="K15" s="29" t="s">
+      <c r="K15" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="L15" s="27" t="s">
+      <c r="L15" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="M15" s="27" t="s">
+      <c r="M15" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="N15" s="31"/>
+      <c r="N15" s="26"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="27" t="s">
+      <c r="A16" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="B16" s="27">
+      <c r="B16" s="22">
         <v>5555627</v>
       </c>
-      <c r="C16" s="27" t="s">
+      <c r="C16" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="D16" s="23">
+      <c r="D16" s="20">
         <v>100673001212128</v>
       </c>
-      <c r="E16" s="27">
+      <c r="E16" s="22">
         <v>9999996</v>
       </c>
-      <c r="F16" s="27">
+      <c r="F16" s="22">
         <v>1000421</v>
       </c>
-      <c r="G16" s="27" t="s">
+      <c r="G16" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="H16" s="27">
+      <c r="H16" s="22">
         <v>6</v>
       </c>
-      <c r="I16" s="27">
+      <c r="I16" s="22">
         <v>2000</v>
       </c>
-      <c r="J16" s="26">
+      <c r="J16" s="21">
         <v>1</v>
       </c>
-      <c r="K16" s="29" t="s">
+      <c r="K16" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="L16" s="27" t="s">
+      <c r="L16" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="M16" s="27" t="s">
+      <c r="M16" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="N16" s="31"/>
+      <c r="N16" s="26"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="27" t="s">
+      <c r="A17" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="B17" s="27">
+      <c r="B17" s="22">
         <v>5555628</v>
       </c>
-      <c r="C17" s="27" t="s">
+      <c r="C17" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="D17" s="23">
+      <c r="D17" s="20">
         <v>100673001212128</v>
       </c>
-      <c r="E17" s="27">
+      <c r="E17" s="22">
         <v>9999996</v>
       </c>
-      <c r="F17" s="27">
+      <c r="F17" s="22">
         <v>1000421</v>
       </c>
-      <c r="G17" s="27" t="s">
+      <c r="G17" s="22" t="s">
         <v>14</v>
       </c>
-      <c r="H17" s="27">
+      <c r="H17" s="22">
         <v>1</v>
       </c>
-      <c r="I17" s="27">
+      <c r="I17" s="22">
         <v>100</v>
       </c>
-      <c r="J17" s="27">
+      <c r="J17" s="22">
         <v>1.7</v>
       </c>
-      <c r="K17" s="29" t="s">
+      <c r="K17" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="L17" s="27" t="s">
+      <c r="L17" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="M17" s="27" t="s">
+      <c r="M17" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="N17" s="31"/>
+      <c r="N17" s="26"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -1703,47 +1679,47 @@
       <c r="S1" s="3"/>
       <c r="T1" s="3"/>
     </row>
-    <row r="2" spans="1:20" s="31" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="27" t="s">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.25">
+      <c r="A2" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B2" s="27">
-        <v>250520261</v>
-      </c>
-      <c r="C2" s="11">
-        <v>178888880001601</v>
-      </c>
-      <c r="D2" s="7">
-        <v>8888999</v>
-      </c>
-      <c r="E2" s="7">
-        <v>3052022</v>
-      </c>
-      <c r="F2" s="27" t="s">
+      <c r="B2" s="22">
+        <v>2952026</v>
+      </c>
+      <c r="C2" s="20">
+        <v>100673000000011</v>
+      </c>
+      <c r="D2" s="22">
+        <v>9999996</v>
+      </c>
+      <c r="E2" s="22">
+        <v>1000421</v>
+      </c>
+      <c r="F2" s="1" t="s">
         <v>29</v>
       </c>
-      <c r="G2" s="27">
-        <v>947</v>
-      </c>
-      <c r="H2" s="27">
-        <v>100</v>
-      </c>
-      <c r="I2" s="32">
-        <v>1.8</v>
-      </c>
-      <c r="J2" s="27" t="s">
-        <v>121</v>
-      </c>
-      <c r="K2" s="27" t="s">
+      <c r="G2" s="1">
         <v>15</v>
       </c>
-      <c r="L2" s="27" t="s">
+      <c r="H2" s="1">
+        <v>2000</v>
+      </c>
+      <c r="I2" s="27">
+        <v>1.7</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="K2" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="M2" s="27">
+      <c r="L2" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="M2" s="1">
         <v>11</v>
       </c>
-      <c r="N2" s="30"/>
+      <c r="N2" s="19"/>
     </row>
     <row r="3" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
@@ -1755,10 +1731,10 @@
       <c r="C3" s="2">
         <v>120733340001420</v>
       </c>
-      <c r="D3" s="27">
+      <c r="D3" s="22">
         <v>9999996</v>
       </c>
-      <c r="E3" s="27">
+      <c r="E3" s="22">
         <v>1000421</v>
       </c>
       <c r="F3" s="1" t="s">
@@ -1770,7 +1746,7 @@
       <c r="H3" s="1">
         <v>700</v>
       </c>
-      <c r="I3" s="32">
+      <c r="I3" s="27">
         <v>1.7</v>
       </c>
       <c r="J3" s="1" t="s">
@@ -1791,16 +1767,16 @@
       <c r="A4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B4" s="27">
+      <c r="B4" s="22">
         <v>4555517</v>
       </c>
-      <c r="C4" s="23">
+      <c r="C4" s="20">
         <v>100673000000011</v>
       </c>
-      <c r="D4" s="27">
+      <c r="D4" s="22">
         <v>9999996</v>
       </c>
-      <c r="E4" s="27">
+      <c r="E4" s="22">
         <v>1000421</v>
       </c>
       <c r="F4" s="1" t="s">
@@ -1812,7 +1788,7 @@
       <c r="H4" s="1">
         <v>700</v>
       </c>
-      <c r="I4" s="32">
+      <c r="I4" s="27">
         <v>1.7</v>
       </c>
       <c r="J4" s="1" t="s">
@@ -1829,95 +1805,95 @@
       </c>
       <c r="N4" s="19"/>
     </row>
-    <row r="5" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A5" s="1" t="s">
+    <row r="5" spans="1:20" s="26" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="B5" s="27">
-        <v>4555519</v>
-      </c>
-      <c r="C5" s="2">
-        <v>100673000000011</v>
-      </c>
-      <c r="D5" s="27">
-        <v>9999996</v>
-      </c>
-      <c r="E5" s="27">
-        <v>1000421</v>
-      </c>
-      <c r="F5" s="1" t="s">
+      <c r="B5" s="22">
+        <v>2952026</v>
+      </c>
+      <c r="C5" s="11">
+        <v>120484000000134</v>
+      </c>
+      <c r="D5" s="7">
+        <v>6656413</v>
+      </c>
+      <c r="E5" s="7">
+        <v>6539191</v>
+      </c>
+      <c r="F5" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="G5" s="1">
-        <v>1</v>
-      </c>
-      <c r="H5" s="1">
-        <v>100</v>
-      </c>
-      <c r="I5" s="32">
+      <c r="G5" s="22">
+        <v>15</v>
+      </c>
+      <c r="H5" s="22">
+        <v>5000</v>
+      </c>
+      <c r="I5" s="27">
         <v>1.7</v>
       </c>
-      <c r="J5" s="29" t="s">
-        <v>102</v>
-      </c>
-      <c r="K5" s="1" t="s">
+      <c r="J5" s="22" t="s">
+        <v>118</v>
+      </c>
+      <c r="K5" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="L5" s="1" t="s">
+      <c r="L5" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="M5" s="1">
+      <c r="M5" s="22">
         <v>11</v>
       </c>
-      <c r="N5" s="19"/>
+      <c r="N5" s="25"/>
     </row>
-    <row r="6" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A6" s="1" t="s">
+    <row r="6" spans="1:20" s="26" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="22" t="s">
         <v>13</v>
       </c>
-      <c r="B6" s="27">
-        <v>4555520</v>
-      </c>
-      <c r="C6" s="2">
-        <v>100673000000011</v>
-      </c>
-      <c r="D6" s="1">
-        <v>9997115</v>
-      </c>
-      <c r="E6" s="1">
-        <v>8211642</v>
-      </c>
-      <c r="F6" s="1" t="s">
+      <c r="B6" s="22">
+        <v>2952026</v>
+      </c>
+      <c r="C6" s="11">
+        <v>178888880001601</v>
+      </c>
+      <c r="D6" s="7">
+        <v>8888999</v>
+      </c>
+      <c r="E6" s="7">
+        <v>8888888</v>
+      </c>
+      <c r="F6" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="G6" s="1">
+      <c r="G6" s="22">
         <v>15</v>
       </c>
-      <c r="H6" s="1">
-        <v>700</v>
-      </c>
-      <c r="I6" s="32">
+      <c r="H6" s="22">
+        <v>5000</v>
+      </c>
+      <c r="I6" s="27">
         <v>1.7</v>
       </c>
-      <c r="J6" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K6" s="1" t="s">
+      <c r="J6" s="22" t="s">
+        <v>118</v>
+      </c>
+      <c r="K6" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="L6" s="1" t="s">
+      <c r="L6" s="22" t="s">
         <v>15</v>
       </c>
-      <c r="M6" s="1">
+      <c r="M6" s="22">
         <v>11</v>
       </c>
-      <c r="N6" s="19"/>
+      <c r="N6" s="25"/>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
       <c r="A7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B7" s="27">
+      <c r="B7" s="22">
         <v>4555522</v>
       </c>
       <c r="C7" s="2">
@@ -1938,7 +1914,7 @@
       <c r="H7" s="1">
         <v>500</v>
       </c>
-      <c r="I7" s="32">
+      <c r="I7" s="27">
         <v>1.7</v>
       </c>
       <c r="J7" s="1" t="s">
@@ -1959,7 +1935,7 @@
       <c r="A8" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B8" s="27">
+      <c r="B8" s="22">
         <v>4555524</v>
       </c>
       <c r="C8" s="2">
@@ -1980,7 +1956,7 @@
       <c r="H8" s="1">
         <v>700</v>
       </c>
-      <c r="I8" s="32">
+      <c r="I8" s="27">
         <v>1.7</v>
       </c>
       <c r="J8" s="1" t="s">
@@ -2001,7 +1977,7 @@
       <c r="A9" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B9" s="27">
+      <c r="B9" s="22">
         <v>4555526</v>
       </c>
       <c r="C9" s="2">
@@ -2022,7 +1998,7 @@
       <c r="H9" s="1">
         <v>700</v>
       </c>
-      <c r="I9" s="32">
+      <c r="I9" s="27">
         <v>1.7</v>
       </c>
       <c r="J9" s="1" t="s">
@@ -2043,7 +2019,7 @@
       <c r="A10" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B10" s="27">
+      <c r="B10" s="22">
         <v>4555528</v>
       </c>
       <c r="C10" s="2">
@@ -2064,7 +2040,7 @@
       <c r="H10" s="1">
         <v>700</v>
       </c>
-      <c r="I10" s="32">
+      <c r="I10" s="27">
         <v>1.7</v>
       </c>
       <c r="J10" s="1" t="s">
@@ -2085,7 +2061,7 @@
       <c r="A11" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B11" s="27">
+      <c r="B11" s="22">
         <v>4555530</v>
       </c>
       <c r="C11" s="2">
@@ -2106,7 +2082,7 @@
       <c r="H11" s="1">
         <v>100</v>
       </c>
-      <c r="I11" s="32">
+      <c r="I11" s="27">
         <v>1.7</v>
       </c>
       <c r="J11" s="1" t="s">
@@ -2126,7 +2102,7 @@
       <c r="A12" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B12" s="27">
+      <c r="B12" s="22">
         <v>4555532</v>
       </c>
       <c r="C12" s="2">
@@ -2147,7 +2123,7 @@
       <c r="H12" s="1">
         <v>100</v>
       </c>
-      <c r="I12" s="32">
+      <c r="I12" s="27">
         <v>1.7</v>
       </c>
       <c r="J12" s="1" t="s">
@@ -2167,16 +2143,16 @@
       <c r="A13" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B13" s="27">
+      <c r="B13" s="22">
         <v>4555534</v>
       </c>
       <c r="C13" s="2">
         <v>120733340001420</v>
       </c>
-      <c r="D13" s="27">
+      <c r="D13" s="22">
         <v>9999996</v>
       </c>
-      <c r="E13" s="27">
+      <c r="E13" s="22">
         <v>1000421</v>
       </c>
       <c r="F13" s="1" t="s">
@@ -2188,7 +2164,7 @@
       <c r="H13" s="1">
         <v>700</v>
       </c>
-      <c r="I13" s="32">
+      <c r="I13" s="27">
         <v>1.7</v>
       </c>
       <c r="J13" s="1" t="s">
@@ -2208,16 +2184,16 @@
       <c r="A14" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B14" s="27">
+      <c r="B14" s="22">
         <v>4555536</v>
       </c>
       <c r="C14" s="2">
         <v>120733340001420</v>
       </c>
-      <c r="D14" s="27">
+      <c r="D14" s="22">
         <v>9999996</v>
       </c>
-      <c r="E14" s="27">
+      <c r="E14" s="22">
         <v>1000421</v>
       </c>
       <c r="F14" s="1" t="s">
@@ -2229,7 +2205,7 @@
       <c r="H14" s="1">
         <v>700</v>
       </c>
-      <c r="I14" s="32">
+      <c r="I14" s="27">
         <v>1.7</v>
       </c>
       <c r="J14" s="1" t="s">
@@ -2249,16 +2225,16 @@
       <c r="A15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="B15" s="27">
+      <c r="B15" s="22">
         <v>4555538</v>
       </c>
       <c r="C15" s="2">
         <v>100673000000011</v>
       </c>
-      <c r="D15" s="27">
+      <c r="D15" s="22">
         <v>9999996</v>
       </c>
-      <c r="E15" s="27">
+      <c r="E15" s="22">
         <v>1000421</v>
       </c>
       <c r="F15" s="1" t="s">
@@ -2270,7 +2246,7 @@
       <c r="H15" s="1">
         <v>700</v>
       </c>
-      <c r="I15" s="32">
+      <c r="I15" s="27">
         <v>1.7</v>
       </c>
       <c r="J15" s="1" t="s">
@@ -2291,7 +2267,7 @@
       <c r="D18" s="7"/>
       <c r="E18" s="11"/>
       <c r="H18" s="17"/>
-      <c r="I18" s="28"/>
+      <c r="I18" s="23"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -2366,108 +2342,108 @@
       </c>
     </row>
     <row r="2" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" x14ac:dyDescent="0.25">
-      <c r="A2" s="29">
+      <c r="A2" s="24">
         <v>220520261</v>
       </c>
-      <c r="B2" s="29" t="s">
+      <c r="B2" s="24" t="s">
         <v>93</v>
       </c>
-      <c r="C2" s="29" t="s">
+      <c r="C2" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="D2" s="29" t="s">
+      <c r="D2" s="24" t="s">
         <v>95</v>
       </c>
-      <c r="E2" s="29">
+      <c r="E2" s="24">
         <v>2025</v>
       </c>
-      <c r="F2" s="29" t="s">
+      <c r="F2" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="G2" s="29" t="s">
+      <c r="G2" s="24" t="s">
         <v>100</v>
       </c>
-      <c r="H2" s="33">
+      <c r="H2" s="28">
         <v>100673001212128</v>
       </c>
-      <c r="I2" s="27">
+      <c r="I2" s="22">
         <v>9999996</v>
       </c>
-      <c r="J2" s="27">
+      <c r="J2" s="22">
         <v>1000421</v>
       </c>
-      <c r="K2" s="29">
+      <c r="K2" s="24">
         <v>100</v>
       </c>
-      <c r="L2" s="29">
+      <c r="L2" s="24">
         <v>6</v>
       </c>
-      <c r="M2" s="29">
+      <c r="M2" s="24">
         <v>1.7</v>
       </c>
-      <c r="N2" s="29" t="s">
+      <c r="N2" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="O2" s="29" t="s">
+      <c r="O2" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="P2" s="29" t="s">
+      <c r="P2" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="Q2" s="29" t="s">
+      <c r="Q2" s="24" t="s">
         <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" x14ac:dyDescent="0.25">
-      <c r="A3" s="29">
+      <c r="A3" s="24">
         <v>5555534</v>
       </c>
-      <c r="B3" s="29" t="s">
+      <c r="B3" s="24" t="s">
         <v>93</v>
       </c>
-      <c r="C3" s="29" t="s">
+      <c r="C3" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="29" t="s">
+      <c r="D3" s="24" t="s">
         <v>95</v>
       </c>
-      <c r="E3" s="29">
+      <c r="E3" s="24">
         <v>2025</v>
       </c>
-      <c r="F3" s="29" t="s">
+      <c r="F3" s="24" t="s">
         <v>98</v>
       </c>
-      <c r="G3" s="29" t="s">
+      <c r="G3" s="24" t="s">
         <v>100</v>
       </c>
-      <c r="H3" s="33">
+      <c r="H3" s="28">
         <v>100673001212128</v>
       </c>
-      <c r="I3" s="27">
+      <c r="I3" s="22">
         <v>9997115</v>
       </c>
-      <c r="J3" s="27">
+      <c r="J3" s="22">
         <v>9997115</v>
       </c>
-      <c r="K3" s="29">
+      <c r="K3" s="24">
         <v>100</v>
       </c>
-      <c r="L3" s="29">
+      <c r="L3" s="24">
         <v>6</v>
       </c>
-      <c r="M3" s="29">
+      <c r="M3" s="24">
         <v>0.5</v>
       </c>
-      <c r="N3" s="29" t="s">
+      <c r="N3" s="24" t="s">
         <v>102</v>
       </c>
-      <c r="O3" s="29" t="s">
+      <c r="O3" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="P3" s="29" t="s">
+      <c r="P3" s="24" t="s">
         <v>15</v>
       </c>
-      <c r="Q3" s="29" t="s">
+      <c r="Q3" s="24" t="s">
         <v>104</v>
       </c>
     </row>
@@ -2498,7 +2474,7 @@
       <c r="E5" s="7"/>
       <c r="F5" s="7"/>
       <c r="G5" s="7"/>
-      <c r="H5" s="33"/>
+      <c r="H5" s="28"/>
       <c r="I5" s="1"/>
       <c r="J5" s="1"/>
       <c r="K5" s="7"/>
@@ -2509,24 +2485,24 @@
       <c r="P5" s="7"/>
       <c r="Q5" s="19"/>
     </row>
-    <row r="6" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" s="38" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="34"/>
-      <c r="B6" s="34"/>
-      <c r="C6" s="34"/>
-      <c r="D6" s="34"/>
-      <c r="E6" s="34"/>
-      <c r="F6" s="34"/>
-      <c r="G6" s="34"/>
-      <c r="H6" s="35"/>
-      <c r="I6" s="36"/>
-      <c r="J6" s="36"/>
-      <c r="K6" s="34"/>
-      <c r="L6" s="34"/>
-      <c r="M6" s="34"/>
-      <c r="N6" s="34"/>
-      <c r="O6" s="34"/>
-      <c r="P6" s="34"/>
-      <c r="Q6" s="37"/>
+    <row r="6" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" s="33" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="29"/>
+      <c r="B6" s="29"/>
+      <c r="C6" s="29"/>
+      <c r="D6" s="29"/>
+      <c r="E6" s="29"/>
+      <c r="F6" s="29"/>
+      <c r="G6" s="29"/>
+      <c r="H6" s="30"/>
+      <c r="I6" s="31"/>
+      <c r="J6" s="31"/>
+      <c r="K6" s="29"/>
+      <c r="L6" s="29"/>
+      <c r="M6" s="29"/>
+      <c r="N6" s="29"/>
+      <c r="O6" s="29"/>
+      <c r="P6" s="29"/>
+      <c r="Q6" s="32"/>
     </row>
     <row r="7" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" x14ac:dyDescent="0.25">
       <c r="A7" s="7"/>
@@ -2536,7 +2512,7 @@
       <c r="E7" s="7"/>
       <c r="F7" s="7"/>
       <c r="G7" s="7"/>
-      <c r="H7" s="33"/>
+      <c r="H7" s="28"/>
       <c r="I7" s="1"/>
       <c r="J7" s="1"/>
       <c r="K7" s="7"/>
@@ -2574,7 +2550,7 @@
       <c r="E9" s="7"/>
       <c r="F9" s="7"/>
       <c r="G9" s="7"/>
-      <c r="H9" s="33"/>
+      <c r="H9" s="28"/>
       <c r="I9" s="1"/>
       <c r="J9" s="1"/>
       <c r="K9" s="7"/>
@@ -2612,7 +2588,7 @@
       <c r="E11" s="7"/>
       <c r="F11" s="7"/>
       <c r="G11" s="7"/>
-      <c r="H11" s="33"/>
+      <c r="H11" s="28"/>
       <c r="I11" s="1"/>
       <c r="J11" s="1"/>
       <c r="K11" s="7"/>
@@ -2650,7 +2626,7 @@
       <c r="E13" s="7"/>
       <c r="F13" s="7"/>
       <c r="G13" s="7"/>
-      <c r="H13" s="33"/>
+      <c r="H13" s="28"/>
       <c r="I13" s="1"/>
       <c r="J13" s="1"/>
       <c r="K13" s="7"/>
@@ -2688,7 +2664,7 @@
       <c r="E15" s="7"/>
       <c r="F15" s="7"/>
       <c r="G15" s="7"/>
-      <c r="H15" s="33"/>
+      <c r="H15" s="28"/>
       <c r="I15" s="1"/>
       <c r="J15" s="1"/>
       <c r="K15" s="7"/>
@@ -8864,7 +8840,7 @@
       <c r="E17" s="7"/>
       <c r="F17" s="7"/>
       <c r="G17" s="7"/>
-      <c r="H17" s="33"/>
+      <c r="H17" s="28"/>
       <c r="I17" s="1"/>
       <c r="J17" s="1"/>
       <c r="K17" s="7"/>
@@ -18189,22 +18165,22 @@
         <v>70</v>
       </c>
       <c r="B2" s="7">
-        <v>1655555</v>
+        <v>270520262</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>29</v>
       </c>
-      <c r="D2" s="7">
+      <c r="D2" s="11">
         <v>11</v>
       </c>
       <c r="E2" s="7">
-        <v>9999996</v>
+        <v>8888999</v>
       </c>
       <c r="F2" s="7">
-        <v>1000421</v>
+        <v>8888888</v>
       </c>
       <c r="G2" s="11">
-        <v>120733340001420</v>
+        <v>178888880001601</v>
       </c>
       <c r="H2" s="7">
         <v>1003</v>
@@ -18213,7 +18189,7 @@
         <v>73</v>
       </c>
       <c r="J2" s="7">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="K2" s="7">
         <v>10</v>
@@ -18222,7 +18198,7 @@
         <v>77</v>
       </c>
       <c r="M2" s="7">
-        <v>5</v>
+        <v>100</v>
       </c>
       <c r="N2" s="7" t="s">
         <v>79</v>
@@ -18319,773 +18295,293 @@
       </c>
       <c r="O4" s="7"/>
     </row>
-    <row r="5" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A5" s="25" t="s">
-        <v>70</v>
-      </c>
-      <c r="B5" s="20">
-        <v>5555554</v>
-      </c>
-      <c r="C5" s="20" t="s">
-        <v>29</v>
-      </c>
-      <c r="D5" s="20">
-        <v>11</v>
-      </c>
-      <c r="E5" s="24">
-        <v>9996059</v>
-      </c>
-      <c r="F5" s="22">
-        <v>5750013</v>
-      </c>
-      <c r="G5" s="21">
-        <v>100673000000011</v>
-      </c>
-      <c r="H5" s="20">
-        <v>1003</v>
-      </c>
-      <c r="I5" s="20" t="s">
-        <v>73</v>
-      </c>
-      <c r="J5" s="20">
-        <v>10</v>
-      </c>
-      <c r="K5" s="20">
-        <v>10</v>
-      </c>
-      <c r="L5" s="20" t="s">
-        <v>77</v>
-      </c>
-      <c r="M5" s="20">
-        <v>50</v>
-      </c>
-      <c r="N5" s="20" t="s">
-        <v>79</v>
-      </c>
-      <c r="O5" s="20" t="s">
-        <v>113</v>
-      </c>
+    <row r="5" spans="1:15" s="26" customFormat="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="34"/>
+      <c r="B5" s="24"/>
+      <c r="C5" s="24"/>
+      <c r="D5" s="24"/>
+      <c r="E5" s="35"/>
+      <c r="F5" s="22"/>
+      <c r="G5" s="28"/>
+      <c r="H5" s="24"/>
+      <c r="I5" s="24"/>
+      <c r="J5" s="24"/>
+      <c r="K5" s="24"/>
+      <c r="L5" s="24"/>
+      <c r="M5" s="24"/>
+      <c r="N5" s="24"/>
+      <c r="O5" s="24"/>
     </row>
     <row r="6" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A6" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="B6" s="7">
-        <v>5555555</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D6" s="7">
-        <v>11</v>
-      </c>
-      <c r="E6" s="7">
-        <v>9999996</v>
-      </c>
-      <c r="F6" s="7">
-        <v>1000421</v>
-      </c>
-      <c r="G6" s="11">
-        <v>100673000000011</v>
-      </c>
-      <c r="H6" s="7">
-        <v>1003</v>
-      </c>
-      <c r="I6" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="J6" s="7">
-        <v>1</v>
-      </c>
-      <c r="K6" s="7">
-        <v>10</v>
-      </c>
-      <c r="L6" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="M6" s="7">
-        <v>50</v>
-      </c>
-      <c r="N6" s="7" t="s">
-        <v>79</v>
-      </c>
-      <c r="O6" s="7" t="s">
-        <v>114</v>
-      </c>
+      <c r="A6" s="10"/>
+      <c r="B6" s="7"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="7"/>
+      <c r="G6" s="11"/>
+      <c r="H6" s="7"/>
+      <c r="I6" s="7"/>
+      <c r="J6" s="7"/>
+      <c r="K6" s="7"/>
+      <c r="L6" s="7"/>
+      <c r="M6" s="7"/>
+      <c r="N6" s="7"/>
+      <c r="O6" s="7"/>
     </row>
     <row r="7" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A7" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="B7" s="7">
-        <v>5555556</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D7" s="7">
-        <v>11</v>
-      </c>
-      <c r="E7" s="7">
-        <v>9999996</v>
-      </c>
-      <c r="F7" s="7">
-        <v>1000421</v>
-      </c>
-      <c r="G7" s="11">
-        <v>100673000000011</v>
-      </c>
-      <c r="H7" s="7">
-        <v>1003</v>
-      </c>
-      <c r="I7" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="J7" s="7">
-        <v>1</v>
-      </c>
-      <c r="K7" s="7">
-        <v>10</v>
-      </c>
-      <c r="L7" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="M7" s="7">
-        <v>1</v>
-      </c>
-      <c r="N7" s="7" t="s">
-        <v>79</v>
-      </c>
+      <c r="A7" s="10"/>
+      <c r="B7" s="7"/>
+      <c r="C7" s="7"/>
+      <c r="D7" s="7"/>
+      <c r="E7" s="7"/>
+      <c r="F7" s="7"/>
+      <c r="G7" s="11"/>
+      <c r="H7" s="7"/>
+      <c r="I7" s="7"/>
+      <c r="J7" s="7"/>
+      <c r="K7" s="7"/>
+      <c r="L7" s="7"/>
+      <c r="M7" s="7"/>
+      <c r="N7" s="7"/>
       <c r="O7" s="7"/>
     </row>
     <row r="8" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A8" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="B8" s="7">
-        <v>5555557</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D8" s="7">
-        <v>11</v>
-      </c>
-      <c r="E8" s="7">
-        <v>9999996</v>
-      </c>
-      <c r="F8" s="7">
-        <v>1000421</v>
-      </c>
-      <c r="G8" s="11">
-        <v>100673000000011</v>
-      </c>
-      <c r="H8" s="7">
-        <v>1003</v>
-      </c>
-      <c r="I8" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="J8" s="7">
-        <v>10</v>
-      </c>
-      <c r="K8" s="7">
-        <v>10</v>
-      </c>
-      <c r="L8" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="M8" s="7">
-        <v>50</v>
-      </c>
-      <c r="N8" s="7" t="s">
-        <v>79</v>
-      </c>
+      <c r="A8" s="10"/>
+      <c r="B8" s="7"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="7"/>
+      <c r="F8" s="7"/>
+      <c r="G8" s="11"/>
+      <c r="H8" s="7"/>
+      <c r="I8" s="7"/>
+      <c r="J8" s="7"/>
+      <c r="K8" s="7"/>
+      <c r="L8" s="7"/>
+      <c r="M8" s="7"/>
+      <c r="N8" s="7"/>
       <c r="O8" s="7"/>
     </row>
     <row r="9" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A9" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="B9" s="7">
-        <v>5555558</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D9" s="7">
-        <v>11</v>
-      </c>
-      <c r="E9" s="7">
-        <v>9999996</v>
-      </c>
-      <c r="F9" s="7">
-        <v>1000421</v>
-      </c>
-      <c r="G9" s="11">
-        <v>100673000000011</v>
-      </c>
-      <c r="H9" s="7">
-        <v>1003</v>
-      </c>
-      <c r="I9" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="J9" s="7">
-        <v>10</v>
-      </c>
-      <c r="K9" s="7">
-        <v>10</v>
-      </c>
-      <c r="L9" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="M9" s="7">
-        <v>50</v>
-      </c>
-      <c r="N9" s="7" t="s">
-        <v>79</v>
-      </c>
+      <c r="A9" s="10"/>
+      <c r="B9" s="7"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="7"/>
+      <c r="F9" s="7"/>
+      <c r="G9" s="11"/>
+      <c r="H9" s="7"/>
+      <c r="I9" s="7"/>
+      <c r="J9" s="7"/>
+      <c r="K9" s="7"/>
+      <c r="L9" s="7"/>
+      <c r="M9" s="7"/>
+      <c r="N9" s="7"/>
       <c r="O9" s="7"/>
     </row>
     <row r="10" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A10" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="B10" s="7">
-        <v>5555559</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D10" s="7">
-        <v>11</v>
-      </c>
-      <c r="E10" s="7">
-        <v>9999996</v>
-      </c>
-      <c r="F10" s="7">
-        <v>1000421</v>
-      </c>
-      <c r="G10" s="11">
-        <v>100673000000011</v>
-      </c>
-      <c r="H10" s="7">
-        <v>1003</v>
-      </c>
-      <c r="I10" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="J10" s="7">
-        <v>10</v>
-      </c>
-      <c r="K10" s="7">
-        <v>10</v>
-      </c>
-      <c r="L10" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="M10" s="7">
-        <v>50</v>
-      </c>
-      <c r="N10" s="7" t="s">
-        <v>79</v>
-      </c>
+      <c r="A10" s="10"/>
+      <c r="B10" s="7"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="7"/>
+      <c r="F10" s="7"/>
+      <c r="G10" s="11"/>
+      <c r="H10" s="7"/>
+      <c r="I10" s="7"/>
+      <c r="J10" s="7"/>
+      <c r="K10" s="7"/>
+      <c r="L10" s="7"/>
+      <c r="M10" s="7"/>
+      <c r="N10" s="7"/>
       <c r="O10" s="7"/>
     </row>
     <row r="11" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A11" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="B11" s="7">
-        <v>5555560</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D11" s="7">
-        <v>11</v>
-      </c>
-      <c r="E11" s="7">
-        <v>9999996</v>
-      </c>
-      <c r="F11" s="7">
-        <v>1000421</v>
-      </c>
-      <c r="G11" s="11">
-        <v>100673000000011</v>
-      </c>
-      <c r="H11" s="7">
-        <v>1003</v>
-      </c>
-      <c r="I11" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="J11" s="7">
-        <v>10</v>
-      </c>
-      <c r="K11" s="7">
-        <v>10</v>
-      </c>
-      <c r="L11" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="M11" s="7">
-        <v>50</v>
-      </c>
-      <c r="N11" s="7" t="s">
-        <v>79</v>
-      </c>
+      <c r="A11" s="10"/>
+      <c r="B11" s="7"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="7"/>
+      <c r="F11" s="7"/>
+      <c r="G11" s="11"/>
+      <c r="H11" s="7"/>
+      <c r="I11" s="7"/>
+      <c r="J11" s="7"/>
+      <c r="K11" s="7"/>
+      <c r="L11" s="7"/>
+      <c r="M11" s="7"/>
+      <c r="N11" s="7"/>
       <c r="O11" s="7"/>
     </row>
     <row r="12" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A12" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="B12" s="7">
-        <v>5555561</v>
-      </c>
-      <c r="C12" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D12" s="7">
-        <v>11</v>
-      </c>
-      <c r="E12" s="7">
-        <v>9999996</v>
-      </c>
-      <c r="F12" s="7">
-        <v>1000421</v>
-      </c>
-      <c r="G12" s="11">
-        <v>100673000000011</v>
-      </c>
-      <c r="H12" s="7">
-        <v>1003</v>
-      </c>
-      <c r="I12" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="J12" s="7">
-        <v>10</v>
-      </c>
-      <c r="K12" s="7">
-        <v>10</v>
-      </c>
-      <c r="L12" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="M12" s="7">
-        <v>50</v>
-      </c>
-      <c r="N12" s="7" t="s">
-        <v>79</v>
-      </c>
+      <c r="A12" s="10"/>
+      <c r="B12" s="7"/>
+      <c r="C12" s="7"/>
+      <c r="D12" s="7"/>
+      <c r="E12" s="7"/>
+      <c r="F12" s="7"/>
+      <c r="G12" s="11"/>
+      <c r="H12" s="7"/>
+      <c r="I12" s="7"/>
+      <c r="J12" s="7"/>
+      <c r="K12" s="7"/>
+      <c r="L12" s="7"/>
+      <c r="M12" s="7"/>
+      <c r="N12" s="7"/>
       <c r="O12" s="7"/>
     </row>
     <row r="13" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A13" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="B13" s="7">
-        <v>5555562</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D13" s="7">
-        <v>11</v>
-      </c>
-      <c r="E13" s="7">
-        <v>9999996</v>
-      </c>
-      <c r="F13" s="7">
-        <v>1000421</v>
-      </c>
-      <c r="G13" s="11">
-        <v>100673000000011</v>
-      </c>
-      <c r="H13" s="7">
-        <v>1003</v>
-      </c>
-      <c r="I13" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="J13" s="7">
-        <v>10</v>
-      </c>
-      <c r="K13" s="7">
-        <v>10</v>
-      </c>
-      <c r="L13" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="M13" s="7">
-        <v>50</v>
-      </c>
-      <c r="N13" s="7" t="s">
-        <v>79</v>
-      </c>
+      <c r="A13" s="10"/>
+      <c r="B13" s="7"/>
+      <c r="C13" s="7"/>
+      <c r="D13" s="7"/>
+      <c r="E13" s="7"/>
+      <c r="F13" s="7"/>
+      <c r="G13" s="11"/>
+      <c r="H13" s="7"/>
+      <c r="I13" s="7"/>
+      <c r="J13" s="7"/>
+      <c r="K13" s="7"/>
+      <c r="L13" s="7"/>
+      <c r="M13" s="7"/>
+      <c r="N13" s="7"/>
       <c r="O13" s="7"/>
     </row>
     <row r="14" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A14" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="B14" s="7">
-        <v>5555563</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D14" s="7">
-        <v>11</v>
-      </c>
-      <c r="E14" s="7">
-        <v>9999996</v>
-      </c>
-      <c r="F14" s="7">
-        <v>1000421</v>
-      </c>
-      <c r="G14" s="11">
-        <v>100673000000011</v>
-      </c>
-      <c r="H14" s="7">
-        <v>1003</v>
-      </c>
-      <c r="I14" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="J14" s="7">
-        <v>10</v>
-      </c>
-      <c r="K14" s="7">
-        <v>10</v>
-      </c>
-      <c r="L14" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="M14" s="7">
-        <v>50</v>
-      </c>
-      <c r="N14" s="7" t="s">
-        <v>79</v>
-      </c>
+      <c r="A14" s="10"/>
+      <c r="B14" s="7"/>
+      <c r="C14" s="7"/>
+      <c r="D14" s="7"/>
+      <c r="E14" s="7"/>
+      <c r="F14" s="7"/>
+      <c r="G14" s="11"/>
+      <c r="H14" s="7"/>
+      <c r="I14" s="7"/>
+      <c r="J14" s="7"/>
+      <c r="K14" s="7"/>
+      <c r="L14" s="7"/>
+      <c r="M14" s="7"/>
+      <c r="N14" s="7"/>
       <c r="O14" s="7"/>
     </row>
     <row r="15" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A15" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="B15" s="7">
-        <v>5555564</v>
-      </c>
-      <c r="C15" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D15" s="7">
-        <v>11</v>
-      </c>
-      <c r="E15" s="7">
-        <v>9999996</v>
-      </c>
-      <c r="F15" s="7">
-        <v>1000421</v>
-      </c>
-      <c r="G15" s="11">
-        <v>100673000000011</v>
-      </c>
-      <c r="H15" s="7">
-        <v>1003</v>
-      </c>
-      <c r="I15" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="J15" s="7">
-        <v>10</v>
-      </c>
-      <c r="K15" s="7">
-        <v>10</v>
-      </c>
-      <c r="L15" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="M15" s="7">
-        <v>50</v>
-      </c>
-      <c r="N15" s="7" t="s">
-        <v>79</v>
-      </c>
+      <c r="A15" s="10"/>
+      <c r="B15" s="7"/>
+      <c r="C15" s="7"/>
+      <c r="D15" s="7"/>
+      <c r="E15" s="7"/>
+      <c r="F15" s="7"/>
+      <c r="G15" s="11"/>
+      <c r="H15" s="7"/>
+      <c r="I15" s="7"/>
+      <c r="J15" s="7"/>
+      <c r="K15" s="7"/>
+      <c r="L15" s="7"/>
+      <c r="M15" s="7"/>
+      <c r="N15" s="7"/>
       <c r="O15" s="7"/>
     </row>
     <row r="16" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A16" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="B16" s="7">
-        <v>5555565</v>
-      </c>
-      <c r="C16" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D16" s="7">
-        <v>11</v>
-      </c>
-      <c r="E16" s="7">
-        <v>9999996</v>
-      </c>
-      <c r="F16" s="7">
-        <v>1000421</v>
-      </c>
-      <c r="G16" s="11">
-        <v>100673000000011</v>
-      </c>
-      <c r="H16" s="7">
-        <v>1003</v>
-      </c>
-      <c r="I16" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="J16" s="7">
-        <v>10</v>
-      </c>
-      <c r="K16" s="7">
-        <v>10</v>
-      </c>
-      <c r="L16" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="M16" s="7">
-        <v>50</v>
-      </c>
-      <c r="N16" s="7" t="s">
-        <v>79</v>
-      </c>
+      <c r="A16" s="10"/>
+      <c r="B16" s="7"/>
+      <c r="C16" s="7"/>
+      <c r="D16" s="7"/>
+      <c r="E16" s="7"/>
+      <c r="F16" s="7"/>
+      <c r="G16" s="11"/>
+      <c r="H16" s="7"/>
+      <c r="I16" s="7"/>
+      <c r="J16" s="7"/>
+      <c r="K16" s="7"/>
+      <c r="L16" s="7"/>
+      <c r="M16" s="7"/>
+      <c r="N16" s="7"/>
       <c r="O16" s="7"/>
     </row>
     <row r="17" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A17" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="B17" s="7">
-        <v>5555566</v>
-      </c>
-      <c r="C17" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D17" s="7">
-        <v>11</v>
-      </c>
-      <c r="E17" s="7">
-        <v>9999996</v>
-      </c>
-      <c r="F17" s="7">
-        <v>1000421</v>
-      </c>
-      <c r="G17" s="11">
-        <v>100673000000011</v>
-      </c>
-      <c r="H17" s="7">
-        <v>1003</v>
-      </c>
-      <c r="I17" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="J17" s="7">
-        <v>10</v>
-      </c>
-      <c r="K17" s="7">
-        <v>10</v>
-      </c>
-      <c r="L17" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="M17" s="7">
-        <v>50</v>
-      </c>
-      <c r="N17" s="7" t="s">
-        <v>79</v>
-      </c>
+      <c r="A17" s="10"/>
+      <c r="B17" s="7"/>
+      <c r="C17" s="7"/>
+      <c r="D17" s="7"/>
+      <c r="E17" s="7"/>
+      <c r="F17" s="7"/>
+      <c r="G17" s="11"/>
+      <c r="H17" s="7"/>
+      <c r="I17" s="7"/>
+      <c r="J17" s="7"/>
+      <c r="K17" s="7"/>
+      <c r="L17" s="7"/>
+      <c r="M17" s="7"/>
+      <c r="N17" s="7"/>
       <c r="O17" s="7"/>
     </row>
     <row r="18" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A18" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="B18" s="7">
-        <v>5555567</v>
-      </c>
-      <c r="C18" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D18" s="7">
-        <v>11</v>
-      </c>
-      <c r="E18" s="7">
-        <v>9999996</v>
-      </c>
-      <c r="F18" s="7">
-        <v>1000421</v>
-      </c>
-      <c r="G18" s="11">
-        <v>100673000000011</v>
-      </c>
-      <c r="H18" s="7">
-        <v>1003</v>
-      </c>
-      <c r="I18" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="J18" s="7">
-        <v>10</v>
-      </c>
-      <c r="K18" s="7">
-        <v>10</v>
-      </c>
-      <c r="L18" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="M18" s="7">
-        <v>50</v>
-      </c>
-      <c r="N18" s="7" t="s">
-        <v>79</v>
-      </c>
+      <c r="A18" s="10"/>
+      <c r="B18" s="7"/>
+      <c r="C18" s="7"/>
+      <c r="D18" s="7"/>
+      <c r="E18" s="7"/>
+      <c r="F18" s="7"/>
+      <c r="G18" s="11"/>
+      <c r="H18" s="7"/>
+      <c r="I18" s="7"/>
+      <c r="J18" s="7"/>
+      <c r="K18" s="7"/>
+      <c r="L18" s="7"/>
+      <c r="M18" s="7"/>
+      <c r="N18" s="7"/>
       <c r="O18" s="7"/>
     </row>
     <row r="19" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A19" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="B19" s="7">
-        <v>5555568</v>
-      </c>
-      <c r="C19" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D19" s="7">
-        <v>11</v>
-      </c>
-      <c r="E19" s="7">
-        <v>9999996</v>
-      </c>
-      <c r="F19" s="7">
-        <v>1000421</v>
-      </c>
-      <c r="G19" s="11">
-        <v>100673000000011</v>
-      </c>
-      <c r="H19" s="7">
-        <v>1003</v>
-      </c>
-      <c r="I19" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="J19" s="7">
-        <v>10</v>
-      </c>
-      <c r="K19" s="7">
-        <v>10</v>
-      </c>
-      <c r="L19" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="M19" s="7">
-        <v>50</v>
-      </c>
-      <c r="N19" s="7" t="s">
-        <v>79</v>
-      </c>
+      <c r="A19" s="10"/>
+      <c r="B19" s="7"/>
+      <c r="C19" s="7"/>
+      <c r="D19" s="7"/>
+      <c r="E19" s="7"/>
+      <c r="F19" s="7"/>
+      <c r="G19" s="11"/>
+      <c r="H19" s="7"/>
+      <c r="I19" s="7"/>
+      <c r="J19" s="7"/>
+      <c r="K19" s="7"/>
+      <c r="L19" s="7"/>
+      <c r="M19" s="7"/>
+      <c r="N19" s="7"/>
       <c r="O19" s="7"/>
     </row>
     <row r="20" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A20" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="B20" s="7">
-        <v>5555569</v>
-      </c>
-      <c r="C20" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D20" s="7">
-        <v>11</v>
-      </c>
-      <c r="E20" s="7">
-        <v>9999996</v>
-      </c>
-      <c r="F20" s="7">
-        <v>1000421</v>
-      </c>
-      <c r="G20" s="11">
-        <v>100673000000011</v>
-      </c>
-      <c r="H20" s="7">
-        <v>1003</v>
-      </c>
-      <c r="I20" s="7" t="s">
-        <v>73</v>
-      </c>
-      <c r="J20" s="7">
-        <v>10</v>
-      </c>
-      <c r="K20" s="7">
-        <v>10</v>
-      </c>
-      <c r="L20" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="M20" s="7">
-        <v>50</v>
-      </c>
-      <c r="N20" s="7" t="s">
-        <v>79</v>
-      </c>
+      <c r="A20" s="10"/>
+      <c r="B20" s="7"/>
+      <c r="C20" s="7"/>
+      <c r="D20" s="7"/>
+      <c r="E20" s="7"/>
+      <c r="F20" s="7"/>
+      <c r="G20" s="11"/>
+      <c r="H20" s="7"/>
+      <c r="I20" s="7"/>
+      <c r="J20" s="7"/>
+      <c r="K20" s="7"/>
+      <c r="L20" s="7"/>
+      <c r="M20" s="7"/>
+      <c r="N20" s="7"/>
       <c r="O20" s="7"/>
     </row>
     <row r="21" spans="1:15" x14ac:dyDescent="0.25">
-      <c r="A21" s="10" t="s">
-        <v>70</v>
-      </c>
-      <c r="B21" s="7">
-        <v>5555570</v>
-      </c>
-      <c r="C21" s="7" t="s">
-        <v>29</v>
-      </c>
-      <c r="D21" s="7">
-        <v>11</v>
-      </c>
-      <c r="E21" s="7">
-        <v>9996059</v>
-      </c>
-      <c r="F21" s="7">
-        <v>5750013</v>
-      </c>
-      <c r="G21" s="11">
-        <v>178888880001601</v>
-      </c>
-      <c r="H21" s="7">
-        <v>1001</v>
-      </c>
-      <c r="I21" s="7" t="s">
-        <v>117</v>
-      </c>
-      <c r="J21" s="7">
-        <v>20</v>
-      </c>
-      <c r="K21" s="7">
-        <v>20</v>
-      </c>
-      <c r="L21" s="7" t="s">
-        <v>77</v>
-      </c>
-      <c r="M21" s="7">
-        <v>100</v>
-      </c>
-      <c r="N21" s="7" t="s">
-        <v>79</v>
-      </c>
+      <c r="A21" s="10"/>
+      <c r="B21" s="7"/>
+      <c r="C21" s="7"/>
+      <c r="D21" s="7"/>
+      <c r="E21" s="7"/>
+      <c r="F21" s="7"/>
+      <c r="G21" s="11"/>
+      <c r="H21" s="7"/>
+      <c r="I21" s="7"/>
+      <c r="J21" s="7"/>
+      <c r="K21" s="7"/>
+      <c r="L21" s="7"/>
+      <c r="M21" s="7"/>
+      <c r="N21" s="7"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -19229,13 +18725,13 @@
         <v>1000012</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>120</v>
+        <v>117</v>
       </c>
       <c r="J2" s="1">
         <v>130009</v>
       </c>
       <c r="K2" s="1">
-        <v>8500</v>
+        <v>3400</v>
       </c>
       <c r="L2" s="1">
         <v>5000</v>
@@ -19289,7 +18785,7 @@
         <v>100</v>
       </c>
       <c r="AC2" s="7">
-        <v>50</v>
+        <v>20</v>
       </c>
     </row>
   </sheetData>
@@ -19299,7 +18795,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ECF7E842-C9CD-4111-B0BA-C4A8FEE6BCD1}">
-  <dimension ref="A1:AB31"/>
+  <dimension ref="A1:AC31"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="12" bestFit="1" customWidth="1"/>
@@ -19313,7 +18809,7 @@
     <col min="21" max="21" width="15.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A1" s="13" t="s">
         <v>31</v>
       </c>
@@ -19351,7 +18847,7 @@
         <v>89</v>
       </c>
       <c r="M1" s="13" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="N1" s="13" t="s">
         <v>38</v>
@@ -19398,8 +18894,11 @@
       <c r="AB1" s="13" t="s">
         <v>57</v>
       </c>
+      <c r="AC1" s="13" t="s">
+        <v>111</v>
+      </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:29" x14ac:dyDescent="0.25">
       <c r="A2" s="7">
         <v>53409</v>
       </c>
@@ -19416,10 +18915,10 @@
         <v>60</v>
       </c>
       <c r="F2" s="7">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="G2" s="7">
-        <v>4000</v>
+        <v>5000</v>
       </c>
       <c r="H2" s="7">
         <v>30</v>
@@ -19431,19 +18930,19 @@
         <v>2</v>
       </c>
       <c r="K2" s="7">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="L2" s="7">
         <v>10</v>
       </c>
       <c r="M2" s="7" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="N2" s="7">
         <v>46202558</v>
       </c>
       <c r="O2" s="7">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="P2" s="7">
         <v>1</v>
@@ -19482,46 +18981,49 @@
         <v>179</v>
       </c>
       <c r="AB2" s="7">
-        <v>200</v>
+        <v>100</v>
+      </c>
+      <c r="AC2" s="19">
+        <v>100</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:29" x14ac:dyDescent="0.25">
       <c r="I4" s="14"/>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:29" x14ac:dyDescent="0.25">
       <c r="I5" s="9"/>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:29" x14ac:dyDescent="0.25">
       <c r="I6" s="9"/>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:29" x14ac:dyDescent="0.25">
       <c r="I7" s="9"/>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:29" x14ac:dyDescent="0.25">
       <c r="I8" s="9"/>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:29" x14ac:dyDescent="0.25">
       <c r="I9" s="9"/>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:29" x14ac:dyDescent="0.25">
       <c r="I10" s="9"/>
     </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:29" x14ac:dyDescent="0.25">
       <c r="I11" s="9"/>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:29" x14ac:dyDescent="0.25">
       <c r="I12" s="9"/>
     </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:29" x14ac:dyDescent="0.25">
       <c r="I13" s="9"/>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:29" x14ac:dyDescent="0.25">
       <c r="I14" s="8"/>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:29" x14ac:dyDescent="0.25">
       <c r="I15" s="8"/>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:29" x14ac:dyDescent="0.25">
       <c r="I16" s="8"/>
     </row>
     <row r="17" spans="9:9" x14ac:dyDescent="0.25">
@@ -19608,7 +19110,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="19">
-        <v>32170092</v>
+        <v>420940</v>
       </c>
       <c r="B2" s="19">
         <v>180</v>
@@ -19652,12 +19154,12 @@
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F10" t="s">
-        <v>118</v>
+        <v>115</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="F11" t="s">
-        <v>119</v>
+        <v>116</v>
       </c>
     </row>
   </sheetData>

--- a/Data/ENWR_Creation.xlsx
+++ b/Data/ENWR_Creation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{463210FD-0A44-46A1-9358-53635E059C5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F92B5BA1-CC28-4D9D-9EE3-1D8EB876CC32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="3" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RP_Deposite_Request_Agriculture" sheetId="1" r:id="rId1"/>
@@ -1684,7 +1684,7 @@
         <v>13</v>
       </c>
       <c r="B2" s="22">
-        <v>2952026</v>
+        <v>1762026</v>
       </c>
       <c r="C2" s="20">
         <v>100673000000011</v>
@@ -19110,7 +19110,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="19">
-        <v>420940</v>
+        <v>420941</v>
       </c>
       <c r="B2" s="19">
         <v>180</v>

--- a/Data/ENWR_Creation.xlsx
+++ b/Data/ENWR_Creation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F92B5BA1-CC28-4D9D-9EE3-1D8EB876CC32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D439A12E-EFCE-4812-BF23-59BB904BE67C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RP_Deposite_Request_Agriculture" sheetId="1" r:id="rId1"/>
@@ -2343,7 +2343,7 @@
     </row>
     <row r="2" spans="1:1018 1032:2042 2056:3066 3080:4090 4104:5114 5128:6138 6152:7162 7176:8186 8200:9210 9224:10234 10248:11258 11272:12282 12296:13306 13320:14330 14344:15354 15368:16378" x14ac:dyDescent="0.25">
       <c r="A2" s="24">
-        <v>220520261</v>
+        <v>18062026</v>
       </c>
       <c r="B2" s="24" t="s">
         <v>93</v>

--- a/Data/ENWR_Creation.xlsx
+++ b/Data/ENWR_Creation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D439A12E-EFCE-4812-BF23-59BB904BE67C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C5AEE15-702D-4328-88FD-92159D7A404E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="1" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RP_Deposite_Request_Agriculture" sheetId="1" r:id="rId1"/>
@@ -395,10 +395,10 @@
     <t>Ali 93</t>
   </si>
   <si>
-    <t>hdjh123</t>
+    <t>DRUM</t>
   </si>
   <si>
-    <t>DRUM</t>
+    <t>Abhi9090</t>
   </si>
 </sst>
 </file>
@@ -1834,7 +1834,7 @@
         <v>1.7</v>
       </c>
       <c r="J5" s="22" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K5" s="22" t="s">
         <v>15</v>
@@ -1876,7 +1876,7 @@
         <v>1.7</v>
       </c>
       <c r="J6" s="22" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="K6" s="22" t="s">
         <v>15</v>
@@ -18719,19 +18719,19 @@
         <v>973015</v>
       </c>
       <c r="G2" s="1">
-        <v>100003</v>
+        <v>100005</v>
       </c>
       <c r="H2" s="1">
         <v>1000012</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="J2" s="1">
-        <v>130009</v>
+        <v>19062026</v>
       </c>
       <c r="K2" s="1">
-        <v>3400</v>
+        <v>170</v>
       </c>
       <c r="L2" s="1">
         <v>5000</v>
@@ -18776,7 +18776,7 @@
         <v>401202</v>
       </c>
       <c r="Z2" s="1">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="AA2" s="1">
         <v>10000</v>

--- a/Data/ENWR_Creation.xlsx
+++ b/Data/ENWR_Creation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3C5AEE15-702D-4328-88FD-92159D7A404E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9DF5D58-9642-489D-9EDC-80662A00EA87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="4" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RP_Deposite_Request_Agriculture" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="350" uniqueCount="119">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="132">
   <si>
     <t>commoditySegment</t>
   </si>
@@ -398,7 +398,46 @@
     <t>DRUM</t>
   </si>
   <si>
-    <t>Abhi9090</t>
+    <t>BABU2</t>
+  </si>
+  <si>
+    <t>Dispatch_Source</t>
+  </si>
+  <si>
+    <t>NameofSLA</t>
+  </si>
+  <si>
+    <t>Type_of_Gunny_Bags</t>
+  </si>
+  <si>
+    <t>Weight_of_Gunny_Bags</t>
+  </si>
+  <si>
+    <t>Status_of_Gunny_Bags</t>
+  </si>
+  <si>
+    <t>Gunny_Bags_Stenciled</t>
+  </si>
+  <si>
+    <t>Gunny_Bags_QR_Tagged</t>
+  </si>
+  <si>
+    <t>Gunny_Bags_Machine_Stitched</t>
+  </si>
+  <si>
+    <t>Others</t>
+  </si>
+  <si>
+    <t>Laxmi Product</t>
+  </si>
+  <si>
+    <t>SBT</t>
+  </si>
+  <si>
+    <t>Old</t>
+  </si>
+  <si>
+    <t>Yes</t>
   </si>
 </sst>
 </file>
@@ -18590,7 +18629,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7F8B609F-0B76-470F-B64C-87241C540723}">
-  <dimension ref="A1:AC2"/>
+  <dimension ref="A1:AK2"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.140625" bestFit="1" customWidth="1"/>
@@ -18608,9 +18647,11 @@
     <col min="20" max="20" width="14.140625" bestFit="1" customWidth="1"/>
     <col min="24" max="24" width="10" bestFit="1" customWidth="1"/>
     <col min="26" max="27" width="10" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="16.140625" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="28.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>31</v>
       </c>
@@ -18698,8 +18739,32 @@
       <c r="AC1" s="5" t="s">
         <v>111</v>
       </c>
+      <c r="AD1" s="5" t="s">
+        <v>119</v>
+      </c>
+      <c r="AE1" s="5" t="s">
+        <v>120</v>
+      </c>
+      <c r="AF1" s="5" t="s">
+        <v>121</v>
+      </c>
+      <c r="AG1" s="5" t="s">
+        <v>122</v>
+      </c>
+      <c r="AH1" s="5" t="s">
+        <v>123</v>
+      </c>
+      <c r="AI1" s="5" t="s">
+        <v>124</v>
+      </c>
+      <c r="AJ1" s="5" t="s">
+        <v>125</v>
+      </c>
+      <c r="AK1" s="5" t="s">
+        <v>126</v>
+      </c>
     </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:37" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>22442</v>
       </c>
@@ -18786,6 +18851,30 @@
       </c>
       <c r="AC2" s="7">
         <v>20</v>
+      </c>
+      <c r="AD2" s="7" t="s">
+        <v>127</v>
+      </c>
+      <c r="AE2" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="AF2" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="AG2" s="7">
+        <v>100</v>
+      </c>
+      <c r="AH2" s="7" t="s">
+        <v>130</v>
+      </c>
+      <c r="AI2" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="AJ2" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="AK2" s="7" t="s">
+        <v>131</v>
       </c>
     </row>
   </sheetData>

--- a/Data/ENWR_Creation.xlsx
+++ b/Data/ENWR_Creation.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E9DF5D58-9642-489D-9EDC-80662A00EA87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{283B9574-ACC3-4139-9962-26C7C5988399}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="19800" windowHeight="11760" firstSheet="2" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="19770" windowHeight="11760" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="RP_Deposite_Request_Agriculture" sheetId="1" r:id="rId1"/>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="365" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="132">
   <si>
     <t>commoditySegment</t>
   </si>
@@ -395,9 +395,6 @@
     <t>Ali 93</t>
   </si>
   <si>
-    <t>DRUM</t>
-  </si>
-  <si>
     <t>BABU2</t>
   </si>
   <si>
@@ -439,6 +436,9 @@
   <si>
     <t>Yes</t>
   </si>
+  <si>
+    <t>Copper</t>
+  </si>
 </sst>
 </file>
 
@@ -447,7 +447,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="0.0"/>
   </numFmts>
-  <fonts count="12" x14ac:knownFonts="1">
+  <fonts count="13" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -532,6 +532,12 @@
       <name val="Consolas"/>
       <family val="3"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="5">
     <fill>
@@ -597,7 +603,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="36">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -640,6 +646,7 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -980,34 +987,34 @@
         <v>13</v>
       </c>
       <c r="B2" s="22">
-        <v>250520262</v>
+        <v>20720271</v>
       </c>
       <c r="C2" s="22" t="s">
         <v>16</v>
       </c>
       <c r="D2" s="20">
-        <v>178888880001601</v>
+        <v>100673000000011</v>
       </c>
       <c r="E2" s="22">
-        <v>8888999</v>
+        <v>9999996</v>
       </c>
       <c r="F2" s="22">
-        <v>9878999</v>
+        <v>1000421</v>
       </c>
       <c r="G2" s="22" t="s">
         <v>14</v>
       </c>
       <c r="H2" s="22">
-        <v>1</v>
+        <v>15</v>
       </c>
       <c r="I2" s="22">
-        <v>5000</v>
+        <v>100</v>
       </c>
       <c r="J2" s="22">
         <v>1.7</v>
       </c>
       <c r="K2" s="24" t="s">
-        <v>102</v>
+        <v>58</v>
       </c>
       <c r="L2" s="22" t="s">
         <v>15</v>
@@ -1018,633 +1025,243 @@
       <c r="N2" s="22"/>
     </row>
     <row r="3" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A3" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="B3" s="22">
-        <v>5555614</v>
-      </c>
-      <c r="C3" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="D3" s="20">
-        <v>155000010000761</v>
-      </c>
-      <c r="E3" s="22">
-        <v>9996059</v>
-      </c>
-      <c r="F3" s="22">
-        <v>5750013</v>
-      </c>
-      <c r="G3" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="H3" s="22">
-        <v>6</v>
-      </c>
-      <c r="I3" s="22">
-        <v>5000</v>
-      </c>
-      <c r="J3" s="22">
-        <v>0.5</v>
-      </c>
-      <c r="K3" s="24" t="s">
-        <v>102</v>
-      </c>
-      <c r="L3" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="M3" s="22" t="s">
-        <v>15</v>
-      </c>
+      <c r="A3" s="22"/>
+      <c r="B3" s="22"/>
+      <c r="C3" s="22"/>
+      <c r="D3" s="20"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="22"/>
+      <c r="G3" s="22"/>
+      <c r="H3" s="22"/>
+      <c r="I3" s="22"/>
+      <c r="J3" s="22"/>
+      <c r="K3" s="24"/>
+      <c r="L3" s="22"/>
+      <c r="M3" s="22"/>
       <c r="N3" s="22"/>
     </row>
     <row r="4" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A4" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="22">
-        <v>5555615</v>
-      </c>
-      <c r="C4" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="D4" s="20">
-        <v>155000010000761</v>
-      </c>
-      <c r="E4" s="22">
-        <v>9996059</v>
-      </c>
-      <c r="F4" s="22">
-        <v>5750013</v>
-      </c>
-      <c r="G4" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="H4" s="22">
-        <v>6</v>
-      </c>
-      <c r="I4" s="22">
-        <v>5000</v>
-      </c>
-      <c r="J4" s="22">
-        <v>1.7</v>
-      </c>
-      <c r="K4" s="24" t="s">
-        <v>102</v>
-      </c>
-      <c r="L4" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="M4" s="22" t="s">
-        <v>15</v>
-      </c>
+      <c r="A4" s="22"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="22"/>
+      <c r="D4" s="20"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="22"/>
+      <c r="G4" s="22"/>
+      <c r="H4" s="22"/>
+      <c r="I4" s="22"/>
+      <c r="J4" s="22"/>
+      <c r="K4" s="24"/>
+      <c r="L4" s="22"/>
+      <c r="M4" s="22"/>
       <c r="N4" s="22"/>
     </row>
     <row r="5" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A5" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="22">
-        <v>5555616</v>
-      </c>
-      <c r="C5" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="D5" s="20">
-        <v>155000010000761</v>
-      </c>
-      <c r="E5" s="22">
-        <v>9999996</v>
-      </c>
-      <c r="F5" s="22">
-        <v>1000421</v>
-      </c>
-      <c r="G5" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="H5" s="22">
-        <v>1</v>
-      </c>
-      <c r="I5" s="22">
-        <v>500</v>
-      </c>
-      <c r="J5" s="22">
-        <v>1.7</v>
-      </c>
-      <c r="K5" s="24" t="s">
-        <v>102</v>
-      </c>
-      <c r="L5" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="M5" s="22" t="s">
-        <v>15</v>
-      </c>
+      <c r="A5" s="22"/>
+      <c r="B5" s="22"/>
+      <c r="C5" s="22"/>
+      <c r="D5" s="20"/>
+      <c r="E5" s="22"/>
+      <c r="F5" s="22"/>
+      <c r="G5" s="22"/>
+      <c r="H5" s="22"/>
+      <c r="I5" s="22"/>
+      <c r="J5" s="22"/>
+      <c r="K5" s="24"/>
+      <c r="L5" s="22"/>
+      <c r="M5" s="22"/>
       <c r="N5" s="22"/>
     </row>
     <row r="6" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A6" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="22">
-        <v>5555617</v>
-      </c>
-      <c r="C6" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="D6" s="20">
-        <v>100673000000011</v>
-      </c>
-      <c r="E6" s="22">
-        <v>9999996</v>
-      </c>
-      <c r="F6" s="22">
-        <v>1000421</v>
-      </c>
-      <c r="G6" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="H6" s="22">
-        <v>1</v>
-      </c>
-      <c r="I6" s="22">
-        <v>700</v>
-      </c>
-      <c r="J6" s="22">
-        <v>1.7</v>
-      </c>
-      <c r="K6" s="24" t="s">
-        <v>102</v>
-      </c>
-      <c r="L6" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="M6" s="22" t="s">
-        <v>15</v>
-      </c>
+      <c r="A6" s="22"/>
+      <c r="B6" s="22"/>
+      <c r="C6" s="22"/>
+      <c r="D6" s="20"/>
+      <c r="E6" s="22"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="22"/>
+      <c r="J6" s="22"/>
+      <c r="K6" s="24"/>
+      <c r="L6" s="22"/>
+      <c r="M6" s="22"/>
       <c r="N6" s="22"/>
     </row>
     <row r="7" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A7" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="22">
-        <v>5555618</v>
-      </c>
-      <c r="C7" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="D7" s="20">
-        <v>100673000000011</v>
-      </c>
-      <c r="E7" s="22">
-        <v>9999996</v>
-      </c>
-      <c r="F7" s="22">
-        <v>1000421</v>
-      </c>
-      <c r="G7" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="H7" s="22">
-        <v>1</v>
-      </c>
-      <c r="I7" s="22">
-        <v>500</v>
-      </c>
-      <c r="J7" s="22">
-        <v>1.7</v>
-      </c>
-      <c r="K7" s="24" t="s">
-        <v>102</v>
-      </c>
-      <c r="L7" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="M7" s="22" t="s">
-        <v>15</v>
-      </c>
+      <c r="A7" s="22"/>
+      <c r="B7" s="22"/>
+      <c r="C7" s="22"/>
+      <c r="D7" s="20"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="22"/>
+      <c r="G7" s="22"/>
+      <c r="H7" s="22"/>
+      <c r="I7" s="22"/>
+      <c r="J7" s="22"/>
+      <c r="K7" s="24"/>
+      <c r="L7" s="22"/>
+      <c r="M7" s="22"/>
       <c r="N7" s="25"/>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A8" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="22">
-        <v>5555619</v>
-      </c>
-      <c r="C8" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="D8" s="20">
-        <v>100673000000011</v>
-      </c>
-      <c r="E8" s="22">
-        <v>9999996</v>
-      </c>
-      <c r="F8" s="22">
-        <v>1000421</v>
-      </c>
-      <c r="G8" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="H8" s="22">
-        <v>1</v>
-      </c>
-      <c r="I8" s="22">
-        <v>700</v>
-      </c>
-      <c r="J8" s="22">
-        <v>1.7</v>
-      </c>
-      <c r="K8" s="24" t="s">
-        <v>102</v>
-      </c>
-      <c r="L8" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="M8" s="22" t="s">
-        <v>15</v>
-      </c>
+      <c r="A8" s="22"/>
+      <c r="B8" s="22"/>
+      <c r="C8" s="22"/>
+      <c r="D8" s="20"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="22"/>
+      <c r="G8" s="22"/>
+      <c r="H8" s="22"/>
+      <c r="I8" s="22"/>
+      <c r="J8" s="22"/>
+      <c r="K8" s="24"/>
+      <c r="L8" s="22"/>
+      <c r="M8" s="22"/>
       <c r="N8" s="25"/>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A9" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="22">
-        <v>5555620</v>
-      </c>
-      <c r="C9" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="D9" s="20">
-        <v>100673000000011</v>
-      </c>
-      <c r="E9" s="22">
-        <v>9999996</v>
-      </c>
-      <c r="F9" s="22">
-        <v>1000421</v>
-      </c>
-      <c r="G9" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="H9" s="22">
-        <v>1</v>
-      </c>
-      <c r="I9" s="22">
-        <v>500</v>
-      </c>
-      <c r="J9" s="22">
-        <v>1.7</v>
-      </c>
-      <c r="K9" s="24" t="s">
-        <v>102</v>
-      </c>
-      <c r="L9" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="M9" s="22" t="s">
-        <v>15</v>
-      </c>
+      <c r="A9" s="22"/>
+      <c r="B9" s="22"/>
+      <c r="C9" s="22"/>
+      <c r="D9" s="20"/>
+      <c r="E9" s="22"/>
+      <c r="F9" s="22"/>
+      <c r="G9" s="22"/>
+      <c r="H9" s="22"/>
+      <c r="I9" s="22"/>
+      <c r="J9" s="22"/>
+      <c r="K9" s="24"/>
+      <c r="L9" s="22"/>
+      <c r="M9" s="22"/>
       <c r="N9" s="25"/>
     </row>
     <row r="10" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A10" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="22">
-        <v>5555621</v>
-      </c>
-      <c r="C10" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="D10" s="20">
-        <v>100673000000011</v>
-      </c>
-      <c r="E10" s="22">
-        <v>9999996</v>
-      </c>
-      <c r="F10" s="22">
-        <v>1000421</v>
-      </c>
-      <c r="G10" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="H10" s="22">
-        <v>15</v>
-      </c>
-      <c r="I10" s="22">
-        <v>700</v>
-      </c>
-      <c r="J10" s="22">
-        <v>1.7</v>
-      </c>
-      <c r="K10" s="24" t="s">
-        <v>58</v>
-      </c>
-      <c r="L10" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="M10" s="22" t="s">
-        <v>15</v>
-      </c>
+      <c r="A10" s="22"/>
+      <c r="B10" s="22"/>
+      <c r="C10" s="22"/>
+      <c r="D10" s="20"/>
+      <c r="E10" s="22"/>
+      <c r="F10" s="22"/>
+      <c r="G10" s="22"/>
+      <c r="H10" s="22"/>
+      <c r="I10" s="22"/>
+      <c r="J10" s="22"/>
+      <c r="K10" s="24"/>
+      <c r="L10" s="22"/>
+      <c r="M10" s="22"/>
       <c r="N10" s="25"/>
     </row>
     <row r="11" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A11" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="22">
-        <v>5555622</v>
-      </c>
-      <c r="C11" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="D11" s="20">
-        <v>100673000000011</v>
-      </c>
-      <c r="E11" s="22">
-        <v>9999996</v>
-      </c>
-      <c r="F11" s="22">
-        <v>1000421</v>
-      </c>
-      <c r="G11" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="H11" s="22">
-        <v>1</v>
-      </c>
-      <c r="I11" s="22">
-        <v>500</v>
-      </c>
-      <c r="J11" s="22">
-        <v>1.7</v>
-      </c>
-      <c r="K11" s="24" t="s">
-        <v>102</v>
-      </c>
-      <c r="L11" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="M11" s="22" t="s">
-        <v>15</v>
-      </c>
+      <c r="A11" s="22"/>
+      <c r="B11" s="22"/>
+      <c r="C11" s="22"/>
+      <c r="D11" s="20"/>
+      <c r="E11" s="22"/>
+      <c r="F11" s="22"/>
+      <c r="G11" s="22"/>
+      <c r="H11" s="22"/>
+      <c r="I11" s="22"/>
+      <c r="J11" s="22"/>
+      <c r="K11" s="24"/>
+      <c r="L11" s="22"/>
+      <c r="M11" s="22"/>
       <c r="N11" s="25"/>
     </row>
     <row r="12" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A12" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="22">
-        <v>5555623</v>
-      </c>
-      <c r="C12" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="D12" s="20">
-        <v>100673000000011</v>
-      </c>
-      <c r="E12" s="22">
-        <v>9999996</v>
-      </c>
-      <c r="F12" s="22">
-        <v>1000421</v>
-      </c>
-      <c r="G12" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="H12" s="22">
-        <v>1</v>
-      </c>
-      <c r="I12" s="22">
-        <v>700</v>
-      </c>
-      <c r="J12" s="22">
-        <v>1.7</v>
-      </c>
-      <c r="K12" s="24" t="s">
-        <v>102</v>
-      </c>
-      <c r="L12" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="M12" s="22" t="s">
-        <v>15</v>
-      </c>
+      <c r="A12" s="22"/>
+      <c r="B12" s="22"/>
+      <c r="C12" s="22"/>
+      <c r="D12" s="20"/>
+      <c r="E12" s="22"/>
+      <c r="F12" s="22"/>
+      <c r="G12" s="22"/>
+      <c r="H12" s="22"/>
+      <c r="I12" s="22"/>
+      <c r="J12" s="22"/>
+      <c r="K12" s="24"/>
+      <c r="L12" s="22"/>
+      <c r="M12" s="22"/>
       <c r="N12" s="25"/>
     </row>
     <row r="13" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A13" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" s="22">
-        <v>5555624</v>
-      </c>
-      <c r="C13" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="D13" s="20">
-        <v>100673000000011</v>
-      </c>
-      <c r="E13" s="22">
-        <v>9999996</v>
-      </c>
-      <c r="F13" s="22">
-        <v>1000421</v>
-      </c>
-      <c r="G13" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="H13" s="22">
-        <v>1</v>
-      </c>
-      <c r="I13" s="22">
-        <v>100</v>
-      </c>
-      <c r="J13" s="22">
-        <v>1.7</v>
-      </c>
-      <c r="K13" s="24" t="s">
-        <v>102</v>
-      </c>
-      <c r="L13" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="M13" s="22" t="s">
-        <v>15</v>
-      </c>
+      <c r="A13" s="22"/>
+      <c r="B13" s="22"/>
+      <c r="C13" s="22"/>
+      <c r="D13" s="20"/>
+      <c r="E13" s="22"/>
+      <c r="F13" s="22"/>
+      <c r="G13" s="22"/>
+      <c r="H13" s="22"/>
+      <c r="I13" s="22"/>
+      <c r="J13" s="22"/>
+      <c r="K13" s="24"/>
+      <c r="L13" s="22"/>
+      <c r="M13" s="22"/>
       <c r="N13" s="25"/>
     </row>
     <row r="14" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A14" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" s="22">
-        <v>5555625</v>
-      </c>
-      <c r="C14" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="D14" s="20">
-        <v>100673000000011</v>
-      </c>
-      <c r="E14" s="22">
-        <v>9999996</v>
-      </c>
-      <c r="F14" s="22">
-        <v>1000421</v>
-      </c>
-      <c r="G14" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="H14" s="22">
-        <v>1</v>
-      </c>
-      <c r="I14" s="22">
-        <v>700</v>
-      </c>
-      <c r="J14" s="22">
-        <v>1.7</v>
-      </c>
-      <c r="K14" s="24" t="s">
-        <v>102</v>
-      </c>
-      <c r="L14" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="M14" s="22" t="s">
-        <v>15</v>
-      </c>
+      <c r="A14" s="22"/>
+      <c r="B14" s="22"/>
+      <c r="C14" s="22"/>
+      <c r="D14" s="20"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="22"/>
+      <c r="G14" s="22"/>
+      <c r="H14" s="22"/>
+      <c r="I14" s="22"/>
+      <c r="J14" s="22"/>
+      <c r="K14" s="24"/>
+      <c r="L14" s="22"/>
+      <c r="M14" s="22"/>
       <c r="N14" s="25"/>
     </row>
     <row r="15" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A15" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" s="22">
-        <v>5555626</v>
-      </c>
-      <c r="C15" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="D15" s="20">
-        <v>178888880001601</v>
-      </c>
-      <c r="E15" s="22">
-        <v>9999996</v>
-      </c>
-      <c r="F15" s="22">
-        <v>1000421</v>
-      </c>
-      <c r="G15" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="H15" s="22">
-        <v>1</v>
-      </c>
-      <c r="I15" s="22">
-        <v>2000</v>
-      </c>
-      <c r="J15" s="21">
-        <v>1</v>
-      </c>
-      <c r="K15" s="24" t="s">
-        <v>102</v>
-      </c>
-      <c r="L15" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="M15" s="22" t="s">
-        <v>15</v>
-      </c>
+      <c r="A15" s="22"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="22"/>
+      <c r="D15" s="20"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="22"/>
+      <c r="G15" s="22"/>
+      <c r="H15" s="22"/>
+      <c r="I15" s="22"/>
+      <c r="J15" s="21"/>
+      <c r="K15" s="24"/>
+      <c r="L15" s="22"/>
+      <c r="M15" s="22"/>
       <c r="N15" s="26"/>
     </row>
     <row r="16" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A16" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="B16" s="22">
-        <v>5555627</v>
-      </c>
-      <c r="C16" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="D16" s="20">
-        <v>100673001212128</v>
-      </c>
-      <c r="E16" s="22">
-        <v>9999996</v>
-      </c>
-      <c r="F16" s="22">
-        <v>1000421</v>
-      </c>
-      <c r="G16" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="H16" s="22">
-        <v>6</v>
-      </c>
-      <c r="I16" s="22">
-        <v>2000</v>
-      </c>
-      <c r="J16" s="21">
-        <v>1</v>
-      </c>
-      <c r="K16" s="24" t="s">
-        <v>102</v>
-      </c>
-      <c r="L16" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="M16" s="22" t="s">
-        <v>15</v>
-      </c>
+      <c r="A16" s="22"/>
+      <c r="B16" s="22"/>
+      <c r="C16" s="22"/>
+      <c r="D16" s="20"/>
+      <c r="E16" s="22"/>
+      <c r="F16" s="22"/>
+      <c r="G16" s="22"/>
+      <c r="H16" s="22"/>
+      <c r="I16" s="22"/>
+      <c r="J16" s="21"/>
+      <c r="K16" s="24"/>
+      <c r="L16" s="22"/>
+      <c r="M16" s="22"/>
       <c r="N16" s="26"/>
     </row>
     <row r="17" spans="1:14" x14ac:dyDescent="0.25">
-      <c r="A17" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="B17" s="22">
-        <v>5555628</v>
-      </c>
-      <c r="C17" s="22" t="s">
-        <v>16</v>
-      </c>
-      <c r="D17" s="20">
-        <v>100673001212128</v>
-      </c>
-      <c r="E17" s="22">
-        <v>9999996</v>
-      </c>
-      <c r="F17" s="22">
-        <v>1000421</v>
-      </c>
-      <c r="G17" s="22" t="s">
-        <v>14</v>
-      </c>
-      <c r="H17" s="22">
-        <v>1</v>
-      </c>
-      <c r="I17" s="22">
-        <v>100</v>
-      </c>
-      <c r="J17" s="22">
-        <v>1.7</v>
-      </c>
-      <c r="K17" s="24" t="s">
-        <v>102</v>
-      </c>
-      <c r="L17" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="M17" s="22" t="s">
-        <v>15</v>
-      </c>
+      <c r="A17" s="22"/>
+      <c r="B17" s="22"/>
+      <c r="C17" s="22"/>
+      <c r="D17" s="20"/>
+      <c r="E17" s="22"/>
+      <c r="F17" s="22"/>
+      <c r="G17" s="22"/>
+      <c r="H17" s="22"/>
+      <c r="I17" s="22"/>
+      <c r="J17" s="22"/>
+      <c r="K17" s="24"/>
+      <c r="L17" s="22"/>
+      <c r="M17" s="22"/>
       <c r="N17" s="26"/>
     </row>
   </sheetData>
@@ -1765,28 +1382,28 @@
         <v>13</v>
       </c>
       <c r="B3" s="1">
-        <v>4555514</v>
+        <v>70720261</v>
       </c>
       <c r="C3" s="2">
-        <v>120733340001420</v>
-      </c>
-      <c r="D3" s="22">
-        <v>9999996</v>
-      </c>
-      <c r="E3" s="22">
-        <v>1000421</v>
+        <v>178888880001601</v>
+      </c>
+      <c r="D3" s="36">
+        <v>8888999</v>
+      </c>
+      <c r="E3" s="36">
+        <v>8888888</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>29</v>
       </c>
       <c r="G3" s="1">
-        <v>15</v>
+        <v>947</v>
       </c>
       <c r="H3" s="1">
-        <v>700</v>
+        <v>40</v>
       </c>
       <c r="I3" s="27">
-        <v>1.7</v>
+        <v>1.8</v>
       </c>
       <c r="J3" s="1" t="s">
         <v>30</v>
@@ -1803,503 +1420,191 @@
       <c r="N3" s="19"/>
     </row>
     <row r="4" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A4" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B4" s="22">
-        <v>4555517</v>
-      </c>
-      <c r="C4" s="20">
-        <v>100673000000011</v>
-      </c>
-      <c r="D4" s="22">
-        <v>9999996</v>
-      </c>
-      <c r="E4" s="22">
-        <v>1000421</v>
-      </c>
-      <c r="F4" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G4" s="1">
-        <v>15</v>
-      </c>
-      <c r="H4" s="1">
-        <v>700</v>
-      </c>
-      <c r="I4" s="27">
-        <v>1.7</v>
-      </c>
-      <c r="J4" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="L4" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M4" s="1">
-        <v>11</v>
-      </c>
+      <c r="A4" s="1"/>
+      <c r="B4" s="22"/>
+      <c r="C4" s="20"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="1"/>
+      <c r="G4" s="1"/>
+      <c r="H4" s="1"/>
+      <c r="I4" s="27"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="1"/>
+      <c r="M4" s="1"/>
       <c r="N4" s="19"/>
     </row>
     <row r="5" spans="1:20" s="26" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="B5" s="22">
-        <v>2952026</v>
-      </c>
-      <c r="C5" s="11">
-        <v>120484000000134</v>
-      </c>
-      <c r="D5" s="7">
-        <v>6656413</v>
-      </c>
-      <c r="E5" s="7">
-        <v>6539191</v>
-      </c>
-      <c r="F5" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="G5" s="22">
-        <v>15</v>
-      </c>
-      <c r="H5" s="22">
-        <v>5000</v>
-      </c>
-      <c r="I5" s="27">
-        <v>1.7</v>
-      </c>
-      <c r="J5" s="22" t="s">
-        <v>117</v>
-      </c>
-      <c r="K5" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="L5" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="M5" s="22">
-        <v>11</v>
-      </c>
+      <c r="A5" s="22"/>
+      <c r="B5" s="22"/>
+      <c r="C5" s="11"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="7"/>
+      <c r="F5" s="22"/>
+      <c r="G5" s="22"/>
+      <c r="H5" s="22"/>
+      <c r="I5" s="27"/>
+      <c r="J5" s="22"/>
+      <c r="K5" s="22"/>
+      <c r="L5" s="22"/>
+      <c r="M5" s="22"/>
       <c r="N5" s="25"/>
     </row>
     <row r="6" spans="1:20" s="26" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="B6" s="22">
-        <v>2952026</v>
-      </c>
-      <c r="C6" s="11">
-        <v>178888880001601</v>
-      </c>
-      <c r="D6" s="7">
-        <v>8888999</v>
-      </c>
-      <c r="E6" s="7">
-        <v>8888888</v>
-      </c>
-      <c r="F6" s="22" t="s">
-        <v>29</v>
-      </c>
-      <c r="G6" s="22">
-        <v>15</v>
-      </c>
-      <c r="H6" s="22">
-        <v>5000</v>
-      </c>
-      <c r="I6" s="27">
-        <v>1.7</v>
-      </c>
-      <c r="J6" s="22" t="s">
-        <v>117</v>
-      </c>
-      <c r="K6" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="L6" s="22" t="s">
-        <v>15</v>
-      </c>
-      <c r="M6" s="22">
-        <v>11</v>
-      </c>
+      <c r="A6" s="22"/>
+      <c r="B6" s="22"/>
+      <c r="C6" s="11"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="7"/>
+      <c r="F6" s="22"/>
+      <c r="G6" s="22"/>
+      <c r="H6" s="22"/>
+      <c r="I6" s="27"/>
+      <c r="J6" s="22"/>
+      <c r="K6" s="22"/>
+      <c r="L6" s="22"/>
+      <c r="M6" s="22"/>
       <c r="N6" s="25"/>
     </row>
     <row r="7" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A7" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7" s="22">
-        <v>4555522</v>
-      </c>
-      <c r="C7" s="2">
-        <v>100673000000011</v>
-      </c>
-      <c r="D7" s="1">
-        <v>9997115</v>
-      </c>
-      <c r="E7" s="1">
-        <v>8211642</v>
-      </c>
-      <c r="F7" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G7" s="1">
-        <v>15</v>
-      </c>
-      <c r="H7" s="1">
-        <v>500</v>
-      </c>
-      <c r="I7" s="27">
-        <v>1.7</v>
-      </c>
-      <c r="J7" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="L7" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M7" s="1">
-        <v>11</v>
-      </c>
+      <c r="A7" s="1"/>
+      <c r="B7" s="22"/>
+      <c r="C7" s="2"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="27"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
+      <c r="M7" s="1"/>
       <c r="N7" s="19"/>
     </row>
     <row r="8" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A8" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B8" s="22">
-        <v>4555524</v>
-      </c>
-      <c r="C8" s="2">
-        <v>100673000000011</v>
-      </c>
-      <c r="D8" s="1">
-        <v>9997115</v>
-      </c>
-      <c r="E8" s="1">
-        <v>8211642</v>
-      </c>
-      <c r="F8" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G8" s="1">
-        <v>15</v>
-      </c>
-      <c r="H8" s="1">
-        <v>700</v>
-      </c>
-      <c r="I8" s="27">
-        <v>1.7</v>
-      </c>
-      <c r="J8" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="L8" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M8" s="1">
-        <v>11</v>
-      </c>
+      <c r="A8" s="1"/>
+      <c r="B8" s="22"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="1"/>
+      <c r="F8" s="1"/>
+      <c r="G8" s="1"/>
+      <c r="H8" s="1"/>
+      <c r="I8" s="27"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="1"/>
+      <c r="M8" s="1"/>
       <c r="N8" s="19"/>
     </row>
     <row r="9" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A9" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B9" s="22">
-        <v>4555526</v>
-      </c>
-      <c r="C9" s="2">
-        <v>100673000000011</v>
-      </c>
-      <c r="D9" s="1">
-        <v>9997115</v>
-      </c>
-      <c r="E9" s="1">
-        <v>8211642</v>
-      </c>
-      <c r="F9" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G9" s="1">
-        <v>15</v>
-      </c>
-      <c r="H9" s="1">
-        <v>700</v>
-      </c>
-      <c r="I9" s="27">
-        <v>1.7</v>
-      </c>
-      <c r="J9" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="L9" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M9" s="1">
-        <v>11</v>
-      </c>
+      <c r="A9" s="1"/>
+      <c r="B9" s="22"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="1"/>
+      <c r="F9" s="1"/>
+      <c r="G9" s="1"/>
+      <c r="H9" s="1"/>
+      <c r="I9" s="27"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="1"/>
+      <c r="M9" s="1"/>
       <c r="N9" s="19"/>
     </row>
     <row r="10" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A10" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B10" s="22">
-        <v>4555528</v>
-      </c>
-      <c r="C10" s="2">
-        <v>100673000000011</v>
-      </c>
-      <c r="D10" s="1">
-        <v>9997115</v>
-      </c>
-      <c r="E10" s="1">
-        <v>8211642</v>
-      </c>
-      <c r="F10" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G10" s="1">
-        <v>15</v>
-      </c>
-      <c r="H10" s="1">
-        <v>700</v>
-      </c>
-      <c r="I10" s="27">
-        <v>1.7</v>
-      </c>
-      <c r="J10" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K10" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="L10" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M10" s="1">
-        <v>11</v>
-      </c>
+      <c r="A10" s="1"/>
+      <c r="B10" s="22"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="1"/>
+      <c r="F10" s="1"/>
+      <c r="G10" s="1"/>
+      <c r="H10" s="1"/>
+      <c r="I10" s="27"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="1"/>
+      <c r="M10" s="1"/>
       <c r="N10" s="19"/>
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A11" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B11" s="22">
-        <v>4555530</v>
-      </c>
-      <c r="C11" s="2">
-        <v>100673000000011</v>
-      </c>
-      <c r="D11" s="1">
-        <v>9997115</v>
-      </c>
-      <c r="E11" s="1">
-        <v>8211642</v>
-      </c>
-      <c r="F11" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G11" s="1">
-        <v>15</v>
-      </c>
-      <c r="H11" s="1">
-        <v>100</v>
-      </c>
-      <c r="I11" s="27">
-        <v>1.7</v>
-      </c>
-      <c r="J11" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K11" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="L11" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M11" s="1">
-        <v>11</v>
-      </c>
+      <c r="A11" s="1"/>
+      <c r="B11" s="22"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="1"/>
+      <c r="F11" s="1"/>
+      <c r="G11" s="1"/>
+      <c r="H11" s="1"/>
+      <c r="I11" s="27"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="1"/>
+      <c r="M11" s="1"/>
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A12" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B12" s="22">
-        <v>4555532</v>
-      </c>
-      <c r="C12" s="2">
-        <v>100673000000011</v>
-      </c>
-      <c r="D12" s="1">
-        <v>9997115</v>
-      </c>
-      <c r="E12" s="1">
-        <v>8211642</v>
-      </c>
-      <c r="F12" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G12" s="1">
-        <v>15</v>
-      </c>
-      <c r="H12" s="1">
-        <v>100</v>
-      </c>
-      <c r="I12" s="27">
-        <v>1.7</v>
-      </c>
-      <c r="J12" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K12" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="L12" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M12" s="1">
-        <v>11</v>
-      </c>
+      <c r="A12" s="1"/>
+      <c r="B12" s="22"/>
+      <c r="C12" s="2"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="1"/>
+      <c r="F12" s="1"/>
+      <c r="G12" s="1"/>
+      <c r="H12" s="1"/>
+      <c r="I12" s="27"/>
+      <c r="J12" s="1"/>
+      <c r="K12" s="1"/>
+      <c r="L12" s="1"/>
+      <c r="M12" s="1"/>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A13" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B13" s="22">
-        <v>4555534</v>
-      </c>
-      <c r="C13" s="2">
-        <v>120733340001420</v>
-      </c>
-      <c r="D13" s="22">
-        <v>9999996</v>
-      </c>
-      <c r="E13" s="22">
-        <v>1000421</v>
-      </c>
-      <c r="F13" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G13" s="1">
-        <v>15</v>
-      </c>
-      <c r="H13" s="1">
-        <v>700</v>
-      </c>
-      <c r="I13" s="27">
-        <v>1.7</v>
-      </c>
-      <c r="J13" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K13" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="L13" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M13" s="1">
-        <v>11</v>
-      </c>
+      <c r="A13" s="1"/>
+      <c r="B13" s="22"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="22"/>
+      <c r="E13" s="22"/>
+      <c r="F13" s="1"/>
+      <c r="G13" s="1"/>
+      <c r="H13" s="1"/>
+      <c r="I13" s="27"/>
+      <c r="J13" s="1"/>
+      <c r="K13" s="1"/>
+      <c r="L13" s="1"/>
+      <c r="M13" s="1"/>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A14" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B14" s="22">
-        <v>4555536</v>
-      </c>
-      <c r="C14" s="2">
-        <v>120733340001420</v>
-      </c>
-      <c r="D14" s="22">
-        <v>9999996</v>
-      </c>
-      <c r="E14" s="22">
-        <v>1000421</v>
-      </c>
-      <c r="F14" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G14" s="1">
-        <v>15</v>
-      </c>
-      <c r="H14" s="1">
-        <v>700</v>
-      </c>
-      <c r="I14" s="27">
-        <v>1.7</v>
-      </c>
-      <c r="J14" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K14" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="L14" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M14" s="1">
-        <v>11</v>
-      </c>
+      <c r="A14" s="1"/>
+      <c r="B14" s="22"/>
+      <c r="C14" s="2"/>
+      <c r="D14" s="22"/>
+      <c r="E14" s="22"/>
+      <c r="F14" s="1"/>
+      <c r="G14" s="1"/>
+      <c r="H14" s="1"/>
+      <c r="I14" s="27"/>
+      <c r="J14" s="1"/>
+      <c r="K14" s="1"/>
+      <c r="L14" s="1"/>
+      <c r="M14" s="1"/>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.25">
-      <c r="A15" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="B15" s="22">
-        <v>4555538</v>
-      </c>
-      <c r="C15" s="2">
-        <v>100673000000011</v>
-      </c>
-      <c r="D15" s="22">
-        <v>9999996</v>
-      </c>
-      <c r="E15" s="22">
-        <v>1000421</v>
-      </c>
-      <c r="F15" s="1" t="s">
-        <v>29</v>
-      </c>
-      <c r="G15" s="1">
-        <v>15</v>
-      </c>
-      <c r="H15" s="1">
-        <v>700</v>
-      </c>
-      <c r="I15" s="27">
-        <v>1.7</v>
-      </c>
-      <c r="J15" s="1" t="s">
-        <v>30</v>
-      </c>
-      <c r="K15" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="L15" s="1" t="s">
-        <v>15</v>
-      </c>
-      <c r="M15" s="1">
-        <v>11</v>
-      </c>
+      <c r="A15" s="1"/>
+      <c r="B15" s="22"/>
+      <c r="C15" s="2"/>
+      <c r="D15" s="22"/>
+      <c r="E15" s="22"/>
+      <c r="F15" s="1"/>
+      <c r="G15" s="1"/>
+      <c r="H15" s="1"/>
+      <c r="I15" s="27"/>
+      <c r="J15" s="1"/>
+      <c r="K15" s="1"/>
+      <c r="L15" s="1"/>
+      <c r="M15" s="1"/>
     </row>
     <row r="18" spans="3:9" x14ac:dyDescent="0.25">
       <c r="C18" s="7"/>
@@ -18204,7 +17509,7 @@
         <v>70</v>
       </c>
       <c r="B2" s="7">
-        <v>270520262</v>
+        <v>90720261</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>29</v>
@@ -18222,13 +17527,13 @@
         <v>178888880001601</v>
       </c>
       <c r="H2" s="7">
-        <v>1003</v>
+        <v>1005</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>73</v>
+        <v>131</v>
       </c>
       <c r="J2" s="7">
-        <v>100</v>
+        <v>150</v>
       </c>
       <c r="K2" s="7">
         <v>10</v>
@@ -18237,7 +17542,7 @@
         <v>77</v>
       </c>
       <c r="M2" s="7">
-        <v>100</v>
+        <v>75000</v>
       </c>
       <c r="N2" s="7" t="s">
         <v>79</v>
@@ -18740,28 +18045,28 @@
         <v>111</v>
       </c>
       <c r="AD1" s="5" t="s">
+        <v>118</v>
+      </c>
+      <c r="AE1" s="5" t="s">
         <v>119</v>
       </c>
-      <c r="AE1" s="5" t="s">
+      <c r="AF1" s="5" t="s">
         <v>120</v>
       </c>
-      <c r="AF1" s="5" t="s">
+      <c r="AG1" s="5" t="s">
         <v>121</v>
       </c>
-      <c r="AG1" s="5" t="s">
+      <c r="AH1" s="5" t="s">
         <v>122</v>
       </c>
-      <c r="AH1" s="5" t="s">
+      <c r="AI1" s="5" t="s">
         <v>123</v>
       </c>
-      <c r="AI1" s="5" t="s">
+      <c r="AJ1" s="5" t="s">
         <v>124</v>
       </c>
-      <c r="AJ1" s="5" t="s">
+      <c r="AK1" s="5" t="s">
         <v>125</v>
-      </c>
-      <c r="AK1" s="5" t="s">
-        <v>126</v>
       </c>
     </row>
     <row r="2" spans="1:37" x14ac:dyDescent="0.25">
@@ -18784,19 +18089,19 @@
         <v>973015</v>
       </c>
       <c r="G2" s="1">
-        <v>100005</v>
+        <v>2072026</v>
       </c>
       <c r="H2" s="1">
         <v>1000012</v>
       </c>
       <c r="I2" s="1" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="J2" s="1">
         <v>19062026</v>
       </c>
       <c r="K2" s="1">
-        <v>170</v>
+        <v>72</v>
       </c>
       <c r="L2" s="1">
         <v>5000</v>
@@ -18847,34 +18152,34 @@
         <v>10000</v>
       </c>
       <c r="AB2" s="11">
-        <v>100</v>
+        <v>2</v>
       </c>
       <c r="AC2" s="7">
         <v>20</v>
       </c>
       <c r="AD2" s="7" t="s">
+        <v>126</v>
+      </c>
+      <c r="AE2" s="7" t="s">
         <v>127</v>
       </c>
-      <c r="AE2" s="7" t="s">
+      <c r="AF2" s="7" t="s">
         <v>128</v>
-      </c>
-      <c r="AF2" s="7" t="s">
-        <v>129</v>
       </c>
       <c r="AG2" s="7">
         <v>100</v>
       </c>
       <c r="AH2" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="AI2" s="7" t="s">
         <v>130</v>
       </c>
-      <c r="AI2" s="7" t="s">
-        <v>131</v>
-      </c>
       <c r="AJ2" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AK2" s="7" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
     </row>
   </sheetData>
@@ -19031,10 +18336,10 @@
         <v>46202558</v>
       </c>
       <c r="O2" s="7">
-        <v>5</v>
+        <v>2500</v>
       </c>
       <c r="P2" s="7">
-        <v>1</v>
+        <v>2500</v>
       </c>
       <c r="Q2" s="7" t="s">
         <v>61</v>
@@ -19070,10 +18375,10 @@
         <v>179</v>
       </c>
       <c r="AB2" s="7">
-        <v>100</v>
+        <v>5</v>
       </c>
       <c r="AC2" s="19">
-        <v>100</v>
+        <v>150</v>
       </c>
     </row>
     <row r="4" spans="1:29" x14ac:dyDescent="0.25">
@@ -19199,7 +18504,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="19">
-        <v>420941</v>
+        <v>421955</v>
       </c>
       <c r="B2" s="19">
         <v>180</v>

--- a/Data/ENWR_Creation.xlsx
+++ b/Data/ENWR_Creation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\abhishekyt\git\repository\Automation\Data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{283B9574-ACC3-4139-9962-26C7C5988399}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2005E197-8424-4502-A1B0-03173C263EAC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="19770" windowHeight="11760" firstSheet="5" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -42,7 +42,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="215" uniqueCount="132">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="217" uniqueCount="132">
   <si>
     <t>commoditySegment</t>
   </si>
@@ -603,7 +603,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="1" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
@@ -645,7 +645,6 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="8" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
@@ -987,19 +986,19 @@
         <v>13</v>
       </c>
       <c r="B2" s="22">
-        <v>20720271</v>
+        <v>180826</v>
       </c>
       <c r="C2" s="22" t="s">
         <v>16</v>
       </c>
-      <c r="D2" s="20">
-        <v>100673000000011</v>
+      <c r="D2" s="2">
+        <v>178888880001601</v>
       </c>
       <c r="E2" s="22">
-        <v>9999996</v>
+        <v>8888999</v>
       </c>
       <c r="F2" s="22">
-        <v>1000421</v>
+        <v>8888888</v>
       </c>
       <c r="G2" s="22" t="s">
         <v>14</v>
@@ -1044,11 +1043,21 @@
       <c r="A4" s="22"/>
       <c r="B4" s="22"/>
       <c r="C4" s="22"/>
-      <c r="D4" s="20"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22"/>
-      <c r="G4" s="22"/>
-      <c r="H4" s="22"/>
+      <c r="D4" s="20">
+        <v>100673000000011</v>
+      </c>
+      <c r="E4" s="22">
+        <v>9999996</v>
+      </c>
+      <c r="F4" s="22">
+        <v>1000421</v>
+      </c>
+      <c r="G4" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="22">
+        <v>15</v>
+      </c>
       <c r="I4" s="22"/>
       <c r="J4" s="22"/>
       <c r="K4" s="24"/>
@@ -1387,10 +1396,10 @@
       <c r="C3" s="2">
         <v>178888880001601</v>
       </c>
-      <c r="D3" s="36">
+      <c r="D3" s="35">
         <v>8888999</v>
       </c>
-      <c r="E3" s="36">
+      <c r="E3" s="35">
         <v>8888888</v>
       </c>
       <c r="F3" s="1" t="s">
@@ -17509,7 +17518,7 @@
         <v>70</v>
       </c>
       <c r="B2" s="7">
-        <v>90720261</v>
+        <v>180826</v>
       </c>
       <c r="C2" s="7" t="s">
         <v>29</v>
@@ -17518,22 +17527,22 @@
         <v>11</v>
       </c>
       <c r="E2" s="7">
-        <v>8888999</v>
+        <v>9999996</v>
       </c>
       <c r="F2" s="7">
-        <v>8888888</v>
+        <v>1000421</v>
       </c>
       <c r="G2" s="11">
-        <v>178888880001601</v>
+        <v>100673000000011</v>
       </c>
       <c r="H2" s="7">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="I2" s="7" t="s">
-        <v>131</v>
+        <v>73</v>
       </c>
       <c r="J2" s="7">
-        <v>150</v>
+        <v>20</v>
       </c>
       <c r="K2" s="7">
         <v>10</v>
@@ -17542,7 +17551,7 @@
         <v>77</v>
       </c>
       <c r="M2" s="7">
-        <v>75000</v>
+        <v>20</v>
       </c>
       <c r="N2" s="7" t="s">
         <v>79</v>
@@ -17644,13 +17653,27 @@
       <c r="B5" s="24"/>
       <c r="C5" s="24"/>
       <c r="D5" s="24"/>
-      <c r="E5" s="35"/>
-      <c r="F5" s="22"/>
-      <c r="G5" s="28"/>
-      <c r="H5" s="24"/>
-      <c r="I5" s="24"/>
-      <c r="J5" s="24"/>
-      <c r="K5" s="24"/>
+      <c r="E5" s="7">
+        <v>8888999</v>
+      </c>
+      <c r="F5" s="7">
+        <v>8888888</v>
+      </c>
+      <c r="G5" s="11">
+        <v>178888880001601</v>
+      </c>
+      <c r="H5" s="7">
+        <v>1005</v>
+      </c>
+      <c r="I5" s="7" t="s">
+        <v>131</v>
+      </c>
+      <c r="J5" s="7">
+        <v>150</v>
+      </c>
+      <c r="K5" s="7">
+        <v>10</v>
+      </c>
       <c r="L5" s="24"/>
       <c r="M5" s="24"/>
       <c r="N5" s="24"/>
@@ -18324,7 +18347,7 @@
         <v>2</v>
       </c>
       <c r="K2" s="7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="L2" s="7">
         <v>10</v>
@@ -18375,7 +18398,7 @@
         <v>179</v>
       </c>
       <c r="AB2" s="7">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="AC2" s="19">
         <v>150</v>
@@ -18504,7 +18527,7 @@
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="19">
-        <v>421955</v>
+        <v>180826</v>
       </c>
       <c r="B2" s="19">
         <v>180</v>
